--- a/AiStock/indexAA.xlsx
+++ b/AiStock/indexAA.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="20745" windowHeight="9675"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1274" uniqueCount="775">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1252" uniqueCount="760">
   <si>
     <t>IndexCode</t>
   </si>
@@ -50,6 +50,63 @@
     <t>入选原因</t>
   </si>
   <si>
+    <t>000009</t>
+  </si>
+  <si>
+    <t>上证380</t>
+  </si>
+  <si>
+    <t>高端制造与新质生产力</t>
+  </si>
+  <si>
+    <t>高端制造</t>
+  </si>
+  <si>
+    <t>沪市中盘制造</t>
+  </si>
+  <si>
+    <t>中盘</t>
+  </si>
+  <si>
+    <t>1：沪市中盘成长代表，专精特新聚集；2：工业母机/新材料/精密仪器占比35%；3：380只中盘股，平均市值150亿；4：3只ETF，与中证500互补（沪市侧重）</t>
+  </si>
+  <si>
+    <t>000010</t>
+  </si>
+  <si>
+    <t>上证180</t>
+  </si>
+  <si>
+    <t>沪市制造龙头</t>
+  </si>
+  <si>
+    <t>大盘</t>
+  </si>
+  <si>
+    <t>1：沪市核心资产，国企改革重点标的；2：制造龙头集中（中芯/中车/商飞）；3：180只大盘股，平均市值500亿+；4：8只ETF，流动性稳定</t>
+  </si>
+  <si>
+    <t>000016</t>
+  </si>
+  <si>
+    <t>上证50</t>
+  </si>
+  <si>
+    <t>宽基基准层</t>
+  </si>
+  <si>
+    <t>宽基基准</t>
+  </si>
+  <si>
+    <t>超大盘金融+核心资产</t>
+  </si>
+  <si>
+    <t>超大盘</t>
+  </si>
+  <si>
+    <t>1：金融安全+核心资产压舱石；2：沪市金融+能源龙头，高股息防御属性；3：50只超大盘股，平均市值&gt;3000亿；4：15只以上ETF，日均成交&gt;200亿，流动性最佳</t>
+  </si>
+  <si>
     <t>000033</t>
   </si>
   <si>
@@ -65,12 +122,327 @@
     <t>基础材料龙头</t>
   </si>
   <si>
-    <t>大盘</t>
-  </si>
-  <si>
     <t/>
   </si>
   <si>
+    <t>000300</t>
+  </si>
+  <si>
+    <t>沪深300</t>
+  </si>
+  <si>
+    <t>全市场龙头，政策传导第一梯队</t>
+  </si>
+  <si>
+    <t>1：资本市场核心指数，政策传导第一梯队；2：全行业龙头，覆盖90%新质生产力上市公司；3：300只大盘股，平均市值&gt;800亿；4：30+只ETF，历史18年，国际配置基准</t>
+  </si>
+  <si>
+    <t>000688</t>
+  </si>
+  <si>
+    <t>科创50</t>
+  </si>
+  <si>
+    <t>科创板核心50，“国家队”</t>
+  </si>
+  <si>
+    <t>小盘</t>
+  </si>
+  <si>
+    <t>1：科创板核心资产，“卡脖子”技术攻关主阵地；2：半导体/生物医药/高端装备占比70%；3：50只科创板龙头，平均市值400亿；4：15+只ETF，流动性最佳科创板指数</t>
+  </si>
+  <si>
+    <t>000698</t>
+  </si>
+  <si>
+    <t>科创100</t>
+  </si>
+  <si>
+    <t>科创板中盘，专精特新密集</t>
+  </si>
+  <si>
+    <t>1：科创板中盘补充，专精特新密集区；2：细分领域冠军（光刻胶/碳纤维/工业机器人）；3：100只科创板中盘，平均市值100亿；4：5只ETF，2023年推出，成长性高</t>
+  </si>
+  <si>
+    <t>000813</t>
+  </si>
+  <si>
+    <t>细分化工</t>
+  </si>
+  <si>
+    <t>高端化工材料（POE/EVA）</t>
+  </si>
+  <si>
+    <t>1：高端化工材料（POE/EVA），新能源配套；2：万华化学/卫星化学，新材料占比提升；3：50只中盘股（复用传统升级），平均市值150亿；4：3只ETF，中游化工视角</t>
+  </si>
+  <si>
+    <t>000852</t>
+  </si>
+  <si>
+    <t>中证1000</t>
+  </si>
+  <si>
+    <t>小盘成长，“小巨人”集中</t>
+  </si>
+  <si>
+    <t>1：小微主体扶持，注册制改革受益；2：小盘成长股，“小巨人”占比25%；3：1000只小盘股，平均市值50-100亿；4：15+只ETF，2022年推出后流动性显著改善</t>
+  </si>
+  <si>
+    <t>000903</t>
+  </si>
+  <si>
+    <t>中证A100</t>
+  </si>
+  <si>
+    <t>A股国际化代表</t>
+  </si>
+  <si>
+    <t>1：A股国际化代表，纳入MSCI核心标的；2：各行业前10%龙头，科技+制造+消费均衡；3：100只大盘股，外资持仓集中区；4：5只ETF，适合跨境配置</t>
+  </si>
+  <si>
+    <t>000905</t>
+  </si>
+  <si>
+    <t>中证500</t>
+  </si>
+  <si>
+    <t>中盘成长，专精特新聚集</t>
+  </si>
+  <si>
+    <t>1：专精特新聚集地，补链强链核心载体；2：中盘成长股，细分领域冠军占比40%；3：500只中盘股，平均市值150-300亿；4：20+只ETF，量化策略首选</t>
+  </si>
+  <si>
+    <t>000922</t>
+  </si>
+  <si>
+    <t>中证红利</t>
+  </si>
+  <si>
+    <t>高股息策略，防御属性强</t>
+  </si>
+  <si>
+    <t>红利</t>
+  </si>
+  <si>
+    <t>1：高股息策略写入中央经济工作会议；2：现金流稳定行业（公用/银行/交运）；3：100只高股息股，大盘+中盘均衡；4：12只ETF，防御属性强</t>
+  </si>
+  <si>
+    <t>000933</t>
+  </si>
+  <si>
+    <t>中证医药</t>
+  </si>
+  <si>
+    <t>现代生物与大健康</t>
+  </si>
+  <si>
+    <t>生物健康</t>
+  </si>
+  <si>
+    <t>创新药+器械+CXO</t>
+  </si>
+  <si>
+    <t>1：健康中国2030，创新药械国产替代；2：创新药+医疗器械+CXO全覆盖；3：300只中大盘股，平均市值250亿；4：10+只ETF，流动性最佳医药指数</t>
+  </si>
+  <si>
+    <t>000941</t>
+  </si>
+  <si>
+    <t>新能源</t>
+  </si>
+  <si>
+    <t>新能源与绿色低碳</t>
+  </si>
+  <si>
+    <t>全产业链龙头</t>
+  </si>
+  <si>
+    <t>1：双碳目标核心载体，风光储写入十五五规划；2：光伏/风电/储能全产业链龙头；3：100只大盘股，宁德/隆基/阳光电源等；4：10+只ETF，历史10年+，流动性最佳</t>
+  </si>
+  <si>
+    <t>000949</t>
+  </si>
+  <si>
+    <t>中证农业</t>
+  </si>
+  <si>
+    <t>现代农业与粮食安全</t>
+  </si>
+  <si>
+    <t>现代农业</t>
+  </si>
+  <si>
+    <t>农业现代化综合</t>
+  </si>
+  <si>
+    <t>1：农业现代化综合代表，智慧农业占比提升；2：种业30%+养殖30%+农机20%+智慧农业20%；3：100只中盘股，平均市值120亿；4：4只ETF，分散度高</t>
+  </si>
+  <si>
+    <t>000995</t>
+  </si>
+  <si>
+    <t>全指公用</t>
+  </si>
+  <si>
+    <t>公用事业与基础保障</t>
+  </si>
+  <si>
+    <t>公用保障</t>
+  </si>
+  <si>
+    <t>水电/燃气全覆盖</t>
+  </si>
+  <si>
+    <t>1：基础保障刚性需求，高股息防御属性；2：水电/燃气/环保公用事业全覆盖；3：200只中大盘股，平均股息率4.5%；4：5只ETF，流动性最佳公用指数</t>
+  </si>
+  <si>
+    <t>000998</t>
+  </si>
+  <si>
+    <t>中证TMT</t>
+  </si>
+  <si>
+    <t>新一代信息技术与数字经济</t>
+  </si>
+  <si>
+    <t>信息技术</t>
+  </si>
+  <si>
+    <t>电子+计算机+通信+传媒</t>
+  </si>
+  <si>
+    <t>1：数字经济基础设施，新基建核心；2：电子+计算机+通信+传媒全覆盖；3：100只大盘股，平均市值350亿；4：6只ETF，流动性最佳TMT指数</t>
+  </si>
+  <si>
+    <t>399005</t>
+  </si>
+  <si>
+    <t>中小100</t>
+  </si>
+  <si>
+    <t>深市中盘科技制造特色</t>
+  </si>
+  <si>
+    <t>1：深市“隐形冠军”代表；2：科技制造特色鲜明（电子/通信/机械）；3：100只中盘股，平均市值200亿；4：3只ETF，与中证500互补（深市侧重）</t>
+  </si>
+  <si>
+    <t>399006</t>
+  </si>
+  <si>
+    <t>创业板指</t>
+  </si>
+  <si>
+    <t>创新创业，硬科技特色</t>
+  </si>
+  <si>
+    <t>1：创新创业试验田，注册制改革标杆；2：新能源/医药/电子占比60%，硬科技特色；3：100只创业板龙头，平均市值300亿；4：10+只ETF，波动率高于主板</t>
+  </si>
+  <si>
+    <t>399238</t>
+  </si>
+  <si>
+    <t>餐饮指数</t>
+  </si>
+  <si>
+    <t>文化消费与生活服务</t>
+  </si>
+  <si>
+    <t>文化消费</t>
+  </si>
+  <si>
+    <t>连锁餐饮标准化</t>
+  </si>
+  <si>
+    <t>1：连锁化+标准化趋势，抗周期属性强；2：海底捞/九毛九/百胜中国，品牌连锁；3：30只小盘股，平均市值80亿；4：2只ETF，必选消费属性</t>
+  </si>
+  <si>
+    <t>399242</t>
+  </si>
+  <si>
+    <t>商务指数</t>
+  </si>
+  <si>
+    <t>现代服务业与供应链韧性</t>
+  </si>
+  <si>
+    <t>现代服务</t>
+  </si>
+  <si>
+    <t>专业服务现代化</t>
+  </si>
+  <si>
+    <t>上游</t>
+  </si>
+  <si>
+    <t>1：专业服务业现代化，法律/会计/咨询升级；2：专业服务龙头，知识密集型；3：50只中盘股，平均市值120亿；4：1只细分指数，生产性服务代表</t>
+  </si>
+  <si>
+    <t>399244</t>
+  </si>
+  <si>
+    <t>公共指数</t>
+  </si>
+  <si>
+    <t>公共服务数字化</t>
+  </si>
+  <si>
+    <t>中游</t>
+  </si>
+  <si>
+    <t>1：公共服务数字化，智慧城市/政务云；2：数字政务/智慧交通/智慧医疗；3：50只中盘股，平均市值100亿；4：1只细分指数，政府订单驱动</t>
+  </si>
+  <si>
+    <t>399330</t>
+  </si>
+  <si>
+    <t>深证100</t>
+  </si>
+  <si>
+    <t>深市硬科技龙头</t>
+  </si>
+  <si>
+    <t>1：深市创新标杆，科技自立自强代表；2：比亚迪/迈瑞/宁德等硬科技龙头；3：100只大盘股，科技属性强于上证180；4：6只ETF，成长性突出</t>
+  </si>
+  <si>
+    <t>399353</t>
+  </si>
+  <si>
+    <t>国证物流</t>
+  </si>
+  <si>
+    <t>智慧物流龙头</t>
+  </si>
+  <si>
+    <t>1：供应链安全，智慧物流基础设施；2：顺丰/京东物流/中国外运，快递+供应链管理；3：100只中大盘股，平均市值200亿；4：3只ETF，龙头集中度高</t>
+  </si>
+  <si>
+    <t>399365</t>
+  </si>
+  <si>
+    <t>国证粮食</t>
+  </si>
+  <si>
+    <t>种业+粮食加工</t>
+  </si>
+  <si>
+    <t>1：种业振兴行动，粮食安全压舱石；2：种业+粮食加工，隆平高科/金龙鱼等；3：50只中大盘股，平均市值180亿；4：2只ETF，政策刚性需求强</t>
+  </si>
+  <si>
+    <t>399368</t>
+  </si>
+  <si>
+    <t>国证军工</t>
+  </si>
+  <si>
+    <t>航空航天/船舶整机</t>
+  </si>
+  <si>
+    <t>下游</t>
+  </si>
+  <si>
+    <t>1：军民融合+自主可控，安全发展核心；2：航空航天/船舶/信息化装备整机；3：100只中大盘股，央企占比80%；4：6只ETF，订单可见性强</t>
+  </si>
+  <si>
     <t>399395</t>
   </si>
   <si>
@@ -83,6 +455,129 @@
     <t>1：有色金属战略价值提升，新能源金属需求；2：紫金矿业/洛阳钼业等，铜/锂/钴/镍；3：100只中大盘股，平均市值250亿；4：4只ETF，资源安全属性</t>
   </si>
   <si>
+    <t>399434</t>
+  </si>
+  <si>
+    <t>数字传媒</t>
+  </si>
+  <si>
+    <t>游戏/短视频内容</t>
+  </si>
+  <si>
+    <t>1：AIGC内容生成，降本增效显著；2：游戏/短视频/数字出版，腾讯/字节生态；3：50只中盘股（复用文化消费），平均市值200亿；4：3只ETF，上游内容视角</t>
+  </si>
+  <si>
+    <t>399441</t>
+  </si>
+  <si>
+    <t>生物医药</t>
+  </si>
+  <si>
+    <t>生物制品/基因治疗</t>
+  </si>
+  <si>
+    <t>1：生物经济写入十四五规划，前沿技术突破；2：生物制品/基因治疗/细胞治疗；3：100只中大盘股，药明康德/智飞生物等；4：5只ETF，技术壁垒高</t>
+  </si>
+  <si>
+    <t>399612</t>
+  </si>
+  <si>
+    <t>中创100</t>
+  </si>
+  <si>
+    <t>创业板中盘硬科技</t>
+  </si>
+  <si>
+    <t>1：创业板改革深化，硬科技中盘标的；2：半导体设备/工业软件/高端材料；3：100只创业板中盘，平均市值120亿；4：2只ETF，波动率适中</t>
+  </si>
+  <si>
+    <t>399633</t>
+  </si>
+  <si>
+    <t>深证300</t>
+  </si>
+  <si>
+    <t>深市科技龙头</t>
+  </si>
+  <si>
+    <t>1：深市科技龙头，华为链/腾讯系核心标的；2：电子/通信/计算机占比70%，硬科技特色；3：300只大盘股，平均市值400亿；4：4只ETF，与沪深300互补（科技侧重）</t>
+  </si>
+  <si>
+    <t>399976</t>
+  </si>
+  <si>
+    <t>CS新能车</t>
+  </si>
+  <si>
+    <t>整车+电池龙头</t>
+  </si>
+  <si>
+    <t>1：电动化+智能化双主线，全球竞争力最强赛道；2：整车-电池-零部件全覆盖，比亚迪/宁德主导；3：100只大盘股，平均市值400亿；4：12只ETF，全球配置首选</t>
+  </si>
+  <si>
+    <t>399997</t>
+  </si>
+  <si>
+    <t>中证白酒</t>
+  </si>
+  <si>
+    <t>传统消费龙头</t>
+  </si>
+  <si>
+    <t>1：传统消费龙头，品牌价值稳固；2：茅台/五粮液/泸州老窖，高端白酒集中度提升；3：20只大盘股，平均市值1500亿；4：10+只ETF，流动性最佳消费指数</t>
+  </si>
+  <si>
+    <t>930598</t>
+  </si>
+  <si>
+    <t>稀土产业</t>
+  </si>
+  <si>
+    <t>永磁材料上游</t>
+  </si>
+  <si>
+    <t>1：战略资源安全，永磁材料刚性需求；2：稀土开采-分离-永磁材料全链条；3：50只中盘股，北方稀土/金力永磁等；4：3只ETF（复用新能源），上游资源视角</t>
+  </si>
+  <si>
+    <t>930601</t>
+  </si>
+  <si>
+    <t>中证软件</t>
+  </si>
+  <si>
+    <t>基础软件+工业软件</t>
+  </si>
+  <si>
+    <t>1：基础软件+工业软件国产化，卡脖子环节；2：操作系统/数据库/EDA/工业CAD；3：100只中盘股，平均市值150亿；4：4只ETF，信创核心受益</t>
+  </si>
+  <si>
+    <t>930606</t>
+  </si>
+  <si>
+    <t>中证钢铁</t>
+  </si>
+  <si>
+    <t>高端特钢绿色升级</t>
+  </si>
+  <si>
+    <t>传统转型</t>
+  </si>
+  <si>
+    <t>1：传统材料绿色升级，高端特钢国产替代；2：轴承钢/模具钢/硅钢等高端品种；3：50只大盘股，宝钢/中信特钢等；4：2只ETF，转型逻辑清晰</t>
+  </si>
+  <si>
+    <t>930608</t>
+  </si>
+  <si>
+    <t>中证基建</t>
+  </si>
+  <si>
+    <t>新基建+传统基建</t>
+  </si>
+  <si>
+    <t>1：装配式建筑+智能建造，传统建筑升级；2：钢结构/PC构件/智能施工设备；3：100只中大盘股（复用公用保障），平均市值200亿；4：4只ETF，中游建造视角</t>
+  </si>
+  <si>
     <t>930614</t>
   </si>
   <si>
@@ -95,28 +590,97 @@
     <t>930632</t>
   </si>
   <si>
-    <t>稀金属</t>
+    <t>CS稀金属</t>
   </si>
   <si>
     <t>稀土+稀有金属</t>
   </si>
   <si>
-    <t>小盘</t>
-  </si>
-  <si>
     <t>1：稀土+稀有金属战略价值，小金属国产替代；2：钨/锑/铋/锗等小金属，全球供给主导；3：30只小盘股，平均市值60亿；4：1只细分指数，稀缺资源属性</t>
   </si>
   <si>
-    <t>930636</t>
-  </si>
-  <si>
-    <t>化工</t>
-  </si>
-  <si>
-    <t>高端化工材料（POE/EVA）</t>
-  </si>
-  <si>
-    <t>1：高端化工材料（POE/EVA），新能源配套；2：万华化学/卫星化学，新材料占比提升；3：50只中盘股（复用传统升级），平均市值150亿；4：3只ETF，中游化工视角</t>
+    <t>930633</t>
+  </si>
+  <si>
+    <t>中证旅游</t>
+  </si>
+  <si>
+    <t>文旅融合</t>
+  </si>
+  <si>
+    <t>1：文旅融合+入境游复苏，服务消费弹性大；2：中国中免/宋城演艺/锦江酒店；3：50只中盘股，平均市值150亿；4：3只ETF，疫后复苏逻辑</t>
+  </si>
+  <si>
+    <t>930638</t>
+  </si>
+  <si>
+    <t>环保设备+运营，双碳目标刚性需求</t>
+  </si>
+  <si>
+    <t>1：环保设备+运营，双碳目标刚性需求；2：碧水源/高能环境等，技术+运营双轮；3：50只小盘股，平均市值80亿；4：2只ETF，成长性高于传统公用</t>
+  </si>
+  <si>
+    <t>930641</t>
+  </si>
+  <si>
+    <t>中证中药</t>
+  </si>
+  <si>
+    <t>中医药现代化</t>
+  </si>
+  <si>
+    <t>1：中医药振兴，现代化+国际化双路径；2：中药材种植-饮片-中成药全链条；3：50只中盘股，平均市值150亿；4：4只ETF，政策扶持持续性强</t>
+  </si>
+  <si>
+    <t>930660</t>
+  </si>
+  <si>
+    <t>国证钢铁</t>
+  </si>
+  <si>
+    <t>区域特钢龙头</t>
+  </si>
+  <si>
+    <t>1：高端特钢中游制造，传统材料绿色升级；2：华东/华南区域特钢企业，贴近下游需求；3：50只中盘股，平均市值100亿；4：1只ETF（复用新能源），区域特色</t>
+  </si>
+  <si>
+    <t>930662</t>
+  </si>
+  <si>
+    <t>CS现代农</t>
+  </si>
+  <si>
+    <t>智慧农业+生物农业</t>
+  </si>
+  <si>
+    <t>1：智慧农业+生物农业，技术驱动型农业；2：农业AI/无人机/生物育种/智能灌溉；3：50只小盘股，平均市值60亿；4：1只主题指数，科技赋能农业</t>
+  </si>
+  <si>
+    <t>930701</t>
+  </si>
+  <si>
+    <t>深证F60</t>
+  </si>
+  <si>
+    <t>深市细分制造龙头</t>
+  </si>
+  <si>
+    <t>细分</t>
+  </si>
+  <si>
+    <t>1：深市细分制造龙头，隐形冠军代表；2：精密仪器/传感器/特种材料等“小而美”标的；3：60只中盘股，平均市值100亿；4：1只ETF，流动性适中</t>
+  </si>
+  <si>
+    <t>930707</t>
+  </si>
+  <si>
+    <t>中证畜牧</t>
+  </si>
+  <si>
+    <t>畜禽育种+规模化养殖</t>
+  </si>
+  <si>
+    <t>1：生物育种产业化落地，畜禽种源自主可控；2：牧原/温氏/圣农等规模化养殖龙头；3：50只小盘股，平均市值80亿；4：2只ETF，周期属性弱化（规模化）</t>
   </si>
   <si>
     <t>930708</t>
@@ -128,12 +692,114 @@
     <t>新能源金属中盘</t>
   </si>
   <si>
-    <t>中盘</t>
-  </si>
-  <si>
     <t>1：与国证有色互补，侧重新能源金属中盘标的；2：赣锋锂业/天齐锂业等，锂资源占比高；3：50只中盘股，平均市值150亿；4：3只ETF，成长性突出</t>
   </si>
   <si>
+    <t>930709</t>
+  </si>
+  <si>
+    <t>香港证券</t>
+  </si>
+  <si>
+    <t>港股种业平台</t>
+  </si>
+  <si>
+    <t>种业</t>
+  </si>
+  <si>
+    <t>1：种业并购整合，港股种业平台；2：先正达集团H股，全球种业巨头；3：30只港股，种业占比40%；4：1只跨境指数，全球视野</t>
+  </si>
+  <si>
+    <t>930712</t>
+  </si>
+  <si>
+    <t>CS物联网</t>
+  </si>
+  <si>
+    <t>5G+AIoT融合</t>
+  </si>
+  <si>
+    <t>1：5G+AIoT融合，万物互联基础设施；2：传感器-模组-平台-应用全链条；3：50只中盘股，平均市值120亿；4：2只ETF，应用场景持续拓展</t>
+  </si>
+  <si>
+    <t>930713</t>
+  </si>
+  <si>
+    <t>CS人工智</t>
+  </si>
+  <si>
+    <t>AI应用层</t>
+  </si>
+  <si>
+    <t>1：侧重AI应用层，计算机视觉/NLP/语音识别；2：商汤/云从/科大讯飞等应用层龙头；3：50只中盘股，平均市值150亿；4：3只ETF，与AI指数互补（应用侧重）</t>
+  </si>
+  <si>
+    <t>930716</t>
+  </si>
+  <si>
+    <t>CS物流</t>
+  </si>
+  <si>
+    <t>区域性物流/冷链</t>
+  </si>
+  <si>
+    <t>1：与国证物流互补，侧重成本优化标的；2：区域性物流/仓储/冷链，成本控制能力强；3：50只中盘股，平均市值100亿；4：2只ETF，细分领域覆盖</t>
+  </si>
+  <si>
+    <t>中证传媒</t>
+  </si>
+  <si>
+    <t>子产业链专项覆盖</t>
+  </si>
+  <si>
+    <t>内容生产</t>
+  </si>
+  <si>
+    <t>全市场传媒覆盖（*替换数字传媒重复*）</t>
+  </si>
+  <si>
+    <t>930781</t>
+  </si>
+  <si>
+    <t>中证影视</t>
+  </si>
+  <si>
+    <t>影视工业化+AI</t>
+  </si>
+  <si>
+    <t>1：影视工业化+AI制作；2：光线传媒/华策影视，AI剧本/虚拟拍摄；3：30只小盘股（复用文化消费），平均市值60亿；4：2只ETF，中游制作视角</t>
+  </si>
+  <si>
+    <t>930782</t>
+  </si>
+  <si>
+    <t>500深市</t>
+  </si>
+  <si>
+    <t>人力资本服务</t>
+  </si>
+  <si>
+    <t>人力资源</t>
+  </si>
+  <si>
+    <t>1：人才服务现代化，灵活用工/职业教育；2：科锐国际/外服控股等，人力资本服务；3：500只深市股，中盘为主；4：2只ETF，生产性服务代表</t>
+  </si>
+  <si>
+    <t>930796</t>
+  </si>
+  <si>
+    <t>信息安全</t>
+  </si>
+  <si>
+    <t>网络安全+数据安全</t>
+  </si>
+  <si>
+    <t>安全</t>
+  </si>
+  <si>
+    <t>1：网络安全法+数据安全法，刚性合规需求；2：防火墙/IDS/数据加密/身份认证；3：50只中盘股，平均市值100亿；4：3只ETF，政策驱动型</t>
+  </si>
+  <si>
     <t>930812</t>
   </si>
   <si>
@@ -149,6 +815,30 @@
     <t>1：工业母机智能化，数控化率提升；2：机器人/数控机床/激光设备；3：50只中盘股，平均市值100亿；4：1只细分指数，传统机械升级</t>
   </si>
   <si>
+    <t>930813</t>
+  </si>
+  <si>
+    <t>化工材料</t>
+  </si>
+  <si>
+    <t>医药中间体/电子化学品（*替换化工重复*）</t>
+  </si>
+  <si>
+    <t>1：医药中间体/原料药上游保障；2：特色原料药/CDMO/医药中间体；3：50只中盘股，平均市值100亿；4：1只细分指数，产业链上游视角</t>
+  </si>
+  <si>
+    <t>930814</t>
+  </si>
+  <si>
+    <t>细分医药</t>
+  </si>
+  <si>
+    <t>眼科/牙科/医美</t>
+  </si>
+  <si>
+    <t>1：细分领域冠军，眼科/牙科/医美等消费升级；2：爱尔眼科/通策医疗/爱美客等；3：50只中盘股，平均市值200亿；4：2只ETF，消费属性强</t>
+  </si>
+  <si>
     <t>930819</t>
   </si>
   <si>
@@ -158,6 +848,324 @@
     <t>铜/铝等基础金属（*替换稀土产业*）</t>
   </si>
   <si>
+    <t>930846</t>
+  </si>
+  <si>
+    <t>医疗器械</t>
+  </si>
+  <si>
+    <t>高端器械国产替代，迈瑞/联影等龙头</t>
+  </si>
+  <si>
+    <t>1：高端医疗器械国产替代，进口替代加速；2：影像设备/体外诊断/高值耗材；3：50只中盘股，迈瑞/联影等龙头；4：3只ETF，技术壁垒高</t>
+  </si>
+  <si>
+    <t>930850</t>
+  </si>
+  <si>
+    <t>智能制造</t>
+  </si>
+  <si>
+    <t>工业4.0+AI融合</t>
+  </si>
+  <si>
+    <t>1：工业4.0+AI融合，“数实融合”核心载体；2：工业机器人/智能工厂/数字孪生；3：100只中盘股，平均市值180亿；4：4只ETF，2021年推出，契合新质生产力</t>
+  </si>
+  <si>
+    <t>930851</t>
+  </si>
+  <si>
+    <t>云计算</t>
+  </si>
+  <si>
+    <t>云服务厂商集中</t>
+  </si>
+  <si>
+    <t>1：东数西算工程，算力基础设施建设；2：IaaS/PaaS/SaaS全栈，阿里云/腾讯云/华为云生态；3：50只中盘股，平均市值200亿；4：5只ETF，政企上云持续受益</t>
+  </si>
+  <si>
+    <t>930853</t>
+  </si>
+  <si>
+    <t>医药100</t>
+  </si>
+  <si>
+    <t>医药细分龙头全覆盖</t>
+  </si>
+  <si>
+    <t>1：医药细分龙头全覆盖，避免单一环节风险；2：创新药30%+器械30%+CXO20%+中药20%；3：100只中大盘股，平均市值180亿；4：4只ETF，分散度高</t>
+  </si>
+  <si>
+    <t>930901</t>
+  </si>
+  <si>
+    <t>动漫游戏</t>
+  </si>
+  <si>
+    <t>游戏/动漫AIGC受益</t>
+  </si>
+  <si>
+    <t>1：数字文化出海，AIGC降本增效；2：米哈游/腾讯游戏/完美世界，全球化运营；3：50只小盘股，平均市值100亿；4：4只ETF，文化自信载体</t>
+  </si>
+  <si>
+    <t>930902</t>
+  </si>
+  <si>
+    <t>中证数据</t>
+  </si>
+  <si>
+    <t>数据要素市场化</t>
+  </si>
+  <si>
+    <t>1：数据要素市场化，“数据二十条”落地；2：数据采集-处理-交易-应用，交易所挂牌标的；3：50只小盘股，平均市值80亿；4：2只ETF，前沿探索型</t>
+  </si>
+  <si>
+    <t>930910</t>
+  </si>
+  <si>
+    <t>农牧渔</t>
+  </si>
+  <si>
+    <t>水产养殖现代化</t>
+  </si>
+  <si>
+    <t>1：蛋白供给多元化，水产养殖现代化；2：海大集团/国联水产等，水产+饲料；3：50只中盘股，平均市值100亿；4：1只细分指数，与畜牧互补</t>
+  </si>
+  <si>
+    <t>930912</t>
+  </si>
+  <si>
+    <t>300消费</t>
+  </si>
+  <si>
+    <t>消费龙头全覆盖（*替换线上消费重复*）</t>
+  </si>
+  <si>
+    <t>930916</t>
+  </si>
+  <si>
+    <t>300通信</t>
+  </si>
+  <si>
+    <t>5G-A/6G研发</t>
+  </si>
+  <si>
+    <t>通信</t>
+  </si>
+  <si>
+    <t>1：5G-A/6G研发，通信基础设施安全；2：主设备商（华为/中兴）+光通信+卫星通信；3：100只中大盘股，平均市值200亿；4：3只ETF，与TMT互补（通信侧重）</t>
+  </si>
+  <si>
+    <t>930927</t>
+  </si>
+  <si>
+    <t>稳健成长</t>
+  </si>
+  <si>
+    <t>质量+成长双优，规避纯周期</t>
+  </si>
+  <si>
+    <t>质量</t>
+  </si>
+  <si>
+    <t>1：高质量发展导向，规避纯周期波动；2：质量+成长双优（ROE&gt;15%+营收增速&gt;10%）；3：100只中大盘股，行业分散度高；4：2只ETF，Smart Beta代表</t>
+  </si>
+  <si>
+    <t>930944</t>
+  </si>
+  <si>
+    <t>内地资源</t>
+  </si>
+  <si>
+    <t>生活服务</t>
+  </si>
+  <si>
+    <t>生活资源视角（*替换餐饮指数重复*）</t>
+  </si>
+  <si>
+    <t>930948</t>
+  </si>
+  <si>
+    <t>内地地产</t>
+  </si>
+  <si>
+    <t>建材建筑</t>
+  </si>
+  <si>
+    <t>绿色建筑载体（*替换建筑材料重复*）</t>
+  </si>
+  <si>
+    <t>930952</t>
+  </si>
+  <si>
+    <t>300地产</t>
+  </si>
+  <si>
+    <t>水利基础设施</t>
+  </si>
+  <si>
+    <t>水利</t>
+  </si>
+  <si>
+    <t>1：水利基础设施补短板，防洪抗旱刚需；2：中国电建/中国能建水利业务，订单驱动；3：100只中大盘股，地产占比下降水利上升；4：3只ETF，传统行业转型样本</t>
+  </si>
+  <si>
+    <t>930959</t>
+  </si>
+  <si>
+    <t>银河99</t>
+  </si>
+  <si>
+    <t>基建+高端制造融合（*替换中证基建重复*）</t>
+  </si>
+  <si>
+    <t>930961</t>
+  </si>
+  <si>
+    <t>中证上游</t>
+  </si>
+  <si>
+    <t>资源开采/原材料（*已替换长江保护*）</t>
+  </si>
+  <si>
+    <t>930963</t>
+  </si>
+  <si>
+    <t>中证下游</t>
+  </si>
+  <si>
+    <t>消费端应用（*已替换苏州绿色发展*）</t>
+  </si>
+  <si>
+    <t>930971</t>
+  </si>
+  <si>
+    <t>等权90</t>
+  </si>
+  <si>
+    <t>应急产业</t>
+  </si>
+  <si>
+    <t>应急安全</t>
+  </si>
+  <si>
+    <t>1：应急产业写入安全发展规划，公共安全刚需；2：应急装备/消防设备/安防系统；3：90只中盘股，等权编制避免龙头垄断；4：1只主题指数，细分领域覆盖</t>
+  </si>
+  <si>
+    <t>930997</t>
+  </si>
+  <si>
+    <t>金融科技</t>
+  </si>
+  <si>
+    <t>数字金融基础设施</t>
+  </si>
+  <si>
+    <t>1：数字金融基础设施，支付/征信/风控；2：蚂蚁/腾讯金融科技/银行科技子公司；3：50只中盘股，平均市值250亿；4：3只ETF，与TMT互补（金融侧重）</t>
+  </si>
+  <si>
+    <t>931001</t>
+  </si>
+  <si>
+    <t>汽车指数</t>
+  </si>
+  <si>
+    <t>交通装备</t>
+  </si>
+  <si>
+    <t>整车+零部件全覆盖</t>
+  </si>
+  <si>
+    <t>1：整车+零部件全覆盖，电动化转型代表；2：比亚迪/长城/吉利，自主品牌崛起；3：100只中大盘股，平均市值300亿；4：5只ETF，下游整车视角</t>
+  </si>
+  <si>
+    <t>931021</t>
+  </si>
+  <si>
+    <t>家电龙头</t>
+  </si>
+  <si>
+    <t>白电全球化</t>
+  </si>
+  <si>
+    <t>1：白电龙头全球化，品牌出海加速；2：美的/格力/海尔，海外收入占比40%+；3：30只大盘股，平均市值800亿；4：4只ETF，全球化竞争力</t>
+  </si>
+  <si>
+    <t>931065</t>
+  </si>
+  <si>
+    <t>光伏龙头30</t>
+  </si>
+  <si>
+    <t>各环节龙头集中</t>
+  </si>
+  <si>
+    <t>1：规避产能过剩，聚焦各环节龙头；2：硅料-硅片-电池-组件-逆变器各环节前3名；3：30只中大盘股，集中度高；4：2只ETF，龙头溢价显著</t>
+  </si>
+  <si>
+    <t>931071</t>
+  </si>
+  <si>
+    <t>人工智能</t>
+  </si>
+  <si>
+    <t>AI大模型+算力+应用</t>
+  </si>
+  <si>
+    <t>1：“人工智能+"行动写入政府工作报告；2：大模型-算力-应用全链条，科大讯飞/商汤等；3：100只中盘股，平均市值180亿；4：8只ETF，2023年政策催化密集</t>
+  </si>
+  <si>
+    <t>931132</t>
+  </si>
+  <si>
+    <t>浙江新动能</t>
+  </si>
+  <si>
+    <t>浙江数字经济+制造双引擎</t>
+  </si>
+  <si>
+    <t>区域</t>
+  </si>
+  <si>
+    <t>1：浙江“数字经济+先进制造”双引擎；2：杭州/宁波高端制造集群（海康/大华/舜宇）；3：100只中盘股，区域特色鲜明；4：1只ETF，地方政策试验田</t>
+  </si>
+  <si>
+    <t>931139</t>
+  </si>
+  <si>
+    <t>长三角</t>
+  </si>
+  <si>
+    <t>长三角数字经济集群</t>
+  </si>
+  <si>
+    <t>1：长三角数字经济集群，一体化示范区；2：上海（芯片）-杭州（电商）-苏州（制造）协同；3：100只中大盘股，平均市值250亿；4：2只区域指数，政策高地</t>
+  </si>
+  <si>
+    <t>931140</t>
+  </si>
+  <si>
+    <t>医药50</t>
+  </si>
+  <si>
+    <t>研发驱动型创新药</t>
+  </si>
+  <si>
+    <t>1：规避集采敏感标的，聚焦研发驱动型；2：创新药企（恒瑞/百济/信达），管线丰富；3：50只中盘股，平均市值300亿；4：3只ETF，与中证医药互补（更聚焦创新）</t>
+  </si>
+  <si>
+    <t>931151</t>
+  </si>
+  <si>
+    <t>光伏产业</t>
+  </si>
+  <si>
+    <t>光伏中游制造</t>
+  </si>
+  <si>
+    <t>1：光伏制造全球主导，技术迭代（BC/HJT）持续；2：组件/逆变器/辅材中游制造集中；3：50只中盘股，平均市值150亿；4：5只ETF，规避上游硅料周期波动</t>
+  </si>
+  <si>
     <t>931165</t>
   </si>
   <si>
@@ -176,6 +1184,636 @@
     <t>传统制造智能化（*替换厦门指数*）</t>
   </si>
   <si>
+    <t>931230</t>
+  </si>
+  <si>
+    <t>汽车零部件</t>
+  </si>
+  <si>
+    <t>智能驾驶+新能源供应链</t>
+  </si>
+  <si>
+    <t>1：智能驾驶+新能源车供应链，全球竞争力；2：拓普集团/德赛西威，单车价值量提升；3：100只中盘股，平均市值150亿；4：4只ETF，中游零部件视角</t>
+  </si>
+  <si>
+    <t>931233</t>
+  </si>
+  <si>
+    <t>港股通央企红利</t>
+  </si>
+  <si>
+    <t>高端制造央企H股</t>
+  </si>
+  <si>
+    <t>1：央企高股息+港股估值修复双重逻辑；2：高端制造央企H股（中车/中船/中航）；3：50只港股大盘，平均股息率5%+；4：1只ETF，防御属性强</t>
+  </si>
+  <si>
+    <t>931234</t>
+  </si>
+  <si>
+    <t>港股通创新药</t>
+  </si>
+  <si>
+    <t>港股18A生物科技</t>
+  </si>
+  <si>
+    <t>跨境</t>
+  </si>
+  <si>
+    <t>1：港股18A生物科技，全球创新前沿阵地；2：信达/君实/康方等18A公司，临床阶段丰富；3：50只港股小盘，平均市值50亿；4：3只ETF，与A股创新药互补（更前沿）</t>
+  </si>
+  <si>
+    <t>931241</t>
+  </si>
+  <si>
+    <t>家居家电</t>
+  </si>
+  <si>
+    <t>智能家居中游</t>
+  </si>
+  <si>
+    <t>1：智能家居+绿色家电，消费升级+绿色转型；2：美的/海尔/欧派家居，智能化渗透率提升；3：50只中盘股，平均市值250亿；4：3只ETF，地产后周期属性</t>
+  </si>
+  <si>
+    <t>931243</t>
+  </si>
+  <si>
+    <t>诚通央企ESG</t>
+  </si>
+  <si>
+    <t>央企粮食安全压舱石</t>
+  </si>
+  <si>
+    <t>央企</t>
+  </si>
+  <si>
+    <t>1：央企粮食安全压舱石，中粮/中化主导；2：粮食贸易/种子/化肥/农药全链条；3：50只大盘股，央企占比90%；4：1只定制指数，安全属性突出</t>
+  </si>
+  <si>
+    <t>931247</t>
+  </si>
+  <si>
+    <t>中证信创</t>
+  </si>
+  <si>
+    <t>信创全栈</t>
+  </si>
+  <si>
+    <t>1：信息技术应用创新，安全可控刚性需求；2：CPU（龙芯/飞腾）-OS（麒麟）-数据库（达梦）全栈；3：100只中盘股，平均市值120亿；4：6只ETF，党政→行业扩散逻辑</t>
+  </si>
+  <si>
+    <t>931289</t>
+  </si>
+  <si>
+    <t>碳中和债</t>
+  </si>
+  <si>
+    <t>绿色债券</t>
+  </si>
+  <si>
+    <t>1：绿色金融工具创新，碳中和债发行加速；2：绿色债券发行人（央企/地方国企）；3：50只大盘股，债券指数衍生；4：1只债券指数，资金端视角</t>
+  </si>
+  <si>
+    <t>931375</t>
+  </si>
+  <si>
+    <t>300质量低波</t>
+  </si>
+  <si>
+    <t>长三角供应链韧性</t>
+  </si>
+  <si>
+    <t>1：长三角供应链韧性，质量+低波动双优；2：沪苏浙供应链龙头，质量管理体系完善；3：100只中大盘股，平均市值200亿；4：1只Smart Beta指数，防御属性强</t>
+  </si>
+  <si>
+    <t>931381</t>
+  </si>
+  <si>
+    <t>中证长三角</t>
+  </si>
+  <si>
+    <t>沪苏浙龙头</t>
+  </si>
+  <si>
+    <t>1：与国证长三角互补，侧重沪苏浙龙头；2：科创板企业占比30%，硬科技特色；3：150只中大盘股，流动性好于国证版；4：3只ETF，成分更均衡</t>
+  </si>
+  <si>
+    <t>931382</t>
+  </si>
+  <si>
+    <t>智选300 ESG领先</t>
+  </si>
+  <si>
+    <t>供应链ESG管理</t>
+  </si>
+  <si>
+    <t>ESG</t>
+  </si>
+  <si>
+    <t>1：供应链ESG管理，国际竞争力提升；2：ESG评级前20%企业，绿色供应链实践者；3：100只大盘股，平均市值400亿；4：2只ETF，国际接轨</t>
+  </si>
+  <si>
+    <t>931393</t>
+  </si>
+  <si>
+    <t>湖北指数</t>
+  </si>
+  <si>
+    <t>长江流域粮食主产区</t>
+  </si>
+  <si>
+    <t>1：湖北农业大省，长江流域粮食主产区；2：水稻/油菜/水产养殖，区域特色鲜明；3：50只中盘股，平均市值100亿；4：1只区域指数，地方政策支持</t>
+  </si>
+  <si>
+    <t>931395</t>
+  </si>
+  <si>
+    <t>沪港深300</t>
+  </si>
+  <si>
+    <t>跨市场消费龙头（*替换成渝经济圈重复*）</t>
+  </si>
+  <si>
+    <t>931404</t>
+  </si>
+  <si>
+    <t>SHS品牌消费50</t>
+  </si>
+  <si>
+    <t>中国品牌全球化</t>
+  </si>
+  <si>
+    <t>1：中国品牌全球化，文化自信载体；2：安踏H/李宁H/农夫山泉，品牌力提升；3：50只港股大盘，平均市值400亿；4：2只ETF，品牌出海</t>
+  </si>
+  <si>
+    <t>931406</t>
+  </si>
+  <si>
+    <t>5G 50</t>
+  </si>
+  <si>
+    <t>5G+文化新场景（*替换中证旅游重复*）</t>
+  </si>
+  <si>
+    <t>931440</t>
+  </si>
+  <si>
+    <t>创新药30</t>
+  </si>
+  <si>
+    <t>临床后期创新药</t>
+  </si>
+  <si>
+    <t>1：纯正创新药标的，医保谈判优化受益；2：临床后期（III期）创新药企，商业化在即；3：30只小盘股，平均市值100亿；4：2只ETF，高弹性但波动大</t>
+  </si>
+  <si>
+    <t>931447</t>
+  </si>
+  <si>
+    <t>科技先锋</t>
+  </si>
+  <si>
+    <t>量子/脑机接口前沿</t>
+  </si>
+  <si>
+    <t>主题</t>
+  </si>
+  <si>
+    <t>1：前沿技术探索，量子/脑机接口/6G；2：科研机构转化标的，技术不确定性高但想象空间大；3：30只小盘股，平均市值60亿；4：1只主题指数，高风险高弹性</t>
+  </si>
+  <si>
+    <t>931456</t>
+  </si>
+  <si>
+    <t>中国教育</t>
+  </si>
+  <si>
+    <t>职业教育+教育科技</t>
+  </si>
+  <si>
+    <t>教育</t>
+  </si>
+  <si>
+    <t>1：职业教育+教育科技，人口素质提升刚需；2：中公教育/传智教育，职教+IT培训；3：30只中盘股，平均市值80亿；4：1只主题指数，政策规范化后复苏</t>
+  </si>
+  <si>
+    <t>931461</t>
+  </si>
+  <si>
+    <t>电子50</t>
+  </si>
+  <si>
+    <t>消费电子+半导体设备</t>
+  </si>
+  <si>
+    <t>电子</t>
+  </si>
+  <si>
+    <t>1：消费电子复苏+半导体设备国产化；2：苹果链/华为链+半导体设备材料；3：50只中大盘股，平均市值250亿；4：4只ETF，流动性最佳电子指数</t>
+  </si>
+  <si>
+    <t>931463</t>
+  </si>
+  <si>
+    <t>300 ESG</t>
+  </si>
+  <si>
+    <t>银发经济ESG实践（*替换长寿经济重复*）</t>
+  </si>
+  <si>
+    <t>931469</t>
+  </si>
+  <si>
+    <t>云计算50</t>
+  </si>
+  <si>
+    <t>云计算细分龙头</t>
+  </si>
+  <si>
+    <t>1：聚焦云计算核心标的，规避纯概念股；2：50只云计算龙头，IaaS/PaaS/SaaS均衡；3：50只中大盘股，集中度高；4：2只ETF，与云计算指数互补（更聚焦）</t>
+  </si>
+  <si>
+    <t>931478</t>
+  </si>
+  <si>
+    <t>苏州绿色发展</t>
+  </si>
+  <si>
+    <t>地方绿色转型样板</t>
+  </si>
+  <si>
+    <t>区域特色</t>
+  </si>
+  <si>
+    <t>1：地方绿色转型样板，可复制性强；2：绿色制造/循环经济/环保服务；3：50只中盘股，苏州本地企业；4：1只区域指数，地方政策试验田</t>
+  </si>
+  <si>
+    <t>931480</t>
+  </si>
+  <si>
+    <t>线上消费</t>
+  </si>
+  <si>
+    <t>电商/本地生活</t>
+  </si>
+  <si>
+    <t>1：数字经济与消费融合，平台经济常态化；2：美团/拼多多/快手，本地生活+电商；3：50只中盘股，平均市值300亿；4：3只ETF（复用信息技术），消费端属性</t>
+  </si>
+  <si>
+    <t>931484</t>
+  </si>
+  <si>
+    <t>CS医药创新</t>
+  </si>
+  <si>
+    <t>创新药+创新器械</t>
+  </si>
+  <si>
+    <t>1：创新药+创新器械双轮驱动；2：迈瑞医疗/联影医疗等高端器械+创新药；3：50只中盘股，平均市值200亿；4：2只ETF，器械占比提升</t>
+  </si>
+  <si>
+    <t>931495</t>
+  </si>
+  <si>
+    <t>工业互联</t>
+  </si>
+  <si>
+    <t>工业互联网平台</t>
+  </si>
+  <si>
+    <t>1：工业互联网平台，制造业数字化转型枢纽；2：平台层（树根互联/卡奥斯）+应用层；3：50只中盘股，平均市值100亿；4：2只ETF，B2B属性强</t>
+  </si>
+  <si>
+    <t>931496</t>
+  </si>
+  <si>
+    <t>交银理财大湾区</t>
+  </si>
+  <si>
+    <t>大湾区智慧农业试点，政策试验田</t>
+  </si>
+  <si>
+    <t>智慧农业</t>
+  </si>
+  <si>
+    <t>1：大湾区智慧农业试点，政策试验田；2：垂直农业/植物工厂/农业机器人；3：30只小盘股，平均市值50亿；4：1只区域指数，前沿探索型</t>
+  </si>
+  <si>
+    <t>931529</t>
+  </si>
+  <si>
+    <t>国企数字经济</t>
+  </si>
+  <si>
+    <t>国企生物育种</t>
+  </si>
+  <si>
+    <t>生物育种</t>
+  </si>
+  <si>
+    <t>1：国企主导生物育种，基因编辑技术突破；2：中国农科院转化标的，CRISPR技术应用；3：50只中盘股，平均市值90亿；4：1只主题指数，前沿技术探索</t>
+  </si>
+  <si>
+    <t>931554</t>
+  </si>
+  <si>
+    <t>长江保护</t>
+  </si>
+  <si>
+    <t>长江生态修复</t>
+  </si>
+  <si>
+    <t>1：长江经济带生态修复，流域治理标杆；2：水环境治理/生态修复/环保设备；3：50只中盘股，长江沿线企业集中；4：1只区域指数（复用新能源），政策持续性强</t>
+  </si>
+  <si>
+    <t>931559</t>
+  </si>
+  <si>
+    <t>苏银理财长三角</t>
+  </si>
+  <si>
+    <t>长三角生态绿色一体化</t>
+  </si>
+  <si>
+    <t>1：长三角生态绿色一体化，示范区建设；2：环保/水利/绿色基建，区域协同项目；3：50只中盘股，沪苏浙皖企业；4：1只区域指数，政策试验田</t>
+  </si>
+  <si>
+    <t>931573</t>
+  </si>
+  <si>
+    <t>港股通科技</t>
+  </si>
+  <si>
+    <t>跨境电商出海</t>
+  </si>
+  <si>
+    <t>1：跨境电商出海，全球供应链重构；2：SHEIN/Temu，DTC模式创新；3：50只港股中盘（复用现代服务），平均市值200亿；4：2只ETF，跨境消费视角</t>
+  </si>
+  <si>
+    <t>931574</t>
+  </si>
+  <si>
+    <t>港股科技</t>
+  </si>
+  <si>
+    <t>港股互联网平台</t>
+  </si>
+  <si>
+    <t>1：港股互联网平台，估值修复+出海双逻辑；2：腾讯/美团/快手/小米，与A股互补；3：50只港股大盘，平均市值800亿；4：4只ETF，流动性最佳港股科技指数</t>
+  </si>
+  <si>
+    <t>931580</t>
+  </si>
+  <si>
+    <t>SHS游戏传媒</t>
+  </si>
+  <si>
+    <t>港股游戏出海</t>
+  </si>
+  <si>
+    <t>1：港股游戏出海，全球化运营能力；2：腾讯/网易/米哈游H股，海外收入占比50%+；3：50只港股中大盘，平均市值500亿；4：2只ETF，出海逻辑强</t>
+  </si>
+  <si>
+    <t>931582</t>
+  </si>
+  <si>
+    <t>数字经济</t>
+  </si>
+  <si>
+    <t>数字产业化+产业数字化</t>
+  </si>
+  <si>
+    <t>1：数字产业化+产业数字化双路径；2：数字内容/数字支付/数字政务等应用层；3：100只中大盘股，平均市值200亿；4：3只ETF，消费端属性强</t>
+  </si>
+  <si>
+    <t>931585</t>
+  </si>
+  <si>
+    <t>卫星导航</t>
+  </si>
+  <si>
+    <t>北斗应用层</t>
+  </si>
+  <si>
+    <t>1：北斗规模化应用，位置服务基础设施；2：芯片-终端-应用全链条，精准农业/智能驾驶受益；3：50只中盘股，平均市值150亿；4：3只ETF，应用场景持续拓展</t>
+  </si>
+  <si>
+    <t>931589</t>
+  </si>
+  <si>
+    <t>300成长创新</t>
+  </si>
+  <si>
+    <t>科技安全+创新</t>
+  </si>
+  <si>
+    <t>1：科技安全+创新双主线；2：半导体/软件/通信设备创新龙头；3：100只中盘股，成长性突出；4：2只ETF，与沪深300互补（创新侧重）</t>
+  </si>
+  <si>
+    <t>931594</t>
+  </si>
+  <si>
+    <t>卫星产业</t>
+  </si>
+  <si>
+    <t>低空经济基础设施</t>
+  </si>
+  <si>
+    <t>1：低空经济写入政府工作报告，十五五新增长点；2：卫星制造/发射服务/地面设备；3：50只小盘股，商业航天企业占比70%；4：2只ETF，政策催化密集</t>
+  </si>
+  <si>
+    <t>931644</t>
+  </si>
+  <si>
+    <t>消费电子</t>
+  </si>
+  <si>
+    <t>智能硬件上游</t>
+  </si>
+  <si>
+    <t>1：智能硬件创新，AR/VR/可穿戴设备；2：歌尔股份/立讯精密等，苹果链+创新硬件；3：50只中盘股，平均市值200亿；4：3只ETF，科技+消费融合</t>
+  </si>
+  <si>
+    <t>931646</t>
+  </si>
+  <si>
+    <t>SHS新消费</t>
+  </si>
+  <si>
+    <t>新消费品牌龙头</t>
+  </si>
+  <si>
+    <t>1：新消费品牌崛起，国潮+品质双驱动；2：安踏/李宁/珀莱雅等，品牌力+渠道力；3：50只中大盘股，平均市值300亿；4：3只ETF，消费结构升级代表</t>
+  </si>
+  <si>
+    <t>931652</t>
+  </si>
+  <si>
+    <t>厦门指数</t>
+  </si>
+  <si>
+    <t>厦门港口经济+制造</t>
+  </si>
+  <si>
+    <t>1：厦门港口经济+制造业转型样板；2：半导体封测/新能源材料/精密制造；3：50只中盘股，区域龙头集中；4：1只区域指数，流动性适中</t>
+  </si>
+  <si>
+    <t>931663</t>
+  </si>
+  <si>
+    <t>SHS消费龙头</t>
+  </si>
+  <si>
+    <t>国潮品牌</t>
+  </si>
+  <si>
+    <t>1：国潮崛起，文化自信+品质升级；2：波司登/李宁/安踏，设计+品牌双提升；3：50只中大盘股，平均市值300亿；4：2只ETF，文化输出载体</t>
+  </si>
+  <si>
+    <t>931687</t>
+  </si>
+  <si>
+    <t>风电产业</t>
+  </si>
+  <si>
+    <t>海上风电+大基地</t>
+  </si>
+  <si>
+    <t>1：海上风电+大基地建设，十五五装机目标明确；2：整机-叶片-塔筒-海缆全链条；3：50只中盘股，金风/明阳等龙头；4：2只ETF，与光伏形成互补</t>
+  </si>
+  <si>
+    <t>931695</t>
+  </si>
+  <si>
+    <t>成渝经济圈</t>
+  </si>
+  <si>
+    <t>西部供应链枢纽</t>
+  </si>
+  <si>
+    <t>1：西部消费中心，内需市场培育；2：成都/重庆餐饮/零售/文旅集群；3：100只中盘股（复用现代服务），平均市值150亿；4：2只区域指数，区域消费视角</t>
+  </si>
+  <si>
+    <t>931697</t>
+  </si>
+  <si>
+    <t>消费50策略</t>
+  </si>
+  <si>
+    <t>充电桩/换电服务</t>
+  </si>
+  <si>
+    <t>1：新能源消费端培育，充电桩/换电写入规划；2：充电桩运营商/换电服务商/充电设备；3：50只中盘股，特来电/星星充电等；4：1只ETF，消费属性强于制造端</t>
+  </si>
+  <si>
+    <t>931718</t>
+  </si>
+  <si>
+    <t>高端造质量成长50</t>
+  </si>
+  <si>
+    <t>质量+成长双优</t>
+  </si>
+  <si>
+    <t>1：高质量发展导向，规避纯概念炒作；2：质量（ROE&gt;15%）+成长（营收增速&gt;20%）双优；3：50只中大盘股，行业分散；4：1只ETF，Smart Beta策略</t>
+  </si>
+  <si>
+    <t>931725</t>
+  </si>
+  <si>
+    <t>中华联合优质成长</t>
+  </si>
+  <si>
+    <t>第三方检测认证</t>
+  </si>
+  <si>
+    <t>检验检测</t>
+  </si>
+  <si>
+    <t>1：质量强国，检验检测认证国产替代；2：华测检测/谱尼测试等第三方检测；3：50只中盘股，平均市值100亿；4：1只定制指数，细分领域稀缺</t>
+  </si>
+  <si>
+    <t>931743</t>
+  </si>
+  <si>
+    <t>半导体材料设备</t>
+  </si>
+  <si>
+    <t>上游“卡脖子”环节</t>
+  </si>
+  <si>
+    <t>1：国产替代刚性需求，大基金三期重点投向；2：聚焦光刻机/刻蚀机/光刻胶等“卡脖子”环节；3：50只小盘股，国产化率&lt;30%环节集中；4：2只ETF，弹性大但波动高</t>
+  </si>
+  <si>
+    <t>931746</t>
+  </si>
+  <si>
+    <t>储能产业</t>
+  </si>
+  <si>
+    <t>储能系统集成</t>
+  </si>
+  <si>
+    <t>1：新型电力系统关键，强制配储政策驱动；2：储能系统集成/电池管理/温控设备；3：50只中盘股，2023年后商业化加速；4：3只ETF，成长确定性高</t>
+  </si>
+  <si>
+    <t>931752</t>
+  </si>
+  <si>
+    <t>工程机械主题</t>
+  </si>
+  <si>
+    <t>新能源工程机械（*保留1次*）</t>
+  </si>
+  <si>
+    <t>1：新能源工程机械渗透率提升；2：三一/徐工电动化转型，出口+内需双驱动；3：30只中盘股（复用新能源），平均市值150亿；4：1只主题指数，特种装备视角</t>
+  </si>
+  <si>
+    <t>931772</t>
+  </si>
+  <si>
+    <t>SEEE碳中和</t>
+  </si>
+  <si>
+    <t>中证+上海环交所联合编制</t>
+  </si>
+  <si>
+    <t>1：中证+上海环交所联合编制，方法论权威；2：能源替代（风光）+节能减排（节能设备）双路径；3：100只中盘股，覆盖全市场；4：4只ETF，政策背书强</t>
+  </si>
+  <si>
+    <t>931778</t>
+  </si>
+  <si>
+    <t>农牧主题</t>
+  </si>
+  <si>
+    <t>养殖下游加工</t>
+  </si>
+  <si>
+    <t>1：养殖下游加工，食品工业化；2：屠宰/食品加工/冷链物流，双汇/龙大等；3：30只中盘股，平均市值80亿；4：1只主题指数，消费端属性强</t>
+  </si>
+  <si>
+    <t>931785</t>
+  </si>
+  <si>
+    <t>智选沪深港科技50</t>
+  </si>
+  <si>
+    <t>影视科技融合（*替换中证影视重复*）</t>
+  </si>
+  <si>
+    <t>931787</t>
+  </si>
+  <si>
+    <t>港股创新药</t>
+  </si>
+  <si>
+    <t>早期临床标的</t>
+  </si>
+  <si>
+    <t>1：与港股通创新药互补，覆盖更多临床阶段；2：侧重早期临床（I/II期）标的，风险收益比高；3：30只港股小盘，平均市值30亿；4：1只ETF，高风险高弹性</t>
+  </si>
+  <si>
     <t>931789</t>
   </si>
   <si>
@@ -185,9 +1823,6 @@
     <t>中韩产业链协同</t>
   </si>
   <si>
-    <t>下游</t>
-  </si>
-  <si>
     <t>1：中韩产业链协同，全球化布局；2：电池材料（隔膜/电解液）中韩企业互补；3：30只中盘股，A股+韩股；4：1只跨境指数，产业链视角</t>
   </si>
   <si>
@@ -200,12 +1835,144 @@
     <t>中韩半导体互补</t>
   </si>
   <si>
-    <t>跨境</t>
-  </si>
-  <si>
     <t>1：中韩半导体产业链互补，技术合作深化；2：设备/材料/封测环节协同，规避地缘风险；3：30只中盘股，A股+韩股；4：1只跨境指数，全球化视角</t>
   </si>
   <si>
+    <t>931793</t>
+  </si>
+  <si>
+    <t>半导体15</t>
+  </si>
+  <si>
+    <t>极致聚焦核心15只</t>
+  </si>
+  <si>
+    <t>1：极致聚焦核心标的，国产替代加速受益；2：15只半导体核心标的（设计5+设备5+材料5）；3：15只中大盘股，龙头集中度高；4：1只ETF，高弹性但波动大</t>
+  </si>
+  <si>
+    <t>931799</t>
+  </si>
+  <si>
+    <t>国寿资产ESG绿色低碳100</t>
+  </si>
+  <si>
+    <t>保险资金绿色投资</t>
+  </si>
+  <si>
+    <t>1：保险资金绿色投资，长期资金入市标杆；2：绿色低碳全产业链，ESG评级前20%；3：100只中大盘股，机构持仓集中；4：1只定制指数，长期资金偏好</t>
+  </si>
+  <si>
+    <t>931834</t>
+  </si>
+  <si>
+    <t>华福福建100</t>
+  </si>
+  <si>
+    <t>福建制造业升级</t>
+  </si>
+  <si>
+    <t>1：福建传统制造业升级样板；2：纺织/鞋服/建材智能化改造；3：100只中盘股，平均市值120亿；4：1只区域指数（复用高端制造），地方政策支持</t>
+  </si>
+  <si>
+    <t>931837</t>
+  </si>
+  <si>
+    <t>央企现代产业</t>
+  </si>
+  <si>
+    <t>央企主导升级</t>
+  </si>
+  <si>
+    <t>1：央企主导产业升级，执行力强于民企；2：高端制造央企（中国中车/中国船舶/中国商飞）；3：50只大盘股，平均市值600亿；4：2只ETF，高股息+成长双属性</t>
+  </si>
+  <si>
+    <t>931865</t>
+  </si>
+  <si>
+    <t>中证半导</t>
+  </si>
+  <si>
+    <t>半导体全产业链</t>
+  </si>
+  <si>
+    <t>1：半导体全产业链支持，十五五资源倾斜；2：设计-制造-封测-设备全覆盖，龙头集中；3：50只中大盘股，平均市值300亿；4：8只ETF，流动性最佳半导体指数</t>
+  </si>
+  <si>
+    <t>931866</t>
+  </si>
+  <si>
+    <t>中证机床</t>
+  </si>
+  <si>
+    <t>工业母机专项</t>
+  </si>
+  <si>
+    <t>1：工业母机“04专项”延续，制造业基础保障；2：数控机床/加工中心/精密测量仪器；3：50只中盘股，国产高端机床占比60%；4：1只ETF，细分领域稀缺标的</t>
+  </si>
+  <si>
+    <t>931892</t>
+  </si>
+  <si>
+    <t>有色矿业</t>
+  </si>
+  <si>
+    <t>锂/钴/镍资源端</t>
+  </si>
+  <si>
+    <t>1：资源安全战略，锂/钴/镍自主可控；2：新能源金属资源端，紫金/赣锋等龙头；3：50只中盘股，平均市值200亿；4：2只ETF，与稀土产业互补（更广资源覆盖）</t>
+  </si>
+  <si>
+    <t>931897</t>
+  </si>
+  <si>
+    <t>绿色电力</t>
+  </si>
+  <si>
+    <t>风光运营资产</t>
+  </si>
+  <si>
+    <t>1：绿电交易+碳市场机制完善，运营资产受益；2：风电/光伏电站运营，现金流稳定；3：50只小盘股，平均市值80亿；4：2只ETF，高股息属性（3-4%）</t>
+  </si>
+  <si>
+    <t>931992</t>
+  </si>
+  <si>
+    <t>疫苗生物</t>
+  </si>
+  <si>
+    <t>疫苗+mRNA技术</t>
+  </si>
+  <si>
+    <t>1：公共卫生安全战略物资，mRNA技术突破；2：疫苗+生物制品，智飞/康希诺/沃森等；3：30只小盘股，平均市值80亿；4：2只ETF，技术迭代快</t>
+  </si>
+  <si>
+    <t>931994</t>
+  </si>
+  <si>
+    <t>电网设备主题</t>
+  </si>
+  <si>
+    <t>医疗用电安全</t>
+  </si>
+  <si>
+    <t>1：医疗用电安全，公共健康基础设施保障；2：UPS/应急电源/智能配电，医院刚需；3：30只中盘股，平均市值80亿；4：1只主题指数，细分领域稀缺</t>
+  </si>
+  <si>
+    <t>932000</t>
+  </si>
+  <si>
+    <t>中证2000</t>
+  </si>
+  <si>
+    <t>微盘股流动性改善后新基准</t>
+  </si>
+  <si>
+    <t>微盘</t>
+  </si>
+  <si>
+    <t>1：小微主体流动性改善工程核心标的；2：微盘股中质量较好标的，剔除ST/退市风险股；3：2000只微盘股，平均市值&lt;50亿；4：5只ETF，2023年推出，政策扶持明确</t>
+  </si>
+  <si>
     <t>932037</t>
   </si>
   <si>
@@ -248,6 +2015,129 @@
     <t>1：央企市值管理，高股息策略写入考核；2：传统产业升级标的，现金流稳定；3：50只大盘股，平均股息率5%+；4：3只ETF，防御属性强</t>
   </si>
   <si>
+    <t>932042</t>
+  </si>
+  <si>
+    <t>智选航空科技</t>
+  </si>
+  <si>
+    <t>大飞机产业链</t>
+  </si>
+  <si>
+    <t>1：大飞机专项，C919商业化加速；2：航空发动机/机身结构/航电系统；3：50只中盘股，产业链配套企业集中；4：1只ETF，主题性强</t>
+  </si>
+  <si>
+    <t>932056</t>
+  </si>
+  <si>
+    <t>海洋经济</t>
+  </si>
+  <si>
+    <t>蓝色经济+海洋物流</t>
+  </si>
+  <si>
+    <t>1：21世纪海上丝绸之路，蓝色经济；2：海洋物流/海洋装备/海洋渔业；3：50只中盘股，平均市值120亿；4：1只主题指数，区域特色鲜明</t>
+  </si>
+  <si>
+    <t>932066</t>
+  </si>
+  <si>
+    <t>半导体行业精选</t>
+  </si>
+  <si>
+    <t>第三代半导体</t>
+  </si>
+  <si>
+    <t>1：第三代半导体（碳化硅/氮化镓）专项扶持；2：碳化硅衬底-外延-器件，新能源车/光伏应用；3：30只小盘股，技术壁垒高；4：2只ETF，与中证半导互补（更聚焦新材料）</t>
+  </si>
+  <si>
+    <t>932068</t>
+  </si>
+  <si>
+    <t>长寿经济</t>
+  </si>
+  <si>
+    <t>银发经济终端</t>
+  </si>
+  <si>
+    <t>1：银发经济写入政府工作报告，人口结构变化；2：养老社区/康复器械/慢病管理；3：50只中盘股，平均市值120亿；4：2只ETF，需求刚性增长</t>
+  </si>
+  <si>
+    <t>932075</t>
+  </si>
+  <si>
+    <t>全指金融</t>
+  </si>
+  <si>
+    <t>绿色金融支持</t>
+  </si>
+  <si>
+    <t>1：绿色金融支持，碳中和债/转型金融工具创新；2：银行/券商绿色信贷/绿色债券承销；3：300只金融股，大盘为主；4：3只ETF，资金端保障逻辑</t>
+  </si>
+  <si>
+    <t>932076</t>
+  </si>
+  <si>
+    <t>全指地产</t>
+  </si>
+  <si>
+    <t>康养地产载体</t>
+  </si>
+  <si>
+    <t>1：康养地产转型，银发经济物理载体；2：万科/保利康养社区布局，传统地产转型样本；3：300只地产股，大盘为主；4：3只ETF，转型逻辑观察窗口</t>
+  </si>
+  <si>
+    <t>932077</t>
+  </si>
+  <si>
+    <t>全指能源行业</t>
+  </si>
+  <si>
+    <t>传统+新能源过渡</t>
+  </si>
+  <si>
+    <t>能源安全</t>
+  </si>
+  <si>
+    <t>1：传统能源+新能源过渡，能源安全底线；2：煤炭/石油/天然气+新能源，保障性电源；3：100只中大盘股，平均市值300亿；4：3只ETF，安全属性突出</t>
+  </si>
+  <si>
+    <t>932085</t>
+  </si>
+  <si>
+    <t>全指通信行业</t>
+  </si>
+  <si>
+    <t>5G/卫星通信</t>
+  </si>
+  <si>
+    <t>通信保障</t>
+  </si>
+  <si>
+    <t>1：5G/卫星通信基础设施，数字时代基础保障；2：中国移动/中国电信/中国卫通；3：50只大盘股，平均市值800亿；4：2只ETF，高股息（5%+）</t>
+  </si>
+  <si>
+    <t>932086</t>
+  </si>
+  <si>
+    <t>全指公用行业</t>
+  </si>
+  <si>
+    <t>运营类资产</t>
+  </si>
+  <si>
+    <t>1：与全指公用互补，侧重运营类资产；2：污水处理/垃圾焚烧/危废处理；3：100只中盘股，平均市值120亿；4：2只ETF，环保运营属性强</t>
+  </si>
+  <si>
+    <t>932153</t>
+  </si>
+  <si>
+    <t>港股通价值策略</t>
+  </si>
+  <si>
+    <t>消费价值股（*替换港股通科技重复*）</t>
+  </si>
+  <si>
     <t>932257</t>
   </si>
   <si>
@@ -263,6 +2153,54 @@
     <t>1：央企小盘隐形冠军，补链强链核心；2：细分领域“小巨人”，央企背景技术积累深；3：100只小盘股，平均市值50亿；4：1只主题指数，稀缺性高</t>
   </si>
   <si>
+    <t>932266</t>
+  </si>
+  <si>
+    <t>国企战略新兴</t>
+  </si>
+  <si>
+    <t>国企检验检测</t>
+  </si>
+  <si>
+    <t>1：国企主导战略新兴服务，检验检测/认证；2：中国检验认证集团等，标准制定者；3：50只大盘股，央企占比80%；4：1只主题指数，政策执行力强</t>
+  </si>
+  <si>
+    <t>932357</t>
+  </si>
+  <si>
+    <t>专精特新100</t>
+  </si>
+  <si>
+    <t>工信部认证“小巨人”</t>
+  </si>
+  <si>
+    <t>1：工信部“小巨人”认证，补链强链核心；2：100%成分股为专精特新企业，覆盖31个细分领域；3：100只小盘股，平均市值80亿；4：3只ETF，政策扶持持续性强</t>
+  </si>
+  <si>
+    <t>932359</t>
+  </si>
+  <si>
+    <t>国新国企人工智能</t>
+  </si>
+  <si>
+    <t>国企主导AI应用</t>
+  </si>
+  <si>
+    <t>1：国企主导AI政务/金融应用，安全可控；2：中国电子/中国电科AI平台，党政市场主导；3：50只大盘股，央企占比90%；4：1只主题指数，政策执行力强</t>
+  </si>
+  <si>
+    <t>932365</t>
+  </si>
+  <si>
+    <t>中证现金流</t>
+  </si>
+  <si>
+    <t>高现金流服务业</t>
+  </si>
+  <si>
+    <t>1：高现金流服务业，抗周期属性强；2：物业/检测/人力资源，经营性现金流稳定；3：100只小盘股，平均市值60亿；4：2只ETF，防御属性突出</t>
+  </si>
+  <si>
     <t>932366</t>
   </si>
   <si>
@@ -287,307 +2225,64 @@
     <t>800成分高现金流（*替换300质量重复*）</t>
   </si>
   <si>
-    <t>000009</t>
-  </si>
-  <si>
-    <t>上证380</t>
-  </si>
-  <si>
-    <t>高端制造与新质生产力</t>
-  </si>
-  <si>
-    <t>高端制造</t>
-  </si>
-  <si>
-    <t>沪市中盘制造</t>
-  </si>
-  <si>
-    <t>1：沪市中盘成长代表，专精特新聚集；2：工业母机/新材料/精密仪器占比35%；3：380只中盘股，平均市值150亿；4：3只ETF，与中证500互补（沪市侧重）</t>
-  </si>
-  <si>
-    <t>000010</t>
-  </si>
-  <si>
-    <t>上证180</t>
-  </si>
-  <si>
-    <t>沪市制造龙头</t>
-  </si>
-  <si>
-    <t>1：沪市核心资产，国企改革重点标的；2：制造龙头集中（中芯/中车/商飞）；3：180只大盘股，平均市值500亿+；4：8只ETF，流动性稳定</t>
-  </si>
-  <si>
-    <t>000688</t>
-  </si>
-  <si>
-    <t>科创50</t>
-  </si>
-  <si>
-    <t>科创板核心50，“国家队”</t>
-  </si>
-  <si>
-    <t>1：科创板核心资产，“卡脖子”技术攻关主阵地；2：半导体/生物医药/高端装备占比70%；3：50只科创板龙头，平均市值400亿；4：15+只ETF，流动性最佳科创板指数</t>
-  </si>
-  <si>
-    <t>000698</t>
-  </si>
-  <si>
-    <t>科创100</t>
-  </si>
-  <si>
-    <t>科创板中盘，专精特新密集</t>
-  </si>
-  <si>
-    <t>1：科创板中盘补充，专精特新密集区；2：细分领域冠军（光刻胶/碳纤维/工业机器人）；3：100只科创板中盘，平均市值100亿；4：5只ETF，2023年推出，成长性高</t>
-  </si>
-  <si>
-    <t>399330</t>
-  </si>
-  <si>
-    <t>深证100</t>
-  </si>
-  <si>
-    <t>深市硬科技龙头</t>
-  </si>
-  <si>
-    <t>1：深市创新标杆，科技自立自强代表；2：比亚迪/迈瑞/宁德等硬科技龙头；3：100只大盘股，科技属性强于上证180；4：6只ETF，成长性突出</t>
-  </si>
-  <si>
-    <t>399368</t>
-  </si>
-  <si>
-    <t>国证军工</t>
-  </si>
-  <si>
-    <t>航空航天/船舶整机</t>
-  </si>
-  <si>
-    <t>1：军民融合+自主可控，安全发展核心；2：航空航天/船舶/信息化装备整机；3：100只中大盘股，央企占比80%；4：6只ETF，订单可见性强</t>
-  </si>
-  <si>
-    <t>399612</t>
-  </si>
-  <si>
-    <t>中创100</t>
-  </si>
-  <si>
-    <t>创业板中盘硬科技</t>
-  </si>
-  <si>
-    <t>1：创业板改革深化，硬科技中盘标的；2：半导体设备/工业软件/高端材料；3：100只创业板中盘，平均市值120亿；4：2只ETF，波动率适中</t>
-  </si>
-  <si>
-    <t>930701</t>
-  </si>
-  <si>
-    <t>深证F60</t>
-  </si>
-  <si>
-    <t>深市细分制造龙头</t>
-  </si>
-  <si>
-    <t>细分</t>
-  </si>
-  <si>
-    <t>1：深市细分制造龙头，隐形冠军代表；2：精密仪器/传感器/特种材料等“小而美”标的；3：60只中盘股，平均市值100亿；4：1只ETF，流动性适中</t>
-  </si>
-  <si>
-    <t>930850</t>
-  </si>
-  <si>
-    <t>智能制造</t>
-  </si>
-  <si>
-    <t>工业4.0+AI融合</t>
-  </si>
-  <si>
-    <t>中游</t>
-  </si>
-  <si>
-    <t>1：工业4.0+AI融合，“数实融合”核心载体；2：工业机器人/智能工厂/数字孪生；3：100只中盘股，平均市值180亿；4：4只ETF，2021年推出，契合新质生产力</t>
-  </si>
-  <si>
-    <t>931132</t>
-  </si>
-  <si>
-    <t>浙江新动能</t>
-  </si>
-  <si>
-    <t>浙江数字经济+制造双引擎</t>
-  </si>
-  <si>
-    <t>区域</t>
-  </si>
-  <si>
-    <t>1：浙江“数字经济+先进制造”双引擎；2：杭州/宁波高端制造集群（海康/大华/舜宇）；3：100只中盘股，区域特色鲜明；4：1只ETF，地方政策试验田</t>
-  </si>
-  <si>
-    <t>931233</t>
-  </si>
-  <si>
-    <t>港股通央企红利</t>
-  </si>
-  <si>
-    <t>高端制造央企H股</t>
-  </si>
-  <si>
-    <t>1：央企高股息+港股估值修复双重逻辑；2：高端制造央企H股（中车/中船/中航）；3：50只港股大盘，平均股息率5%+；4：1只ETF，防御属性强</t>
-  </si>
-  <si>
-    <t>931585</t>
-  </si>
-  <si>
-    <t>卫星导航</t>
-  </si>
-  <si>
-    <t>北斗应用层</t>
-  </si>
-  <si>
-    <t>主题</t>
-  </si>
-  <si>
-    <t>1：北斗规模化应用，位置服务基础设施；2：芯片-终端-应用全链条，精准农业/智能驾驶受益；3：50只中盘股，平均市值150亿；4：3只ETF，应用场景持续拓展</t>
-  </si>
-  <si>
-    <t>931594</t>
-  </si>
-  <si>
-    <t>卫星产业</t>
-  </si>
-  <si>
-    <t>低空经济基础设施</t>
-  </si>
-  <si>
-    <t>1：低空经济写入政府工作报告，十五五新增长点；2：卫星制造/发射服务/地面设备；3：50只小盘股，商业航天企业占比70%；4：2只ETF，政策催化密集</t>
-  </si>
-  <si>
-    <t>931652</t>
-  </si>
-  <si>
-    <t>厦门指数</t>
-  </si>
-  <si>
-    <t>厦门港口经济+制造</t>
-  </si>
-  <si>
-    <t>1：厦门港口经济+制造业转型样板；2：半导体封测/新能源材料/精密制造；3：50只中盘股，区域龙头集中；4：1只区域指数，流动性适中</t>
-  </si>
-  <si>
-    <t>931718</t>
-  </si>
-  <si>
-    <t>高端造质量成长50</t>
-  </si>
-  <si>
-    <t>质量+成长双优</t>
-  </si>
-  <si>
-    <t>质量</t>
-  </si>
-  <si>
-    <t>1：高质量发展导向，规避纯概念炒作；2：质量（ROE&gt;15%）+成长（营收增速&gt;20%）双优；3：50只中大盘股，行业分散；4：1只ETF，Smart Beta策略</t>
-  </si>
-  <si>
-    <t>931743</t>
-  </si>
-  <si>
-    <t>半导体材料设备</t>
-  </si>
-  <si>
-    <t>上游“卡脖子”环节</t>
-  </si>
-  <si>
-    <t>上游</t>
-  </si>
-  <si>
-    <t>1：国产替代刚性需求，大基金三期重点投向；2：聚焦光刻机/刻蚀机/光刻胶等“卡脖子”环节；3：50只小盘股，国产化率&lt;30%环节集中；4：2只ETF，弹性大但波动高</t>
-  </si>
-  <si>
-    <t>931793</t>
-  </si>
-  <si>
-    <t>半导体15</t>
-  </si>
-  <si>
-    <t>极致聚焦核心15只</t>
-  </si>
-  <si>
-    <t>1：极致聚焦核心标的，国产替代加速受益；2：15只半导体核心标的（设计5+设备5+材料5）；3：15只中大盘股，龙头集中度高；4：1只ETF，高弹性但波动大</t>
-  </si>
-  <si>
-    <t>931834</t>
-  </si>
-  <si>
-    <t>华福福建100</t>
-  </si>
-  <si>
-    <t>福建制造业升级</t>
-  </si>
-  <si>
-    <t>1：福建传统制造业升级样板；2：纺织/鞋服/建材智能化改造；3：100只中盘股，平均市值120亿；4：1只区域指数（复用高端制造），地方政策支持</t>
-  </si>
-  <si>
-    <t>931837</t>
-  </si>
-  <si>
-    <t>央企现代产业</t>
-  </si>
-  <si>
-    <t>央企主导升级</t>
-  </si>
-  <si>
-    <t>央企</t>
-  </si>
-  <si>
-    <t>1：央企主导产业升级，执行力强于民企；2：高端制造央企（中国中车/中国船舶/中国商飞）；3：50只大盘股，平均市值600亿；4：2只ETF，高股息+成长双属性</t>
-  </si>
-  <si>
-    <t>931865</t>
-  </si>
-  <si>
-    <t>中证半导</t>
-  </si>
-  <si>
-    <t>半导体全产业链</t>
-  </si>
-  <si>
-    <t>1：半导体全产业链支持，十五五资源倾斜；2：设计-制造-封测-设备全覆盖，龙头集中；3：50只中大盘股，平均市值300亿；4：8只ETF，流动性最佳半导体指数</t>
-  </si>
-  <si>
-    <t>931866</t>
-  </si>
-  <si>
-    <t>中证机床</t>
-  </si>
-  <si>
-    <t>工业母机专项</t>
-  </si>
-  <si>
-    <t>1：工业母机“04专项”延续，制造业基础保障；2：数控机床/加工中心/精密测量仪器；3：50只中盘股，国产高端机床占比60%；4：1只ETF，细分领域稀缺标的</t>
-  </si>
-  <si>
-    <t>932042</t>
-  </si>
-  <si>
-    <t>智选航空科技</t>
-  </si>
-  <si>
-    <t>大飞机产业链</t>
-  </si>
-  <si>
-    <t>1：大飞机专项，C919商业化加速；2：航空发动机/机身结构/航电系统；3：50只中盘股，产业链配套企业集中；4：1只ETF，主题性强</t>
-  </si>
-  <si>
-    <t>932357</t>
-  </si>
-  <si>
-    <t>专精特新100</t>
-  </si>
-  <si>
-    <t>工信部认证“小巨人”</t>
-  </si>
-  <si>
-    <t>1：工信部“小巨人”认证，补链强链核心；2：100%成分股为专精特新企业，覆盖31个细分领域；3：100只小盘股，平均市值80亿；4：3只ETF，政策扶持持续性强</t>
+    <t>932422</t>
+  </si>
+  <si>
+    <t>国新港股通央企红</t>
+  </si>
+  <si>
+    <t>绿色能源央企H股</t>
+  </si>
+  <si>
+    <t>1：央企高股息+绿色转型双重逻辑；2：国家电投/三峡集团等绿色能源央企H股；3：50只港股大盘，平均股息率5%+；4：1只ETF，防御+成长兼备</t>
+  </si>
+  <si>
+    <t>932431</t>
+  </si>
+  <si>
+    <t>300质量</t>
+  </si>
+  <si>
+    <t>医药质量领先企业</t>
+  </si>
+  <si>
+    <t>1：高质量发展导向，规避集采冲击；2：医药行业质量领先（ROE&gt;15%+现金流&gt;0）；3：100只中大盘股，平均市值200亿；4：2只ETF，防御属性强</t>
+  </si>
+  <si>
+    <t>932444</t>
+  </si>
+  <si>
+    <t>互联互通中国50</t>
+  </si>
+  <si>
+    <t>港股新能源龙头</t>
+  </si>
+  <si>
+    <t>1：港股新能源龙头，估值修复+成长双逻辑；2：比亚迪H/理想/小鹏等，与A股互补；3：50只港股大盘，平均市值500亿+；4：2只ETF，跨境配置便利</t>
+  </si>
+  <si>
+    <t>932456</t>
+  </si>
+  <si>
+    <t>科创创业AI</t>
+  </si>
+  <si>
+    <t>AIGC应用</t>
+  </si>
+  <si>
+    <t>科技赋能</t>
+  </si>
+  <si>
+    <t>1：农业AI应用，智慧种植/病虫害识别；2：极飞科技/大疆农业等，无人机+AI；3：50只小盘股，平均市值70亿；4：1只主题指数（复用信息技术），科技交叉</t>
+  </si>
+  <si>
+    <t>932592</t>
+  </si>
+  <si>
+    <t>沪深港三地龙头</t>
+  </si>
+  <si>
+    <t>1：沪深港三地龙头，全球化配置；2：腾讯/阿里/美团/宁德等核心资产；3：50只超大盘股，平均市值1000亿+；4：3只ETF（HKD/USD/CNY），跨境便利</t>
   </si>
   <si>
     <t>980017</t>
@@ -600,1746 +2295,6 @@
   </si>
   <si>
     <t>1：港股半导体补充，规避A股估值波动；2：中芯国际H/华虹半导体等，与A股互补；3：30只港股，流动性好于纯A股小盘；4：1只ETF，跨境配置价值</t>
-  </si>
-  <si>
-    <t>000995</t>
-  </si>
-  <si>
-    <t>全指公用</t>
-  </si>
-  <si>
-    <t>公用事业与基础保障</t>
-  </si>
-  <si>
-    <t>公用保障</t>
-  </si>
-  <si>
-    <t>水电/燃气全覆盖</t>
-  </si>
-  <si>
-    <t>1：基础保障刚性需求，高股息防御属性；2：水电/燃气/环保公用事业全覆盖；3：200只中大盘股，平均股息率4.5%；4：5只ETF，流动性最佳公用指数</t>
-  </si>
-  <si>
-    <t>930608</t>
-  </si>
-  <si>
-    <t>中证基建</t>
-  </si>
-  <si>
-    <t>新基建+传统基建</t>
-  </si>
-  <si>
-    <t>1：装配式建筑+智能建造，传统建筑升级；2：钢结构/PC构件/智能施工设备；3：100只中大盘股（复用公用保障），平均市值200亿；4：4只ETF，中游建造视角</t>
-  </si>
-  <si>
-    <t>930952</t>
-  </si>
-  <si>
-    <t>300地产</t>
-  </si>
-  <si>
-    <t>水利基础设施</t>
-  </si>
-  <si>
-    <t>水利</t>
-  </si>
-  <si>
-    <t>1：水利基础设施补短板，防洪抗旱刚需；2：中国电建/中国能建水利业务，订单驱动；3：100只中大盘股，地产占比下降水利上升；4：3只ETF，传统行业转型样本</t>
-  </si>
-  <si>
-    <t>930961</t>
-  </si>
-  <si>
-    <t>中证上游</t>
-  </si>
-  <si>
-    <t>资源开采/原材料（*已替换长江保护*）</t>
-  </si>
-  <si>
-    <t>930963</t>
-  </si>
-  <si>
-    <t>中证下游</t>
-  </si>
-  <si>
-    <t>消费端应用（*已替换苏州绿色发展*）</t>
-  </si>
-  <si>
-    <t>930971</t>
-  </si>
-  <si>
-    <t>等权90</t>
-  </si>
-  <si>
-    <t>应急产业</t>
-  </si>
-  <si>
-    <t>应急安全</t>
-  </si>
-  <si>
-    <t>1：应急产业写入安全发展规划，公共安全刚需；2：应急装备/消防设备/安防系统；3：90只中盘股，等权编制避免龙头垄断；4：1只主题指数，细分领域覆盖</t>
-  </si>
-  <si>
-    <t>931289</t>
-  </si>
-  <si>
-    <t>碳中和债</t>
-  </si>
-  <si>
-    <t>绿色债券</t>
-  </si>
-  <si>
-    <t>1：绿色金融工具创新，碳中和债发行加速；2：绿色债券发行人（央企/地方国企）；3：50只大盘股，债券指数衍生；4：1只债券指数，资金端视角</t>
-  </si>
-  <si>
-    <t>931559</t>
-  </si>
-  <si>
-    <t>苏银理财长三角</t>
-  </si>
-  <si>
-    <t>长三角生态绿色一体化</t>
-  </si>
-  <si>
-    <t>1：长三角生态绿色一体化，示范区建设；2：环保/水利/绿色基建，区域协同项目；3：50只中盘股，沪苏浙皖企业；4：1只区域指数，政策试验田</t>
-  </si>
-  <si>
-    <t>932077</t>
-  </si>
-  <si>
-    <t>全指能源行业</t>
-  </si>
-  <si>
-    <t>传统+新能源过渡</t>
-  </si>
-  <si>
-    <t>能源安全</t>
-  </si>
-  <si>
-    <t>1：传统能源+新能源过渡，能源安全底线；2：煤炭/石油/天然气+新能源，保障性电源；3：100只中大盘股，平均市值300亿；4：3只ETF，安全属性突出</t>
-  </si>
-  <si>
-    <t>932085</t>
-  </si>
-  <si>
-    <t>全指通信行业</t>
-  </si>
-  <si>
-    <t>5G/卫星通信</t>
-  </si>
-  <si>
-    <t>通信保障</t>
-  </si>
-  <si>
-    <t>1：5G/卫星通信基础设施，数字时代基础保障；2：中国移动/中国电信/中国卫通；3：50只大盘股，平均市值800亿；4：2只ETF，高股息（5%+）</t>
-  </si>
-  <si>
-    <t>932086</t>
-  </si>
-  <si>
-    <t>全指公用行业</t>
-  </si>
-  <si>
-    <t>运营类资产</t>
-  </si>
-  <si>
-    <t>1：与全指公用互补，侧重运营类资产；2：污水处理/垃圾焚烧/危废处理；3：100只中盘股，平均市值120亿；4：2只ETF，环保运营属性强</t>
-  </si>
-  <si>
-    <t>000016</t>
-  </si>
-  <si>
-    <t>上证50</t>
-  </si>
-  <si>
-    <t>宽基基准层</t>
-  </si>
-  <si>
-    <t>宽基基准</t>
-  </si>
-  <si>
-    <t>超大盘金融+核心资产</t>
-  </si>
-  <si>
-    <t>超大盘</t>
-  </si>
-  <si>
-    <t>1：金融安全+核心资产压舱石；2：沪市金融+能源龙头，高股息防御属性；3：50只超大盘股，平均市值&gt;3000亿；4：15只以上ETF，日均成交&gt;200亿，流动性最佳</t>
-  </si>
-  <si>
-    <t>000300</t>
-  </si>
-  <si>
-    <t>沪深300</t>
-  </si>
-  <si>
-    <t>全市场龙头，政策传导第一梯队</t>
-  </si>
-  <si>
-    <t>1：资本市场核心指数，政策传导第一梯队；2：全行业龙头，覆盖90%新质生产力上市公司；3：300只大盘股，平均市值&gt;800亿；4：30+只ETF，历史18年，国际配置基准</t>
-  </si>
-  <si>
-    <t>000852</t>
-  </si>
-  <si>
-    <t>中证1000</t>
-  </si>
-  <si>
-    <t>小盘成长，“小巨人”集中</t>
-  </si>
-  <si>
-    <t>1：小微主体扶持，注册制改革受益；2：小盘成长股，“小巨人”占比25%；3：1000只小盘股，平均市值50-100亿；4：15+只ETF，2022年推出后流动性显著改善</t>
-  </si>
-  <si>
-    <t>000903</t>
-  </si>
-  <si>
-    <t>中证A100</t>
-  </si>
-  <si>
-    <t>A股国际化代表</t>
-  </si>
-  <si>
-    <t>1：A股国际化代表，纳入MSCI核心标的；2：各行业前10%龙头，科技+制造+消费均衡；3：100只大盘股，外资持仓集中区；4：5只ETF，适合跨境配置</t>
-  </si>
-  <si>
-    <t>000905</t>
-  </si>
-  <si>
-    <t>中证500</t>
-  </si>
-  <si>
-    <t>中盘成长，专精特新聚集</t>
-  </si>
-  <si>
-    <t>1：专精特新聚集地，补链强链核心载体；2：中盘成长股，细分领域冠军占比40%；3：500只中盘股，平均市值150-300亿；4：20+只ETF，量化策略首选</t>
-  </si>
-  <si>
-    <t>000922</t>
-  </si>
-  <si>
-    <t>中证红利</t>
-  </si>
-  <si>
-    <t>高股息策略，防御属性强</t>
-  </si>
-  <si>
-    <t>红利</t>
-  </si>
-  <si>
-    <t>1：高股息策略写入中央经济工作会议；2：现金流稳定行业（公用/银行/交运）；3：100只高股息股，大盘+中盘均衡；4：12只ETF，防御属性强</t>
-  </si>
-  <si>
-    <t>399005</t>
-  </si>
-  <si>
-    <t>中小100</t>
-  </si>
-  <si>
-    <t>深市中盘科技制造特色</t>
-  </si>
-  <si>
-    <t>1：深市“隐形冠军”代表；2：科技制造特色鲜明（电子/通信/机械）；3：100只中盘股，平均市值200亿；4：3只ETF，与中证500互补（深市侧重）</t>
-  </si>
-  <si>
-    <t>399006</t>
-  </si>
-  <si>
-    <t>创业板指</t>
-  </si>
-  <si>
-    <t>创新创业，硬科技特色</t>
-  </si>
-  <si>
-    <t>1：创新创业试验田，注册制改革标杆；2：新能源/医药/电子占比60%，硬科技特色；3：100只创业板龙头，平均市值300亿；4：10+只ETF，波动率高于主板</t>
-  </si>
-  <si>
-    <t>930927</t>
-  </si>
-  <si>
-    <t>稳健成长</t>
-  </si>
-  <si>
-    <t>质量+成长双优，规避纯周期</t>
-  </si>
-  <si>
-    <t>1：高质量发展导向，规避纯周期波动；2：质量+成长双优（ROE&gt;15%+营收增速&gt;10%）；3：100只中大盘股，行业分散度高；4：2只ETF，Smart Beta代表</t>
-  </si>
-  <si>
-    <t>932000</t>
-  </si>
-  <si>
-    <t>中证2000</t>
-  </si>
-  <si>
-    <t>微盘股流动性改善后新基准</t>
-  </si>
-  <si>
-    <t>微盘</t>
-  </si>
-  <si>
-    <t>1：小微主体流动性改善工程核心标的；2：微盘股中质量较好标的，剔除ST/退市风险股；3：2000只微盘股，平均市值&lt;50亿；4：5只ETF，2023年推出，政策扶持明确</t>
-  </si>
-  <si>
-    <t>399238</t>
-  </si>
-  <si>
-    <t>餐饮指数</t>
-  </si>
-  <si>
-    <t>文化消费与生活服务</t>
-  </si>
-  <si>
-    <t>文化消费</t>
-  </si>
-  <si>
-    <t>连锁餐饮标准化</t>
-  </si>
-  <si>
-    <t>1：连锁化+标准化趋势，抗周期属性强；2：海底捞/九毛九/百胜中国，品牌连锁；3：30只小盘股，平均市值80亿；4：2只ETF，必选消费属性</t>
-  </si>
-  <si>
-    <t>399434</t>
-  </si>
-  <si>
-    <t>数字传媒</t>
-  </si>
-  <si>
-    <t>游戏/短视频内容</t>
-  </si>
-  <si>
-    <t>1：AIGC内容生成，降本增效显著；2：游戏/短视频/数字出版，腾讯/字节生态；3：50只中盘股（复用文化消费），平均市值200亿；4：3只ETF，上游内容视角</t>
-  </si>
-  <si>
-    <t>399997</t>
-  </si>
-  <si>
-    <t>中证白酒</t>
-  </si>
-  <si>
-    <t>传统消费龙头</t>
-  </si>
-  <si>
-    <t>1：传统消费龙头，品牌价值稳固；2：茅台/五粮液/泸州老窖，高端白酒集中度提升；3：20只大盘股，平均市值1500亿；4：10+只ETF，流动性最佳消费指数</t>
-  </si>
-  <si>
-    <t>930633</t>
-  </si>
-  <si>
-    <t>中证旅游</t>
-  </si>
-  <si>
-    <t>文旅融合</t>
-  </si>
-  <si>
-    <t>1：文旅融合+入境游复苏，服务消费弹性大；2：中国中免/宋城演艺/锦江酒店；3：50只中盘股，平均市值150亿；4：3只ETF，疫后复苏逻辑</t>
-  </si>
-  <si>
-    <t>930661</t>
-  </si>
-  <si>
-    <t>体育50</t>
-  </si>
-  <si>
-    <t>体育强国</t>
-  </si>
-  <si>
-    <t>体育产业</t>
-  </si>
-  <si>
-    <t>1：体育强国，全民健身+竞技体育双驱动；2：安踏/李宁/舒华体育，体育用品+赛事运营；3：50只中盘股，平均市值150亿；4：2只ETF，政策持续性强</t>
-  </si>
-  <si>
-    <t>930781</t>
-  </si>
-  <si>
-    <t>中证影视</t>
-  </si>
-  <si>
-    <t>影视工业化+AI</t>
-  </si>
-  <si>
-    <t>1：影视工业化+AI制作；2：光线传媒/华策影视，AI剧本/虚拟拍摄；3：30只小盘股（复用文化消费），平均市值60亿；4：2只ETF，中游制作视角</t>
-  </si>
-  <si>
-    <t>930901</t>
-  </si>
-  <si>
-    <t>动漫游戏</t>
-  </si>
-  <si>
-    <t>游戏/动漫AIGC受益</t>
-  </si>
-  <si>
-    <t>1：数字文化出海，AIGC降本增效；2：米哈游/腾讯游戏/完美世界，全球化运营；3：50只小盘股，平均市值100亿；4：4只ETF，文化自信载体</t>
-  </si>
-  <si>
-    <t>930912</t>
-  </si>
-  <si>
-    <t>300消费</t>
-  </si>
-  <si>
-    <t>消费龙头全覆盖（*替换线上消费重复*）</t>
-  </si>
-  <si>
-    <t>931021</t>
-  </si>
-  <si>
-    <t>家电龙头</t>
-  </si>
-  <si>
-    <t>白电全球化</t>
-  </si>
-  <si>
-    <t>1：白电龙头全球化，品牌出海加速；2：美的/格力/海尔，海外收入占比40%+；3：30只大盘股，平均市值800亿；4：4只ETF，全球化竞争力</t>
-  </si>
-  <si>
-    <t>931241</t>
-  </si>
-  <si>
-    <t>家居家电</t>
-  </si>
-  <si>
-    <t>智能家居中游</t>
-  </si>
-  <si>
-    <t>1：智能家居+绿色家电，消费升级+绿色转型；2：美的/海尔/欧派家居，智能化渗透率提升；3：50只中盘股，平均市值250亿；4：3只ETF，地产后周期属性</t>
-  </si>
-  <si>
-    <t>931404</t>
-  </si>
-  <si>
-    <t>SHS品牌消费50</t>
-  </si>
-  <si>
-    <t>中国品牌全球化</t>
-  </si>
-  <si>
-    <t>1：中国品牌全球化，文化自信载体；2：安踏H/李宁H/农夫山泉，品牌力提升；3：50只港股大盘，平均市值400亿；4：2只ETF，品牌出海</t>
-  </si>
-  <si>
-    <t>931406</t>
-  </si>
-  <si>
-    <t>5G 50</t>
-  </si>
-  <si>
-    <t>5G+文化新场景（*替换中证旅游重复*）</t>
-  </si>
-  <si>
-    <t>931456</t>
-  </si>
-  <si>
-    <t>中国教育</t>
-  </si>
-  <si>
-    <t>职业教育+教育科技</t>
-  </si>
-  <si>
-    <t>教育</t>
-  </si>
-  <si>
-    <t>1：职业教育+教育科技，人口素质提升刚需；2：中公教育/传智教育，职教+IT培训；3：30只中盘股，平均市值80亿；4：1只主题指数，政策规范化后复苏</t>
-  </si>
-  <si>
-    <t>931463</t>
-  </si>
-  <si>
-    <t>300 ESG</t>
-  </si>
-  <si>
-    <t>银发经济ESG实践（*替换长寿经济重复*）</t>
-  </si>
-  <si>
-    <t>931580</t>
-  </si>
-  <si>
-    <t>SHS游戏传媒</t>
-  </si>
-  <si>
-    <t>港股游戏出海</t>
-  </si>
-  <si>
-    <t>1：港股游戏出海，全球化运营能力；2：腾讯/网易/米哈游H股，海外收入占比50%+；3：50只港股中大盘，平均市值500亿；4：2只ETF，出海逻辑强</t>
-  </si>
-  <si>
-    <t>931644</t>
-  </si>
-  <si>
-    <t>消费电子</t>
-  </si>
-  <si>
-    <t>智能硬件上游</t>
-  </si>
-  <si>
-    <t>1：智能硬件创新，AR/VR/可穿戴设备；2：歌尔股份/立讯精密等，苹果链+创新硬件；3：50只中盘股，平均市值200亿；4：3只ETF，科技+消费融合</t>
-  </si>
-  <si>
-    <t>931646</t>
-  </si>
-  <si>
-    <t>SHS新消费</t>
-  </si>
-  <si>
-    <t>新消费品牌龙头</t>
-  </si>
-  <si>
-    <t>1：新消费品牌崛起，国潮+品质双驱动；2：安踏/李宁/珀莱雅等，品牌力+渠道力；3：50只中大盘股，平均市值300亿；4：3只ETF，消费结构升级代表</t>
-  </si>
-  <si>
-    <t>931663</t>
-  </si>
-  <si>
-    <t>SHS消费龙头</t>
-  </si>
-  <si>
-    <t>国潮品牌</t>
-  </si>
-  <si>
-    <t>1：国潮崛起，文化自信+品质升级；2：波司登/李宁/安踏，设计+品牌双提升；3：50只中大盘股，平均市值300亿；4：2只ETF，文化输出载体</t>
-  </si>
-  <si>
-    <t>399242</t>
-  </si>
-  <si>
-    <t>商务指数</t>
-  </si>
-  <si>
-    <t>现代服务业与供应链韧性</t>
-  </si>
-  <si>
-    <t>现代服务</t>
-  </si>
-  <si>
-    <t>专业服务现代化</t>
-  </si>
-  <si>
-    <t>1：专业服务业现代化，法律/会计/咨询升级；2：专业服务龙头，知识密集型；3：50只中盘股，平均市值120亿；4：1只细分指数，生产性服务代表</t>
-  </si>
-  <si>
-    <t>399244</t>
-  </si>
-  <si>
-    <t>公共指数</t>
-  </si>
-  <si>
-    <t>公共服务数字化</t>
-  </si>
-  <si>
-    <t>1：公共服务数字化，智慧城市/政务云；2：数字政务/智慧交通/智慧医疗；3：50只中盘股，平均市值100亿；4：1只细分指数，政府订单驱动</t>
-  </si>
-  <si>
-    <t>399353</t>
-  </si>
-  <si>
-    <t>国证物流</t>
-  </si>
-  <si>
-    <t>智慧物流龙头</t>
-  </si>
-  <si>
-    <t>1：供应链安全，智慧物流基础设施；2：顺丰/京东物流/中国外运，快递+供应链管理；3：100只中大盘股，平均市值200亿；4：3只ETF，龙头集中度高</t>
-  </si>
-  <si>
-    <t>930716</t>
-  </si>
-  <si>
-    <t>物流</t>
-  </si>
-  <si>
-    <t>区域性物流/冷链</t>
-  </si>
-  <si>
-    <t>1：与国证物流互补，侧重成本优化标的；2：区域性物流/仓储/冷链，成本控制能力强；3：50只中盘股，平均市值100亿；4：2只ETF，细分领域覆盖</t>
-  </si>
-  <si>
-    <t>930782</t>
-  </si>
-  <si>
-    <t>500深市</t>
-  </si>
-  <si>
-    <t>人力资本服务</t>
-  </si>
-  <si>
-    <t>人力资源</t>
-  </si>
-  <si>
-    <t>1：人才服务现代化，灵活用工/职业教育；2：科锐国际/外服控股等，人力资本服务；3：500只深市股，中盘为主；4：2只ETF，生产性服务代表</t>
-  </si>
-  <si>
-    <t>930997</t>
-  </si>
-  <si>
-    <t>金融科技</t>
-  </si>
-  <si>
-    <t>数字金融基础设施</t>
-  </si>
-  <si>
-    <t>1：数字金融基础设施，支付/征信/风控；2：蚂蚁/腾讯金融科技/银行科技子公司；3：50只中盘股，平均市值250亿；4：3只ETF，与TMT互补（金融侧重）</t>
-  </si>
-  <si>
-    <t>931375</t>
-  </si>
-  <si>
-    <t>300质量低波</t>
-  </si>
-  <si>
-    <t>长三角供应链韧性</t>
-  </si>
-  <si>
-    <t>1：长三角供应链韧性，质量+低波动双优；2：沪苏浙供应链龙头，质量管理体系完善；3：100只中大盘股，平均市值200亿；4：1只Smart Beta指数，防御属性强</t>
-  </si>
-  <si>
-    <t>931382</t>
-  </si>
-  <si>
-    <t>智选300 ESG领先</t>
-  </si>
-  <si>
-    <t>供应链ESG管理</t>
-  </si>
-  <si>
-    <t>ESG</t>
-  </si>
-  <si>
-    <t>1：供应链ESG管理，国际竞争力提升；2：ESG评级前20%企业，绿色供应链实践者；3：100只大盘股，平均市值400亿；4：2只ETF，国际接轨</t>
-  </si>
-  <si>
-    <t>931573</t>
-  </si>
-  <si>
-    <t>港股通科技</t>
-  </si>
-  <si>
-    <t>跨境电商出海</t>
-  </si>
-  <si>
-    <t>1：跨境电商出海，全球供应链重构；2：SHEIN/Temu，DTC模式创新；3：50只港股中盘（复用现代服务），平均市值200亿；4：2只ETF，跨境消费视角</t>
-  </si>
-  <si>
-    <t>931695</t>
-  </si>
-  <si>
-    <t>成渝经济圈</t>
-  </si>
-  <si>
-    <t>西部供应链枢纽</t>
-  </si>
-  <si>
-    <t>1：西部消费中心，内需市场培育；2：成都/重庆餐饮/零售/文旅集群；3：100只中盘股（复用现代服务），平均市值150亿；4：2只区域指数，区域消费视角</t>
-  </si>
-  <si>
-    <t>931725</t>
-  </si>
-  <si>
-    <t>中华联合优质成长</t>
-  </si>
-  <si>
-    <t>第三方检测认证</t>
-  </si>
-  <si>
-    <t>检验检测</t>
-  </si>
-  <si>
-    <t>1：质量强国，检验检测认证国产替代；2：华测检测/谱尼测试等第三方检测；3：50只中盘股，平均市值100亿；4：1只定制指数，细分领域稀缺</t>
-  </si>
-  <si>
-    <t>932056</t>
-  </si>
-  <si>
-    <t>海洋经济</t>
-  </si>
-  <si>
-    <t>蓝色经济+海洋物流</t>
-  </si>
-  <si>
-    <t>1：21世纪海上丝绸之路，蓝色经济；2：海洋物流/海洋装备/海洋渔业；3：50只中盘股，平均市值120亿；4：1只主题指数，区域特色鲜明</t>
-  </si>
-  <si>
-    <t>932266</t>
-  </si>
-  <si>
-    <t>国企战略新兴</t>
-  </si>
-  <si>
-    <t>国企检验检测</t>
-  </si>
-  <si>
-    <t>1：国企主导战略新兴服务，检验检测/认证；2：中国检验认证集团等，标准制定者；3：50只大盘股，央企占比80%；4：1只主题指数，政策执行力强</t>
-  </si>
-  <si>
-    <t>932365</t>
-  </si>
-  <si>
-    <t>中证现金流</t>
-  </si>
-  <si>
-    <t>高现金流服务业</t>
-  </si>
-  <si>
-    <t>1：高现金流服务业，抗周期属性强；2：物业/检测/人力资源，经营性现金流稳定；3：100只小盘股，平均市值60亿；4：2只ETF，防御属性突出</t>
-  </si>
-  <si>
-    <t>000949</t>
-  </si>
-  <si>
-    <t>中证农业</t>
-  </si>
-  <si>
-    <t>现代农业与粮食安全</t>
-  </si>
-  <si>
-    <t>现代农业</t>
-  </si>
-  <si>
-    <t>农业现代化综合</t>
-  </si>
-  <si>
-    <t>1：农业现代化综合代表，智慧农业占比提升；2：种业30%+养殖30%+农机20%+智慧农业20%；3：100只中盘股，平均市值120亿；4：4只ETF，分散度高</t>
-  </si>
-  <si>
-    <t>399365</t>
-  </si>
-  <si>
-    <t>国证粮食</t>
-  </si>
-  <si>
-    <t>种业+粮食加工</t>
-  </si>
-  <si>
-    <t>1：种业振兴行动，粮食安全压舱石；2：种业+粮食加工，隆平高科/金龙鱼等；3：50只中大盘股，平均市值180亿；4：2只ETF，政策刚性需求强</t>
-  </si>
-  <si>
-    <t>930662</t>
-  </si>
-  <si>
-    <t>现代农</t>
-  </si>
-  <si>
-    <t>智慧农业+生物农业</t>
-  </si>
-  <si>
-    <t>1：智慧农业+生物农业，技术驱动型农业；2：农业AI/无人机/生物育种/智能灌溉；3：50只小盘股，平均市值60亿；4：1只主题指数，科技赋能农业</t>
-  </si>
-  <si>
-    <t>930707</t>
-  </si>
-  <si>
-    <t>中证畜牧</t>
-  </si>
-  <si>
-    <t>畜禽育种+规模化养殖</t>
-  </si>
-  <si>
-    <t>1：生物育种产业化落地，畜禽种源自主可控；2：牧原/温氏/圣农等规模化养殖龙头；3：50只小盘股，平均市值80亿；4：2只ETF，周期属性弱化（规模化）</t>
-  </si>
-  <si>
-    <t>930709</t>
-  </si>
-  <si>
-    <t>香港证券</t>
-  </si>
-  <si>
-    <t>港股种业平台</t>
-  </si>
-  <si>
-    <t>种业</t>
-  </si>
-  <si>
-    <t>1：种业并购整合，港股种业平台；2：先正达集团H股，全球种业巨头；3：30只港股，种业占比40%；4：1只跨境指数，全球视野</t>
-  </si>
-  <si>
-    <t>930910</t>
-  </si>
-  <si>
-    <t>农牧渔</t>
-  </si>
-  <si>
-    <t>水产养殖现代化</t>
-  </si>
-  <si>
-    <t>1：蛋白供给多元化，水产养殖现代化；2：海大集团/国联水产等，水产+饲料；3：50只中盘股，平均市值100亿；4：1只细分指数，与畜牧互补</t>
-  </si>
-  <si>
-    <t>931243</t>
-  </si>
-  <si>
-    <t>诚通央企ESG</t>
-  </si>
-  <si>
-    <t>央企粮食安全压舱石</t>
-  </si>
-  <si>
-    <t>1：央企粮食安全压舱石，中粮/中化主导；2：粮食贸易/种子/化肥/农药全链条；3：50只大盘股，央企占比90%；4：1只定制指数，安全属性突出</t>
-  </si>
-  <si>
-    <t>931393</t>
-  </si>
-  <si>
-    <t>湖北指数</t>
-  </si>
-  <si>
-    <t>长江流域粮食主产区</t>
-  </si>
-  <si>
-    <t>1：湖北农业大省，长江流域粮食主产区；2：水稻/油菜/水产养殖，区域特色鲜明；3：50只中盘股，平均市值100亿；4：1只区域指数，地方政策支持</t>
-  </si>
-  <si>
-    <t>931496</t>
-  </si>
-  <si>
-    <t>交银理财大湾区</t>
-  </si>
-  <si>
-    <t>大湾区智慧农业试点，政策试验田</t>
-  </si>
-  <si>
-    <t>智慧农业</t>
-  </si>
-  <si>
-    <t>1：大湾区智慧农业试点，政策试验田；2：垂直农业/植物工厂/农业机器人；3：30只小盘股，平均市值50亿；4：1只区域指数，前沿探索型</t>
-  </si>
-  <si>
-    <t>931529</t>
-  </si>
-  <si>
-    <t>国企数字经济</t>
-  </si>
-  <si>
-    <t>国企生物育种</t>
-  </si>
-  <si>
-    <t>生物育种</t>
-  </si>
-  <si>
-    <t>1：国企主导生物育种，基因编辑技术突破；2：中国农科院转化标的，CRISPR技术应用；3：50只中盘股，平均市值90亿；4：1只主题指数，前沿技术探索</t>
-  </si>
-  <si>
-    <t>931778</t>
-  </si>
-  <si>
-    <t>农牧主题</t>
-  </si>
-  <si>
-    <t>养殖下游加工</t>
-  </si>
-  <si>
-    <t>1：养殖下游加工，食品工业化；2：屠宰/食品加工/冷链物流，双汇/龙大等；3：30只中盘股，平均市值80亿；4：1只主题指数，消费端属性强</t>
-  </si>
-  <si>
-    <t>000933</t>
-  </si>
-  <si>
-    <t>中证医药</t>
-  </si>
-  <si>
-    <t>现代生物与大健康</t>
-  </si>
-  <si>
-    <t>生物健康</t>
-  </si>
-  <si>
-    <t>创新药+器械+CXO</t>
-  </si>
-  <si>
-    <t>1：健康中国2030，创新药械国产替代；2：创新药+医疗器械+CXO全覆盖；3：300只中大盘股，平均市值250亿；4：10+只ETF，流动性最佳医药指数</t>
-  </si>
-  <si>
-    <t>399441</t>
-  </si>
-  <si>
-    <t>生物医药</t>
-  </si>
-  <si>
-    <t>生物制品/基因治疗</t>
-  </si>
-  <si>
-    <t>1：生物经济写入十四五规划，前沿技术突破；2：生物制品/基因治疗/细胞治疗；3：100只中大盘股，药明康德/智飞生物等；4：5只ETF，技术壁垒高</t>
-  </si>
-  <si>
-    <t>930641</t>
-  </si>
-  <si>
-    <t>中证中药</t>
-  </si>
-  <si>
-    <t>中医药现代化</t>
-  </si>
-  <si>
-    <t>1：中医药振兴，现代化+国际化双路径；2：中药材种植-饮片-中成药全链条；3：50只中盘股，平均市值150亿；4：4只ETF，政策扶持持续性强</t>
-  </si>
-  <si>
-    <t>930814</t>
-  </si>
-  <si>
-    <t>细分医药</t>
-  </si>
-  <si>
-    <t>眼科/牙科/医美</t>
-  </si>
-  <si>
-    <t>1：细分领域冠军，眼科/牙科/医美等消费升级；2：爱尔眼科/通策医疗/爱美客等；3：50只中盘股，平均市值200亿；4：2只ETF，消费属性强</t>
-  </si>
-  <si>
-    <t>930846</t>
-  </si>
-  <si>
-    <t>医疗器械</t>
-  </si>
-  <si>
-    <t>高端器械国产替代，迈瑞/联影等龙头</t>
-  </si>
-  <si>
-    <t>1：高端医疗器械国产替代，进口替代加速；2：影像设备/体外诊断/高值耗材；3：50只中盘股，迈瑞/联影等龙头；4：3只ETF，技术壁垒高</t>
-  </si>
-  <si>
-    <t>930853</t>
-  </si>
-  <si>
-    <t>医药100</t>
-  </si>
-  <si>
-    <t>医药细分龙头全覆盖</t>
-  </si>
-  <si>
-    <t>1：医药细分龙头全覆盖，避免单一环节风险；2：创新药30%+器械30%+CXO20%+中药20%；3：100只中大盘股，平均市值180亿；4：4只ETF，分散度高</t>
-  </si>
-  <si>
-    <t>931140</t>
-  </si>
-  <si>
-    <t>医药50</t>
-  </si>
-  <si>
-    <t>研发驱动型创新药</t>
-  </si>
-  <si>
-    <t>1：规避集采敏感标的，聚焦研发驱动型；2：创新药企（恒瑞/百济/信达），管线丰富；3：50只中盘股，平均市值300亿；4：3只ETF，与中证医药互补（更聚焦创新）</t>
-  </si>
-  <si>
-    <t>931234</t>
-  </si>
-  <si>
-    <t>港股通创新药</t>
-  </si>
-  <si>
-    <t>港股18A生物科技</t>
-  </si>
-  <si>
-    <t>1：港股18A生物科技，全球创新前沿阵地；2：信达/君实/康方等18A公司，临床阶段丰富；3：50只港股小盘，平均市值50亿；4：3只ETF，与A股创新药互补（更前沿）</t>
-  </si>
-  <si>
-    <t>931440</t>
-  </si>
-  <si>
-    <t>创新药30</t>
-  </si>
-  <si>
-    <t>临床后期创新药</t>
-  </si>
-  <si>
-    <t>1：纯正创新药标的，医保谈判优化受益；2：临床后期（III期）创新药企，商业化在即；3：30只小盘股，平均市值100亿；4：2只ETF，高弹性但波动大</t>
-  </si>
-  <si>
-    <t>931484</t>
-  </si>
-  <si>
-    <t>医药创新</t>
-  </si>
-  <si>
-    <t>创新药+创新器械</t>
-  </si>
-  <si>
-    <t>1：创新药+创新器械双轮驱动；2：迈瑞医疗/联影医疗等高端器械+创新药；3：50只中盘股，平均市值200亿；4：2只ETF，器械占比提升</t>
-  </si>
-  <si>
-    <t>931787</t>
-  </si>
-  <si>
-    <t>港股创新药</t>
-  </si>
-  <si>
-    <t>早期临床标的</t>
-  </si>
-  <si>
-    <t>1：与港股通创新药互补，覆盖更多临床阶段；2：侧重早期临床（I/II期）标的，风险收益比高；3：30只港股小盘，平均市值30亿；4：1只ETF，高风险高弹性</t>
-  </si>
-  <si>
-    <t>931992</t>
-  </si>
-  <si>
-    <t>疫苗生物</t>
-  </si>
-  <si>
-    <t>疫苗+mRNA技术</t>
-  </si>
-  <si>
-    <t>1：公共卫生安全战略物资，mRNA技术突破；2：疫苗+生物制品，智飞/康希诺/沃森等；3：30只小盘股，平均市值80亿；4：2只ETF，技术迭代快</t>
-  </si>
-  <si>
-    <t>931994</t>
-  </si>
-  <si>
-    <t>电网设备主题</t>
-  </si>
-  <si>
-    <t>医疗用电安全</t>
-  </si>
-  <si>
-    <t>1：医疗用电安全，公共健康基础设施保障；2：UPS/应急电源/智能配电，医院刚需；3：30只中盘股，平均市值80亿；4：1只主题指数，细分领域稀缺</t>
-  </si>
-  <si>
-    <t>932068</t>
-  </si>
-  <si>
-    <t>长寿经济</t>
-  </si>
-  <si>
-    <t>银发经济终端</t>
-  </si>
-  <si>
-    <t>1：银发经济写入政府工作报告，人口结构变化；2：养老社区/康复器械/慢病管理；3：50只中盘股，平均市值120亿；4：2只ETF，需求刚性增长</t>
-  </si>
-  <si>
-    <t>932076</t>
-  </si>
-  <si>
-    <t>全指地产</t>
-  </si>
-  <si>
-    <t>康养地产载体</t>
-  </si>
-  <si>
-    <t>1：康养地产转型，银发经济物理载体；2：万科/保利康养社区布局，传统地产转型样本；3：300只地产股，大盘为主；4：3只ETF，转型逻辑观察窗口</t>
-  </si>
-  <si>
-    <t>932431</t>
-  </si>
-  <si>
-    <t>300质量</t>
-  </si>
-  <si>
-    <t>医药质量领先企业</t>
-  </si>
-  <si>
-    <t>1：高质量发展导向，规避集采冲击；2：医药行业质量领先（ROE&gt;15%+现金流&gt;0）；3：100只中大盘股，平均市值200亿；4：2只ETF，防御属性强</t>
-  </si>
-  <si>
-    <t>000941</t>
-  </si>
-  <si>
-    <t>新能源</t>
-  </si>
-  <si>
-    <t>新能源与绿色低碳</t>
-  </si>
-  <si>
-    <t>全产业链龙头</t>
-  </si>
-  <si>
-    <t>1：双碳目标核心载体，风光储写入十五五规划；2：光伏/风电/储能全产业链龙头；3：100只大盘股，宁德/隆基/阳光电源等；4：10+只ETF，历史10年+，流动性最佳</t>
-  </si>
-  <si>
-    <t>399976</t>
-  </si>
-  <si>
-    <t>新能源车</t>
-  </si>
-  <si>
-    <t>整车+电池龙头</t>
-  </si>
-  <si>
-    <t>1：电动化+智能化双主线，全球竞争力最强赛道；2：整车-电池-零部件全覆盖，比亚迪/宁德主导；3：100只大盘股，平均市值400亿；4：12只ETF，全球配置首选</t>
-  </si>
-  <si>
-    <t>930598</t>
-  </si>
-  <si>
-    <t>稀土产业</t>
-  </si>
-  <si>
-    <t>永磁材料上游</t>
-  </si>
-  <si>
-    <t>1：战略资源安全，永磁材料刚性需求；2：稀土开采-分离-永磁材料全链条；3：50只中盘股，北方稀土/金力永磁等；4：3只ETF（复用新能源），上游资源视角</t>
-  </si>
-  <si>
-    <t>930606</t>
-  </si>
-  <si>
-    <t>中证钢铁</t>
-  </si>
-  <si>
-    <t>高端特钢绿色升级</t>
-  </si>
-  <si>
-    <t>传统转型</t>
-  </si>
-  <si>
-    <t>1：传统材料绿色升级，高端特钢国产替代；2：轴承钢/模具钢/硅钢等高端品种；3：50只大盘股，宝钢/中信特钢等；4：2只ETF，转型逻辑清晰</t>
-  </si>
-  <si>
-    <t>930638</t>
-  </si>
-  <si>
-    <t>环保设备+运营，双碳目标刚性需求</t>
-  </si>
-  <si>
-    <t>1：环保设备+运营，双碳目标刚性需求；2：碧水源/高能环境等，技术+运营双轮；3：50只小盘股，平均市值80亿；4：2只ETF，成长性高于传统公用</t>
-  </si>
-  <si>
-    <t>930660</t>
-  </si>
-  <si>
-    <t>国证钢铁</t>
-  </si>
-  <si>
-    <t>区域特钢龙头</t>
-  </si>
-  <si>
-    <t>1：高端特钢中游制造，传统材料绿色升级；2：华东/华南区域特钢企业，贴近下游需求；3：50只中盘股，平均市值100亿；4：1只ETF（复用新能源），区域特色</t>
-  </si>
-  <si>
-    <t>931065</t>
-  </si>
-  <si>
-    <t>光伏龙头30</t>
-  </si>
-  <si>
-    <t>各环节龙头集中</t>
-  </si>
-  <si>
-    <t>1：规避产能过剩，聚焦各环节龙头；2：硅料-硅片-电池-组件-逆变器各环节前3名；3：30只中大盘股，集中度高；4：2只ETF，龙头溢价显著</t>
-  </si>
-  <si>
-    <t>931151</t>
-  </si>
-  <si>
-    <t>光伏产业</t>
-  </si>
-  <si>
-    <t>光伏中游制造</t>
-  </si>
-  <si>
-    <t>1：光伏制造全球主导，技术迭代（BC/HJT）持续；2：组件/逆变器/辅材中游制造集中；3：50只中盘股，平均市值150亿；4：5只ETF，规避上游硅料周期波动</t>
-  </si>
-  <si>
-    <t>931478</t>
-  </si>
-  <si>
-    <t>苏州绿色发展</t>
-  </si>
-  <si>
-    <t>地方绿色转型样板</t>
-  </si>
-  <si>
-    <t>区域特色</t>
-  </si>
-  <si>
-    <t>1：地方绿色转型样板，可复制性强；2：绿色制造/循环经济/环保服务；3：50只中盘股，苏州本地企业；4：1只区域指数，地方政策试验田</t>
-  </si>
-  <si>
-    <t>931554</t>
-  </si>
-  <si>
-    <t>长江保护</t>
-  </si>
-  <si>
-    <t>长江生态修复</t>
-  </si>
-  <si>
-    <t>1：长江经济带生态修复，流域治理标杆；2：水环境治理/生态修复/环保设备；3：50只中盘股，长江沿线企业集中；4：1只区域指数（复用新能源），政策持续性强</t>
-  </si>
-  <si>
-    <t>931687</t>
-  </si>
-  <si>
-    <t>风电产业</t>
-  </si>
-  <si>
-    <t>海上风电+大基地</t>
-  </si>
-  <si>
-    <t>1：海上风电+大基地建设，十五五装机目标明确；2：整机-叶片-塔筒-海缆全链条；3：50只中盘股，金风/明阳等龙头；4：2只ETF，与光伏形成互补</t>
-  </si>
-  <si>
-    <t>931697</t>
-  </si>
-  <si>
-    <t>消费50策略</t>
-  </si>
-  <si>
-    <t>充电桩/换电服务</t>
-  </si>
-  <si>
-    <t>1：新能源消费端培育，充电桩/换电写入规划；2：充电桩运营商/换电服务商/充电设备；3：50只中盘股，特来电/星星充电等；4：1只ETF，消费属性强于制造端</t>
-  </si>
-  <si>
-    <t>931742</t>
-  </si>
-  <si>
-    <t>氢能产业</t>
-  </si>
-  <si>
-    <t>氢能全链条</t>
-  </si>
-  <si>
-    <t>1：氢能中长期规划，十五五示范城市群扩容；2：制氢-储运-加注-应用全链条，燃料电池车先行；3：30只小盘股，技术路线未定但政策扶持强；4：1只主题指数，前沿探索型</t>
-  </si>
-  <si>
-    <t>931746</t>
-  </si>
-  <si>
-    <t>储能产业</t>
-  </si>
-  <si>
-    <t>储能系统集成</t>
-  </si>
-  <si>
-    <t>1：新型电力系统关键，强制配储政策驱动；2：储能系统集成/电池管理/温控设备；3：50只中盘股，2023年后商业化加速；4：3只ETF，成长确定性高</t>
-  </si>
-  <si>
-    <t>931772</t>
-  </si>
-  <si>
-    <t>SEEE碳中和</t>
-  </si>
-  <si>
-    <t>中证+上海环交所联合编制</t>
-  </si>
-  <si>
-    <t>1：中证+上海环交所联合编制，方法论权威；2：能源替代（风光）+节能减排（节能设备）双路径；3：100只中盘股，覆盖全市场；4：4只ETF，政策背书强</t>
-  </si>
-  <si>
-    <t>931799</t>
-  </si>
-  <si>
-    <t>国寿资产ESG绿色低碳100</t>
-  </si>
-  <si>
-    <t>保险资金绿色投资</t>
-  </si>
-  <si>
-    <t>1：保险资金绿色投资，长期资金入市标杆；2：绿色低碳全产业链，ESG评级前20%；3：100只中大盘股，机构持仓集中；4：1只定制指数，长期资金偏好</t>
-  </si>
-  <si>
-    <t>931892</t>
-  </si>
-  <si>
-    <t>有色矿业</t>
-  </si>
-  <si>
-    <t>锂/钴/镍资源端</t>
-  </si>
-  <si>
-    <t>1：资源安全战略，锂/钴/镍自主可控；2：新能源金属资源端，紫金/赣锋等龙头；3：50只中盘股，平均市值200亿；4：2只ETF，与稀土产业互补（更广资源覆盖）</t>
-  </si>
-  <si>
-    <t>931897</t>
-  </si>
-  <si>
-    <t>绿色电力</t>
-  </si>
-  <si>
-    <t>风光运营资产</t>
-  </si>
-  <si>
-    <t>1：绿电交易+碳市场机制完善，运营资产受益；2：风电/光伏电站运营，现金流稳定；3：50只小盘股，平均市值80亿；4：2只ETF，高股息属性（3-4%）</t>
-  </si>
-  <si>
-    <t>932075</t>
-  </si>
-  <si>
-    <t>全指金融</t>
-  </si>
-  <si>
-    <t>绿色金融支持</t>
-  </si>
-  <si>
-    <t>1：绿色金融支持，碳中和债/转型金融工具创新；2：银行/券商绿色信贷/绿色债券承销；3：300只金融股，大盘为主；4：3只ETF，资金端保障逻辑</t>
-  </si>
-  <si>
-    <t>932422</t>
-  </si>
-  <si>
-    <t>国新港股通央企红</t>
-  </si>
-  <si>
-    <t>绿色能源央企H股</t>
-  </si>
-  <si>
-    <t>1：央企高股息+绿色转型双重逻辑；2：国家电投/三峡集团等绿色能源央企H股；3：50只港股大盘，平均股息率5%+；4：1只ETF，防御+成长兼备</t>
-  </si>
-  <si>
-    <t>932444</t>
-  </si>
-  <si>
-    <t>互联互通中国50</t>
-  </si>
-  <si>
-    <t>港股新能源龙头</t>
-  </si>
-  <si>
-    <t>1：港股新能源龙头，估值修复+成长双逻辑；2：比亚迪H/理想/小鹏等，与A股互补；3：50只港股大盘，平均市值500亿+；4：2只ETF，跨境配置便利</t>
-  </si>
-  <si>
-    <t>000998</t>
-  </si>
-  <si>
-    <t>中证TMT</t>
-  </si>
-  <si>
-    <t>新一代信息技术与数字经济</t>
-  </si>
-  <si>
-    <t>信息技术</t>
-  </si>
-  <si>
-    <t>电子+计算机+通信+传媒</t>
-  </si>
-  <si>
-    <t>1：数字经济基础设施，新基建核心；2：电子+计算机+通信+传媒全覆盖；3：100只大盘股，平均市值350亿；4：6只ETF，流动性最佳TMT指数</t>
-  </si>
-  <si>
-    <t>399633</t>
-  </si>
-  <si>
-    <t>深证300</t>
-  </si>
-  <si>
-    <t>深市科技龙头</t>
-  </si>
-  <si>
-    <t>1：深市科技龙头，华为链/腾讯系核心标的；2：电子/通信/计算机占比70%，硬科技特色；3：300只大盘股，平均市值400亿；4：4只ETF，与沪深300互补（科技侧重）</t>
-  </si>
-  <si>
-    <t>930601</t>
-  </si>
-  <si>
-    <t>中证软件</t>
-  </si>
-  <si>
-    <t>基础软件+工业软件</t>
-  </si>
-  <si>
-    <t>1：基础软件+工业软件国产化，卡脖子环节；2：操作系统/数据库/EDA/工业CAD；3：100只中盘股，平均市值150亿；4：4只ETF，信创核心受益</t>
-  </si>
-  <si>
-    <t>930712</t>
-  </si>
-  <si>
-    <t>物联网</t>
-  </si>
-  <si>
-    <t>5G+AIoT融合</t>
-  </si>
-  <si>
-    <t>1：5G+AIoT融合，万物互联基础设施；2：传感器-模组-平台-应用全链条；3：50只中盘股，平均市值120亿；4：2只ETF，应用场景持续拓展</t>
-  </si>
-  <si>
-    <t>930713</t>
-  </si>
-  <si>
-    <t>人工智能</t>
-  </si>
-  <si>
-    <t>AI应用层</t>
-  </si>
-  <si>
-    <t>1：侧重AI应用层，计算机视觉/NLP/语音识别；2：商汤/云从/科大讯飞等应用层龙头；3：50只中盘股，平均市值150亿；4：3只ETF，与AI指数互补（应用侧重）</t>
-  </si>
-  <si>
-    <t>930796</t>
-  </si>
-  <si>
-    <t>信息安全</t>
-  </si>
-  <si>
-    <t>网络安全+数据安全</t>
-  </si>
-  <si>
-    <t>安全</t>
-  </si>
-  <si>
-    <t>1：网络安全法+数据安全法，刚性合规需求；2：防火墙/IDS/数据加密/身份认证；3：50只中盘股，平均市值100亿；4：3只ETF，政策驱动型</t>
-  </si>
-  <si>
-    <t>930851</t>
-  </si>
-  <si>
-    <t>云计算</t>
-  </si>
-  <si>
-    <t>云服务厂商集中</t>
-  </si>
-  <si>
-    <t>1：东数西算工程，算力基础设施建设；2：IaaS/PaaS/SaaS全栈，阿里云/腾讯云/华为云生态；3：50只中盘股，平均市值200亿；4：5只ETF，政企上云持续受益</t>
-  </si>
-  <si>
-    <t>930902</t>
-  </si>
-  <si>
-    <t>中证数据</t>
-  </si>
-  <si>
-    <t>数据要素市场化</t>
-  </si>
-  <si>
-    <t>1：数据要素市场化，“数据二十条”落地；2：数据采集-处理-交易-应用，交易所挂牌标的；3：50只小盘股，平均市值80亿；4：2只ETF，前沿探索型</t>
-  </si>
-  <si>
-    <t>930916</t>
-  </si>
-  <si>
-    <t>300通信</t>
-  </si>
-  <si>
-    <t>5G-A/6G研发</t>
-  </si>
-  <si>
-    <t>通信</t>
-  </si>
-  <si>
-    <t>1：5G-A/6G研发，通信基础设施安全；2：主设备商（华为/中兴）+光通信+卫星通信；3：100只中大盘股，平均市值200亿；4：3只ETF，与TMT互补（通信侧重）</t>
-  </si>
-  <si>
-    <t>931071</t>
-  </si>
-  <si>
-    <t>AI大模型+算力+应用</t>
-  </si>
-  <si>
-    <t>1：“人工智能+"行动写入政府工作报告；2：大模型-算力-应用全链条，科大讯飞/商汤等；3：100只中盘股，平均市值180亿；4：8只ETF，2023年政策催化密集</t>
-  </si>
-  <si>
-    <t>931139</t>
-  </si>
-  <si>
-    <t>长三角</t>
-  </si>
-  <si>
-    <t>长三角数字经济集群</t>
-  </si>
-  <si>
-    <t>1：长三角数字经济集群，一体化示范区；2：上海（芯片）-杭州（电商）-苏州（制造）协同；3：100只中大盘股，平均市值250亿；4：2只区域指数，政策高地</t>
-  </si>
-  <si>
-    <t>931247</t>
-  </si>
-  <si>
-    <t>中证信创</t>
-  </si>
-  <si>
-    <t>信创全栈</t>
-  </si>
-  <si>
-    <t>1：信息技术应用创新，安全可控刚性需求；2：CPU（龙芯/飞腾）-OS（麒麟）-数据库（达梦）全栈；3：100只中盘股，平均市值120亿；4：6只ETF，党政→行业扩散逻辑</t>
-  </si>
-  <si>
-    <t>931381</t>
-  </si>
-  <si>
-    <t>中证长三角</t>
-  </si>
-  <si>
-    <t>沪苏浙龙头</t>
-  </si>
-  <si>
-    <t>1：与国证长三角互补，侧重沪苏浙龙头；2：科创板企业占比30%，硬科技特色；3：150只中大盘股，流动性好于国证版；4：3只ETF，成分更均衡</t>
-  </si>
-  <si>
-    <t>931447</t>
-  </si>
-  <si>
-    <t>科技先锋</t>
-  </si>
-  <si>
-    <t>量子/脑机接口前沿</t>
-  </si>
-  <si>
-    <t>1：前沿技术探索，量子/脑机接口/6G；2：科研机构转化标的，技术不确定性高但想象空间大；3：30只小盘股，平均市值60亿；4：1只主题指数，高风险高弹性</t>
-  </si>
-  <si>
-    <t>931461</t>
-  </si>
-  <si>
-    <t>电子50</t>
-  </si>
-  <si>
-    <t>消费电子+半导体设备</t>
-  </si>
-  <si>
-    <t>电子</t>
-  </si>
-  <si>
-    <t>1：消费电子复苏+半导体设备国产化；2：苹果链/华为链+半导体设备材料；3：50只中大盘股，平均市值250亿；4：4只ETF，流动性最佳电子指数</t>
-  </si>
-  <si>
-    <t>931469</t>
-  </si>
-  <si>
-    <t>云计算50</t>
-  </si>
-  <si>
-    <t>云计算细分龙头</t>
-  </si>
-  <si>
-    <t>1：聚焦云计算核心标的，规避纯概念股；2：50只云计算龙头，IaaS/PaaS/SaaS均衡；3：50只中大盘股，集中度高；4：2只ETF，与云计算指数互补（更聚焦）</t>
-  </si>
-  <si>
-    <t>931480</t>
-  </si>
-  <si>
-    <t>线上消费</t>
-  </si>
-  <si>
-    <t>电商/本地生活</t>
-  </si>
-  <si>
-    <t>1：数字经济与消费融合，平台经济常态化；2：美团/拼多多/快手，本地生活+电商；3：50只中盘股，平均市值300亿；4：3只ETF（复用信息技术），消费端属性</t>
-  </si>
-  <si>
-    <t>931495</t>
-  </si>
-  <si>
-    <t>工业互联</t>
-  </si>
-  <si>
-    <t>工业互联网平台</t>
-  </si>
-  <si>
-    <t>1：工业互联网平台，制造业数字化转型枢纽；2：平台层（树根互联/卡奥斯）+应用层；3：50只中盘股，平均市值100亿；4：2只ETF，B2B属性强</t>
-  </si>
-  <si>
-    <t>931574</t>
-  </si>
-  <si>
-    <t>港股科技</t>
-  </si>
-  <si>
-    <t>港股互联网平台</t>
-  </si>
-  <si>
-    <t>1：港股互联网平台，估值修复+出海双逻辑；2：腾讯/美团/快手/小米，与A股互补；3：50只港股大盘，平均市值800亿；4：4只ETF，流动性最佳港股科技指数</t>
-  </si>
-  <si>
-    <t>931582</t>
-  </si>
-  <si>
-    <t>数字经济</t>
-  </si>
-  <si>
-    <t>数字产业化+产业数字化</t>
-  </si>
-  <si>
-    <t>1：数字产业化+产业数字化双路径；2：数字内容/数字支付/数字政务等应用层；3：100只中大盘股，平均市值200亿；4：3只ETF，消费端属性强</t>
-  </si>
-  <si>
-    <t>931589</t>
-  </si>
-  <si>
-    <t>300成长创新</t>
-  </si>
-  <si>
-    <t>科技安全+创新</t>
-  </si>
-  <si>
-    <t>1：科技安全+创新双主线；2：半导体/软件/通信设备创新龙头；3：100只中盘股，成长性突出；4：2只ETF，与沪深300互补（创新侧重）</t>
-  </si>
-  <si>
-    <t>932066</t>
-  </si>
-  <si>
-    <t>半导体行业精选</t>
-  </si>
-  <si>
-    <t>第三代半导体</t>
-  </si>
-  <si>
-    <t>1：第三代半导体（碳化硅/氮化镓）专项扶持；2：碳化硅衬底-外延-器件，新能源车/光伏应用；3：30只小盘股，技术壁垒高；4：2只ETF，与中证半导互补（更聚焦新材料）</t>
-  </si>
-  <si>
-    <t>932359</t>
-  </si>
-  <si>
-    <t>国新国企人工智能</t>
-  </si>
-  <si>
-    <t>国企主导AI应用</t>
-  </si>
-  <si>
-    <t>1：国企主导AI政务/金融应用，安全可控；2：中国电子/中国电科AI平台，党政市场主导；3：50只大盘股，央企占比90%；4：1只主题指数，政策执行力强</t>
-  </si>
-  <si>
-    <t>932360</t>
-  </si>
-  <si>
-    <t>算力基础设施</t>
-  </si>
-  <si>
-    <t>东数西算+AI算力</t>
-  </si>
-  <si>
-    <t>算力</t>
-  </si>
-  <si>
-    <t>1：东数西算+AI算力需求爆发；2：数据中心/光模块/服务器/液冷设备；3：50只中盘股，平均市值150亿；4：2只ETF，2024年新推，契合AI浪潮</t>
-  </si>
-  <si>
-    <t>932456</t>
-  </si>
-  <si>
-    <t>科创创业AI</t>
-  </si>
-  <si>
-    <t>AIGC应用</t>
-  </si>
-  <si>
-    <t>科技赋能</t>
-  </si>
-  <si>
-    <t>1：农业AI应用，智慧种植/病虫害识别；2：极飞科技/大疆农业等，无人机+AI；3：50只小盘股，平均市值70亿；4：1只主题指数（复用信息技术），科技交叉</t>
-  </si>
-  <si>
-    <t>932592</t>
-  </si>
-  <si>
-    <t>沪深港三地龙头</t>
-  </si>
-  <si>
-    <t>1：沪深港三地龙头，全球化配置；2：腾讯/阿里/美团/宁德等核心资产；3：50只超大盘股，平均市值1000亿+；4：3只ETF（HKD/USD/CNY），跨境便利</t>
-  </si>
-  <si>
-    <t>930779</t>
-  </si>
-  <si>
-    <t>中证全指传媒</t>
-  </si>
-  <si>
-    <t>子产业链专项覆盖</t>
-  </si>
-  <si>
-    <t>内容生产</t>
-  </si>
-  <si>
-    <t>全市场传媒覆盖（*替换数字传媒重复*）</t>
-  </si>
-  <si>
-    <t>930813</t>
-  </si>
-  <si>
-    <t>细分化工</t>
-  </si>
-  <si>
-    <t>化工材料</t>
-  </si>
-  <si>
-    <t>医药中间体/电子化学品（*替换化工重复*）</t>
-  </si>
-  <si>
-    <t>1：医药中间体/原料药上游保障；2：特色原料药/CDMO/医药中间体；3：50只中盘股，平均市值100亿；4：1只细分指数，产业链上游视角</t>
-  </si>
-  <si>
-    <t>930944</t>
-  </si>
-  <si>
-    <t>内地资源</t>
-  </si>
-  <si>
-    <t>生活服务</t>
-  </si>
-  <si>
-    <t>生活资源视角（*替换餐饮指数重复*）</t>
-  </si>
-  <si>
-    <t>930948</t>
-  </si>
-  <si>
-    <t>内地地产</t>
-  </si>
-  <si>
-    <t>建材建筑</t>
-  </si>
-  <si>
-    <t>绿色建筑载体（*替换建筑材料重复*）</t>
-  </si>
-  <si>
-    <t>930959</t>
-  </si>
-  <si>
-    <t>银河99</t>
-  </si>
-  <si>
-    <t>基建+高端制造融合（*替换中证基建重复*）</t>
-  </si>
-  <si>
-    <t>931001</t>
-  </si>
-  <si>
-    <t>汽车指数</t>
-  </si>
-  <si>
-    <t>交通装备</t>
-  </si>
-  <si>
-    <t>整车+零部件全覆盖</t>
-  </si>
-  <si>
-    <t>1：整车+零部件全覆盖，电动化转型代表；2：比亚迪/长城/吉利，自主品牌崛起；3：100只中大盘股，平均市值300亿；4：5只ETF，下游整车视角</t>
-  </si>
-  <si>
-    <t>931230</t>
-  </si>
-  <si>
-    <t>汽车零部件</t>
-  </si>
-  <si>
-    <t>智能驾驶+新能源供应链</t>
-  </si>
-  <si>
-    <t>1：智能驾驶+新能源车供应链，全球竞争力；2：拓普集团/德赛西威，单车价值量提升；3：100只中盘股，平均市值150亿；4：4只ETF，中游零部件视角</t>
-  </si>
-  <si>
-    <t>931395</t>
-  </si>
-  <si>
-    <t>沪港深300</t>
-  </si>
-  <si>
-    <t>跨市场消费龙头（*替换成渝经济圈重复*）</t>
-  </si>
-  <si>
-    <t>931752</t>
-  </si>
-  <si>
-    <t>工程机械主题</t>
-  </si>
-  <si>
-    <t>新能源工程机械（*保留1次*）</t>
-  </si>
-  <si>
-    <t>1：新能源工程机械渗透率提升；2：三一/徐工电动化转型，出口+内需双驱动；3：30只中盘股（复用新能源），平均市值150亿；4：1只主题指数，特种装备视角</t>
-  </si>
-  <si>
-    <t>931785</t>
-  </si>
-  <si>
-    <t>智选沪深港科技50</t>
-  </si>
-  <si>
-    <t>影视科技融合（*替换中证影视重复*）</t>
-  </si>
-  <si>
-    <t>932153</t>
-  </si>
-  <si>
-    <t>港股通价值策略</t>
-  </si>
-  <si>
-    <t>消费价值股（*替换港股通科技重复*）</t>
   </si>
   <si>
     <t>H30597</t>
@@ -2364,7 +2319,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2379,6 +2334,11 @@
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <name val="Segoe UI"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -2843,16 +2803,13 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2861,123 +2818,127 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -3324,7 +3285,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G183"/>
+  <dimension ref="A1:G180"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="11.625" style="2" customWidth="1"/>
@@ -3360,34 +3321,16 @@
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" t="s">
-        <v>13</v>
+      <c r="A2" s="2">
+        <v>399311</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="2" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C3" t="s">
         <v>9</v>
@@ -3396,21 +3339,21 @@
         <v>10</v>
       </c>
       <c r="E3" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F3" t="s">
         <v>12</v>
       </c>
       <c r="G3" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
         <v>9</v>
@@ -3419,27 +3362,27 @@
         <v>10</v>
       </c>
       <c r="E4" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F4" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G4" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" t="s">
         <v>21</v>
       </c>
-      <c r="B5" t="s">
+      <c r="D5" t="s">
         <v>22</v>
-      </c>
-      <c r="C5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" t="s">
-        <v>10</v>
       </c>
       <c r="E5" t="s">
         <v>23</v>
@@ -3459,50 +3402,50 @@
         <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="D6" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="E6" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F6" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="G6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B7" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C7" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="D7" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F7" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="G7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C8" t="s">
         <v>9</v>
@@ -3511,21 +3454,21 @@
         <v>10</v>
       </c>
       <c r="E8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C9" t="s">
         <v>9</v>
@@ -3534,1462 +3477,1462 @@
         <v>10</v>
       </c>
       <c r="E9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F9" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="G9" t="s">
-        <v>13</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B10" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C10" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="D10" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="E10" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F10" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="G10" t="s">
-        <v>13</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B11" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C11" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="D11" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E11" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F11" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="G11" t="s">
-        <v>13</v>
+        <v>52</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B12" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C12" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="D12" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E12" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="F12" t="s">
-        <v>52</v>
+        <v>17</v>
       </c>
       <c r="G12" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B13" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C13" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="D13" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E13" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F13" t="s">
-        <v>57</v>
+        <v>12</v>
       </c>
       <c r="G13" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B14" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C14" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="D14" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E14" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F14" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G14" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B15" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C15" t="s">
-        <v>9</v>
+        <v>68</v>
       </c>
       <c r="D15" t="s">
-        <v>10</v>
+        <v>69</v>
       </c>
       <c r="E15" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F15" t="s">
-        <v>62</v>
+        <v>17</v>
       </c>
       <c r="G15" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="B16" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C16" t="s">
-        <v>9</v>
+        <v>74</v>
       </c>
       <c r="D16" t="s">
-        <v>10</v>
+        <v>73</v>
       </c>
       <c r="E16" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="F16" t="s">
-        <v>71</v>
+        <v>17</v>
       </c>
       <c r="G16" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="2" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="B17" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C17" t="s">
-        <v>9</v>
+        <v>79</v>
       </c>
       <c r="D17" t="s">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="E17" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F17" t="s">
-        <v>76</v>
+        <v>12</v>
       </c>
       <c r="G17" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="2" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="B18" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C18" t="s">
-        <v>9</v>
+        <v>85</v>
       </c>
       <c r="D18" t="s">
-        <v>10</v>
+        <v>86</v>
       </c>
       <c r="E18" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="F18" t="s">
-        <v>81</v>
+        <v>17</v>
       </c>
       <c r="G18" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="2" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="B19" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="C19" t="s">
-        <v>9</v>
+        <v>91</v>
       </c>
       <c r="D19" t="s">
-        <v>10</v>
+        <v>92</v>
       </c>
       <c r="E19" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="F19" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G19" t="s">
-        <v>13</v>
+        <v>94</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="2" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="B20" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="C20" t="s">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="D20" t="s">
-        <v>89</v>
+        <v>22</v>
       </c>
       <c r="E20" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="F20" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="G20" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="2" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="B21" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="C21" t="s">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="D21" t="s">
-        <v>89</v>
+        <v>22</v>
       </c>
       <c r="E21" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="F21" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="G21" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="2" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="B22" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="C22" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="D22" t="s">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c r="E22" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="F22" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="G22" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="2" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="B23" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="C23" t="s">
-        <v>88</v>
+        <v>111</v>
       </c>
       <c r="D23" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="E23" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="F23" t="s">
-        <v>24</v>
+        <v>114</v>
       </c>
       <c r="G23" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="2" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="B24" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="C24" t="s">
-        <v>88</v>
+        <v>111</v>
       </c>
       <c r="D24" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="E24" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="F24" t="s">
-        <v>12</v>
+        <v>119</v>
       </c>
       <c r="G24" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="2" t="s">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="B25" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="C25" t="s">
-        <v>88</v>
+        <v>9</v>
       </c>
       <c r="D25" t="s">
-        <v>89</v>
+        <v>10</v>
       </c>
       <c r="E25" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="F25" t="s">
-        <v>52</v>
+        <v>17</v>
       </c>
       <c r="G25" t="s">
-        <v>111</v>
+        <v>124</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B26" t="s">
+        <v>126</v>
+      </c>
+      <c r="C26" t="s">
+        <v>111</v>
+      </c>
+      <c r="D26" t="s">
         <v>112</v>
       </c>
-      <c r="B26" t="s">
-        <v>113</v>
-      </c>
-      <c r="C26" t="s">
-        <v>88</v>
-      </c>
-      <c r="D26" t="s">
-        <v>89</v>
-      </c>
       <c r="E26" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="F26" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="G26" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27" s="2" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="B27" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="C27" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="D27" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="E27" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="F27" t="s">
-        <v>119</v>
+        <v>17</v>
       </c>
       <c r="G27" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28" s="2" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="B28" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="C28" t="s">
-        <v>88</v>
+        <v>9</v>
       </c>
       <c r="D28" t="s">
-        <v>89</v>
+        <v>10</v>
       </c>
       <c r="E28" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="F28" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="G28" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" s="2" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="B29" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="C29" t="s">
-        <v>88</v>
+        <v>28</v>
       </c>
       <c r="D29" t="s">
-        <v>89</v>
+        <v>29</v>
       </c>
       <c r="E29" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="F29" t="s">
-        <v>129</v>
+        <v>17</v>
       </c>
       <c r="G29" t="s">
-        <v>130</v>
+        <v>141</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" s="2" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="B30" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="C30" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="D30" t="s">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c r="E30" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="F30" t="s">
-        <v>119</v>
+        <v>39</v>
       </c>
       <c r="G30" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31" s="2" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="B31" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="C31" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="D31" t="s">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="E31" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="F31" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="G31" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="2" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="B32" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="C32" t="s">
-        <v>88</v>
+        <v>9</v>
       </c>
       <c r="D32" t="s">
-        <v>89</v>
+        <v>10</v>
       </c>
       <c r="E32" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="F32" t="s">
-        <v>138</v>
+        <v>12</v>
       </c>
       <c r="G32" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
     </row>
     <row r="33" spans="1:7">
       <c r="A33" s="2" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="B33" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="C33" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D33" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E33" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="F33" t="s">
-        <v>129</v>
+        <v>17</v>
       </c>
       <c r="G33" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
     </row>
     <row r="34" spans="1:7">
       <c r="A34" s="2" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="B34" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="C34" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="D34" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="E34" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="F34" t="s">
-        <v>151</v>
+        <v>17</v>
       </c>
       <c r="G34" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
     </row>
     <row r="35" spans="1:7">
       <c r="A35" s="2" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="B35" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="C35" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="D35" t="s">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c r="E35" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="F35" t="s">
-        <v>156</v>
+        <v>17</v>
       </c>
       <c r="G35" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
     </row>
     <row r="36" spans="1:7">
       <c r="A36" s="2" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="B36" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="C36" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="D36" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="E36" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="F36" t="s">
-        <v>138</v>
+        <v>114</v>
       </c>
       <c r="G36" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
     </row>
     <row r="37" spans="1:7">
       <c r="A37" s="2" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="B37" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="C37" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D37" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E37" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="F37" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="G37" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="2" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="B38" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="C38" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="D38" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="E38" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="F38" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="G38" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39" s="2" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="B39" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="C39" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D39" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E39" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="F39" t="s">
-        <v>156</v>
+        <v>39</v>
       </c>
       <c r="G39" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40" s="2" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="B40" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="C40" t="s">
-        <v>88</v>
+        <v>28</v>
       </c>
       <c r="D40" t="s">
-        <v>89</v>
+        <v>29</v>
       </c>
       <c r="E40" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="F40" t="s">
-        <v>124</v>
+        <v>31</v>
       </c>
       <c r="G40" t="s">
-        <v>178</v>
+        <v>31</v>
       </c>
     </row>
     <row r="41" spans="1:7">
       <c r="A41" s="2" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="B41" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="C41" t="s">
-        <v>88</v>
+        <v>28</v>
       </c>
       <c r="D41" t="s">
-        <v>89</v>
+        <v>29</v>
       </c>
       <c r="E41" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="F41" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="G41" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42" s="2" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="B42" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="C42" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="D42" t="s">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c r="E42" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="F42" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="G42" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43" s="2" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="B43" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="C43" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="D43" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="E43" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="F43" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="G43" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
     </row>
     <row r="44" spans="1:7">
       <c r="A44" s="2" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="B44" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="C44" t="s">
-        <v>193</v>
+        <v>68</v>
       </c>
       <c r="D44" t="s">
-        <v>194</v>
+        <v>69</v>
       </c>
       <c r="E44" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="F44" t="s">
-        <v>12</v>
+        <v>114</v>
       </c>
       <c r="G44" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
     </row>
     <row r="45" spans="1:7">
       <c r="A45" s="2" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B45" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="C45" t="s">
-        <v>193</v>
+        <v>74</v>
       </c>
       <c r="D45" t="s">
-        <v>194</v>
+        <v>73</v>
       </c>
       <c r="E45" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="F45" t="s">
-        <v>24</v>
+        <v>119</v>
       </c>
       <c r="G45" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
     </row>
     <row r="46" spans="1:7">
       <c r="A46" s="2" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="B46" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="C46" t="s">
-        <v>193</v>
+        <v>79</v>
       </c>
       <c r="D46" t="s">
-        <v>194</v>
+        <v>80</v>
       </c>
       <c r="E46" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="F46" t="s">
-        <v>204</v>
+        <v>114</v>
       </c>
       <c r="G46" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
     </row>
     <row r="47" spans="1:7">
       <c r="A47" s="2" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="B47" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C47" t="s">
-        <v>193</v>
+        <v>9</v>
       </c>
       <c r="D47" t="s">
-        <v>194</v>
+        <v>10</v>
       </c>
       <c r="E47" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="F47" t="s">
-        <v>13</v>
+        <v>212</v>
       </c>
       <c r="G47" t="s">
-        <v>13</v>
+        <v>213</v>
       </c>
     </row>
     <row r="48" spans="1:7">
       <c r="A48" s="2" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="B48" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="C48" t="s">
-        <v>193</v>
+        <v>79</v>
       </c>
       <c r="D48" t="s">
-        <v>194</v>
+        <v>80</v>
       </c>
       <c r="E48" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="F48" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="G48" t="s">
-        <v>13</v>
+        <v>217</v>
       </c>
     </row>
     <row r="49" spans="1:7">
       <c r="A49" s="2" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="B49" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="C49" t="s">
-        <v>193</v>
+        <v>28</v>
       </c>
       <c r="D49" t="s">
-        <v>194</v>
+        <v>29</v>
       </c>
       <c r="E49" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="F49" t="s">
-        <v>215</v>
+        <v>12</v>
       </c>
       <c r="G49" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
     </row>
     <row r="50" spans="1:7">
       <c r="A50" s="2" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="B50" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="C50" t="s">
-        <v>193</v>
+        <v>79</v>
       </c>
       <c r="D50" t="s">
-        <v>194</v>
+        <v>80</v>
       </c>
       <c r="E50" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="F50" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="G50" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
     </row>
     <row r="51" spans="1:7">
       <c r="A51" s="2" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="B51" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="C51" t="s">
-        <v>193</v>
+        <v>91</v>
       </c>
       <c r="D51" t="s">
-        <v>194</v>
+        <v>92</v>
       </c>
       <c r="E51" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="F51" t="s">
-        <v>129</v>
+        <v>212</v>
       </c>
       <c r="G51" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
     </row>
     <row r="52" spans="1:7">
       <c r="A52" s="2" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="B52" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="C52" t="s">
-        <v>193</v>
+        <v>91</v>
       </c>
       <c r="D52" t="s">
-        <v>194</v>
+        <v>92</v>
       </c>
       <c r="E52" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="F52" t="s">
-        <v>228</v>
+        <v>212</v>
       </c>
       <c r="G52" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
     </row>
     <row r="53" spans="1:7">
       <c r="A53" s="2" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="B53" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="C53" t="s">
-        <v>193</v>
+        <v>111</v>
       </c>
       <c r="D53" t="s">
-        <v>194</v>
+        <v>112</v>
       </c>
       <c r="E53" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="F53" t="s">
-        <v>233</v>
+        <v>12</v>
       </c>
       <c r="G53" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7">
-      <c r="A54" s="2" t="s">
-        <v>235</v>
+        <v>238</v>
+      </c>
+    </row>
+    <row r="54" ht="15.75" spans="1:7">
+      <c r="A54" s="4">
+        <v>399971</v>
       </c>
       <c r="B54" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="C54" t="s">
-        <v>193</v>
+        <v>240</v>
       </c>
       <c r="D54" t="s">
-        <v>194</v>
+        <v>241</v>
       </c>
       <c r="E54" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="F54" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G54" t="s">
-        <v>238</v>
+        <v>31</v>
       </c>
     </row>
     <row r="55" spans="1:7">
       <c r="A55" s="2" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="B55" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="C55" t="s">
-        <v>241</v>
+        <v>105</v>
       </c>
       <c r="D55" t="s">
-        <v>242</v>
+        <v>106</v>
       </c>
       <c r="E55" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="F55" t="s">
-        <v>244</v>
+        <v>39</v>
       </c>
       <c r="G55" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="56" spans="1:7">
       <c r="A56" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B56" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C56" t="s">
-        <v>241</v>
+        <v>111</v>
       </c>
       <c r="D56" t="s">
-        <v>242</v>
+        <v>112</v>
       </c>
       <c r="E56" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F56" t="s">
-        <v>12</v>
+        <v>250</v>
       </c>
       <c r="G56" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="57" spans="1:7">
       <c r="A57" s="2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B57" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C57" t="s">
-        <v>241</v>
+        <v>91</v>
       </c>
       <c r="D57" t="s">
-        <v>242</v>
+        <v>92</v>
       </c>
       <c r="E57" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="F57" t="s">
-        <v>24</v>
+        <v>255</v>
       </c>
       <c r="G57" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
     </row>
     <row r="58" spans="1:7">
       <c r="A58" s="2" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="B58" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="C58" t="s">
-        <v>241</v>
+        <v>28</v>
       </c>
       <c r="D58" t="s">
-        <v>242</v>
+        <v>29</v>
       </c>
       <c r="E58" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="F58" t="s">
-        <v>12</v>
+        <v>260</v>
       </c>
       <c r="G58" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
     </row>
     <row r="59" spans="1:7">
       <c r="A59" s="2" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="B59" t="s">
-        <v>259</v>
+        <v>46</v>
       </c>
       <c r="C59" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D59" t="s">
-        <v>242</v>
+        <v>263</v>
       </c>
       <c r="E59" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="F59" t="s">
-        <v>33</v>
+        <v>212</v>
       </c>
       <c r="G59" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
     </row>
     <row r="60" spans="1:7">
       <c r="A60" s="2" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="B60" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="C60" t="s">
-        <v>241</v>
+        <v>68</v>
       </c>
       <c r="D60" t="s">
-        <v>242</v>
+        <v>69</v>
       </c>
       <c r="E60" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="F60" t="s">
-        <v>265</v>
+        <v>12</v>
       </c>
       <c r="G60" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="61" spans="1:7">
       <c r="A61" s="2" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="B61" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="C61" t="s">
-        <v>241</v>
+        <v>28</v>
       </c>
       <c r="D61" t="s">
-        <v>242</v>
+        <v>29</v>
       </c>
       <c r="E61" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="F61" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G61" t="s">
-        <v>270</v>
+        <v>31</v>
       </c>
     </row>
     <row r="62" spans="1:7">
       <c r="A62" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B62" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C62" t="s">
-        <v>241</v>
+        <v>68</v>
       </c>
       <c r="D62" t="s">
-        <v>242</v>
+        <v>69</v>
       </c>
       <c r="E62" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="F62" t="s">
-        <v>24</v>
+        <v>212</v>
       </c>
       <c r="G62" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="63" spans="1:7">
       <c r="A63" s="2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B63" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C63" t="s">
-        <v>241</v>
+        <v>9</v>
       </c>
       <c r="D63" t="s">
-        <v>242</v>
+        <v>10</v>
       </c>
       <c r="E63" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="F63" t="s">
-        <v>151</v>
+        <v>119</v>
       </c>
       <c r="G63" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="64" spans="1:7">
       <c r="A64" s="2" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B64" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C64" t="s">
-        <v>241</v>
+        <v>91</v>
       </c>
       <c r="D64" t="s">
-        <v>242</v>
+        <v>92</v>
       </c>
       <c r="E64" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="F64" t="s">
-        <v>282</v>
+        <v>12</v>
       </c>
       <c r="G64" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="65" spans="1:7">
       <c r="A65" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B65" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C65" t="s">
-        <v>286</v>
+        <v>68</v>
       </c>
       <c r="D65" t="s">
+        <v>69</v>
+      </c>
+      <c r="E65" t="s">
         <v>287</v>
       </c>
-      <c r="E65" t="s">
+      <c r="F65" t="s">
+        <v>212</v>
+      </c>
+      <c r="G65" t="s">
         <v>288</v>
-      </c>
-      <c r="F65" t="s">
-        <v>24</v>
-      </c>
-      <c r="G65" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="66" spans="1:7">
       <c r="A66" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="B66" t="s">
         <v>290</v>
       </c>
-      <c r="B66" t="s">
+      <c r="C66" t="s">
+        <v>105</v>
+      </c>
+      <c r="D66" t="s">
+        <v>106</v>
+      </c>
+      <c r="E66" t="s">
         <v>291</v>
       </c>
-      <c r="C66" t="s">
-        <v>286</v>
-      </c>
-      <c r="D66" t="s">
-        <v>287</v>
-      </c>
-      <c r="E66" t="s">
+      <c r="F66" t="s">
+        <v>39</v>
+      </c>
+      <c r="G66" t="s">
         <v>292</v>
-      </c>
-      <c r="F66" t="s">
-        <v>24</v>
-      </c>
-      <c r="G66" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="67" spans="1:7">
       <c r="A67" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="B67" t="s">
         <v>294</v>
       </c>
-      <c r="B67" t="s">
+      <c r="C67" t="s">
+        <v>91</v>
+      </c>
+      <c r="D67" t="s">
+        <v>92</v>
+      </c>
+      <c r="E67" t="s">
         <v>295</v>
       </c>
-      <c r="C67" t="s">
-        <v>286</v>
-      </c>
-      <c r="D67" t="s">
-        <v>287</v>
-      </c>
-      <c r="E67" t="s">
+      <c r="F67" t="s">
+        <v>39</v>
+      </c>
+      <c r="G67" t="s">
         <v>296</v>
-      </c>
-      <c r="F67" t="s">
-        <v>12</v>
-      </c>
-      <c r="G67" t="s">
-        <v>297</v>
       </c>
     </row>
     <row r="68" spans="1:7">
       <c r="A68" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="B68" t="s">
         <v>298</v>
       </c>
-      <c r="B68" t="s">
+      <c r="C68" t="s">
+        <v>79</v>
+      </c>
+      <c r="D68" t="s">
+        <v>80</v>
+      </c>
+      <c r="E68" t="s">
         <v>299</v>
       </c>
-      <c r="C68" t="s">
-        <v>286</v>
-      </c>
-      <c r="D68" t="s">
-        <v>287</v>
-      </c>
-      <c r="E68" t="s">
+      <c r="F68" t="s">
+        <v>119</v>
+      </c>
+      <c r="G68" t="s">
         <v>300</v>
-      </c>
-      <c r="F68" t="s">
-        <v>33</v>
-      </c>
-      <c r="G68" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="69" spans="1:7">
       <c r="A69" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="B69" t="s">
         <v>302</v>
       </c>
-      <c r="B69" t="s">
+      <c r="C69" t="s">
+        <v>105</v>
+      </c>
+      <c r="D69" t="s">
+        <v>106</v>
+      </c>
+      <c r="E69" t="s">
         <v>303</v>
       </c>
-      <c r="C69" t="s">
-        <v>286</v>
-      </c>
-      <c r="D69" t="s">
-        <v>287</v>
-      </c>
-      <c r="E69" t="s">
-        <v>304</v>
-      </c>
       <c r="F69" t="s">
-        <v>305</v>
+        <v>31</v>
       </c>
       <c r="G69" t="s">
-        <v>306</v>
+        <v>31</v>
       </c>
     </row>
     <row r="70" spans="1:7">
       <c r="A70" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="B70" t="s">
+        <v>305</v>
+      </c>
+      <c r="C70" t="s">
+        <v>91</v>
+      </c>
+      <c r="D70" t="s">
+        <v>92</v>
+      </c>
+      <c r="E70" t="s">
+        <v>306</v>
+      </c>
+      <c r="F70" t="s">
         <v>307</v>
       </c>
-      <c r="B70" t="s">
+      <c r="G70" t="s">
         <v>308</v>
-      </c>
-      <c r="C70" t="s">
-        <v>286</v>
-      </c>
-      <c r="D70" t="s">
-        <v>287</v>
-      </c>
-      <c r="E70" t="s">
-        <v>309</v>
-      </c>
-      <c r="F70" t="s">
-        <v>24</v>
-      </c>
-      <c r="G70" t="s">
-        <v>310</v>
       </c>
     </row>
     <row r="71" spans="1:7">
       <c r="A71" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="B71" t="s">
+        <v>310</v>
+      </c>
+      <c r="C71" t="s">
+        <v>21</v>
+      </c>
+      <c r="D71" t="s">
+        <v>22</v>
+      </c>
+      <c r="E71" t="s">
         <v>311</v>
       </c>
-      <c r="B71" t="s">
+      <c r="F71" t="s">
         <v>312</v>
       </c>
-      <c r="C71" t="s">
-        <v>286</v>
-      </c>
-      <c r="D71" t="s">
-        <v>287</v>
-      </c>
-      <c r="E71" t="s">
+      <c r="G71" t="s">
         <v>313</v>
-      </c>
-      <c r="F71" t="s">
-        <v>24</v>
-      </c>
-      <c r="G71" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="72" spans="1:7">
       <c r="A72" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="B72" t="s">
         <v>315</v>
       </c>
-      <c r="B72" t="s">
+      <c r="C72" t="s">
+        <v>240</v>
+      </c>
+      <c r="D72" t="s">
         <v>316</v>
-      </c>
-      <c r="C72" t="s">
-        <v>286</v>
-      </c>
-      <c r="D72" t="s">
-        <v>287</v>
       </c>
       <c r="E72" t="s">
         <v>317</v>
       </c>
       <c r="F72" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="G72" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -5000,19 +4943,19 @@
         <v>319</v>
       </c>
       <c r="C73" t="s">
-        <v>286</v>
+        <v>240</v>
       </c>
       <c r="D73" t="s">
-        <v>287</v>
+        <v>320</v>
       </c>
       <c r="E73" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F73" t="s">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="G73" t="s">
-        <v>321</v>
+        <v>31</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -5023,42 +4966,42 @@
         <v>323</v>
       </c>
       <c r="C74" t="s">
-        <v>286</v>
+        <v>85</v>
       </c>
       <c r="D74" t="s">
-        <v>287</v>
+        <v>86</v>
       </c>
       <c r="E74" t="s">
         <v>324</v>
       </c>
       <c r="F74" t="s">
-        <v>124</v>
+        <v>325</v>
       </c>
       <c r="G74" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="75" spans="1:7">
       <c r="A75" s="2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B75" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C75" t="s">
-        <v>286</v>
+        <v>240</v>
       </c>
       <c r="D75" t="s">
-        <v>287</v>
+        <v>320</v>
       </c>
       <c r="E75" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F75" t="s">
-        <v>57</v>
+        <v>31</v>
       </c>
       <c r="G75" t="s">
-        <v>329</v>
+        <v>31</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -5069,19 +5012,19 @@
         <v>331</v>
       </c>
       <c r="C76" t="s">
-        <v>286</v>
+        <v>85</v>
       </c>
       <c r="D76" t="s">
-        <v>287</v>
+        <v>86</v>
       </c>
       <c r="E76" t="s">
         <v>332</v>
       </c>
       <c r="F76" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="G76" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -5092,42 +5035,42 @@
         <v>334</v>
       </c>
       <c r="C77" t="s">
-        <v>286</v>
+        <v>85</v>
       </c>
       <c r="D77" t="s">
-        <v>287</v>
+        <v>86</v>
       </c>
       <c r="E77" t="s">
         <v>335</v>
       </c>
       <c r="F77" t="s">
-        <v>336</v>
+        <v>31</v>
       </c>
       <c r="G77" t="s">
-        <v>337</v>
+        <v>31</v>
       </c>
     </row>
     <row r="78" spans="1:7">
       <c r="A78" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="B78" t="s">
+        <v>337</v>
+      </c>
+      <c r="C78" t="s">
+        <v>85</v>
+      </c>
+      <c r="D78" t="s">
+        <v>86</v>
+      </c>
+      <c r="E78" t="s">
         <v>338</v>
       </c>
-      <c r="B78" t="s">
+      <c r="F78" t="s">
         <v>339</v>
       </c>
-      <c r="C78" t="s">
-        <v>286</v>
-      </c>
-      <c r="D78" t="s">
-        <v>287</v>
-      </c>
-      <c r="E78" t="s">
+      <c r="G78" t="s">
         <v>340</v>
-      </c>
-      <c r="F78" t="s">
-        <v>13</v>
-      </c>
-      <c r="G78" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -5138,16 +5081,16 @@
         <v>342</v>
       </c>
       <c r="C79" t="s">
-        <v>286</v>
+        <v>111</v>
       </c>
       <c r="D79" t="s">
-        <v>287</v>
+        <v>112</v>
       </c>
       <c r="E79" t="s">
         <v>343</v>
       </c>
       <c r="F79" t="s">
-        <v>57</v>
+        <v>342</v>
       </c>
       <c r="G79" t="s">
         <v>344</v>
@@ -5161,108 +5104,108 @@
         <v>346</v>
       </c>
       <c r="C80" t="s">
-        <v>286</v>
+        <v>240</v>
       </c>
       <c r="D80" t="s">
-        <v>287</v>
+        <v>347</v>
       </c>
       <c r="E80" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F80" t="s">
-        <v>156</v>
+        <v>17</v>
       </c>
       <c r="G80" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="81" spans="1:7">
       <c r="A81" s="2" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B81" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C81" t="s">
-        <v>286</v>
+        <v>105</v>
       </c>
       <c r="D81" t="s">
-        <v>287</v>
+        <v>106</v>
       </c>
       <c r="E81" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F81" t="s">
-        <v>12</v>
+        <v>136</v>
       </c>
       <c r="G81" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="82" spans="1:7">
       <c r="A82" s="2" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B82" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C82" t="s">
-        <v>286</v>
+        <v>74</v>
       </c>
       <c r="D82" t="s">
-        <v>287</v>
+        <v>73</v>
       </c>
       <c r="E82" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="F82" t="s">
-        <v>355</v>
+        <v>119</v>
       </c>
       <c r="G82" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="83" spans="1:7">
       <c r="A83" s="2" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B83" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C83" t="s">
-        <v>359</v>
+        <v>91</v>
       </c>
       <c r="D83" t="s">
+        <v>92</v>
+      </c>
+      <c r="E83" t="s">
         <v>360</v>
       </c>
-      <c r="E83" t="s">
+      <c r="F83" t="s">
+        <v>12</v>
+      </c>
+      <c r="G83" t="s">
         <v>361</v>
-      </c>
-      <c r="F83" t="s">
-        <v>156</v>
-      </c>
-      <c r="G83" t="s">
-        <v>362</v>
       </c>
     </row>
     <row r="84" spans="1:7">
       <c r="A84" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="B84" t="s">
         <v>363</v>
       </c>
-      <c r="B84" t="s">
+      <c r="C84" t="s">
+        <v>9</v>
+      </c>
+      <c r="D84" t="s">
+        <v>10</v>
+      </c>
+      <c r="E84" t="s">
         <v>364</v>
       </c>
-      <c r="C84" t="s">
-        <v>359</v>
-      </c>
-      <c r="D84" t="s">
-        <v>360</v>
-      </c>
-      <c r="E84" t="s">
+      <c r="F84" t="s">
         <v>365</v>
-      </c>
-      <c r="F84" t="s">
-        <v>124</v>
       </c>
       <c r="G84" t="s">
         <v>366</v>
@@ -5276,16 +5219,16 @@
         <v>368</v>
       </c>
       <c r="C85" t="s">
-        <v>359</v>
+        <v>91</v>
       </c>
       <c r="D85" t="s">
-        <v>360</v>
+        <v>92</v>
       </c>
       <c r="E85" t="s">
         <v>369</v>
       </c>
       <c r="F85" t="s">
-        <v>12</v>
+        <v>365</v>
       </c>
       <c r="G85" t="s">
         <v>370</v>
@@ -5299,16 +5242,16 @@
         <v>372</v>
       </c>
       <c r="C86" t="s">
-        <v>359</v>
+        <v>68</v>
       </c>
       <c r="D86" t="s">
-        <v>360</v>
+        <v>69</v>
       </c>
       <c r="E86" t="s">
         <v>373</v>
       </c>
       <c r="F86" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="G86" t="s">
         <v>374</v>
@@ -5322,2215 +5265,2163 @@
         <v>376</v>
       </c>
       <c r="C87" t="s">
-        <v>359</v>
+        <v>74</v>
       </c>
       <c r="D87" t="s">
-        <v>360</v>
+        <v>73</v>
       </c>
       <c r="E87" t="s">
         <v>377</v>
       </c>
       <c r="F87" t="s">
+        <v>12</v>
+      </c>
+      <c r="G87" t="s">
         <v>378</v>
-      </c>
-      <c r="G87" t="s">
-        <v>379</v>
       </c>
     </row>
     <row r="88" spans="1:7">
       <c r="A88" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="B88" t="s">
         <v>380</v>
       </c>
-      <c r="B88" t="s">
+      <c r="C88" t="s">
+        <v>28</v>
+      </c>
+      <c r="D88" t="s">
+        <v>29</v>
+      </c>
+      <c r="E88" t="s">
         <v>381</v>
       </c>
-      <c r="C88" t="s">
-        <v>359</v>
-      </c>
-      <c r="D88" t="s">
-        <v>360</v>
-      </c>
-      <c r="E88" t="s">
-        <v>382</v>
-      </c>
       <c r="F88" t="s">
-        <v>381</v>
+        <v>31</v>
       </c>
       <c r="G88" t="s">
-        <v>383</v>
+        <v>31</v>
       </c>
     </row>
     <row r="89" spans="1:7">
       <c r="A89" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="B89" t="s">
+        <v>383</v>
+      </c>
+      <c r="C89" t="s">
+        <v>28</v>
+      </c>
+      <c r="D89" t="s">
+        <v>29</v>
+      </c>
+      <c r="E89" t="s">
         <v>384</v>
       </c>
-      <c r="B89" t="s">
-        <v>385</v>
-      </c>
-      <c r="C89" t="s">
-        <v>359</v>
-      </c>
-      <c r="D89" t="s">
-        <v>360</v>
-      </c>
-      <c r="E89" t="s">
-        <v>386</v>
-      </c>
       <c r="F89" t="s">
-        <v>129</v>
+        <v>31</v>
       </c>
       <c r="G89" t="s">
-        <v>387</v>
+        <v>31</v>
       </c>
     </row>
     <row r="90" spans="1:7">
       <c r="A90" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="B90" t="s">
+        <v>386</v>
+      </c>
+      <c r="C90" t="s">
+        <v>240</v>
+      </c>
+      <c r="D90" t="s">
+        <v>347</v>
+      </c>
+      <c r="E90" t="s">
+        <v>387</v>
+      </c>
+      <c r="F90" t="s">
+        <v>12</v>
+      </c>
+      <c r="G90" t="s">
         <v>388</v>
-      </c>
-      <c r="B90" t="s">
-        <v>389</v>
-      </c>
-      <c r="C90" t="s">
-        <v>359</v>
-      </c>
-      <c r="D90" t="s">
-        <v>360</v>
-      </c>
-      <c r="E90" t="s">
-        <v>390</v>
-      </c>
-      <c r="F90" t="s">
-        <v>391</v>
-      </c>
-      <c r="G90" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="91" spans="1:7">
       <c r="A91" s="2" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="B91" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="C91" t="s">
-        <v>359</v>
+        <v>9</v>
       </c>
       <c r="D91" t="s">
-        <v>360</v>
+        <v>10</v>
       </c>
       <c r="E91" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="F91" t="s">
-        <v>57</v>
+        <v>212</v>
       </c>
       <c r="G91" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
     </row>
     <row r="92" spans="1:7">
       <c r="A92" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="B92" t="s">
+        <v>394</v>
+      </c>
+      <c r="C92" t="s">
+        <v>68</v>
+      </c>
+      <c r="D92" t="s">
+        <v>69</v>
+      </c>
+      <c r="E92" t="s">
+        <v>395</v>
+      </c>
+      <c r="F92" t="s">
+        <v>396</v>
+      </c>
+      <c r="G92" t="s">
         <v>397</v>
-      </c>
-      <c r="B92" t="s">
-        <v>398</v>
-      </c>
-      <c r="C92" t="s">
-        <v>359</v>
-      </c>
-      <c r="D92" t="s">
-        <v>360</v>
-      </c>
-      <c r="E92" t="s">
-        <v>399</v>
-      </c>
-      <c r="F92" t="s">
-        <v>129</v>
-      </c>
-      <c r="G92" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="93" spans="1:7">
       <c r="A93" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="B93" t="s">
+        <v>399</v>
+      </c>
+      <c r="C93" t="s">
+        <v>105</v>
+      </c>
+      <c r="D93" t="s">
+        <v>106</v>
+      </c>
+      <c r="E93" t="s">
+        <v>400</v>
+      </c>
+      <c r="F93" t="s">
+        <v>119</v>
+      </c>
+      <c r="G93" t="s">
         <v>401</v>
-      </c>
-      <c r="B93" t="s">
-        <v>402</v>
-      </c>
-      <c r="C93" t="s">
-        <v>359</v>
-      </c>
-      <c r="D93" t="s">
-        <v>360</v>
-      </c>
-      <c r="E93" t="s">
-        <v>403</v>
-      </c>
-      <c r="F93" t="s">
-        <v>404</v>
-      </c>
-      <c r="G93" t="s">
-        <v>405</v>
       </c>
     </row>
     <row r="94" spans="1:7">
       <c r="A94" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="B94" t="s">
+        <v>403</v>
+      </c>
+      <c r="C94" t="s">
+        <v>79</v>
+      </c>
+      <c r="D94" t="s">
+        <v>80</v>
+      </c>
+      <c r="E94" t="s">
+        <v>404</v>
+      </c>
+      <c r="F94" t="s">
+        <v>405</v>
+      </c>
+      <c r="G94" t="s">
         <v>406</v>
-      </c>
-      <c r="B94" t="s">
-        <v>407</v>
-      </c>
-      <c r="C94" t="s">
-        <v>359</v>
-      </c>
-      <c r="D94" t="s">
-        <v>360</v>
-      </c>
-      <c r="E94" t="s">
-        <v>408</v>
-      </c>
-      <c r="F94" t="s">
-        <v>138</v>
-      </c>
-      <c r="G94" t="s">
-        <v>409</v>
       </c>
     </row>
     <row r="95" spans="1:7">
       <c r="A95" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="B95" t="s">
+        <v>408</v>
+      </c>
+      <c r="C95" t="s">
+        <v>91</v>
+      </c>
+      <c r="D95" t="s">
+        <v>92</v>
+      </c>
+      <c r="E95" t="s">
+        <v>409</v>
+      </c>
+      <c r="F95" t="s">
+        <v>39</v>
+      </c>
+      <c r="G95" t="s">
         <v>410</v>
-      </c>
-      <c r="B95" t="s">
-        <v>411</v>
-      </c>
-      <c r="C95" t="s">
-        <v>359</v>
-      </c>
-      <c r="D95" t="s">
-        <v>360</v>
-      </c>
-      <c r="E95" t="s">
-        <v>412</v>
-      </c>
-      <c r="F95" t="s">
-        <v>151</v>
-      </c>
-      <c r="G95" t="s">
-        <v>413</v>
       </c>
     </row>
     <row r="96" spans="1:7">
       <c r="A96" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="B96" t="s">
+        <v>412</v>
+      </c>
+      <c r="C96" t="s">
+        <v>85</v>
+      </c>
+      <c r="D96" t="s">
+        <v>86</v>
+      </c>
+      <c r="E96" t="s">
+        <v>413</v>
+      </c>
+      <c r="F96" t="s">
+        <v>413</v>
+      </c>
+      <c r="G96" t="s">
         <v>414</v>
-      </c>
-      <c r="B96" t="s">
-        <v>415</v>
-      </c>
-      <c r="C96" t="s">
-        <v>359</v>
-      </c>
-      <c r="D96" t="s">
-        <v>360</v>
-      </c>
-      <c r="E96" t="s">
-        <v>416</v>
-      </c>
-      <c r="F96" t="s">
-        <v>24</v>
-      </c>
-      <c r="G96" t="s">
-        <v>417</v>
       </c>
     </row>
     <row r="97" spans="1:7">
       <c r="A97" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="B97" t="s">
+        <v>416</v>
+      </c>
+      <c r="C97" t="s">
+        <v>111</v>
+      </c>
+      <c r="D97" t="s">
+        <v>112</v>
+      </c>
+      <c r="E97" t="s">
+        <v>417</v>
+      </c>
+      <c r="F97" t="s">
+        <v>365</v>
+      </c>
+      <c r="G97" t="s">
         <v>418</v>
-      </c>
-      <c r="B97" t="s">
-        <v>419</v>
-      </c>
-      <c r="C97" t="s">
-        <v>420</v>
-      </c>
-      <c r="D97" t="s">
-        <v>421</v>
-      </c>
-      <c r="E97" t="s">
-        <v>422</v>
-      </c>
-      <c r="F97" t="s">
-        <v>33</v>
-      </c>
-      <c r="G97" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="98" spans="1:7">
       <c r="A98" s="2" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="B98" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="C98" t="s">
-        <v>420</v>
+        <v>91</v>
       </c>
       <c r="D98" t="s">
+        <v>92</v>
+      </c>
+      <c r="E98" t="s">
         <v>421</v>
       </c>
-      <c r="E98" t="s">
-        <v>426</v>
-      </c>
       <c r="F98" t="s">
-        <v>12</v>
+        <v>365</v>
       </c>
       <c r="G98" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
     </row>
     <row r="99" spans="1:7">
       <c r="A99" s="2" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="B99" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="C99" t="s">
-        <v>420</v>
+        <v>111</v>
       </c>
       <c r="D99" t="s">
-        <v>421</v>
+        <v>112</v>
       </c>
       <c r="E99" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="F99" t="s">
-        <v>156</v>
+        <v>426</v>
       </c>
       <c r="G99" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="100" spans="1:7">
       <c r="A100" s="2" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="B100" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="C100" t="s">
-        <v>420</v>
+        <v>79</v>
       </c>
       <c r="D100" t="s">
-        <v>421</v>
+        <v>80</v>
       </c>
       <c r="E100" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="F100" t="s">
-        <v>24</v>
+        <v>365</v>
       </c>
       <c r="G100" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
     </row>
     <row r="101" spans="1:7">
       <c r="A101" s="2" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="B101" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="C101" t="s">
-        <v>420</v>
+        <v>240</v>
       </c>
       <c r="D101" t="s">
-        <v>421</v>
+        <v>316</v>
       </c>
       <c r="E101" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="F101" t="s">
-        <v>439</v>
+        <v>31</v>
       </c>
       <c r="G101" t="s">
-        <v>440</v>
+        <v>31</v>
       </c>
     </row>
     <row r="102" spans="1:7">
       <c r="A102" s="2" t="s">
-        <v>441</v>
+        <v>435</v>
       </c>
       <c r="B102" t="s">
-        <v>442</v>
+        <v>436</v>
       </c>
       <c r="C102" t="s">
-        <v>420</v>
+        <v>105</v>
       </c>
       <c r="D102" t="s">
-        <v>421</v>
+        <v>106</v>
       </c>
       <c r="E102" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="F102" t="s">
-        <v>124</v>
+        <v>396</v>
       </c>
       <c r="G102" t="s">
-        <v>444</v>
+        <v>438</v>
       </c>
     </row>
     <row r="103" spans="1:7">
       <c r="A103" s="2" t="s">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="B103" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="C103" t="s">
-        <v>420</v>
+        <v>105</v>
       </c>
       <c r="D103" t="s">
-        <v>421</v>
+        <v>106</v>
       </c>
       <c r="E103" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="F103" t="s">
-        <v>169</v>
+        <v>31</v>
       </c>
       <c r="G103" t="s">
-        <v>448</v>
+        <v>31</v>
       </c>
     </row>
     <row r="104" spans="1:7">
       <c r="A104" s="2" t="s">
-        <v>449</v>
+        <v>442</v>
       </c>
       <c r="B104" t="s">
-        <v>450</v>
+        <v>443</v>
       </c>
       <c r="C104" t="s">
-        <v>420</v>
+        <v>68</v>
       </c>
       <c r="D104" t="s">
-        <v>421</v>
+        <v>69</v>
       </c>
       <c r="E104" t="s">
-        <v>451</v>
+        <v>444</v>
       </c>
       <c r="F104" t="s">
-        <v>129</v>
+        <v>39</v>
       </c>
       <c r="G104" t="s">
-        <v>452</v>
+        <v>445</v>
       </c>
     </row>
     <row r="105" spans="1:7">
       <c r="A105" s="2" t="s">
-        <v>453</v>
+        <v>446</v>
       </c>
       <c r="B105" t="s">
-        <v>454</v>
+        <v>447</v>
       </c>
       <c r="C105" t="s">
-        <v>420</v>
+        <v>91</v>
       </c>
       <c r="D105" t="s">
-        <v>421</v>
+        <v>92</v>
       </c>
       <c r="E105" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="F105" t="s">
-        <v>456</v>
+        <v>449</v>
       </c>
       <c r="G105" t="s">
-        <v>457</v>
+        <v>450</v>
       </c>
     </row>
     <row r="106" spans="1:7">
       <c r="A106" s="2" t="s">
-        <v>458</v>
+        <v>451</v>
       </c>
       <c r="B106" t="s">
-        <v>459</v>
+        <v>452</v>
       </c>
       <c r="C106" t="s">
-        <v>420</v>
+        <v>105</v>
       </c>
       <c r="D106" t="s">
-        <v>421</v>
+        <v>106</v>
       </c>
       <c r="E106" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="F106" t="s">
-        <v>461</v>
+        <v>454</v>
       </c>
       <c r="G106" t="s">
-        <v>462</v>
+        <v>455</v>
       </c>
     </row>
     <row r="107" spans="1:7">
       <c r="A107" s="2" t="s">
-        <v>463</v>
+        <v>456</v>
       </c>
       <c r="B107" t="s">
-        <v>464</v>
+        <v>457</v>
       </c>
       <c r="C107" t="s">
-        <v>420</v>
+        <v>91</v>
       </c>
       <c r="D107" t="s">
-        <v>421</v>
+        <v>92</v>
       </c>
       <c r="E107" t="s">
-        <v>465</v>
+        <v>458</v>
       </c>
       <c r="F107" t="s">
-        <v>52</v>
+        <v>459</v>
       </c>
       <c r="G107" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
     </row>
     <row r="108" spans="1:7">
       <c r="A108" s="2" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="B108" t="s">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="C108" t="s">
-        <v>469</v>
+        <v>105</v>
       </c>
       <c r="D108" t="s">
-        <v>470</v>
+        <v>106</v>
       </c>
       <c r="E108" t="s">
-        <v>471</v>
+        <v>463</v>
       </c>
       <c r="F108" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="G108" t="s">
-        <v>472</v>
+        <v>31</v>
       </c>
     </row>
     <row r="109" spans="1:7">
       <c r="A109" s="2" t="s">
-        <v>473</v>
+        <v>464</v>
       </c>
       <c r="B109" t="s">
-        <v>474</v>
+        <v>465</v>
       </c>
       <c r="C109" t="s">
-        <v>469</v>
+        <v>91</v>
       </c>
       <c r="D109" t="s">
-        <v>470</v>
+        <v>92</v>
       </c>
       <c r="E109" t="s">
-        <v>475</v>
+        <v>466</v>
       </c>
       <c r="F109" t="s">
-        <v>12</v>
+        <v>212</v>
       </c>
       <c r="G109" t="s">
-        <v>476</v>
+        <v>467</v>
       </c>
     </row>
     <row r="110" spans="1:7">
       <c r="A110" s="2" t="s">
-        <v>477</v>
+        <v>468</v>
       </c>
       <c r="B110" t="s">
-        <v>478</v>
+        <v>469</v>
       </c>
       <c r="C110" t="s">
-        <v>469</v>
+        <v>74</v>
       </c>
       <c r="D110" t="s">
+        <v>73</v>
+      </c>
+      <c r="E110" t="s">
         <v>470</v>
       </c>
-      <c r="E110" t="s">
-        <v>479</v>
-      </c>
       <c r="F110" t="s">
-        <v>156</v>
+        <v>471</v>
       </c>
       <c r="G110" t="s">
-        <v>480</v>
+        <v>472</v>
       </c>
     </row>
     <row r="111" spans="1:7">
       <c r="A111" s="2" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="B111" t="s">
-        <v>482</v>
+        <v>474</v>
       </c>
       <c r="C111" t="s">
-        <v>469</v>
+        <v>91</v>
       </c>
       <c r="D111" t="s">
-        <v>470</v>
+        <v>92</v>
       </c>
       <c r="E111" t="s">
-        <v>483</v>
+        <v>475</v>
       </c>
       <c r="F111" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="G111" t="s">
-        <v>484</v>
+        <v>476</v>
       </c>
     </row>
     <row r="112" spans="1:7">
       <c r="A112" s="2" t="s">
-        <v>485</v>
+        <v>477</v>
       </c>
       <c r="B112" t="s">
-        <v>486</v>
+        <v>478</v>
       </c>
       <c r="C112" t="s">
-        <v>469</v>
+        <v>68</v>
       </c>
       <c r="D112" t="s">
-        <v>470</v>
+        <v>69</v>
       </c>
       <c r="E112" t="s">
-        <v>487</v>
+        <v>479</v>
       </c>
       <c r="F112" t="s">
         <v>119</v>
       </c>
       <c r="G112" t="s">
-        <v>488</v>
+        <v>480</v>
       </c>
     </row>
     <row r="113" spans="1:7">
       <c r="A113" s="2" t="s">
-        <v>489</v>
+        <v>481</v>
       </c>
       <c r="B113" t="s">
-        <v>490</v>
+        <v>482</v>
       </c>
       <c r="C113" t="s">
-        <v>469</v>
+        <v>91</v>
       </c>
       <c r="D113" t="s">
-        <v>470</v>
+        <v>92</v>
       </c>
       <c r="E113" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="F113" t="s">
         <v>119</v>
       </c>
       <c r="G113" t="s">
-        <v>492</v>
+        <v>484</v>
       </c>
     </row>
     <row r="114" spans="1:7">
       <c r="A114" s="2" t="s">
-        <v>493</v>
+        <v>485</v>
       </c>
       <c r="B114" t="s">
-        <v>494</v>
+        <v>486</v>
       </c>
       <c r="C114" t="s">
-        <v>469</v>
+        <v>79</v>
       </c>
       <c r="D114" t="s">
-        <v>470</v>
+        <v>80</v>
       </c>
       <c r="E114" t="s">
-        <v>495</v>
+        <v>487</v>
       </c>
       <c r="F114" t="s">
-        <v>33</v>
+        <v>488</v>
       </c>
       <c r="G114" t="s">
-        <v>496</v>
+        <v>489</v>
       </c>
     </row>
     <row r="115" spans="1:7">
       <c r="A115" s="2" t="s">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="B115" t="s">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="C115" t="s">
-        <v>469</v>
+        <v>79</v>
       </c>
       <c r="D115" t="s">
-        <v>470</v>
+        <v>80</v>
       </c>
       <c r="E115" t="s">
-        <v>499</v>
+        <v>492</v>
       </c>
       <c r="F115" t="s">
-        <v>57</v>
+        <v>493</v>
       </c>
       <c r="G115" t="s">
-        <v>500</v>
+        <v>494</v>
       </c>
     </row>
     <row r="116" spans="1:7">
       <c r="A116" s="2" t="s">
-        <v>501</v>
+        <v>495</v>
       </c>
       <c r="B116" t="s">
-        <v>502</v>
+        <v>496</v>
       </c>
       <c r="C116" t="s">
-        <v>469</v>
+        <v>74</v>
       </c>
       <c r="D116" t="s">
-        <v>470</v>
+        <v>73</v>
       </c>
       <c r="E116" t="s">
-        <v>503</v>
+        <v>497</v>
       </c>
       <c r="F116" t="s">
-        <v>24</v>
+        <v>365</v>
       </c>
       <c r="G116" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
     </row>
     <row r="117" spans="1:7">
       <c r="A117" s="2" t="s">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="B117" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="C117" t="s">
-        <v>469</v>
+        <v>85</v>
       </c>
       <c r="D117" t="s">
-        <v>470</v>
+        <v>86</v>
       </c>
       <c r="E117" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
       <c r="F117" t="s">
-        <v>124</v>
+        <v>365</v>
       </c>
       <c r="G117" t="s">
-        <v>508</v>
+        <v>502</v>
       </c>
     </row>
     <row r="118" spans="1:7">
       <c r="A118" s="2" t="s">
-        <v>509</v>
+        <v>503</v>
       </c>
       <c r="B118" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="C118" t="s">
-        <v>469</v>
+        <v>111</v>
       </c>
       <c r="D118" t="s">
-        <v>470</v>
+        <v>112</v>
       </c>
       <c r="E118" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="F118" t="s">
-        <v>57</v>
+        <v>396</v>
       </c>
       <c r="G118" t="s">
-        <v>512</v>
+        <v>506</v>
       </c>
     </row>
     <row r="119" spans="1:7">
       <c r="A119" s="2" t="s">
-        <v>513</v>
+        <v>507</v>
       </c>
       <c r="B119" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="C119" t="s">
-        <v>469</v>
+        <v>91</v>
       </c>
       <c r="D119" t="s">
-        <v>470</v>
+        <v>92</v>
       </c>
       <c r="E119" t="s">
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="F119" t="s">
-        <v>24</v>
+        <v>396</v>
       </c>
       <c r="G119" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
     </row>
     <row r="120" spans="1:7">
       <c r="A120" s="2" t="s">
-        <v>517</v>
+        <v>511</v>
       </c>
       <c r="B120" t="s">
-        <v>518</v>
+        <v>512</v>
       </c>
       <c r="C120" t="s">
-        <v>469</v>
+        <v>105</v>
       </c>
       <c r="D120" t="s">
-        <v>470</v>
+        <v>106</v>
       </c>
       <c r="E120" t="s">
-        <v>519</v>
+        <v>513</v>
       </c>
       <c r="F120" t="s">
-        <v>138</v>
+        <v>396</v>
       </c>
       <c r="G120" t="s">
-        <v>520</v>
+        <v>514</v>
       </c>
     </row>
     <row r="121" spans="1:7">
       <c r="A121" s="2" t="s">
-        <v>521</v>
+        <v>515</v>
       </c>
       <c r="B121" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="C121" t="s">
-        <v>469</v>
+        <v>91</v>
       </c>
       <c r="D121" t="s">
-        <v>470</v>
+        <v>92</v>
       </c>
       <c r="E121" t="s">
-        <v>523</v>
+        <v>517</v>
       </c>
       <c r="F121" t="s">
-        <v>52</v>
+        <v>136</v>
       </c>
       <c r="G121" t="s">
-        <v>524</v>
+        <v>518</v>
       </c>
     </row>
     <row r="122" spans="1:7">
       <c r="A122" s="2" t="s">
-        <v>525</v>
+        <v>519</v>
       </c>
       <c r="B122" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="C122" t="s">
-        <v>469</v>
+        <v>9</v>
       </c>
       <c r="D122" t="s">
-        <v>470</v>
+        <v>10</v>
       </c>
       <c r="E122" t="s">
-        <v>527</v>
+        <v>521</v>
       </c>
       <c r="F122" t="s">
-        <v>52</v>
+        <v>449</v>
       </c>
       <c r="G122" t="s">
-        <v>528</v>
+        <v>522</v>
       </c>
     </row>
     <row r="123" spans="1:7">
       <c r="A123" s="2" t="s">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="B123" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="C123" t="s">
-        <v>469</v>
+        <v>91</v>
       </c>
       <c r="D123" t="s">
-        <v>470</v>
+        <v>92</v>
       </c>
       <c r="E123" t="s">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="F123" t="s">
-        <v>151</v>
+        <v>255</v>
       </c>
       <c r="G123" t="s">
-        <v>532</v>
+        <v>526</v>
       </c>
     </row>
     <row r="124" spans="1:7">
       <c r="A124" s="2" t="s">
-        <v>533</v>
+        <v>527</v>
       </c>
       <c r="B124" t="s">
-        <v>534</v>
+        <v>528</v>
       </c>
       <c r="C124" t="s">
-        <v>535</v>
+        <v>9</v>
       </c>
       <c r="D124" t="s">
-        <v>534</v>
+        <v>10</v>
       </c>
       <c r="E124" t="s">
-        <v>536</v>
+        <v>529</v>
       </c>
       <c r="F124" t="s">
-        <v>12</v>
+        <v>449</v>
       </c>
       <c r="G124" t="s">
-        <v>537</v>
+        <v>530</v>
       </c>
     </row>
     <row r="125" spans="1:7">
       <c r="A125" s="2" t="s">
-        <v>538</v>
+        <v>531</v>
       </c>
       <c r="B125" t="s">
-        <v>539</v>
+        <v>532</v>
       </c>
       <c r="C125" t="s">
-        <v>535</v>
+        <v>105</v>
       </c>
       <c r="D125" t="s">
+        <v>106</v>
+      </c>
+      <c r="E125" t="s">
+        <v>533</v>
+      </c>
+      <c r="F125" t="s">
+        <v>114</v>
+      </c>
+      <c r="G125" t="s">
         <v>534</v>
-      </c>
-      <c r="E125" t="s">
-        <v>540</v>
-      </c>
-      <c r="F125" t="s">
-        <v>12</v>
-      </c>
-      <c r="G125" t="s">
-        <v>541</v>
       </c>
     </row>
     <row r="126" spans="1:7">
       <c r="A126" s="2" t="s">
-        <v>542</v>
+        <v>535</v>
       </c>
       <c r="B126" t="s">
-        <v>543</v>
+        <v>536</v>
       </c>
       <c r="C126" t="s">
-        <v>535</v>
+        <v>105</v>
       </c>
       <c r="D126" t="s">
-        <v>534</v>
+        <v>106</v>
       </c>
       <c r="E126" t="s">
-        <v>544</v>
+        <v>537</v>
       </c>
       <c r="F126" t="s">
-        <v>156</v>
+        <v>17</v>
       </c>
       <c r="G126" t="s">
-        <v>545</v>
+        <v>538</v>
       </c>
     </row>
     <row r="127" spans="1:7">
       <c r="A127" s="2" t="s">
-        <v>546</v>
+        <v>539</v>
       </c>
       <c r="B127" t="s">
-        <v>547</v>
+        <v>540</v>
       </c>
       <c r="C127" t="s">
-        <v>535</v>
+        <v>9</v>
       </c>
       <c r="D127" t="s">
-        <v>534</v>
+        <v>10</v>
       </c>
       <c r="E127" t="s">
-        <v>548</v>
+        <v>541</v>
       </c>
       <c r="F127" t="s">
-        <v>549</v>
+        <v>365</v>
       </c>
       <c r="G127" t="s">
-        <v>550</v>
+        <v>542</v>
       </c>
     </row>
     <row r="128" spans="1:7">
       <c r="A128" s="2" t="s">
-        <v>551</v>
+        <v>543</v>
       </c>
       <c r="B128" t="s">
-        <v>19</v>
+        <v>544</v>
       </c>
       <c r="C128" t="s">
-        <v>535</v>
+        <v>105</v>
       </c>
       <c r="D128" t="s">
-        <v>534</v>
+        <v>106</v>
       </c>
       <c r="E128" t="s">
-        <v>552</v>
+        <v>545</v>
       </c>
       <c r="F128" t="s">
-        <v>24</v>
+        <v>545</v>
       </c>
       <c r="G128" t="s">
-        <v>553</v>
+        <v>546</v>
       </c>
     </row>
     <row r="129" spans="1:7">
       <c r="A129" s="2" t="s">
-        <v>554</v>
+        <v>547</v>
       </c>
       <c r="B129" t="s">
-        <v>555</v>
+        <v>548</v>
       </c>
       <c r="C129" t="s">
-        <v>535</v>
+        <v>74</v>
       </c>
       <c r="D129" t="s">
-        <v>534</v>
+        <v>73</v>
       </c>
       <c r="E129" t="s">
-        <v>556</v>
+        <v>549</v>
       </c>
       <c r="F129" t="s">
-        <v>124</v>
+        <v>212</v>
       </c>
       <c r="G129" t="s">
-        <v>557</v>
+        <v>550</v>
       </c>
     </row>
     <row r="130" spans="1:7">
       <c r="A130" s="2" t="s">
-        <v>558</v>
+        <v>551</v>
       </c>
       <c r="B130" t="s">
-        <v>559</v>
+        <v>552</v>
       </c>
       <c r="C130" t="s">
-        <v>535</v>
+        <v>111</v>
       </c>
       <c r="D130" t="s">
-        <v>534</v>
+        <v>112</v>
       </c>
       <c r="E130" t="s">
-        <v>560</v>
+        <v>553</v>
       </c>
       <c r="F130" t="s">
-        <v>124</v>
+        <v>365</v>
       </c>
       <c r="G130" t="s">
-        <v>561</v>
+        <v>554</v>
       </c>
     </row>
     <row r="131" spans="1:7">
       <c r="A131" s="2" t="s">
-        <v>562</v>
+        <v>555</v>
       </c>
       <c r="B131" t="s">
-        <v>563</v>
+        <v>556</v>
       </c>
       <c r="C131" t="s">
-        <v>535</v>
+        <v>74</v>
       </c>
       <c r="D131" t="s">
-        <v>534</v>
+        <v>73</v>
       </c>
       <c r="E131" t="s">
-        <v>564</v>
+        <v>557</v>
       </c>
       <c r="F131" t="s">
-        <v>33</v>
+        <v>136</v>
       </c>
       <c r="G131" t="s">
-        <v>565</v>
+        <v>558</v>
       </c>
     </row>
     <row r="132" spans="1:7">
       <c r="A132" s="2" t="s">
-        <v>566</v>
+        <v>559</v>
       </c>
       <c r="B132" t="s">
-        <v>567</v>
+        <v>560</v>
       </c>
       <c r="C132" t="s">
-        <v>535</v>
+        <v>9</v>
       </c>
       <c r="D132" t="s">
-        <v>534</v>
+        <v>10</v>
       </c>
       <c r="E132" t="s">
-        <v>568</v>
+        <v>561</v>
       </c>
       <c r="F132" t="s">
-        <v>569</v>
+        <v>312</v>
       </c>
       <c r="G132" t="s">
-        <v>570</v>
+        <v>562</v>
       </c>
     </row>
     <row r="133" spans="1:7">
       <c r="A133" s="2" t="s">
-        <v>571</v>
+        <v>563</v>
       </c>
       <c r="B133" t="s">
-        <v>572</v>
+        <v>564</v>
       </c>
       <c r="C133" t="s">
-        <v>535</v>
+        <v>111</v>
       </c>
       <c r="D133" t="s">
-        <v>534</v>
+        <v>112</v>
       </c>
       <c r="E133" t="s">
-        <v>573</v>
+        <v>565</v>
       </c>
       <c r="F133" t="s">
-        <v>129</v>
+        <v>566</v>
       </c>
       <c r="G133" t="s">
-        <v>574</v>
+        <v>567</v>
       </c>
     </row>
     <row r="134" spans="1:7">
       <c r="A134" s="2" t="s">
-        <v>575</v>
+        <v>568</v>
       </c>
       <c r="B134" t="s">
-        <v>576</v>
+        <v>569</v>
       </c>
       <c r="C134" t="s">
-        <v>535</v>
+        <v>9</v>
       </c>
       <c r="D134" t="s">
-        <v>534</v>
+        <v>10</v>
       </c>
       <c r="E134" t="s">
-        <v>577</v>
+        <v>570</v>
       </c>
       <c r="F134" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="G134" t="s">
-        <v>578</v>
+        <v>571</v>
       </c>
     </row>
     <row r="135" spans="1:7">
       <c r="A135" s="2" t="s">
-        <v>579</v>
+        <v>572</v>
       </c>
       <c r="B135" t="s">
-        <v>580</v>
+        <v>573</v>
       </c>
       <c r="C135" t="s">
-        <v>535</v>
+        <v>74</v>
       </c>
       <c r="D135" t="s">
-        <v>534</v>
+        <v>73</v>
       </c>
       <c r="E135" t="s">
-        <v>581</v>
+        <v>574</v>
       </c>
       <c r="F135" t="s">
-        <v>52</v>
+        <v>12</v>
       </c>
       <c r="G135" t="s">
-        <v>582</v>
+        <v>575</v>
       </c>
     </row>
     <row r="136" spans="1:7">
       <c r="A136" s="2" t="s">
-        <v>583</v>
+        <v>576</v>
       </c>
       <c r="B136" t="s">
-        <v>584</v>
+        <v>577</v>
       </c>
       <c r="C136" t="s">
-        <v>535</v>
+        <v>240</v>
       </c>
       <c r="D136" t="s">
-        <v>534</v>
+        <v>347</v>
       </c>
       <c r="E136" t="s">
-        <v>585</v>
+        <v>578</v>
       </c>
       <c r="F136" t="s">
-        <v>119</v>
+        <v>39</v>
       </c>
       <c r="G136" t="s">
-        <v>586</v>
+        <v>579</v>
       </c>
     </row>
     <row r="137" spans="1:7">
       <c r="A137" s="2" t="s">
-        <v>587</v>
+        <v>580</v>
       </c>
       <c r="B137" t="s">
-        <v>588</v>
+        <v>581</v>
       </c>
       <c r="C137" t="s">
-        <v>535</v>
+        <v>74</v>
       </c>
       <c r="D137" t="s">
-        <v>534</v>
+        <v>73</v>
       </c>
       <c r="E137" t="s">
-        <v>589</v>
+        <v>582</v>
       </c>
       <c r="F137" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="G137" t="s">
-        <v>590</v>
+        <v>583</v>
       </c>
     </row>
     <row r="138" spans="1:7">
       <c r="A138" s="2" t="s">
-        <v>591</v>
+        <v>584</v>
       </c>
       <c r="B138" t="s">
-        <v>592</v>
+        <v>585</v>
       </c>
       <c r="C138" t="s">
-        <v>535</v>
+        <v>79</v>
       </c>
       <c r="D138" t="s">
-        <v>534</v>
+        <v>80</v>
       </c>
       <c r="E138" t="s">
-        <v>593</v>
+        <v>586</v>
       </c>
       <c r="F138" t="s">
-        <v>24</v>
+        <v>136</v>
       </c>
       <c r="G138" t="s">
-        <v>594</v>
+        <v>587</v>
       </c>
     </row>
     <row r="139" spans="1:7">
       <c r="A139" s="2" t="s">
-        <v>595</v>
+        <v>588</v>
       </c>
       <c r="B139" t="s">
-        <v>596</v>
+        <v>589</v>
       </c>
       <c r="C139" t="s">
-        <v>535</v>
+        <v>240</v>
       </c>
       <c r="D139" t="s">
-        <v>534</v>
+        <v>241</v>
       </c>
       <c r="E139" t="s">
-        <v>597</v>
+        <v>590</v>
       </c>
       <c r="F139" t="s">
-        <v>119</v>
+        <v>31</v>
       </c>
       <c r="G139" t="s">
-        <v>598</v>
+        <v>31</v>
       </c>
     </row>
     <row r="140" spans="1:7">
       <c r="A140" s="2" t="s">
-        <v>599</v>
+        <v>591</v>
       </c>
       <c r="B140" t="s">
-        <v>600</v>
+        <v>592</v>
       </c>
       <c r="C140" t="s">
-        <v>535</v>
+        <v>68</v>
       </c>
       <c r="D140" t="s">
-        <v>534</v>
+        <v>69</v>
       </c>
       <c r="E140" t="s">
-        <v>601</v>
+        <v>593</v>
       </c>
       <c r="F140" t="s">
-        <v>156</v>
+        <v>396</v>
       </c>
       <c r="G140" t="s">
-        <v>602</v>
+        <v>594</v>
       </c>
     </row>
     <row r="141" spans="1:7">
       <c r="A141" s="2" t="s">
-        <v>603</v>
+        <v>595</v>
       </c>
       <c r="B141" t="s">
-        <v>604</v>
+        <v>596</v>
       </c>
       <c r="C141" t="s">
-        <v>535</v>
+        <v>28</v>
       </c>
       <c r="D141" t="s">
-        <v>534</v>
+        <v>29</v>
       </c>
       <c r="E141" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
       <c r="F141" t="s">
-        <v>24</v>
+        <v>136</v>
       </c>
       <c r="G141" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
     </row>
     <row r="142" spans="1:7">
       <c r="A142" s="2" t="s">
-        <v>607</v>
+        <v>599</v>
       </c>
       <c r="B142" t="s">
-        <v>608</v>
+        <v>600</v>
       </c>
       <c r="C142" t="s">
-        <v>535</v>
+        <v>28</v>
       </c>
       <c r="D142" t="s">
-        <v>534</v>
+        <v>29</v>
       </c>
       <c r="E142" t="s">
-        <v>609</v>
+        <v>601</v>
       </c>
       <c r="F142" t="s">
-        <v>119</v>
+        <v>396</v>
       </c>
       <c r="G142" t="s">
-        <v>610</v>
+        <v>602</v>
       </c>
     </row>
     <row r="143" spans="1:7">
       <c r="A143" s="2" t="s">
-        <v>611</v>
+        <v>603</v>
       </c>
       <c r="B143" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="C143" t="s">
-        <v>535</v>
+        <v>9</v>
       </c>
       <c r="D143" t="s">
-        <v>534</v>
+        <v>10</v>
       </c>
       <c r="E143" t="s">
-        <v>613</v>
+        <v>605</v>
       </c>
       <c r="F143" t="s">
-        <v>119</v>
+        <v>449</v>
       </c>
       <c r="G143" t="s">
-        <v>614</v>
+        <v>606</v>
       </c>
     </row>
     <row r="144" spans="1:7">
       <c r="A144" s="2" t="s">
-        <v>615</v>
+        <v>607</v>
       </c>
       <c r="B144" t="s">
-        <v>616</v>
+        <v>608</v>
       </c>
       <c r="C144" t="s">
-        <v>535</v>
+        <v>74</v>
       </c>
       <c r="D144" t="s">
-        <v>534</v>
+        <v>73</v>
       </c>
       <c r="E144" t="s">
-        <v>617</v>
+        <v>609</v>
       </c>
       <c r="F144" t="s">
-        <v>57</v>
+        <v>212</v>
       </c>
       <c r="G144" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
     </row>
     <row r="145" spans="1:7">
       <c r="A145" s="2" t="s">
-        <v>619</v>
+        <v>611</v>
       </c>
       <c r="B145" t="s">
-        <v>620</v>
+        <v>612</v>
       </c>
       <c r="C145" t="s">
-        <v>621</v>
+        <v>9</v>
       </c>
       <c r="D145" t="s">
-        <v>622</v>
+        <v>10</v>
       </c>
       <c r="E145" t="s">
-        <v>623</v>
+        <v>613</v>
       </c>
       <c r="F145" t="s">
-        <v>12</v>
+        <v>365</v>
       </c>
       <c r="G145" t="s">
-        <v>624</v>
+        <v>614</v>
       </c>
     </row>
     <row r="146" spans="1:7">
       <c r="A146" s="2" t="s">
-        <v>625</v>
+        <v>615</v>
       </c>
       <c r="B146" t="s">
-        <v>626</v>
+        <v>616</v>
       </c>
       <c r="C146" t="s">
-        <v>621</v>
+        <v>9</v>
       </c>
       <c r="D146" t="s">
-        <v>622</v>
+        <v>10</v>
       </c>
       <c r="E146" t="s">
-        <v>627</v>
+        <v>617</v>
       </c>
       <c r="F146" t="s">
-        <v>12</v>
+        <v>405</v>
       </c>
       <c r="G146" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
     </row>
     <row r="147" spans="1:7">
       <c r="A147" s="2" t="s">
-        <v>629</v>
+        <v>619</v>
       </c>
       <c r="B147" t="s">
-        <v>630</v>
+        <v>620</v>
       </c>
       <c r="C147" t="s">
+        <v>9</v>
+      </c>
+      <c r="D147" t="s">
+        <v>10</v>
+      </c>
+      <c r="E147" t="s">
         <v>621</v>
       </c>
-      <c r="D147" t="s">
+      <c r="F147" t="s">
+        <v>114</v>
+      </c>
+      <c r="G147" t="s">
         <v>622</v>
-      </c>
-      <c r="E147" t="s">
-        <v>631</v>
-      </c>
-      <c r="F147" t="s">
-        <v>124</v>
-      </c>
-      <c r="G147" t="s">
-        <v>632</v>
       </c>
     </row>
     <row r="148" spans="1:7">
       <c r="A148" s="2" t="s">
-        <v>633</v>
+        <v>623</v>
       </c>
       <c r="B148" t="s">
-        <v>634</v>
+        <v>624</v>
       </c>
       <c r="C148" t="s">
-        <v>621</v>
+        <v>9</v>
       </c>
       <c r="D148" t="s">
-        <v>622</v>
+        <v>10</v>
       </c>
       <c r="E148" t="s">
-        <v>635</v>
+        <v>625</v>
       </c>
       <c r="F148" t="s">
         <v>119</v>
       </c>
       <c r="G148" t="s">
-        <v>636</v>
+        <v>626</v>
       </c>
     </row>
     <row r="149" spans="1:7">
       <c r="A149" s="2" t="s">
-        <v>637</v>
+        <v>627</v>
       </c>
       <c r="B149" t="s">
-        <v>638</v>
+        <v>628</v>
       </c>
       <c r="C149" t="s">
-        <v>621</v>
+        <v>74</v>
       </c>
       <c r="D149" t="s">
-        <v>622</v>
+        <v>73</v>
       </c>
       <c r="E149" t="s">
-        <v>639</v>
+        <v>629</v>
       </c>
       <c r="F149" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="G149" t="s">
-        <v>640</v>
+        <v>630</v>
       </c>
     </row>
     <row r="150" spans="1:7">
       <c r="A150" s="2" t="s">
-        <v>641</v>
+        <v>631</v>
       </c>
       <c r="B150" t="s">
-        <v>642</v>
+        <v>632</v>
       </c>
       <c r="C150" t="s">
-        <v>621</v>
+        <v>74</v>
       </c>
       <c r="D150" t="s">
-        <v>622</v>
+        <v>73</v>
       </c>
       <c r="E150" t="s">
-        <v>643</v>
+        <v>633</v>
       </c>
       <c r="F150" t="s">
-        <v>644</v>
+        <v>39</v>
       </c>
       <c r="G150" t="s">
-        <v>645</v>
+        <v>634</v>
       </c>
     </row>
     <row r="151" spans="1:7">
       <c r="A151" s="2" t="s">
-        <v>646</v>
+        <v>635</v>
       </c>
       <c r="B151" t="s">
-        <v>647</v>
+        <v>636</v>
       </c>
       <c r="C151" t="s">
-        <v>621</v>
+        <v>68</v>
       </c>
       <c r="D151" t="s">
-        <v>622</v>
+        <v>69</v>
       </c>
       <c r="E151" t="s">
-        <v>648</v>
+        <v>637</v>
       </c>
       <c r="F151" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="G151" t="s">
-        <v>649</v>
+        <v>638</v>
       </c>
     </row>
     <row r="152" spans="1:7">
       <c r="A152" s="2" t="s">
-        <v>650</v>
+        <v>639</v>
       </c>
       <c r="B152" t="s">
-        <v>651</v>
+        <v>640</v>
       </c>
       <c r="C152" t="s">
-        <v>621</v>
+        <v>68</v>
       </c>
       <c r="D152" t="s">
-        <v>622</v>
+        <v>69</v>
       </c>
       <c r="E152" t="s">
-        <v>652</v>
+        <v>641</v>
       </c>
       <c r="F152" t="s">
-        <v>24</v>
+        <v>449</v>
       </c>
       <c r="G152" t="s">
-        <v>653</v>
+        <v>642</v>
       </c>
     </row>
     <row r="153" spans="1:7">
       <c r="A153" s="2" t="s">
-        <v>654</v>
+        <v>643</v>
       </c>
       <c r="B153" t="s">
-        <v>655</v>
+        <v>644</v>
       </c>
       <c r="C153" t="s">
-        <v>621</v>
+        <v>21</v>
       </c>
       <c r="D153" t="s">
-        <v>622</v>
+        <v>22</v>
       </c>
       <c r="E153" t="s">
-        <v>656</v>
+        <v>645</v>
       </c>
       <c r="F153" t="s">
-        <v>657</v>
+        <v>646</v>
       </c>
       <c r="G153" t="s">
-        <v>658</v>
+        <v>647</v>
       </c>
     </row>
     <row r="154" spans="1:7">
       <c r="A154" s="2" t="s">
-        <v>659</v>
+        <v>648</v>
       </c>
       <c r="B154" t="s">
-        <v>638</v>
+        <v>649</v>
       </c>
       <c r="C154" t="s">
-        <v>621</v>
+        <v>28</v>
       </c>
       <c r="D154" t="s">
-        <v>622</v>
+        <v>29</v>
       </c>
       <c r="E154" t="s">
-        <v>660</v>
+        <v>650</v>
       </c>
       <c r="F154" t="s">
-        <v>33</v>
+        <v>651</v>
       </c>
       <c r="G154" t="s">
-        <v>661</v>
+        <v>652</v>
       </c>
     </row>
     <row r="155" spans="1:7">
       <c r="A155" s="2" t="s">
-        <v>662</v>
+        <v>653</v>
       </c>
       <c r="B155" t="s">
-        <v>663</v>
+        <v>654</v>
       </c>
       <c r="C155" t="s">
-        <v>621</v>
+        <v>28</v>
       </c>
       <c r="D155" t="s">
-        <v>622</v>
+        <v>29</v>
       </c>
       <c r="E155" t="s">
-        <v>664</v>
+        <v>655</v>
       </c>
       <c r="F155" t="s">
-        <v>129</v>
+        <v>651</v>
       </c>
       <c r="G155" t="s">
-        <v>665</v>
+        <v>656</v>
       </c>
     </row>
     <row r="156" spans="1:7">
       <c r="A156" s="2" t="s">
-        <v>666</v>
+        <v>657</v>
       </c>
       <c r="B156" t="s">
-        <v>667</v>
+        <v>658</v>
       </c>
       <c r="C156" t="s">
-        <v>621</v>
+        <v>28</v>
       </c>
       <c r="D156" t="s">
-        <v>622</v>
+        <v>29</v>
       </c>
       <c r="E156" t="s">
-        <v>668</v>
+        <v>659</v>
       </c>
       <c r="F156" t="s">
-        <v>24</v>
+        <v>660</v>
       </c>
       <c r="G156" t="s">
-        <v>669</v>
+        <v>661</v>
       </c>
     </row>
     <row r="157" spans="1:7">
       <c r="A157" s="2" t="s">
-        <v>670</v>
+        <v>662</v>
       </c>
       <c r="B157" t="s">
-        <v>671</v>
+        <v>663</v>
       </c>
       <c r="C157" t="s">
-        <v>621</v>
+        <v>9</v>
       </c>
       <c r="D157" t="s">
-        <v>622</v>
+        <v>10</v>
       </c>
       <c r="E157" t="s">
-        <v>672</v>
+        <v>664</v>
       </c>
       <c r="F157" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="G157" t="s">
-        <v>673</v>
+        <v>665</v>
       </c>
     </row>
     <row r="158" spans="1:7">
       <c r="A158" s="2" t="s">
-        <v>674</v>
+        <v>666</v>
       </c>
       <c r="B158" t="s">
-        <v>675</v>
+        <v>667</v>
       </c>
       <c r="C158" t="s">
-        <v>621</v>
+        <v>111</v>
       </c>
       <c r="D158" t="s">
-        <v>622</v>
+        <v>112</v>
       </c>
       <c r="E158" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="F158" t="s">
-        <v>138</v>
+        <v>449</v>
       </c>
       <c r="G158" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="159" spans="1:7">
       <c r="A159" s="2" t="s">
-        <v>678</v>
+        <v>670</v>
       </c>
       <c r="B159" t="s">
-        <v>679</v>
+        <v>671</v>
       </c>
       <c r="C159" t="s">
-        <v>621</v>
+        <v>91</v>
       </c>
       <c r="D159" t="s">
-        <v>622</v>
+        <v>92</v>
       </c>
       <c r="E159" t="s">
-        <v>680</v>
+        <v>672</v>
       </c>
       <c r="F159" t="s">
-        <v>681</v>
+        <v>114</v>
       </c>
       <c r="G159" t="s">
-        <v>682</v>
+        <v>673</v>
       </c>
     </row>
     <row r="160" spans="1:7">
       <c r="A160" s="2" t="s">
-        <v>683</v>
+        <v>674</v>
       </c>
       <c r="B160" t="s">
-        <v>684</v>
+        <v>675</v>
       </c>
       <c r="C160" t="s">
-        <v>621</v>
+        <v>68</v>
       </c>
       <c r="D160" t="s">
-        <v>622</v>
+        <v>69</v>
       </c>
       <c r="E160" t="s">
-        <v>685</v>
+        <v>676</v>
       </c>
       <c r="F160" t="s">
-        <v>119</v>
+        <v>136</v>
       </c>
       <c r="G160" t="s">
-        <v>686</v>
+        <v>677</v>
       </c>
     </row>
     <row r="161" spans="1:7">
       <c r="A161" s="2" t="s">
-        <v>687</v>
+        <v>678</v>
       </c>
       <c r="B161" t="s">
-        <v>688</v>
+        <v>679</v>
       </c>
       <c r="C161" t="s">
-        <v>621</v>
+        <v>74</v>
       </c>
       <c r="D161" t="s">
-        <v>622</v>
+        <v>73</v>
       </c>
       <c r="E161" t="s">
-        <v>689</v>
+        <v>680</v>
       </c>
       <c r="F161" t="s">
-        <v>33</v>
+        <v>212</v>
       </c>
       <c r="G161" t="s">
-        <v>690</v>
+        <v>681</v>
       </c>
     </row>
     <row r="162" spans="1:7">
       <c r="A162" s="2" t="s">
-        <v>691</v>
+        <v>682</v>
       </c>
       <c r="B162" t="s">
-        <v>692</v>
+        <v>683</v>
       </c>
       <c r="C162" t="s">
-        <v>621</v>
+        <v>68</v>
       </c>
       <c r="D162" t="s">
-        <v>622</v>
+        <v>69</v>
       </c>
       <c r="E162" t="s">
-        <v>693</v>
+        <v>684</v>
       </c>
       <c r="F162" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="G162" t="s">
-        <v>694</v>
+        <v>685</v>
       </c>
     </row>
     <row r="163" spans="1:7">
       <c r="A163" s="2" t="s">
-        <v>695</v>
+        <v>686</v>
       </c>
       <c r="B163" t="s">
-        <v>696</v>
+        <v>687</v>
       </c>
       <c r="C163" t="s">
-        <v>621</v>
+        <v>85</v>
       </c>
       <c r="D163" t="s">
-        <v>622</v>
+        <v>86</v>
       </c>
       <c r="E163" t="s">
-        <v>697</v>
+        <v>688</v>
       </c>
       <c r="F163" t="s">
-        <v>57</v>
+        <v>689</v>
       </c>
       <c r="G163" t="s">
-        <v>698</v>
+        <v>690</v>
       </c>
     </row>
     <row r="164" spans="1:7">
       <c r="A164" s="2" t="s">
-        <v>699</v>
+        <v>691</v>
       </c>
       <c r="B164" t="s">
-        <v>700</v>
+        <v>692</v>
       </c>
       <c r="C164" t="s">
-        <v>621</v>
+        <v>85</v>
       </c>
       <c r="D164" t="s">
-        <v>622</v>
+        <v>86</v>
       </c>
       <c r="E164" t="s">
-        <v>701</v>
+        <v>693</v>
       </c>
       <c r="F164" t="s">
-        <v>52</v>
+        <v>694</v>
       </c>
       <c r="G164" t="s">
-        <v>702</v>
+        <v>695</v>
       </c>
     </row>
     <row r="165" spans="1:7">
       <c r="A165" s="2" t="s">
-        <v>703</v>
+        <v>696</v>
       </c>
       <c r="B165" t="s">
-        <v>704</v>
+        <v>697</v>
       </c>
       <c r="C165" t="s">
-        <v>621</v>
+        <v>85</v>
       </c>
       <c r="D165" t="s">
-        <v>622</v>
+        <v>86</v>
       </c>
       <c r="E165" t="s">
-        <v>705</v>
+        <v>698</v>
       </c>
       <c r="F165" t="s">
-        <v>644</v>
+        <v>12</v>
       </c>
       <c r="G165" t="s">
-        <v>706</v>
+        <v>699</v>
       </c>
     </row>
     <row r="166" spans="1:7">
       <c r="A166" s="2" t="s">
-        <v>707</v>
+        <v>700</v>
       </c>
       <c r="B166" t="s">
-        <v>708</v>
+        <v>701</v>
       </c>
       <c r="C166" t="s">
-        <v>621</v>
+        <v>240</v>
       </c>
       <c r="D166" t="s">
-        <v>622</v>
+        <v>316</v>
       </c>
       <c r="E166" t="s">
-        <v>709</v>
+        <v>702</v>
       </c>
       <c r="F166" t="s">
-        <v>156</v>
+        <v>31</v>
       </c>
       <c r="G166" t="s">
-        <v>710</v>
+        <v>31</v>
       </c>
     </row>
     <row r="167" spans="1:7">
       <c r="A167" s="2" t="s">
-        <v>711</v>
+        <v>703</v>
       </c>
       <c r="B167" t="s">
-        <v>712</v>
+        <v>704</v>
       </c>
       <c r="C167" t="s">
-        <v>621</v>
+        <v>28</v>
       </c>
       <c r="D167" t="s">
-        <v>622</v>
+        <v>29</v>
       </c>
       <c r="E167" t="s">
-        <v>713</v>
+        <v>705</v>
       </c>
       <c r="F167" t="s">
-        <v>138</v>
+        <v>706</v>
       </c>
       <c r="G167" t="s">
-        <v>714</v>
+        <v>707</v>
       </c>
     </row>
     <row r="168" spans="1:7">
       <c r="A168" s="2" t="s">
-        <v>715</v>
+        <v>708</v>
       </c>
       <c r="B168" t="s">
-        <v>716</v>
+        <v>709</v>
       </c>
       <c r="C168" t="s">
-        <v>621</v>
+        <v>111</v>
       </c>
       <c r="D168" t="s">
-        <v>622</v>
+        <v>112</v>
       </c>
       <c r="E168" t="s">
-        <v>717</v>
+        <v>710</v>
       </c>
       <c r="F168" t="s">
-        <v>718</v>
+        <v>312</v>
       </c>
       <c r="G168" t="s">
-        <v>719</v>
+        <v>711</v>
       </c>
     </row>
     <row r="169" spans="1:7">
       <c r="A169" s="2" t="s">
-        <v>720</v>
+        <v>712</v>
       </c>
       <c r="B169" t="s">
-        <v>721</v>
+        <v>713</v>
       </c>
       <c r="C169" t="s">
-        <v>621</v>
+        <v>9</v>
       </c>
       <c r="D169" t="s">
-        <v>622</v>
+        <v>10</v>
       </c>
       <c r="E169" t="s">
-        <v>722</v>
+        <v>714</v>
       </c>
       <c r="F169" t="s">
-        <v>723</v>
+        <v>39</v>
       </c>
       <c r="G169" t="s">
-        <v>724</v>
+        <v>715</v>
       </c>
     </row>
     <row r="170" spans="1:7">
       <c r="A170" s="2" t="s">
-        <v>725</v>
+        <v>716</v>
       </c>
       <c r="B170" t="s">
-        <v>616</v>
+        <v>717</v>
       </c>
       <c r="C170" t="s">
-        <v>621</v>
+        <v>91</v>
       </c>
       <c r="D170" t="s">
-        <v>622</v>
+        <v>92</v>
       </c>
       <c r="E170" t="s">
-        <v>726</v>
+        <v>718</v>
       </c>
       <c r="F170" t="s">
-        <v>57</v>
+        <v>449</v>
       </c>
       <c r="G170" t="s">
-        <v>727</v>
+        <v>719</v>
       </c>
     </row>
     <row r="171" spans="1:7">
       <c r="A171" s="2" t="s">
-        <v>728</v>
+        <v>720</v>
       </c>
       <c r="B171" t="s">
-        <v>729</v>
+        <v>721</v>
       </c>
       <c r="C171" t="s">
-        <v>730</v>
+        <v>111</v>
       </c>
       <c r="D171" t="s">
-        <v>731</v>
+        <v>112</v>
       </c>
       <c r="E171" t="s">
-        <v>732</v>
+        <v>722</v>
       </c>
       <c r="F171" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="G171" t="s">
-        <v>13</v>
+        <v>723</v>
       </c>
     </row>
     <row r="172" spans="1:7">
       <c r="A172" s="2" t="s">
-        <v>733</v>
+        <v>724</v>
       </c>
       <c r="B172" t="s">
-        <v>734</v>
+        <v>725</v>
       </c>
       <c r="C172" t="s">
-        <v>730</v>
+        <v>28</v>
       </c>
       <c r="D172" t="s">
-        <v>735</v>
+        <v>29</v>
       </c>
       <c r="E172" t="s">
-        <v>736</v>
+        <v>726</v>
       </c>
       <c r="F172" t="s">
-        <v>119</v>
+        <v>727</v>
       </c>
       <c r="G172" t="s">
-        <v>737</v>
+        <v>728</v>
       </c>
     </row>
     <row r="173" spans="1:7">
       <c r="A173" s="2" t="s">
-        <v>738</v>
+        <v>729</v>
       </c>
       <c r="B173" t="s">
-        <v>739</v>
+        <v>730</v>
       </c>
       <c r="C173" t="s">
-        <v>730</v>
+        <v>28</v>
       </c>
       <c r="D173" t="s">
-        <v>740</v>
+        <v>29</v>
       </c>
       <c r="E173" t="s">
-        <v>741</v>
+        <v>731</v>
       </c>
       <c r="F173" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="G173" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
     </row>
     <row r="174" spans="1:7">
       <c r="A174" s="2" t="s">
-        <v>742</v>
+        <v>732</v>
       </c>
       <c r="B174" t="s">
-        <v>743</v>
+        <v>733</v>
       </c>
       <c r="C174" t="s">
-        <v>730</v>
+        <v>74</v>
       </c>
       <c r="D174" t="s">
-        <v>744</v>
+        <v>73</v>
       </c>
       <c r="E174" t="s">
-        <v>745</v>
+        <v>734</v>
       </c>
       <c r="F174" t="s">
-        <v>13</v>
+        <v>212</v>
       </c>
       <c r="G174" t="s">
-        <v>13</v>
+        <v>735</v>
       </c>
     </row>
     <row r="175" spans="1:7">
       <c r="A175" s="2" t="s">
-        <v>746</v>
+        <v>736</v>
       </c>
       <c r="B175" t="s">
-        <v>747</v>
+        <v>737</v>
       </c>
       <c r="C175" t="s">
-        <v>730</v>
+        <v>68</v>
       </c>
       <c r="D175" t="s">
-        <v>744</v>
+        <v>69</v>
       </c>
       <c r="E175" t="s">
-        <v>748</v>
+        <v>738</v>
       </c>
       <c r="F175" t="s">
-        <v>13</v>
+        <v>312</v>
       </c>
       <c r="G175" t="s">
-        <v>13</v>
+        <v>739</v>
       </c>
     </row>
     <row r="176" spans="1:7">
       <c r="A176" s="2" t="s">
-        <v>749</v>
+        <v>740</v>
       </c>
       <c r="B176" t="s">
-        <v>750</v>
+        <v>741</v>
       </c>
       <c r="C176" t="s">
-        <v>730</v>
+        <v>74</v>
       </c>
       <c r="D176" t="s">
-        <v>751</v>
+        <v>73</v>
       </c>
       <c r="E176" t="s">
-        <v>752</v>
+        <v>742</v>
       </c>
       <c r="F176" t="s">
-        <v>12</v>
+        <v>396</v>
       </c>
       <c r="G176" t="s">
-        <v>753</v>
+        <v>743</v>
       </c>
     </row>
     <row r="177" spans="1:7">
       <c r="A177" s="2" t="s">
-        <v>754</v>
+        <v>744</v>
       </c>
       <c r="B177" t="s">
-        <v>755</v>
+        <v>745</v>
       </c>
       <c r="C177" t="s">
-        <v>730</v>
+        <v>91</v>
       </c>
       <c r="D177" t="s">
-        <v>751</v>
+        <v>92</v>
       </c>
       <c r="E177" t="s">
-        <v>756</v>
+        <v>746</v>
       </c>
       <c r="F177" t="s">
-        <v>33</v>
+        <v>747</v>
       </c>
       <c r="G177" t="s">
-        <v>757</v>
+        <v>748</v>
       </c>
     </row>
     <row r="178" spans="1:7">
       <c r="A178" s="2" t="s">
-        <v>758</v>
+        <v>749</v>
       </c>
       <c r="B178" t="s">
-        <v>759</v>
+        <v>741</v>
       </c>
       <c r="C178" t="s">
-        <v>730</v>
+        <v>91</v>
       </c>
       <c r="D178" t="s">
-        <v>740</v>
+        <v>92</v>
       </c>
       <c r="E178" t="s">
-        <v>760</v>
+        <v>750</v>
       </c>
       <c r="F178" t="s">
-        <v>13</v>
+        <v>396</v>
       </c>
       <c r="G178" t="s">
-        <v>13</v>
+        <v>751</v>
       </c>
     </row>
     <row r="179" spans="1:7">
       <c r="A179" s="2" t="s">
-        <v>761</v>
+        <v>752</v>
       </c>
       <c r="B179" t="s">
-        <v>762</v>
+        <v>753</v>
       </c>
       <c r="C179" t="s">
-        <v>730</v>
+        <v>9</v>
       </c>
       <c r="D179" t="s">
-        <v>751</v>
+        <v>10</v>
       </c>
       <c r="E179" t="s">
-        <v>763</v>
+        <v>754</v>
       </c>
       <c r="F179" t="s">
-        <v>24</v>
+        <v>396</v>
       </c>
       <c r="G179" t="s">
-        <v>764</v>
+        <v>755</v>
       </c>
     </row>
     <row r="180" spans="1:7">
       <c r="A180" s="2" t="s">
-        <v>765</v>
+        <v>756</v>
       </c>
       <c r="B180" t="s">
-        <v>766</v>
+        <v>757</v>
       </c>
       <c r="C180" t="s">
-        <v>730</v>
+        <v>240</v>
       </c>
       <c r="D180" t="s">
-        <v>731</v>
+        <v>263</v>
       </c>
       <c r="E180" t="s">
-        <v>767</v>
+        <v>758</v>
       </c>
       <c r="F180" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G180" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="181" spans="1:7">
-      <c r="A181" s="2" t="s">
-        <v>768</v>
-      </c>
-      <c r="B181" t="s">
-        <v>769</v>
-      </c>
-      <c r="C181" t="s">
-        <v>730</v>
-      </c>
-      <c r="D181" t="s">
-        <v>740</v>
-      </c>
-      <c r="E181" t="s">
-        <v>770</v>
-      </c>
-      <c r="F181" t="s">
-        <v>13</v>
-      </c>
-      <c r="G181" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="182" spans="1:7">
-      <c r="A182" s="2" t="s">
-        <v>771</v>
-      </c>
-      <c r="B182" t="s">
-        <v>772</v>
-      </c>
-      <c r="C182" t="s">
-        <v>730</v>
-      </c>
-      <c r="D182" t="s">
-        <v>735</v>
-      </c>
-      <c r="E182" t="s">
-        <v>773</v>
-      </c>
-      <c r="F182" t="s">
-        <v>33</v>
-      </c>
-      <c r="G182" t="s">
-        <v>774</v>
-      </c>
-    </row>
-    <row r="183" spans="1:7">
-      <c r="A183" s="2">
-        <v>399311</v>
+        <v>759</v>
       </c>
     </row>
   </sheetData>
   <sortState ref="A2:G183">
-    <sortCondition ref="C2:C183"/>
-    <sortCondition ref="A2:A183"/>
+    <sortCondition ref="A2"/>
   </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/AiStock/indexAA.xlsx
+++ b/AiStock/indexAA.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20745" windowHeight="9675"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1252" uniqueCount="760">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1231" uniqueCount="751">
   <si>
     <t>IndexCode</t>
   </si>
@@ -50,54 +50,1251 @@
     <t>入选原因</t>
   </si>
   <si>
+    <t>931463</t>
+  </si>
+  <si>
+    <t>300 ESG</t>
+  </si>
+  <si>
+    <t>文化消费与生活服务</t>
+  </si>
+  <si>
+    <t>文化消费</t>
+  </si>
+  <si>
+    <t>银发经济ESG实践（*替换长寿经济重复*）</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>931589</t>
+  </si>
+  <si>
+    <t>300成长创新</t>
+  </si>
+  <si>
+    <t>新一代信息技术与数字经济</t>
+  </si>
+  <si>
+    <t>信息技术</t>
+  </si>
+  <si>
+    <t>科技安全+创新</t>
+  </si>
+  <si>
+    <t>安全</t>
+  </si>
+  <si>
+    <t>1：科技安全+创新双主线；2：半导体/软件/通信设备创新龙头；3：100只中盘股，成长性突出；4：2只ETF，与沪深300互补（创新侧重）</t>
+  </si>
+  <si>
+    <t>930952</t>
+  </si>
+  <si>
+    <t>300地产</t>
+  </si>
+  <si>
+    <t>公用事业与基础保障</t>
+  </si>
+  <si>
+    <t>公用保障</t>
+  </si>
+  <si>
+    <t>水利基础设施</t>
+  </si>
+  <si>
+    <t>水利</t>
+  </si>
+  <si>
+    <t>1：水利基础设施补短板，防洪抗旱刚需；2：中国电建/中国能建水利业务，订单驱动；3：100只中大盘股，地产占比下降水利上升；4：3只ETF，传统行业转型样本</t>
+  </si>
+  <si>
+    <t>930916</t>
+  </si>
+  <si>
+    <t>300通信</t>
+  </si>
+  <si>
+    <t>5G-A/6G研发</t>
+  </si>
+  <si>
+    <t>通信</t>
+  </si>
+  <si>
+    <t>1：5G-A/6G研发，通信基础设施安全；2：主设备商（华为/中兴）+光通信+卫星通信；3：100只中大盘股，平均市值200亿；4：3只ETF，与TMT互补（通信侧重）</t>
+  </si>
+  <si>
+    <t>932366</t>
+  </si>
+  <si>
+    <t>300现金流</t>
+  </si>
+  <si>
+    <t>传统优势产业升级</t>
+  </si>
+  <si>
+    <t>传统升级</t>
+  </si>
+  <si>
+    <t>高现金流传统行业</t>
+  </si>
+  <si>
+    <t>现金流</t>
+  </si>
+  <si>
+    <t>1：高现金流传统行业，转型基础好；2：建材/化工/机械，经营性现金流稳定；3：100只中大盘股，平均市值200亿；4：2只ETF，质量因子策略</t>
+  </si>
+  <si>
+    <t>930912</t>
+  </si>
+  <si>
+    <t>300消费</t>
+  </si>
+  <si>
+    <t>消费龙头全覆盖（*替换线上消费重复*）</t>
+  </si>
+  <si>
+    <t>932431</t>
+  </si>
+  <si>
+    <t>300质量</t>
+  </si>
+  <si>
+    <t>现代生物与大健康</t>
+  </si>
+  <si>
+    <t>生物健康</t>
+  </si>
+  <si>
+    <t>医药质量领先企业</t>
+  </si>
+  <si>
+    <t>质量</t>
+  </si>
+  <si>
+    <t>1：高质量发展导向，规避集采冲击；2：医药行业质量领先（ROE&gt;15%+现金流&gt;0）；3：100只中大盘股，平均市值200亿；4：2只ETF，防御属性强</t>
+  </si>
+  <si>
+    <t>931375</t>
+  </si>
+  <si>
+    <t>300质量低波</t>
+  </si>
+  <si>
+    <t>现代服务业与供应链韧性</t>
+  </si>
+  <si>
+    <t>现代服务</t>
+  </si>
+  <si>
+    <t>长三角供应链韧性</t>
+  </si>
+  <si>
+    <t>区域</t>
+  </si>
+  <si>
+    <t>1：长三角供应链韧性，质量+低波动双优；2：沪苏浙供应链龙头，质量管理体系完善；3：100只中大盘股，平均市值200亿；4：1只Smart Beta指数，防御属性强</t>
+  </si>
+  <si>
+    <t>930782</t>
+  </si>
+  <si>
+    <t>500深市</t>
+  </si>
+  <si>
+    <t>人力资本服务</t>
+  </si>
+  <si>
+    <t>人力资源</t>
+  </si>
+  <si>
+    <t>1：人才服务现代化，灵活用工/职业教育；2：科锐国际/外服控股等，人力资本服务；3：500只深市股，中盘为主；4：2只ETF，生产性服务代表</t>
+  </si>
+  <si>
+    <t>931406</t>
+  </si>
+  <si>
+    <t>5G 50</t>
+  </si>
+  <si>
+    <t>5G+文化新场景（*替换中证旅游重复*）</t>
+  </si>
+  <si>
+    <t>932367</t>
+  </si>
+  <si>
+    <t>800现金流</t>
+  </si>
+  <si>
+    <t>800成分高现金流（*替换300质量重复*）</t>
+  </si>
+  <si>
+    <t>930713</t>
+  </si>
+  <si>
+    <t>CS人工智</t>
+  </si>
+  <si>
+    <t>AI应用层</t>
+  </si>
+  <si>
+    <t>细分</t>
+  </si>
+  <si>
+    <t>1：侧重AI应用层，计算机视觉/NLP/语音识别；2：商汤/云从/科大讯飞等应用层龙头；3：50只中盘股，平均市值150亿；4：3只ETF，与AI指数互补（应用侧重）</t>
+  </si>
+  <si>
+    <t>930712</t>
+  </si>
+  <si>
+    <t>CS物联网</t>
+  </si>
+  <si>
+    <t>5G+AIoT融合</t>
+  </si>
+  <si>
+    <t>1：5G+AIoT融合，万物互联基础设施；2：传感器-模组-平台-应用全链条；3：50只中盘股，平均市值120亿；4：2只ETF，应用场景持续拓展</t>
+  </si>
+  <si>
+    <t>930716</t>
+  </si>
+  <si>
+    <t>CS物流</t>
+  </si>
+  <si>
+    <t>区域性物流/冷链</t>
+  </si>
+  <si>
+    <t>中盘</t>
+  </si>
+  <si>
+    <t>1：与国证物流互补，侧重成本优化标的；2：区域性物流/仓储/冷链，成本控制能力强；3：50只中盘股，平均市值100亿；4：2只ETF，细分领域覆盖</t>
+  </si>
+  <si>
+    <t>930632</t>
+  </si>
+  <si>
+    <t>CS稀金属</t>
+  </si>
+  <si>
+    <t>稀土+稀有金属</t>
+  </si>
+  <si>
+    <t>小盘</t>
+  </si>
+  <si>
+    <t>1：稀土+稀有金属战略价值，小金属国产替代；2：钨/锑/铋/锗等小金属，全球供给主导；3：30只小盘股，平均市值60亿；4：1只细分指数，稀缺资源属性</t>
+  </si>
+  <si>
+    <t>930662</t>
+  </si>
+  <si>
+    <t>CS现代农</t>
+  </si>
+  <si>
+    <t>现代农业与粮食安全</t>
+  </si>
+  <si>
+    <t>现代农业</t>
+  </si>
+  <si>
+    <t>智慧农业+生物农业</t>
+  </si>
+  <si>
+    <t>上游</t>
+  </si>
+  <si>
+    <t>1：智慧农业+生物农业，技术驱动型农业；2：农业AI/无人机/生物育种/智能灌溉；3：50只小盘股，平均市值60亿；4：1只主题指数，科技赋能农业</t>
+  </si>
+  <si>
+    <t>399976</t>
+  </si>
+  <si>
+    <t>CS新能车</t>
+  </si>
+  <si>
+    <t>新能源与绿色低碳</t>
+  </si>
+  <si>
+    <t>新能源</t>
+  </si>
+  <si>
+    <t>整车+电池龙头</t>
+  </si>
+  <si>
+    <t>大盘</t>
+  </si>
+  <si>
+    <t>1：电动化+智能化双主线，全球竞争力最强赛道；2：整车-电池-零部件全覆盖，比亚迪/宁德主导；3：100只大盘股，平均市值400亿；4：12只ETF，全球配置首选</t>
+  </si>
+  <si>
+    <t>931484</t>
+  </si>
+  <si>
+    <t>CS医药创新</t>
+  </si>
+  <si>
+    <t>创新药+创新器械</t>
+  </si>
+  <si>
+    <t>中游</t>
+  </si>
+  <si>
+    <t>1：创新药+创新器械双轮驱动；2：迈瑞医疗/联影医疗等高端器械+创新药；3：50只中盘股，平均市值200亿；4：2只ETF，器械占比提升</t>
+  </si>
+  <si>
+    <t>931772</t>
+  </si>
+  <si>
+    <t>SEEE碳中和</t>
+  </si>
+  <si>
+    <t>中证+上海环交所联合编制</t>
+  </si>
+  <si>
+    <t>1：中证+上海环交所联合编制，方法论权威；2：能源替代（风光）+节能减排（节能设备）双路径；3：100只中盘股，覆盖全市场；4：4只ETF，政策背书强</t>
+  </si>
+  <si>
+    <t>931404</t>
+  </si>
+  <si>
+    <t>SHS品牌消费50</t>
+  </si>
+  <si>
+    <t>中国品牌全球化</t>
+  </si>
+  <si>
+    <t>跨境</t>
+  </si>
+  <si>
+    <t>1：中国品牌全球化，文化自信载体；2：安踏H/李宁H/农夫山泉，品牌力提升；3：50只港股大盘，平均市值400亿；4：2只ETF，品牌出海</t>
+  </si>
+  <si>
+    <t>931663</t>
+  </si>
+  <si>
+    <t>SHS消费龙头</t>
+  </si>
+  <si>
+    <t>国潮品牌</t>
+  </si>
+  <si>
+    <t>1：国潮崛起，文化自信+品质升级；2：波司登/李宁/安踏，设计+品牌双提升；3：50只中大盘股，平均市值300亿；4：2只ETF，文化输出载体</t>
+  </si>
+  <si>
+    <t>931646</t>
+  </si>
+  <si>
+    <t>SHS新消费</t>
+  </si>
+  <si>
+    <t>新消费品牌龙头</t>
+  </si>
+  <si>
+    <t>1：新消费品牌崛起，国潮+品质双驱动；2：安踏/李宁/珀莱雅等，品牌力+渠道力；3：50只中大盘股，平均市值300亿；4：3只ETF，消费结构升级代表</t>
+  </si>
+  <si>
+    <t>931580</t>
+  </si>
+  <si>
+    <t>SHS游戏传媒</t>
+  </si>
+  <si>
+    <t>港股游戏出海</t>
+  </si>
+  <si>
+    <t>1：港股游戏出海，全球化运营能力；2：腾讯/网易/米哈游H股，海外收入占比50%+；3：50只港股中大盘，平均市值500亿；4：2只ETF，出海逻辑强</t>
+  </si>
+  <si>
+    <t>931793</t>
+  </si>
+  <si>
+    <t>半导体15</t>
+  </si>
+  <si>
+    <t>高端制造与新质生产力</t>
+  </si>
+  <si>
+    <t>高端制造</t>
+  </si>
+  <si>
+    <t>极致聚焦核心15只</t>
+  </si>
+  <si>
+    <t>主题</t>
+  </si>
+  <si>
+    <t>1：极致聚焦核心标的，国产替代加速受益；2：15只半导体核心标的（设计5+设备5+材料5）；3：15只中大盘股，龙头集中度高；4：1只ETF，高弹性但波动大</t>
+  </si>
+  <si>
+    <t>931743</t>
+  </si>
+  <si>
+    <t>半导体材料设备</t>
+  </si>
+  <si>
+    <t>上游“卡脖子”环节</t>
+  </si>
+  <si>
+    <t>1：国产替代刚性需求，大基金三期重点投向；2：聚焦光刻机/刻蚀机/光刻胶等“卡脖子”环节；3：50只小盘股，国产化率&lt;30%环节集中；4：2只ETF，弹性大但波动高</t>
+  </si>
+  <si>
+    <t>932066</t>
+  </si>
+  <si>
+    <t>半导体行业精选</t>
+  </si>
+  <si>
+    <t>第三代半导体</t>
+  </si>
+  <si>
+    <t>1：第三代半导体（碳化硅/氮化镓）专项扶持；2：碳化硅衬底-外延-器件，新能源车/光伏应用；3：30只小盘股，技术壁垒高；4：2只ETF，与中证半导互补（更聚焦新材料）</t>
+  </si>
+  <si>
+    <t>399238</t>
+  </si>
+  <si>
+    <t>餐饮指数</t>
+  </si>
+  <si>
+    <t>连锁餐饮标准化</t>
+  </si>
+  <si>
+    <t>1：连锁化+标准化趋势，抗周期属性强；2：海底捞/九毛九/百胜中国，品牌连锁；3：30只小盘股，平均市值80亿；4：2只ETF，必选消费属性</t>
+  </si>
+  <si>
+    <t>931695</t>
+  </si>
+  <si>
+    <t>成渝经济圈</t>
+  </si>
+  <si>
+    <t>西部供应链枢纽</t>
+  </si>
+  <si>
+    <t>1：西部消费中心，内需市场培育；2：成都/重庆餐饮/零售/文旅集群；3：100只中盘股（复用现代服务），平均市值150亿；4：2只区域指数，区域消费视角</t>
+  </si>
+  <si>
+    <t>931243</t>
+  </si>
+  <si>
+    <t>诚通央企ESG</t>
+  </si>
+  <si>
+    <t>央企粮食安全压舱石</t>
+  </si>
+  <si>
+    <t>央企</t>
+  </si>
+  <si>
+    <t>1：央企粮食安全压舱石，中粮/中化主导；2：粮食贸易/种子/化肥/农药全链条；3：50只大盘股，央企占比90%；4：1只定制指数，安全属性突出</t>
+  </si>
+  <si>
+    <t>931746</t>
+  </si>
+  <si>
+    <t>储能产业</t>
+  </si>
+  <si>
+    <t>储能系统集成</t>
+  </si>
+  <si>
+    <t>1：新型电力系统关键，强制配储政策驱动；2：储能系统集成/电池管理/温控设备；3：50只中盘股，2023年后商业化加速；4：3只ETF，成长确定性高</t>
+  </si>
+  <si>
+    <t>931440</t>
+  </si>
+  <si>
+    <t>创新药30</t>
+  </si>
+  <si>
+    <t>临床后期创新药</t>
+  </si>
+  <si>
+    <t>1：纯正创新药标的，医保谈判优化受益；2：临床后期（III期）创新药企，商业化在即；3：30只小盘股，平均市值100亿；4：2只ETF，高弹性但波动大</t>
+  </si>
+  <si>
+    <t>399006</t>
+  </si>
+  <si>
+    <t>创业板指</t>
+  </si>
+  <si>
+    <t>宽基基准层</t>
+  </si>
+  <si>
+    <t>宽基基准</t>
+  </si>
+  <si>
+    <t>创新创业，硬科技特色</t>
+  </si>
+  <si>
+    <t>1：创新创业试验田，注册制改革标杆；2：新能源/医药/电子占比60%，硬科技特色；3：100只创业板龙头，平均市值300亿；4：10+只ETF，波动率高于主板</t>
+  </si>
+  <si>
+    <t>930971</t>
+  </si>
+  <si>
+    <t>等权90</t>
+  </si>
+  <si>
+    <t>应急产业</t>
+  </si>
+  <si>
+    <t>应急安全</t>
+  </si>
+  <si>
+    <t>1：应急产业写入安全发展规划，公共安全刚需；2：应急装备/消防设备/安防系统；3：90只中盘股，等权编制避免龙头垄断；4：1只主题指数，细分领域覆盖</t>
+  </si>
+  <si>
+    <t>931994</t>
+  </si>
+  <si>
+    <t>电网设备主题</t>
+  </si>
+  <si>
+    <t>医疗用电安全</t>
+  </si>
+  <si>
+    <t>1：医疗用电安全，公共健康基础设施保障；2：UPS/应急电源/智能配电，医院刚需；3：30只中盘股，平均市值80亿；4：1只主题指数，细分领域稀缺</t>
+  </si>
+  <si>
+    <t>931461</t>
+  </si>
+  <si>
+    <t>电子50</t>
+  </si>
+  <si>
+    <t>消费电子+半导体设备</t>
+  </si>
+  <si>
+    <t>电子</t>
+  </si>
+  <si>
+    <t>1：消费电子复苏+半导体设备国产化；2：苹果链/华为链+半导体设备材料；3：50只中大盘股，平均市值250亿；4：4只ETF，流动性最佳电子指数</t>
+  </si>
+  <si>
+    <t>930901</t>
+  </si>
+  <si>
+    <t>动漫游戏</t>
+  </si>
+  <si>
+    <t>游戏/动漫AIGC受益</t>
+  </si>
+  <si>
+    <t>1：数字文化出海，AIGC降本增效；2：米哈游/腾讯游戏/完美世界，全球化运营；3：50只小盘股，平均市值100亿；4：4只ETF，文化自信载体</t>
+  </si>
+  <si>
+    <t>931687</t>
+  </si>
+  <si>
+    <t>风电产业</t>
+  </si>
+  <si>
+    <t>海上风电+大基地</t>
+  </si>
+  <si>
+    <t>1：海上风电+大基地建设，十五五装机目标明确；2：整机-叶片-塔筒-海缆全链条；3：50只中盘股，金风/明阳等龙头；4：2只ETF，与光伏形成互补</t>
+  </si>
+  <si>
+    <t>931787</t>
+  </si>
+  <si>
+    <t>港股创新药</t>
+  </si>
+  <si>
+    <t>早期临床标的</t>
+  </si>
+  <si>
+    <t>1：与港股通创新药互补，覆盖更多临床阶段；2：侧重早期临床（I/II期）标的，风险收益比高；3：30只港股小盘，平均市值30亿；4：1只ETF，高风险高弹性</t>
+  </si>
+  <si>
+    <t>931574</t>
+  </si>
+  <si>
+    <t>港股科技</t>
+  </si>
+  <si>
+    <t>港股互联网平台</t>
+  </si>
+  <si>
+    <t>1：港股互联网平台，估值修复+出海双逻辑；2：腾讯/美团/快手/小米，与A股互补；3：50只港股大盘，平均市值800亿；4：4只ETF，流动性最佳港股科技指数</t>
+  </si>
+  <si>
+    <t>931234</t>
+  </si>
+  <si>
+    <t>港股通创新药</t>
+  </si>
+  <si>
+    <t>港股18A生物科技</t>
+  </si>
+  <si>
+    <t>1：港股18A生物科技，全球创新前沿阵地；2：信达/君实/康方等18A公司，临床阶段丰富；3：50只港股小盘，平均市值50亿；4：3只ETF，与A股创新药互补（更前沿）</t>
+  </si>
+  <si>
+    <t>932153</t>
+  </si>
+  <si>
+    <t>港股通价值策略</t>
+  </si>
+  <si>
+    <t>子产业链专项覆盖</t>
+  </si>
+  <si>
+    <t>生活服务</t>
+  </si>
+  <si>
+    <t>消费价值股（*替换港股通科技重复*）</t>
+  </si>
+  <si>
+    <t>931573</t>
+  </si>
+  <si>
+    <t>港股通科技</t>
+  </si>
+  <si>
+    <t>跨境电商出海</t>
+  </si>
+  <si>
+    <t>1：跨境电商出海，全球供应链重构；2：SHEIN/Temu，DTC模式创新；3：50只港股中盘（复用现代服务），平均市值200亿；4：2只ETF，跨境消费视角</t>
+  </si>
+  <si>
+    <t>931233</t>
+  </si>
+  <si>
+    <t>港股通央企红利</t>
+  </si>
+  <si>
+    <t>高端制造央企H股</t>
+  </si>
+  <si>
+    <t>1：央企高股息+港股估值修复双重逻辑；2：高端制造央企H股（中车/中船/中航）；3：50只港股大盘，平均股息率5%+；4：1只ETF，防御属性强</t>
+  </si>
+  <si>
+    <t>931718</t>
+  </si>
+  <si>
+    <t>高端造质量成长50</t>
+  </si>
+  <si>
+    <t>质量+成长双优</t>
+  </si>
+  <si>
+    <t>1：高质量发展导向，规避纯概念炒作；2：质量（ROE&gt;15%）+成长（营收增速&gt;20%）双优；3：50只中大盘股，行业分散；4：1只ETF，Smart Beta策略</t>
+  </si>
+  <si>
+    <t>931752</t>
+  </si>
+  <si>
+    <t>工程机械主题</t>
+  </si>
+  <si>
+    <t>交通装备</t>
+  </si>
+  <si>
+    <t>新能源工程机械（*保留1次*）</t>
+  </si>
+  <si>
+    <t>1：新能源工程机械渗透率提升；2：三一/徐工电动化转型，出口+内需双驱动；3：30只中盘股（复用新能源），平均市值150亿；4：1只主题指数，特种装备视角</t>
+  </si>
+  <si>
+    <t>931495</t>
+  </si>
+  <si>
+    <t>工业互联</t>
+  </si>
+  <si>
+    <t>工业互联网平台</t>
+  </si>
+  <si>
+    <t>1：工业互联网平台，制造业数字化转型枢纽；2：平台层（树根互联/卡奥斯）+应用层；3：50只中盘股，平均市值100亿；4：2只ETF，B2B属性强</t>
+  </si>
+  <si>
+    <t>399244</t>
+  </si>
+  <si>
+    <t>公共指数</t>
+  </si>
+  <si>
+    <t>公共服务数字化</t>
+  </si>
+  <si>
+    <t>1：公共服务数字化，智慧城市/政务云；2：数字政务/智慧交通/智慧医疗；3：50只中盘股，平均市值100亿；4：1只细分指数，政府订单驱动</t>
+  </si>
+  <si>
+    <t>931151</t>
+  </si>
+  <si>
+    <t>光伏产业</t>
+  </si>
+  <si>
+    <t>光伏中游制造</t>
+  </si>
+  <si>
+    <t>1：光伏制造全球主导，技术迭代（BC/HJT）持续；2：组件/逆变器/辅材中游制造集中；3：50只中盘股，平均市值150亿；4：5只ETF，规避上游硅料周期波动</t>
+  </si>
+  <si>
+    <t>931065</t>
+  </si>
+  <si>
+    <t>光伏龙头30</t>
+  </si>
+  <si>
+    <t>各环节龙头集中</t>
+  </si>
+  <si>
+    <t>1：规避产能过剩，聚焦各环节龙头；2：硅料-硅片-电池-组件-逆变器各环节前3名；3：30只中大盘股，集中度高；4：2只ETF，龙头溢价显著</t>
+  </si>
+  <si>
+    <t>931529</t>
+  </si>
+  <si>
+    <t>国企数字经济</t>
+  </si>
+  <si>
+    <t>国企生物育种</t>
+  </si>
+  <si>
+    <t>生物育种</t>
+  </si>
+  <si>
+    <t>1：国企主导生物育种，基因编辑技术突破；2：中国农科院转化标的，CRISPR技术应用；3：50只中盘股，平均市值90亿；4：1只主题指数，前沿技术探索</t>
+  </si>
+  <si>
+    <t>932266</t>
+  </si>
+  <si>
+    <t>国企战略新兴</t>
+  </si>
+  <si>
+    <t>国企检验检测</t>
+  </si>
+  <si>
+    <t>1：国企主导战略新兴服务，检验检测/认证；2：中国检验认证集团等，标准制定者；3：50只大盘股，央企占比80%；4：1只主题指数，政策执行力强</t>
+  </si>
+  <si>
+    <t>931799</t>
+  </si>
+  <si>
+    <t>国寿资产ESG绿色低碳100</t>
+  </si>
+  <si>
+    <t>保险资金绿色投资</t>
+  </si>
+  <si>
+    <t>1：保险资金绿色投资，长期资金入市标杆；2：绿色低碳全产业链，ESG评级前20%；3：100只中大盘股，机构持仓集中；4：1只定制指数，长期资金偏好</t>
+  </si>
+  <si>
+    <t>932422</t>
+  </si>
+  <si>
+    <t>国新港股通央企红</t>
+  </si>
+  <si>
+    <t>绿色能源央企H股</t>
+  </si>
+  <si>
+    <t>1：央企高股息+绿色转型双重逻辑；2：国家电投/三峡集团等绿色能源央企H股；3：50只港股大盘，平均股息率5%+；4：1只ETF，防御+成长兼备</t>
+  </si>
+  <si>
+    <t>932359</t>
+  </si>
+  <si>
+    <t>国新国企人工智能</t>
+  </si>
+  <si>
+    <t>国企主导AI应用</t>
+  </si>
+  <si>
+    <t>1：国企主导AI政务/金融应用，安全可控；2：中国电子/中国电科AI平台，党政市场主导；3：50只大盘股，央企占比90%；4：1只主题指数，政策执行力强</t>
+  </si>
+  <si>
+    <t>932257</t>
+  </si>
+  <si>
+    <t>国新央企小盘</t>
+  </si>
+  <si>
+    <t>央企隐形冠军</t>
+  </si>
+  <si>
+    <t>小盘成长</t>
+  </si>
+  <si>
+    <t>1：央企小盘隐形冠军，补链强链核心；2：细分领域“小巨人”，央企背景技术积累深；3：100只小盘股，平均市值50亿；4：1只主题指数，稀缺性高</t>
+  </si>
+  <si>
+    <t>930660</t>
+  </si>
+  <si>
+    <t>国证钢铁</t>
+  </si>
+  <si>
+    <t>区域特钢龙头</t>
+  </si>
+  <si>
+    <t>1：高端特钢中游制造，传统材料绿色升级；2：华东/华南区域特钢企业，贴近下游需求；3：50只中盘股，平均市值100亿；4：1只ETF（复用新能源），区域特色</t>
+  </si>
+  <si>
+    <t>399368</t>
+  </si>
+  <si>
+    <t>国证军工</t>
+  </si>
+  <si>
+    <t>航空航天/船舶整机</t>
+  </si>
+  <si>
+    <t>下游</t>
+  </si>
+  <si>
+    <t>1：军民融合+自主可控，安全发展核心；2：航空航天/船舶/信息化装备整机；3：100只中大盘股，央企占比80%；4：6只ETF，订单可见性强</t>
+  </si>
+  <si>
+    <t>399365</t>
+  </si>
+  <si>
+    <t>国证粮食</t>
+  </si>
+  <si>
+    <t>种业+粮食加工</t>
+  </si>
+  <si>
+    <t>1：种业振兴行动，粮食安全压舱石；2：种业+粮食加工，隆平高科/金龙鱼等；3：50只中大盘股，平均市值180亿；4：2只ETF，政策刚性需求强</t>
+  </si>
+  <si>
+    <t>399353</t>
+  </si>
+  <si>
+    <t>国证物流</t>
+  </si>
+  <si>
+    <t>智慧物流龙头</t>
+  </si>
+  <si>
+    <t>1：供应链安全，智慧物流基础设施；2：顺丰/京东物流/中国外运，快递+供应链管理；3：100只中大盘股，平均市值200亿；4：3只ETF，龙头集中度高</t>
+  </si>
+  <si>
+    <t>980017</t>
+  </si>
+  <si>
+    <t>国证芯片</t>
+  </si>
+  <si>
+    <t>港股半导体补充</t>
+  </si>
+  <si>
+    <t>1：港股半导体补充，规避A股估值波动；2：中芯国际H/华虹半导体等，与A股互补；3：30只港股，流动性好于纯A股小盘；4：1只ETF，跨境配置价值</t>
+  </si>
+  <si>
+    <t>399395</t>
+  </si>
+  <si>
+    <t>国证有色</t>
+  </si>
+  <si>
+    <t>有色金属龙头</t>
+  </si>
+  <si>
+    <t>1：有色金属战略价值提升，新能源金属需求；2：紫金矿业/洛阳钼业等，铜/锂/钴/镍；3：100只中大盘股，平均市值250亿；4：4只ETF，资源安全属性</t>
+  </si>
+  <si>
+    <t>932056</t>
+  </si>
+  <si>
+    <t>海洋经济</t>
+  </si>
+  <si>
+    <t>蓝色经济+海洋物流</t>
+  </si>
+  <si>
+    <t>1：21世纪海上丝绸之路，蓝色经济；2：海洋物流/海洋装备/海洋渔业；3：50只中盘股，平均市值120亿；4：1只主题指数，区域特色鲜明</t>
+  </si>
+  <si>
+    <t>931393</t>
+  </si>
+  <si>
+    <t>湖北指数</t>
+  </si>
+  <si>
+    <t>长江流域粮食主产区</t>
+  </si>
+  <si>
+    <t>1：湖北农业大省，长江流域粮食主产区；2：水稻/油菜/水产养殖，区域特色鲜明；3：50只中盘股，平均市值100亿；4：1只区域指数，地方政策支持</t>
+  </si>
+  <si>
+    <t>931395</t>
+  </si>
+  <si>
+    <t>沪港深300</t>
+  </si>
+  <si>
+    <t>跨市场消费龙头（*替换成渝经济圈重复*）</t>
+  </si>
+  <si>
+    <t>000300</t>
+  </si>
+  <si>
+    <t>沪深300</t>
+  </si>
+  <si>
+    <t>全市场龙头，政策传导第一梯队</t>
+  </si>
+  <si>
+    <t>1：资本市场核心指数，政策传导第一梯队；2：全行业龙头，覆盖90%新质生产力上市公司；3：300只大盘股，平均市值&gt;800亿；4：30+只ETF，历史18年，国际配置基准</t>
+  </si>
+  <si>
+    <t>931834</t>
+  </si>
+  <si>
+    <t>华福福建100</t>
+  </si>
+  <si>
+    <t>福建制造业升级</t>
+  </si>
+  <si>
+    <t>1：福建传统制造业升级样板；2：纺织/鞋服/建材智能化改造；3：100只中盘股，平均市值120亿；4：1只区域指数（复用高端制造），地方政策支持</t>
+  </si>
+  <si>
+    <t>930614</t>
+  </si>
+  <si>
+    <t>环保50</t>
+  </si>
+  <si>
+    <t>工业绿色化转型（*替换国证钢铁*）</t>
+  </si>
+  <si>
+    <t>931021</t>
+  </si>
+  <si>
+    <t>家电龙头</t>
+  </si>
+  <si>
+    <t>白电全球化</t>
+  </si>
+  <si>
+    <t>1：白电龙头全球化，品牌出海加速；2：美的/格力/海尔，海外收入占比40%+；3：30只大盘股，平均市值800亿；4：4只ETF，全球化竞争力</t>
+  </si>
+  <si>
+    <t>931241</t>
+  </si>
+  <si>
+    <t>家居家电</t>
+  </si>
+  <si>
+    <t>智能家居中游</t>
+  </si>
+  <si>
+    <t>1：智能家居+绿色家电，消费升级+绿色转型；2：美的/海尔/欧派家居，智能化渗透率提升；3：50只中盘股，平均市值250亿；4：3只ETF，地产后周期属性</t>
+  </si>
+  <si>
+    <t>931496</t>
+  </si>
+  <si>
+    <t>交银理财大湾区</t>
+  </si>
+  <si>
+    <t>大湾区智慧农业试点，政策试验田</t>
+  </si>
+  <si>
+    <t>智慧农业</t>
+  </si>
+  <si>
+    <t>1：大湾区智慧农业试点，政策试验田；2：垂直农业/植物工厂/农业机器人；3：30只小盘股，平均市值50亿；4：1只区域指数，前沿探索型</t>
+  </si>
+  <si>
+    <t>930986</t>
+  </si>
+  <si>
+    <t>金融科技</t>
+  </si>
+  <si>
+    <t>数字金融基础设施</t>
+  </si>
+  <si>
+    <t>1：数字金融基础设施，支付/征信/风控；2：蚂蚁/腾讯金融科技/银行科技子公司；3：50只中盘股，平均市值250亿；4：3只ETF，与TMT互补（金融侧重）</t>
+  </si>
+  <si>
+    <t>000698</t>
+  </si>
+  <si>
+    <t>科创100</t>
+  </si>
+  <si>
+    <t>科创板中盘，专精特新密集</t>
+  </si>
+  <si>
+    <t>1：科创板中盘补充，专精特新密集区；2：细分领域冠军（光刻胶/碳纤维/工业机器人）；3：100只科创板中盘，平均市值100亿；4：5只ETF，2023年推出，成长性高</t>
+  </si>
+  <si>
+    <t>000688</t>
+  </si>
+  <si>
+    <t>科创50</t>
+  </si>
+  <si>
+    <t>科创板核心50，“国家队”</t>
+  </si>
+  <si>
+    <t>1：科创板核心资产，“卡脖子”技术攻关主阵地；2：半导体/生物医药/高端装备占比70%；3：50只科创板龙头，平均市值400亿；4：15+只ETF，流动性最佳科创板指数</t>
+  </si>
+  <si>
+    <t>932456</t>
+  </si>
+  <si>
+    <t>科创创业AI</t>
+  </si>
+  <si>
+    <t>AIGC应用</t>
+  </si>
+  <si>
+    <t>科技赋能</t>
+  </si>
+  <si>
+    <t>1：农业AI应用，智慧种植/病虫害识别；2：极飞科技/大疆农业等，无人机+AI；3：50只小盘股，平均市值70亿；4：1只主题指数（复用信息技术），科技交叉</t>
+  </si>
+  <si>
+    <t>931447</t>
+  </si>
+  <si>
+    <t>科技先锋</t>
+  </si>
+  <si>
+    <t>量子/脑机接口前沿</t>
+  </si>
+  <si>
+    <t>1：前沿技术探索，量子/脑机接口/6G；2：科研机构转化标的，技术不确定性高但想象空间大；3：30只小盘股，平均市值60亿；4：1只主题指数，高风险高弹性</t>
+  </si>
+  <si>
+    <t>931897</t>
+  </si>
+  <si>
+    <t>绿色电力</t>
+  </si>
+  <si>
+    <t>风光运营资产</t>
+  </si>
+  <si>
+    <t>1：绿电交易+碳市场机制完善，运营资产受益；2：风电/光伏电站运营，现金流稳定；3：50只小盘股，平均市值80亿；4：2只ETF，高股息属性（3-4%）</t>
+  </si>
+  <si>
+    <t>930948</t>
+  </si>
+  <si>
+    <t>内地地产</t>
+  </si>
+  <si>
+    <t>建材建筑</t>
+  </si>
+  <si>
+    <t>绿色建筑载体（*替换建筑材料重复*）</t>
+  </si>
+  <si>
+    <t>930944</t>
+  </si>
+  <si>
+    <t>内地资源</t>
+  </si>
+  <si>
+    <t>生活资源视角（*替换餐饮指数重复*）</t>
+  </si>
+  <si>
+    <t>930910</t>
+  </si>
+  <si>
+    <t>农牧渔</t>
+  </si>
+  <si>
+    <t>水产养殖现代化</t>
+  </si>
+  <si>
+    <t>1：蛋白供给多元化，水产养殖现代化；2：海大集团/国联水产等，水产+饲料；3：50只中盘股，平均市值100亿；4：1只细分指数，与畜牧互补</t>
+  </si>
+  <si>
+    <t>931778</t>
+  </si>
+  <si>
+    <t>农牧主题</t>
+  </si>
+  <si>
+    <t>养殖下游加工</t>
+  </si>
+  <si>
+    <t>1：养殖下游加工，食品工业化；2：屠宰/食品加工/冷链物流，双汇/龙大等；3：30只中盘股，平均市值80亿；4：1只主题指数，消费端属性强</t>
+  </si>
+  <si>
+    <t>931230</t>
+  </si>
+  <si>
+    <t>汽车零部件</t>
+  </si>
+  <si>
+    <t>智能驾驶+新能源供应链</t>
+  </si>
+  <si>
+    <t>1：智能驾驶+新能源车供应链，全球竞争力；2：拓普集团/德赛西威，单车价值量提升；3：100只中盘股，平均市值150亿；4：4只ETF，中游零部件视角</t>
+  </si>
+  <si>
+    <t>931001</t>
+  </si>
+  <si>
+    <t>汽车指数</t>
+  </si>
+  <si>
+    <t>整车+零部件全覆盖</t>
+  </si>
+  <si>
+    <t>1：整车+零部件全覆盖，电动化转型代表；2：比亚迪/长城/吉利，自主品牌崛起；3：100只中大盘股，平均市值300亿；4：5只ETF，下游整车视角</t>
+  </si>
+  <si>
+    <t>932076</t>
+  </si>
+  <si>
+    <t>全指地产</t>
+  </si>
+  <si>
+    <t>康养地产载体</t>
+  </si>
+  <si>
+    <t>1：康养地产转型，银发经济物理载体；2：万科/保利康养社区布局，传统地产转型样本；3：300只地产股，大盘为主；4：3只ETF，转型逻辑观察窗口</t>
+  </si>
+  <si>
+    <t>000995</t>
+  </si>
+  <si>
+    <t>全指公用</t>
+  </si>
+  <si>
+    <t>水电/燃气全覆盖</t>
+  </si>
+  <si>
+    <t>1：基础保障刚性需求，高股息防御属性；2：水电/燃气/环保公用事业全覆盖；3：200只中大盘股，平均股息率4.5%；4：5只ETF，流动性最佳公用指数</t>
+  </si>
+  <si>
+    <t>932086</t>
+  </si>
+  <si>
+    <t>全指公用行业</t>
+  </si>
+  <si>
+    <t>运营类资产</t>
+  </si>
+  <si>
+    <t>1：与全指公用互补，侧重运营类资产；2：污水处理/垃圾焚烧/危废处理；3：100只中盘股，平均市值120亿；4：2只ETF，环保运营属性强</t>
+  </si>
+  <si>
+    <t>932075</t>
+  </si>
+  <si>
+    <t>全指金融</t>
+  </si>
+  <si>
+    <t>绿色金融支持</t>
+  </si>
+  <si>
+    <t>1：绿色金融支持，碳中和债/转型金融工具创新；2：银行/券商绿色信贷/绿色债券承销；3：300只金融股，大盘为主；4：3只ETF，资金端保障逻辑</t>
+  </si>
+  <si>
+    <t>932077</t>
+  </si>
+  <si>
+    <t>全指能源行业</t>
+  </si>
+  <si>
+    <t>传统+新能源过渡</t>
+  </si>
+  <si>
+    <t>能源安全</t>
+  </si>
+  <si>
+    <t>1：传统能源+新能源过渡，能源安全底线；2：煤炭/石油/天然气+新能源，保障性电源；3：100只中大盘股，平均市值300亿；4：3只ETF，安全属性突出</t>
+  </si>
+  <si>
+    <t>932085</t>
+  </si>
+  <si>
+    <t>全指通信行业</t>
+  </si>
+  <si>
+    <t>5G/卫星通信</t>
+  </si>
+  <si>
+    <t>通信保障</t>
+  </si>
+  <si>
+    <t>1：5G/卫星通信基础设施，数字时代基础保障；2：中国移动/中国电信/中国卫通；3：50只大盘股，平均市值800亿；4：2只ETF，高股息（5%+）</t>
+  </si>
+  <si>
+    <t>931071</t>
+  </si>
+  <si>
+    <t>人工智能</t>
+  </si>
+  <si>
+    <t>AI大模型+算力+应用</t>
+  </si>
+  <si>
+    <t>1：“人工智能+"行动写入政府工作报告；2：大模型-算力-应用全链条，科大讯飞/商汤等；3：100只中盘股，平均市值180亿；4：8只ETF，2023年政策催化密集</t>
+  </si>
+  <si>
+    <t>931652</t>
+  </si>
+  <si>
+    <t>厦门指数</t>
+  </si>
+  <si>
+    <t>厦门港口经济+制造</t>
+  </si>
+  <si>
+    <t>1：厦门港口经济+制造业转型样板；2：半导体封测/新能源材料/精密制造；3：50只中盘股，区域龙头集中；4：1只区域指数，流动性适中</t>
+  </si>
+  <si>
+    <t>399242</t>
+  </si>
+  <si>
+    <t>商务指数</t>
+  </si>
+  <si>
+    <t>专业服务现代化</t>
+  </si>
+  <si>
+    <t>1：专业服务业现代化，法律/会计/咨询升级；2：专业服务龙头，知识密集型；3：50只中盘股，平均市值120亿；4：1只细分指数，生产性服务代表</t>
+  </si>
+  <si>
+    <t>000010</t>
+  </si>
+  <si>
+    <t>上证180</t>
+  </si>
+  <si>
+    <t>沪市制造龙头</t>
+  </si>
+  <si>
+    <t>1：沪市核心资产，国企改革重点标的；2：制造龙头集中（中芯/中车/商飞）；3：180只大盘股，平均市值500亿+；4：8只ETF，流动性稳定</t>
+  </si>
+  <si>
     <t>000009</t>
   </si>
   <si>
     <t>上证380</t>
   </si>
   <si>
-    <t>高端制造与新质生产力</t>
-  </si>
-  <si>
-    <t>高端制造</t>
-  </si>
-  <si>
     <t>沪市中盘制造</t>
   </si>
   <si>
-    <t>中盘</t>
-  </si>
-  <si>
     <t>1：沪市中盘成长代表，专精特新聚集；2：工业母机/新材料/精密仪器占比35%；3：380只中盘股，平均市值150亿；4：3只ETF，与中证500互补（沪市侧重）</t>
   </si>
   <si>
-    <t>000010</t>
-  </si>
-  <si>
-    <t>上证180</t>
-  </si>
-  <si>
-    <t>沪市制造龙头</t>
-  </si>
-  <si>
-    <t>大盘</t>
-  </si>
-  <si>
-    <t>1：沪市核心资产，国企改革重点标的；2：制造龙头集中（中芯/中车/商飞）；3：180只大盘股，平均市值500亿+；4：8只ETF，流动性稳定</t>
-  </si>
-  <si>
     <t>000016</t>
   </si>
   <si>
     <t>上证50</t>
   </si>
   <si>
-    <t>宽基基准层</t>
-  </si>
-  <si>
-    <t>宽基基准</t>
-  </si>
-  <si>
     <t>超大盘金融+核心资产</t>
   </si>
   <si>
@@ -113,55 +1310,166 @@
     <t>上证材料</t>
   </si>
   <si>
-    <t>传统优势产业升级</t>
-  </si>
-  <si>
-    <t>传统升级</t>
-  </si>
-  <si>
     <t>基础材料龙头</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
-    <t>000300</t>
-  </si>
-  <si>
-    <t>沪深300</t>
-  </si>
-  <si>
-    <t>全市场龙头，政策传导第一梯队</t>
-  </si>
-  <si>
-    <t>1：资本市场核心指数，政策传导第一梯队；2：全行业龙头，覆盖90%新质生产力上市公司；3：300只大盘股，平均市值&gt;800亿；4：30+只ETF，历史18年，国际配置基准</t>
-  </si>
-  <si>
-    <t>000688</t>
-  </si>
-  <si>
-    <t>科创50</t>
-  </si>
-  <si>
-    <t>科创板核心50，“国家队”</t>
-  </si>
-  <si>
-    <t>小盘</t>
-  </si>
-  <si>
-    <t>1：科创板核心资产，“卡脖子”技术攻关主阵地；2：半导体/生物医药/高端装备占比70%；3：50只科创板龙头，平均市值400亿；4：15+只ETF，流动性最佳科创板指数</t>
-  </si>
-  <si>
-    <t>000698</t>
-  </si>
-  <si>
-    <t>科创100</t>
-  </si>
-  <si>
-    <t>科创板中盘，专精特新密集</t>
-  </si>
-  <si>
-    <t>1：科创板中盘补充，专精特新密集区；2：细分领域冠军（光刻胶/碳纤维/工业机器人）；3：100只科创板中盘，平均市值100亿；4：5只ETF，2023年推出，成长性高</t>
+    <t>399330</t>
+  </si>
+  <si>
+    <t>深证100</t>
+  </si>
+  <si>
+    <t>深市硬科技龙头</t>
+  </si>
+  <si>
+    <t>1：深市创新标杆，科技自立自强代表；2：比亚迪/迈瑞/宁德等硬科技龙头；3：100只大盘股，科技属性强于上证180；4：6只ETF，成长性突出</t>
+  </si>
+  <si>
+    <t>399633</t>
+  </si>
+  <si>
+    <t>深证300</t>
+  </si>
+  <si>
+    <t>深市科技龙头</t>
+  </si>
+  <si>
+    <t>1：深市科技龙头，华为链/腾讯系核心标的；2：电子/通信/计算机占比70%，硬科技特色；3：300只大盘股，平均市值400亿；4：4只ETF，与沪深300互补（科技侧重）</t>
+  </si>
+  <si>
+    <t>930701</t>
+  </si>
+  <si>
+    <t>深证F60</t>
+  </si>
+  <si>
+    <t>深市细分制造龙头</t>
+  </si>
+  <si>
+    <t>1：深市细分制造龙头，隐形冠军代表；2：精密仪器/传感器/特种材料等“小而美”标的；3：60只中盘股，平均市值100亿；4：1只ETF，流动性适中</t>
+  </si>
+  <si>
+    <t>399441</t>
+  </si>
+  <si>
+    <t>生物医药</t>
+  </si>
+  <si>
+    <t>生物制品/基因治疗</t>
+  </si>
+  <si>
+    <t>1：生物经济写入十四五规划，前沿技术突破；2：生物制品/基因治疗/细胞治疗；3：100只中大盘股，药明康德/智飞生物等；4：5只ETF，技术壁垒高</t>
+  </si>
+  <si>
+    <t>399434</t>
+  </si>
+  <si>
+    <t>数字传媒</t>
+  </si>
+  <si>
+    <t>游戏/短视频内容</t>
+  </si>
+  <si>
+    <t>1：AIGC内容生成，降本增效显著；2：游戏/短视频/数字出版，腾讯/字节生态；3：50只中盘股（复用文化消费），平均市值200亿；4：3只ETF，上游内容视角</t>
+  </si>
+  <si>
+    <t>931582</t>
+  </si>
+  <si>
+    <t>数字经济</t>
+  </si>
+  <si>
+    <t>数字产业化+产业数字化</t>
+  </si>
+  <si>
+    <t>1：数字产业化+产业数字化双路径；2：数字内容/数字支付/数字政务等应用层；3：100只中大盘股，平均市值200亿；4：3只ETF，消费端属性强</t>
+  </si>
+  <si>
+    <t>931559</t>
+  </si>
+  <si>
+    <t>苏银理财长三角</t>
+  </si>
+  <si>
+    <t>长三角生态绿色一体化</t>
+  </si>
+  <si>
+    <t>1：长三角生态绿色一体化，示范区建设；2：环保/水利/绿色基建，区域协同项目；3：50只中盘股，沪苏浙皖企业；4：1只区域指数，政策试验田</t>
+  </si>
+  <si>
+    <t>931478</t>
+  </si>
+  <si>
+    <t>苏州绿色发展</t>
+  </si>
+  <si>
+    <t>地方绿色转型样板</t>
+  </si>
+  <si>
+    <t>区域特色</t>
+  </si>
+  <si>
+    <t>1：地方绿色转型样板，可复制性强；2：绿色制造/循环经济/环保服务；3：50只中盘股，苏州本地企业；4：1只区域指数，地方政策试验田</t>
+  </si>
+  <si>
+    <t>931289</t>
+  </si>
+  <si>
+    <t>碳中和债</t>
+  </si>
+  <si>
+    <t>绿色债券</t>
+  </si>
+  <si>
+    <t>1：绿色金融工具创新，碳中和债发行加速；2：绿色债券发行人（央企/地方国企）；3：50只大盘股，债券指数衍生；4：1只债券指数，资金端视角</t>
+  </si>
+  <si>
+    <t>931594</t>
+  </si>
+  <si>
+    <t>卫星产业</t>
+  </si>
+  <si>
+    <t>低空经济基础设施</t>
+  </si>
+  <si>
+    <t>1：低空经济写入政府工作报告，十五五新增长点；2：卫星制造/发射服务/地面设备；3：50只小盘股，商业航天企业占比70%；4：2只ETF，政策催化密集</t>
+  </si>
+  <si>
+    <t>931585</t>
+  </si>
+  <si>
+    <t>卫星导航</t>
+  </si>
+  <si>
+    <t>北斗应用层</t>
+  </si>
+  <si>
+    <t>1：北斗规模化应用，位置服务基础设施；2：芯片-终端-应用全链条，精准农业/智能驾驶受益；3：50只中盘股，平均市值150亿；4：3只ETF，应用场景持续拓展</t>
+  </si>
+  <si>
+    <t>930927</t>
+  </si>
+  <si>
+    <t>稳健成长</t>
+  </si>
+  <si>
+    <t>质量+成长双优，规避纯周期</t>
+  </si>
+  <si>
+    <t>1：高质量发展导向，规避纯周期波动；2：质量+成长双优（ROE&gt;15%+营收增速&gt;10%）；3：100只中大盘股，行业分散度高；4：2只ETF，Smart Beta代表</t>
+  </si>
+  <si>
+    <t>930598</t>
+  </si>
+  <si>
+    <t>稀土产业</t>
+  </si>
+  <si>
+    <t>永磁材料上游</t>
+  </si>
+  <si>
+    <t>1：战略资源安全，永磁材料刚性需求；2：稀土开采-分离-永磁材料全链条；3：50只中盘股，北方稀土/金力永磁等；4：3只ETF（复用新能源），上游资源视角</t>
   </si>
   <si>
     <t>000813</t>
@@ -176,6 +1484,471 @@
     <t>1：高端化工材料（POE/EVA），新能源配套；2：万华化学/卫星化学，新材料占比提升；3：50只中盘股（复用传统升级），平均市值150亿；4：3只ETF，中游化工视角</t>
   </si>
   <si>
+    <t>930812</t>
+  </si>
+  <si>
+    <t>细分机械</t>
+  </si>
+  <si>
+    <t>工业母机智能化</t>
+  </si>
+  <si>
+    <t>机械智能化</t>
+  </si>
+  <si>
+    <t>1：工业母机智能化，数控化率提升；2：机器人/数控机床/激光设备；3：50只中盘股，平均市值100亿；4：1只细分指数，传统机械升级</t>
+  </si>
+  <si>
+    <t>930814</t>
+  </si>
+  <si>
+    <t>细分医药</t>
+  </si>
+  <si>
+    <t>眼科/牙科/医美</t>
+  </si>
+  <si>
+    <t>1：细分领域冠军，眼科/牙科/医美等消费升级；2：爱尔眼科/通策医疗/爱美客等；3：50只中盘股，平均市值200亿；4：2只ETF，消费属性强</t>
+  </si>
+  <si>
+    <t>931167</t>
+  </si>
+  <si>
+    <t>先进制造100</t>
+  </si>
+  <si>
+    <t>传统制造智能化（*替换厦门指数*）</t>
+  </si>
+  <si>
+    <t>931480</t>
+  </si>
+  <si>
+    <t>线上消费</t>
+  </si>
+  <si>
+    <t>电商/本地生活</t>
+  </si>
+  <si>
+    <t>1：数字经济与消费融合，平台经济常态化；2：美团/拼多多/快手，本地生活+电商；3：50只中盘股，平均市值300亿；4：3只ETF（复用信息技术），消费端属性</t>
+  </si>
+  <si>
+    <t>930709</t>
+  </si>
+  <si>
+    <t>香港证券</t>
+  </si>
+  <si>
+    <t>港股种业平台</t>
+  </si>
+  <si>
+    <t>种业</t>
+  </si>
+  <si>
+    <t>1：种业并购整合，港股种业平台；2：先正达集团H股，全球种业巨头；3：30只港股，种业占比40%；4：1只跨境指数，全球视野</t>
+  </si>
+  <si>
+    <t>931697</t>
+  </si>
+  <si>
+    <t>消费50策略</t>
+  </si>
+  <si>
+    <t>充电桩/换电服务</t>
+  </si>
+  <si>
+    <t>1：新能源消费端培育，充电桩/换电写入规划；2：充电桩运营商/换电服务商/充电设备；3：50只中盘股，特来电/星星充电等；4：1只ETF，消费属性强于制造端</t>
+  </si>
+  <si>
+    <t>931494</t>
+  </si>
+  <si>
+    <t>消费电子</t>
+  </si>
+  <si>
+    <t>智能硬件上游</t>
+  </si>
+  <si>
+    <t>1：智能硬件创新，AR/VR/可穿戴设备；2：歌尔股份/立讯精密等，苹果链+创新硬件；3：50只中盘股，平均市值200亿；4：3只ETF，科技+消费融合</t>
+  </si>
+  <si>
+    <t>H30597</t>
+  </si>
+  <si>
+    <t>新材料</t>
+  </si>
+  <si>
+    <t>化工材料</t>
+  </si>
+  <si>
+    <t>高性能纤维/电子化学品</t>
+  </si>
+  <si>
+    <t>1：高性能纤维/电子化学品，“卡脖子”材料国产替代；2：碳纤维/芳纶/光刻胶/电子特气；3：50只中盘股，平均市值150亿；4：2只ETF，上游材料视角</t>
+  </si>
+  <si>
+    <t>000941</t>
+  </si>
+  <si>
+    <t>全产业链龙头</t>
+  </si>
+  <si>
+    <t>1：双碳目标核心载体，风光储写入十五五规划；2：光伏/风电/储能全产业链龙头；3：100只大盘股，宁德/隆基/阳光电源等；4：10+只ETF，历史10年+，流动性最佳</t>
+  </si>
+  <si>
+    <t>931165</t>
+  </si>
+  <si>
+    <t>新兴科技100</t>
+  </si>
+  <si>
+    <t>科技赋能传统（*替换华福福建100*）</t>
+  </si>
+  <si>
+    <t>930796</t>
+  </si>
+  <si>
+    <t>信息安全</t>
+  </si>
+  <si>
+    <t>网络安全+数据安全</t>
+  </si>
+  <si>
+    <t>1：网络安全法+数据安全法，刚性合规需求；2：防火墙/IDS/数据加密/身份认证；3：50只中盘股，平均市值100亿；4：3只ETF，政策驱动型</t>
+  </si>
+  <si>
+    <t>932039</t>
+  </si>
+  <si>
+    <t>央企股东回报</t>
+  </si>
+  <si>
+    <t>高股息转型标的</t>
+  </si>
+  <si>
+    <t>高股息</t>
+  </si>
+  <si>
+    <t>1：央企市值管理，高股息策略写入考核；2：传统产业升级标的，现金流稳定；3：50只大盘股，平均股息率5%+；4：3只ETF，防御属性强</t>
+  </si>
+  <si>
+    <t>932038</t>
+  </si>
+  <si>
+    <t>央企科技引领</t>
+  </si>
+  <si>
+    <t>科技赋能传统</t>
+  </si>
+  <si>
+    <t>央企转型</t>
+  </si>
+  <si>
+    <t>1：央企科技赋能传统产业升级；2：中国宝武工业互联网/中国建材新材料；3：50只大盘股，平均市值600亿；4：2只ETF，科技+传统融合</t>
+  </si>
+  <si>
+    <t>931837</t>
+  </si>
+  <si>
+    <t>央企现代产业</t>
+  </si>
+  <si>
+    <t>央企主导升级</t>
+  </si>
+  <si>
+    <t>1：央企主导产业升级，执行力强于民企；2：高端制造央企（中国中车/中国船舶/中国商飞）；3：50只大盘股，平均市值600亿；4：2只ETF，高股息+成长双属性</t>
+  </si>
+  <si>
+    <t>932037</t>
+  </si>
+  <si>
+    <t>央企现代能源</t>
+  </si>
+  <si>
+    <t>传统能源清洁化</t>
+  </si>
+  <si>
+    <t>1：央企主导传统能源清洁化转型；2：国家能源集团/中国华能新能源装机提升；3：50只大盘股，平均市值500亿；4：2只ETF，转型执行力强</t>
+  </si>
+  <si>
+    <t>930846</t>
+  </si>
+  <si>
+    <t>医疗器械</t>
+  </si>
+  <si>
+    <t>高端器械国产替代，迈瑞/联影等龙头</t>
+  </si>
+  <si>
+    <t>1：高端医疗器械国产替代，进口替代加速；2：影像设备/体外诊断/高值耗材；3：50只中盘股，迈瑞/联影等龙头；4：3只ETF，技术壁垒高</t>
+  </si>
+  <si>
+    <t>930853</t>
+  </si>
+  <si>
+    <t>医药100</t>
+  </si>
+  <si>
+    <t>医药细分龙头全覆盖</t>
+  </si>
+  <si>
+    <t>1：医药细分龙头全覆盖，避免单一环节风险；2：创新药30%+器械30%+CXO20%+中药20%；3：100只中大盘股，平均市值180亿；4：4只ETF，分散度高</t>
+  </si>
+  <si>
+    <t>931140</t>
+  </si>
+  <si>
+    <t>医药50</t>
+  </si>
+  <si>
+    <t>研发驱动型创新药</t>
+  </si>
+  <si>
+    <t>1：规避集采敏感标的，聚焦研发驱动型；2：创新药企（恒瑞/百济/信达），管线丰富；3：50只中盘股，平均市值300亿；4：3只ETF，与中证医药互补（更聚焦创新）</t>
+  </si>
+  <si>
+    <t>931992</t>
+  </si>
+  <si>
+    <t>疫苗生物</t>
+  </si>
+  <si>
+    <t>疫苗+mRNA技术</t>
+  </si>
+  <si>
+    <t>1：公共卫生安全战略物资，mRNA技术突破；2：疫苗+生物制品，智飞/康希诺/沃森等；3：30只小盘股，平均市值80亿；4：2只ETF，技术迭代快</t>
+  </si>
+  <si>
+    <t>930959</t>
+  </si>
+  <si>
+    <t>银河99</t>
+  </si>
+  <si>
+    <t>基建+高端制造融合（*替换中证基建重复*）</t>
+  </si>
+  <si>
+    <t>930819</t>
+  </si>
+  <si>
+    <t>有色金属</t>
+  </si>
+  <si>
+    <t>铜/铝等基础金属（*替换稀土产业*）</t>
+  </si>
+  <si>
+    <t>931892</t>
+  </si>
+  <si>
+    <t>有色矿业</t>
+  </si>
+  <si>
+    <t>锂/钴/镍资源端</t>
+  </si>
+  <si>
+    <t>1：资源安全战略，锂/钴/镍自主可控；2：新能源金属资源端，紫金/赣锋等龙头；3：50只中盘股，平均市值200亿；4：2只ETF，与稀土产业互补（更广资源覆盖）</t>
+  </si>
+  <si>
+    <t>930851</t>
+  </si>
+  <si>
+    <t>云计算</t>
+  </si>
+  <si>
+    <t>云服务厂商集中</t>
+  </si>
+  <si>
+    <t>1：东数西算工程，算力基础设施建设；2：IaaS/PaaS/SaaS全栈，阿里云/腾讯云/华为云生态；3：50只中盘股，平均市值200亿；4：5只ETF，政企上云持续受益</t>
+  </si>
+  <si>
+    <t>931469</t>
+  </si>
+  <si>
+    <t>云计算50</t>
+  </si>
+  <si>
+    <t>云计算细分龙头</t>
+  </si>
+  <si>
+    <t>1：聚焦云计算核心标的，规避纯概念股；2：50只云计算龙头，IaaS/PaaS/SaaS均衡；3：50只中大盘股，集中度高；4：2只ETF，与云计算指数互补（更聚焦）</t>
+  </si>
+  <si>
+    <t>931554</t>
+  </si>
+  <si>
+    <t>长江保护</t>
+  </si>
+  <si>
+    <t>长江生态修复</t>
+  </si>
+  <si>
+    <t>1：长江经济带生态修复，流域治理标杆；2：水环境治理/生态修复/环保设备；3：50只中盘股，长江沿线企业集中；4：1只区域指数（复用新能源），政策持续性强</t>
+  </si>
+  <si>
+    <t>931139</t>
+  </si>
+  <si>
+    <t>长三角</t>
+  </si>
+  <si>
+    <t>长三角数字经济集群</t>
+  </si>
+  <si>
+    <t>1：长三角数字经济集群，一体化示范区；2：上海（芯片）-杭州（电商）-苏州（制造）协同；3：100只中大盘股，平均市值250亿；4：2只区域指数，政策高地</t>
+  </si>
+  <si>
+    <t>932068</t>
+  </si>
+  <si>
+    <t>长寿经济</t>
+  </si>
+  <si>
+    <t>银发经济终端</t>
+  </si>
+  <si>
+    <t>1：银发经济写入政府工作报告，人口结构变化；2：养老社区/康复器械/慢病管理；3：50只中盘股，平均市值120亿；4：2只ETF，需求刚性增长</t>
+  </si>
+  <si>
+    <t>931132</t>
+  </si>
+  <si>
+    <t>浙江新动能</t>
+  </si>
+  <si>
+    <t>浙江数字经济+制造双引擎</t>
+  </si>
+  <si>
+    <t>1：浙江“数字经济+先进制造”双引擎；2：杭州/宁波高端制造集群（海康/大华/舜宇）；3：100只中盘股，区域特色鲜明；4：1只ETF，地方政策试验田</t>
+  </si>
+  <si>
+    <t>930850</t>
+  </si>
+  <si>
+    <t>智能制造</t>
+  </si>
+  <si>
+    <t>工业4.0+AI融合</t>
+  </si>
+  <si>
+    <t>1：工业4.0+AI融合，“数实融合”核心载体；2：工业机器人/智能工厂/数字孪生；3：100只中盘股，平均市值180亿；4：4只ETF，2021年推出，契合新质生产力</t>
+  </si>
+  <si>
+    <t>931382</t>
+  </si>
+  <si>
+    <t>智选300 ESG领先</t>
+  </si>
+  <si>
+    <t>供应链ESG管理</t>
+  </si>
+  <si>
+    <t>ESG</t>
+  </si>
+  <si>
+    <t>1：供应链ESG管理，国际竞争力提升；2：ESG评级前20%企业，绿色供应链实践者；3：100只大盘股，平均市值400亿；4：2只ETF，国际接轨</t>
+  </si>
+  <si>
+    <t>932042</t>
+  </si>
+  <si>
+    <t>智选航空科技</t>
+  </si>
+  <si>
+    <t>大飞机产业链</t>
+  </si>
+  <si>
+    <t>1：大飞机专项，C919商业化加速；2：航空发动机/机身结构/航电系统；3：50只中盘股，产业链配套企业集中；4：1只ETF，主题性强</t>
+  </si>
+  <si>
+    <t>931785</t>
+  </si>
+  <si>
+    <t>智选沪深港科技50</t>
+  </si>
+  <si>
+    <t>内容生产</t>
+  </si>
+  <si>
+    <t>影视科技融合（*替换中证影视重复*）</t>
+  </si>
+  <si>
+    <t>399612</t>
+  </si>
+  <si>
+    <t>中创100</t>
+  </si>
+  <si>
+    <t>创业板中盘硬科技</t>
+  </si>
+  <si>
+    <t>1：创业板改革深化，硬科技中盘标的；2：半导体设备/工业软件/高端材料；3：100只创业板中盘，平均市值120亿；4：2只ETF，波动率适中</t>
+  </si>
+  <si>
+    <t>931456</t>
+  </si>
+  <si>
+    <t>中国教育</t>
+  </si>
+  <si>
+    <t>职业教育+教育科技</t>
+  </si>
+  <si>
+    <t>教育</t>
+  </si>
+  <si>
+    <t>1：职业教育+教育科技，人口素质提升刚需；2：中公教育/传智教育，职教+IT培训；3：30只中盘股，平均市值80亿；4：1只主题指数，政策规范化后复苏</t>
+  </si>
+  <si>
+    <t>931790</t>
+  </si>
+  <si>
+    <t>中韩半导体</t>
+  </si>
+  <si>
+    <t>中韩半导体互补</t>
+  </si>
+  <si>
+    <t>1：中韩半导体产业链互补，技术合作深化；2：设备/材料/封测环节协同，规避地缘风险；3：30只中盘股，A股+韩股；4：1只跨境指数，全球化视角</t>
+  </si>
+  <si>
+    <t>931789</t>
+  </si>
+  <si>
+    <t>中韩新能车</t>
+  </si>
+  <si>
+    <t>中韩产业链协同</t>
+  </si>
+  <si>
+    <t>1：中韩产业链协同，全球化布局；2：电池材料（隔膜/电解液）中韩企业互补；3：30只中盘股，A股+韩股；4：1只跨境指数，产业链视角</t>
+  </si>
+  <si>
+    <t>931725</t>
+  </si>
+  <si>
+    <t>中华联合优质成长</t>
+  </si>
+  <si>
+    <t>第三方检测认证</t>
+  </si>
+  <si>
+    <t>检验检测</t>
+  </si>
+  <si>
+    <t>1：质量强国，检验检测认证国产替代；2：华测检测/谱尼测试等第三方检测；3：50只中盘股，平均市值100亿；4：1只定制指数，细分领域稀缺</t>
+  </si>
+  <si>
+    <t>399005</t>
+  </si>
+  <si>
+    <t>中小100</t>
+  </si>
+  <si>
+    <t>深市中盘科技制造特色</t>
+  </si>
+  <si>
+    <t>1：深市“隐形冠军”代表；2：科技制造特色鲜明（电子/通信/机械）；3：100只中盘股，平均市值200亿；4：3只ETF，与中证500互补（深市侧重）</t>
+  </si>
+  <si>
     <t>000852</t>
   </si>
   <si>
@@ -188,6 +1961,33 @@
     <t>1：小微主体扶持，注册制改革受益；2：小盘成长股，“小巨人”占比25%；3：1000只小盘股，平均市值50-100亿；4：15+只ETF，2022年推出后流动性显著改善</t>
   </si>
   <si>
+    <t>932000</t>
+  </si>
+  <si>
+    <t>中证2000</t>
+  </si>
+  <si>
+    <t>微盘股流动性改善后新基准</t>
+  </si>
+  <si>
+    <t>微盘</t>
+  </si>
+  <si>
+    <t>1：小微主体流动性改善工程核心标的；2：微盘股中质量较好标的，剔除ST/退市风险股；3：2000只微盘股，平均市值&lt;50亿；4：5只ETF，2023年推出，政策扶持明确</t>
+  </si>
+  <si>
+    <t>000905</t>
+  </si>
+  <si>
+    <t>中证500</t>
+  </si>
+  <si>
+    <t>中盘成长，专精特新聚集</t>
+  </si>
+  <si>
+    <t>1：专精特新聚集地，补链强链核心载体；2：中盘成长股，细分领域冠军占比40%；3：500只中盘股，平均市值150-300亿；4：20+只ETF，量化策略首选</t>
+  </si>
+  <si>
     <t>000903</t>
   </si>
   <si>
@@ -200,16 +2000,73 @@
     <t>1：A股国际化代表，纳入MSCI核心标的；2：各行业前10%龙头，科技+制造+消费均衡；3：100只大盘股，外资持仓集中区；4：5只ETF，适合跨境配置</t>
   </si>
   <si>
-    <t>000905</t>
-  </si>
-  <si>
-    <t>中证500</t>
-  </si>
-  <si>
-    <t>中盘成长，专精特新聚集</t>
-  </si>
-  <si>
-    <t>1：专精特新聚集地，补链强链核心载体；2：中盘成长股，细分领域冠军占比40%；3：500只中盘股，平均市值150-300亿；4：20+只ETF，量化策略首选</t>
+    <t>000998</t>
+  </si>
+  <si>
+    <t>中证TMT</t>
+  </si>
+  <si>
+    <t>电子+计算机+通信+传媒</t>
+  </si>
+  <si>
+    <t>1：数字经济基础设施，新基建核心；2：电子+计算机+通信+传媒全覆盖；3：100只大盘股，平均市值350亿；4：6只ETF，流动性最佳TMT指数</t>
+  </si>
+  <si>
+    <t>399997</t>
+  </si>
+  <si>
+    <t>中证白酒</t>
+  </si>
+  <si>
+    <t>传统消费龙头</t>
+  </si>
+  <si>
+    <t>1：传统消费龙头，品牌价值稳固；2：茅台/五粮液/泸州老窖，高端白酒集中度提升；3：20只大盘股，平均市值1500亿；4：10+只ETF，流动性最佳消费指数</t>
+  </si>
+  <si>
+    <t>931865</t>
+  </si>
+  <si>
+    <t>中证半导</t>
+  </si>
+  <si>
+    <t>半导体全产业链</t>
+  </si>
+  <si>
+    <t>1：半导体全产业链支持，十五五资源倾斜；2：设计-制造-封测-设备全覆盖，龙头集中；3：50只中大盘股，平均市值300亿；4：8只ETF，流动性最佳半导体指数</t>
+  </si>
+  <si>
+    <t>930707</t>
+  </si>
+  <si>
+    <t>中证畜牧</t>
+  </si>
+  <si>
+    <t>畜禽育种+规模化养殖</t>
+  </si>
+  <si>
+    <t>1：生物育种产业化落地，畜禽种源自主可控；2：牧原/温氏/圣农等规模化养殖龙头；3：50只小盘股，平均市值80亿；4：2只ETF，周期属性弱化（规模化）</t>
+  </si>
+  <si>
+    <t>中证传媒</t>
+  </si>
+  <si>
+    <t>全市场传媒覆盖（*替换数字传媒重复*）</t>
+  </si>
+  <si>
+    <t>930606</t>
+  </si>
+  <si>
+    <t>中证钢铁</t>
+  </si>
+  <si>
+    <t>高端特钢绿色升级</t>
+  </si>
+  <si>
+    <t>传统转型</t>
+  </si>
+  <si>
+    <t>1：传统材料绿色升级，高端特钢国产替代；2：轴承钢/模具钢/硅钢等高端品种；3：50只大盘股，宝钢/中信特钢等；4：2只ETF，转型逻辑清晰</t>
   </si>
   <si>
     <t>000922</t>
@@ -227,397 +2084,178 @@
     <t>1：高股息策略写入中央经济工作会议；2：现金流稳定行业（公用/银行/交运）；3：100只高股息股，大盘+中盘均衡；4：12只ETF，防御属性强</t>
   </si>
   <si>
+    <t>000827</t>
+  </si>
+  <si>
+    <t>中证环保</t>
+  </si>
+  <si>
+    <t>环保设备+运营，双碳目标刚性需求</t>
+  </si>
+  <si>
+    <t>1：环保设备+运营，双碳目标刚性需求；2：碧水源/高能环境等，技术+运营双轮；3：50只小盘股，平均市值80亿；4：2只ETF，成长性高于传统公用</t>
+  </si>
+  <si>
+    <t>931866</t>
+  </si>
+  <si>
+    <t>中证机床</t>
+  </si>
+  <si>
+    <t>工业母机专项</t>
+  </si>
+  <si>
+    <t>1：工业母机“04专项”延续，制造业基础保障；2：数控机床/加工中心/精密测量仪器；3：50只中盘股，国产高端机床占比60%；4：1只ETF，细分领域稀缺标的</t>
+  </si>
+  <si>
+    <t>930608</t>
+  </si>
+  <si>
+    <t>中证基建</t>
+  </si>
+  <si>
+    <t>新基建+传统基建</t>
+  </si>
+  <si>
+    <t>1：装配式建筑+智能建造，传统建筑升级；2：钢结构/PC构件/智能施工设备；3：100只中大盘股（复用公用保障），平均市值200亿；4：4只ETF，中游建造视角</t>
+  </si>
+  <si>
+    <t>930633</t>
+  </si>
+  <si>
+    <t>中证旅游</t>
+  </si>
+  <si>
+    <t>文旅融合</t>
+  </si>
+  <si>
+    <t>1：文旅融合+入境游复苏，服务消费弹性大；2：中国中免/宋城演艺/锦江酒店；3：50只中盘股，平均市值150亿；4：3只ETF，疫后复苏逻辑</t>
+  </si>
+  <si>
+    <t>000949</t>
+  </si>
+  <si>
+    <t>中证农业</t>
+  </si>
+  <si>
+    <t>农业现代化综合</t>
+  </si>
+  <si>
+    <t>1：农业现代化综合代表，智慧农业占比提升；2：种业30%+养殖30%+农机20%+智慧农业20%；3：100只中盘股，平均市值120亿；4：4只ETF，分散度高</t>
+  </si>
+  <si>
+    <t>930601</t>
+  </si>
+  <si>
+    <t>中证软件</t>
+  </si>
+  <si>
+    <t>基础软件+工业软件</t>
+  </si>
+  <si>
+    <t>1：基础软件+工业软件国产化，卡脖子环节；2：操作系统/数据库/EDA/工业CAD；3：100只中盘股，平均市值150亿；4：4只ETF，信创核心受益</t>
+  </si>
+  <si>
+    <t>930961</t>
+  </si>
+  <si>
+    <t>中证上游</t>
+  </si>
+  <si>
+    <t>资源开采/原材料（*已替换长江保护*）</t>
+  </si>
+  <si>
+    <t>930902</t>
+  </si>
+  <si>
+    <t>中证数据</t>
+  </si>
+  <si>
+    <t>数据要素市场化</t>
+  </si>
+  <si>
+    <t>1：数据要素市场化，“数据二十条”落地；2：数据采集-处理-交易-应用，交易所挂牌标的；3：50只小盘股，平均市值80亿；4：2只ETF，前沿探索型</t>
+  </si>
+  <si>
+    <t>930963</t>
+  </si>
+  <si>
+    <t>中证下游</t>
+  </si>
+  <si>
+    <t>消费端应用（*已替换苏州绿色发展*）</t>
+  </si>
+  <si>
+    <t>932365</t>
+  </si>
+  <si>
+    <t>中证现金流</t>
+  </si>
+  <si>
+    <t>高现金流服务业</t>
+  </si>
+  <si>
+    <t>1：高现金流服务业，抗周期属性强；2：物业/检测/人力资源，经营性现金流稳定；3：100只小盘股，平均市值60亿；4：2只ETF，防御属性突出</t>
+  </si>
+  <si>
+    <t>931247</t>
+  </si>
+  <si>
+    <t>中证信创</t>
+  </si>
+  <si>
+    <t>信创全栈</t>
+  </si>
+  <si>
+    <t>1：信息技术应用创新，安全可控刚性需求；2：CPU（龙芯/飞腾）-OS（麒麟）-数据库（达梦）全栈；3：100只中盘股，平均市值120亿；4：6只ETF，党政→行业扩散逻辑</t>
+  </si>
+  <si>
     <t>000933</t>
   </si>
   <si>
     <t>中证医药</t>
   </si>
   <si>
-    <t>现代生物与大健康</t>
-  </si>
-  <si>
-    <t>生物健康</t>
-  </si>
-  <si>
     <t>创新药+器械+CXO</t>
   </si>
   <si>
     <t>1：健康中国2030，创新药械国产替代；2：创新药+医疗器械+CXO全覆盖；3：300只中大盘股，平均市值250亿；4：10+只ETF，流动性最佳医药指数</t>
   </si>
   <si>
-    <t>000941</t>
-  </si>
-  <si>
-    <t>新能源</t>
-  </si>
-  <si>
-    <t>新能源与绿色低碳</t>
-  </si>
-  <si>
-    <t>全产业链龙头</t>
-  </si>
-  <si>
-    <t>1：双碳目标核心载体，风光储写入十五五规划；2：光伏/风电/储能全产业链龙头；3：100只大盘股，宁德/隆基/阳光电源等；4：10+只ETF，历史10年+，流动性最佳</t>
-  </si>
-  <si>
-    <t>000949</t>
-  </si>
-  <si>
-    <t>中证农业</t>
-  </si>
-  <si>
-    <t>现代农业与粮食安全</t>
-  </si>
-  <si>
-    <t>现代农业</t>
-  </si>
-  <si>
-    <t>农业现代化综合</t>
-  </si>
-  <si>
-    <t>1：农业现代化综合代表，智慧农业占比提升；2：种业30%+养殖30%+农机20%+智慧农业20%；3：100只中盘股，平均市值120亿；4：4只ETF，分散度高</t>
-  </si>
-  <si>
-    <t>000995</t>
-  </si>
-  <si>
-    <t>全指公用</t>
-  </si>
-  <si>
-    <t>公用事业与基础保障</t>
-  </si>
-  <si>
-    <t>公用保障</t>
-  </si>
-  <si>
-    <t>水电/燃气全覆盖</t>
-  </si>
-  <si>
-    <t>1：基础保障刚性需求，高股息防御属性；2：水电/燃气/环保公用事业全覆盖；3：200只中大盘股，平均股息率4.5%；4：5只ETF，流动性最佳公用指数</t>
-  </si>
-  <si>
-    <t>000998</t>
-  </si>
-  <si>
-    <t>中证TMT</t>
-  </si>
-  <si>
-    <t>新一代信息技术与数字经济</t>
-  </si>
-  <si>
-    <t>信息技术</t>
-  </si>
-  <si>
-    <t>电子+计算机+通信+传媒</t>
-  </si>
-  <si>
-    <t>1：数字经济基础设施，新基建核心；2：电子+计算机+通信+传媒全覆盖；3：100只大盘股，平均市值350亿；4：6只ETF，流动性最佳TMT指数</t>
-  </si>
-  <si>
-    <t>399005</t>
-  </si>
-  <si>
-    <t>中小100</t>
-  </si>
-  <si>
-    <t>深市中盘科技制造特色</t>
-  </si>
-  <si>
-    <t>1：深市“隐形冠军”代表；2：科技制造特色鲜明（电子/通信/机械）；3：100只中盘股，平均市值200亿；4：3只ETF，与中证500互补（深市侧重）</t>
-  </si>
-  <si>
-    <t>399006</t>
-  </si>
-  <si>
-    <t>创业板指</t>
-  </si>
-  <si>
-    <t>创新创业，硬科技特色</t>
-  </si>
-  <si>
-    <t>1：创新创业试验田，注册制改革标杆；2：新能源/医药/电子占比60%，硬科技特色；3：100只创业板龙头，平均市值300亿；4：10+只ETF，波动率高于主板</t>
-  </si>
-  <si>
-    <t>399238</t>
-  </si>
-  <si>
-    <t>餐饮指数</t>
-  </si>
-  <si>
-    <t>文化消费与生活服务</t>
-  </si>
-  <si>
-    <t>文化消费</t>
-  </si>
-  <si>
-    <t>连锁餐饮标准化</t>
-  </si>
-  <si>
-    <t>1：连锁化+标准化趋势，抗周期属性强；2：海底捞/九毛九/百胜中国，品牌连锁；3：30只小盘股，平均市值80亿；4：2只ETF，必选消费属性</t>
-  </si>
-  <si>
-    <t>399242</t>
-  </si>
-  <si>
-    <t>商务指数</t>
-  </si>
-  <si>
-    <t>现代服务业与供应链韧性</t>
-  </si>
-  <si>
-    <t>现代服务</t>
-  </si>
-  <si>
-    <t>专业服务现代化</t>
-  </si>
-  <si>
-    <t>上游</t>
-  </si>
-  <si>
-    <t>1：专业服务业现代化，法律/会计/咨询升级；2：专业服务龙头，知识密集型；3：50只中盘股，平均市值120亿；4：1只细分指数，生产性服务代表</t>
-  </si>
-  <si>
-    <t>399244</t>
-  </si>
-  <si>
-    <t>公共指数</t>
-  </si>
-  <si>
-    <t>公共服务数字化</t>
-  </si>
-  <si>
-    <t>中游</t>
-  </si>
-  <si>
-    <t>1：公共服务数字化，智慧城市/政务云；2：数字政务/智慧交通/智慧医疗；3：50只中盘股，平均市值100亿；4：1只细分指数，政府订单驱动</t>
-  </si>
-  <si>
-    <t>399330</t>
-  </si>
-  <si>
-    <t>深证100</t>
-  </si>
-  <si>
-    <t>深市硬科技龙头</t>
-  </si>
-  <si>
-    <t>1：深市创新标杆，科技自立自强代表；2：比亚迪/迈瑞/宁德等硬科技龙头；3：100只大盘股，科技属性强于上证180；4：6只ETF，成长性突出</t>
-  </si>
-  <si>
-    <t>399353</t>
-  </si>
-  <si>
-    <t>国证物流</t>
-  </si>
-  <si>
-    <t>智慧物流龙头</t>
-  </si>
-  <si>
-    <t>1：供应链安全，智慧物流基础设施；2：顺丰/京东物流/中国外运，快递+供应链管理；3：100只中大盘股，平均市值200亿；4：3只ETF，龙头集中度高</t>
-  </si>
-  <si>
-    <t>399365</t>
-  </si>
-  <si>
-    <t>国证粮食</t>
-  </si>
-  <si>
-    <t>种业+粮食加工</t>
-  </si>
-  <si>
-    <t>1：种业振兴行动，粮食安全压舱石；2：种业+粮食加工，隆平高科/金龙鱼等；3：50只中大盘股，平均市值180亿；4：2只ETF，政策刚性需求强</t>
-  </si>
-  <si>
-    <t>399368</t>
-  </si>
-  <si>
-    <t>国证军工</t>
-  </si>
-  <si>
-    <t>航空航天/船舶整机</t>
-  </si>
-  <si>
-    <t>下游</t>
-  </si>
-  <si>
-    <t>1：军民融合+自主可控，安全发展核心；2：航空航天/船舶/信息化装备整机；3：100只中大盘股，央企占比80%；4：6只ETF，订单可见性强</t>
-  </si>
-  <si>
-    <t>399395</t>
-  </si>
-  <si>
-    <t>国证有色</t>
-  </si>
-  <si>
-    <t>有色金属龙头</t>
-  </si>
-  <si>
-    <t>1：有色金属战略价值提升，新能源金属需求；2：紫金矿业/洛阳钼业等，铜/锂/钴/镍；3：100只中大盘股，平均市值250亿；4：4只ETF，资源安全属性</t>
-  </si>
-  <si>
-    <t>399434</t>
-  </si>
-  <si>
-    <t>数字传媒</t>
-  </si>
-  <si>
-    <t>游戏/短视频内容</t>
-  </si>
-  <si>
-    <t>1：AIGC内容生成，降本增效显著；2：游戏/短视频/数字出版，腾讯/字节生态；3：50只中盘股（复用文化消费），平均市值200亿；4：3只ETF，上游内容视角</t>
-  </si>
-  <si>
-    <t>399441</t>
-  </si>
-  <si>
-    <t>生物医药</t>
-  </si>
-  <si>
-    <t>生物制品/基因治疗</t>
-  </si>
-  <si>
-    <t>1：生物经济写入十四五规划，前沿技术突破；2：生物制品/基因治疗/细胞治疗；3：100只中大盘股，药明康德/智飞生物等；4：5只ETF，技术壁垒高</t>
-  </si>
-  <si>
-    <t>399612</t>
-  </si>
-  <si>
-    <t>中创100</t>
-  </si>
-  <si>
-    <t>创业板中盘硬科技</t>
-  </si>
-  <si>
-    <t>1：创业板改革深化，硬科技中盘标的；2：半导体设备/工业软件/高端材料；3：100只创业板中盘，平均市值120亿；4：2只ETF，波动率适中</t>
-  </si>
-  <si>
-    <t>399633</t>
-  </si>
-  <si>
-    <t>深证300</t>
-  </si>
-  <si>
-    <t>深市科技龙头</t>
-  </si>
-  <si>
-    <t>1：深市科技龙头，华为链/腾讯系核心标的；2：电子/通信/计算机占比70%，硬科技特色；3：300只大盘股，平均市值400亿；4：4只ETF，与沪深300互补（科技侧重）</t>
-  </si>
-  <si>
-    <t>399976</t>
-  </si>
-  <si>
-    <t>CS新能车</t>
-  </si>
-  <si>
-    <t>整车+电池龙头</t>
-  </si>
-  <si>
-    <t>1：电动化+智能化双主线，全球竞争力最强赛道；2：整车-电池-零部件全覆盖，比亚迪/宁德主导；3：100只大盘股，平均市值400亿；4：12只ETF，全球配置首选</t>
-  </si>
-  <si>
-    <t>399997</t>
-  </si>
-  <si>
-    <t>中证白酒</t>
-  </si>
-  <si>
-    <t>传统消费龙头</t>
-  </si>
-  <si>
-    <t>1：传统消费龙头，品牌价值稳固；2：茅台/五粮液/泸州老窖，高端白酒集中度提升；3：20只大盘股，平均市值1500亿；4：10+只ETF，流动性最佳消费指数</t>
-  </si>
-  <si>
-    <t>930598</t>
-  </si>
-  <si>
-    <t>稀土产业</t>
-  </si>
-  <si>
-    <t>永磁材料上游</t>
-  </si>
-  <si>
-    <t>1：战略资源安全，永磁材料刚性需求；2：稀土开采-分离-永磁材料全链条；3：50只中盘股，北方稀土/金力永磁等；4：3只ETF（复用新能源），上游资源视角</t>
-  </si>
-  <si>
-    <t>930601</t>
-  </si>
-  <si>
-    <t>中证软件</t>
-  </si>
-  <si>
-    <t>基础软件+工业软件</t>
-  </si>
-  <si>
-    <t>1：基础软件+工业软件国产化，卡脖子环节；2：操作系统/数据库/EDA/工业CAD；3：100只中盘股，平均市值150亿；4：4只ETF，信创核心受益</t>
-  </si>
-  <si>
-    <t>930606</t>
-  </si>
-  <si>
-    <t>中证钢铁</t>
-  </si>
-  <si>
-    <t>高端特钢绿色升级</t>
-  </si>
-  <si>
-    <t>传统转型</t>
-  </si>
-  <si>
-    <t>1：传统材料绿色升级，高端特钢国产替代；2：轴承钢/模具钢/硅钢等高端品种；3：50只大盘股，宝钢/中信特钢等；4：2只ETF，转型逻辑清晰</t>
-  </si>
-  <si>
-    <t>930608</t>
-  </si>
-  <si>
-    <t>中证基建</t>
-  </si>
-  <si>
-    <t>新基建+传统基建</t>
-  </si>
-  <si>
-    <t>1：装配式建筑+智能建造，传统建筑升级；2：钢结构/PC构件/智能施工设备；3：100只中大盘股（复用公用保障），平均市值200亿；4：4只ETF，中游建造视角</t>
-  </si>
-  <si>
-    <t>930614</t>
-  </si>
-  <si>
-    <t>环保50</t>
-  </si>
-  <si>
-    <t>工业绿色化转型（*替换国证钢铁*）</t>
-  </si>
-  <si>
-    <t>930632</t>
-  </si>
-  <si>
-    <t>CS稀金属</t>
-  </si>
-  <si>
-    <t>稀土+稀有金属</t>
-  </si>
-  <si>
-    <t>1：稀土+稀有金属战略价值，小金属国产替代；2：钨/锑/铋/锗等小金属，全球供给主导；3：30只小盘股，平均市值60亿；4：1只细分指数，稀缺资源属性</t>
-  </si>
-  <si>
-    <t>930633</t>
-  </si>
-  <si>
-    <t>中证旅游</t>
-  </si>
-  <si>
-    <t>文旅融合</t>
-  </si>
-  <si>
-    <t>1：文旅融合+入境游复苏，服务消费弹性大；2：中国中免/宋城演艺/锦江酒店；3：50只中盘股，平均市值150亿；4：3只ETF，疫后复苏逻辑</t>
-  </si>
-  <si>
-    <t>930638</t>
-  </si>
-  <si>
-    <t>环保设备+运营，双碳目标刚性需求</t>
-  </si>
-  <si>
-    <t>1：环保设备+运营，双碳目标刚性需求；2：碧水源/高能环境等，技术+运营双轮；3：50只小盘股，平均市值80亿；4：2只ETF，成长性高于传统公用</t>
+    <t>930781</t>
+  </si>
+  <si>
+    <t>中证影视</t>
+  </si>
+  <si>
+    <t>影视工业化+AI</t>
+  </si>
+  <si>
+    <t>1：影视工业化+AI制作；2：光线传媒/华策影视，AI剧本/虚拟拍摄；3：30只小盘股（复用文化消费），平均市值60亿；4：2只ETF，中游制作视角</t>
+  </si>
+  <si>
+    <t>930708</t>
+  </si>
+  <si>
+    <t>中证有色</t>
+  </si>
+  <si>
+    <t>新能源金属中盘</t>
+  </si>
+  <si>
+    <t>1：与国证有色互补，侧重新能源金属中盘标的；2：赣锋锂业/天齐锂业等，锂资源占比高；3：50只中盘股，平均市值150亿；4：3只ETF，成长性突出</t>
+  </si>
+  <si>
+    <t>931381</t>
+  </si>
+  <si>
+    <t>中证长三角</t>
+  </si>
+  <si>
+    <t>沪苏浙龙头</t>
+  </si>
+  <si>
+    <t>1：与国证长三角互补，侧重沪苏浙龙头；2：科创板企业占比30%，硬科技特色；3：150只中大盘股，流动性好于国证版；4：3只ETF，成分更均衡</t>
   </si>
   <si>
     <t>930641</t>
@@ -632,1539 +2270,6 @@
     <t>1：中医药振兴，现代化+国际化双路径；2：中药材种植-饮片-中成药全链条；3：50只中盘股，平均市值150亿；4：4只ETF，政策扶持持续性强</t>
   </si>
   <si>
-    <t>930660</t>
-  </si>
-  <si>
-    <t>国证钢铁</t>
-  </si>
-  <si>
-    <t>区域特钢龙头</t>
-  </si>
-  <si>
-    <t>1：高端特钢中游制造，传统材料绿色升级；2：华东/华南区域特钢企业，贴近下游需求；3：50只中盘股，平均市值100亿；4：1只ETF（复用新能源），区域特色</t>
-  </si>
-  <si>
-    <t>930662</t>
-  </si>
-  <si>
-    <t>CS现代农</t>
-  </si>
-  <si>
-    <t>智慧农业+生物农业</t>
-  </si>
-  <si>
-    <t>1：智慧农业+生物农业，技术驱动型农业；2：农业AI/无人机/生物育种/智能灌溉；3：50只小盘股，平均市值60亿；4：1只主题指数，科技赋能农业</t>
-  </si>
-  <si>
-    <t>930701</t>
-  </si>
-  <si>
-    <t>深证F60</t>
-  </si>
-  <si>
-    <t>深市细分制造龙头</t>
-  </si>
-  <si>
-    <t>细分</t>
-  </si>
-  <si>
-    <t>1：深市细分制造龙头，隐形冠军代表；2：精密仪器/传感器/特种材料等“小而美”标的；3：60只中盘股，平均市值100亿；4：1只ETF，流动性适中</t>
-  </si>
-  <si>
-    <t>930707</t>
-  </si>
-  <si>
-    <t>中证畜牧</t>
-  </si>
-  <si>
-    <t>畜禽育种+规模化养殖</t>
-  </si>
-  <si>
-    <t>1：生物育种产业化落地，畜禽种源自主可控；2：牧原/温氏/圣农等规模化养殖龙头；3：50只小盘股，平均市值80亿；4：2只ETF，周期属性弱化（规模化）</t>
-  </si>
-  <si>
-    <t>930708</t>
-  </si>
-  <si>
-    <t>中证有色</t>
-  </si>
-  <si>
-    <t>新能源金属中盘</t>
-  </si>
-  <si>
-    <t>1：与国证有色互补，侧重新能源金属中盘标的；2：赣锋锂业/天齐锂业等，锂资源占比高；3：50只中盘股，平均市值150亿；4：3只ETF，成长性突出</t>
-  </si>
-  <si>
-    <t>930709</t>
-  </si>
-  <si>
-    <t>香港证券</t>
-  </si>
-  <si>
-    <t>港股种业平台</t>
-  </si>
-  <si>
-    <t>种业</t>
-  </si>
-  <si>
-    <t>1：种业并购整合，港股种业平台；2：先正达集团H股，全球种业巨头；3：30只港股，种业占比40%；4：1只跨境指数，全球视野</t>
-  </si>
-  <si>
-    <t>930712</t>
-  </si>
-  <si>
-    <t>CS物联网</t>
-  </si>
-  <si>
-    <t>5G+AIoT融合</t>
-  </si>
-  <si>
-    <t>1：5G+AIoT融合，万物互联基础设施；2：传感器-模组-平台-应用全链条；3：50只中盘股，平均市值120亿；4：2只ETF，应用场景持续拓展</t>
-  </si>
-  <si>
-    <t>930713</t>
-  </si>
-  <si>
-    <t>CS人工智</t>
-  </si>
-  <si>
-    <t>AI应用层</t>
-  </si>
-  <si>
-    <t>1：侧重AI应用层，计算机视觉/NLP/语音识别；2：商汤/云从/科大讯飞等应用层龙头；3：50只中盘股，平均市值150亿；4：3只ETF，与AI指数互补（应用侧重）</t>
-  </si>
-  <si>
-    <t>930716</t>
-  </si>
-  <si>
-    <t>CS物流</t>
-  </si>
-  <si>
-    <t>区域性物流/冷链</t>
-  </si>
-  <si>
-    <t>1：与国证物流互补，侧重成本优化标的；2：区域性物流/仓储/冷链，成本控制能力强；3：50只中盘股，平均市值100亿；4：2只ETF，细分领域覆盖</t>
-  </si>
-  <si>
-    <t>中证传媒</t>
-  </si>
-  <si>
-    <t>子产业链专项覆盖</t>
-  </si>
-  <si>
-    <t>内容生产</t>
-  </si>
-  <si>
-    <t>全市场传媒覆盖（*替换数字传媒重复*）</t>
-  </si>
-  <si>
-    <t>930781</t>
-  </si>
-  <si>
-    <t>中证影视</t>
-  </si>
-  <si>
-    <t>影视工业化+AI</t>
-  </si>
-  <si>
-    <t>1：影视工业化+AI制作；2：光线传媒/华策影视，AI剧本/虚拟拍摄；3：30只小盘股（复用文化消费），平均市值60亿；4：2只ETF，中游制作视角</t>
-  </si>
-  <si>
-    <t>930782</t>
-  </si>
-  <si>
-    <t>500深市</t>
-  </si>
-  <si>
-    <t>人力资本服务</t>
-  </si>
-  <si>
-    <t>人力资源</t>
-  </si>
-  <si>
-    <t>1：人才服务现代化，灵活用工/职业教育；2：科锐国际/外服控股等，人力资本服务；3：500只深市股，中盘为主；4：2只ETF，生产性服务代表</t>
-  </si>
-  <si>
-    <t>930796</t>
-  </si>
-  <si>
-    <t>信息安全</t>
-  </si>
-  <si>
-    <t>网络安全+数据安全</t>
-  </si>
-  <si>
-    <t>安全</t>
-  </si>
-  <si>
-    <t>1：网络安全法+数据安全法，刚性合规需求；2：防火墙/IDS/数据加密/身份认证；3：50只中盘股，平均市值100亿；4：3只ETF，政策驱动型</t>
-  </si>
-  <si>
-    <t>930812</t>
-  </si>
-  <si>
-    <t>细分机械</t>
-  </si>
-  <si>
-    <t>工业母机智能化</t>
-  </si>
-  <si>
-    <t>机械智能化</t>
-  </si>
-  <si>
-    <t>1：工业母机智能化，数控化率提升；2：机器人/数控机床/激光设备；3：50只中盘股，平均市值100亿；4：1只细分指数，传统机械升级</t>
-  </si>
-  <si>
-    <t>930813</t>
-  </si>
-  <si>
-    <t>化工材料</t>
-  </si>
-  <si>
-    <t>医药中间体/电子化学品（*替换化工重复*）</t>
-  </si>
-  <si>
-    <t>1：医药中间体/原料药上游保障；2：特色原料药/CDMO/医药中间体；3：50只中盘股，平均市值100亿；4：1只细分指数，产业链上游视角</t>
-  </si>
-  <si>
-    <t>930814</t>
-  </si>
-  <si>
-    <t>细分医药</t>
-  </si>
-  <si>
-    <t>眼科/牙科/医美</t>
-  </si>
-  <si>
-    <t>1：细分领域冠军，眼科/牙科/医美等消费升级；2：爱尔眼科/通策医疗/爱美客等；3：50只中盘股，平均市值200亿；4：2只ETF，消费属性强</t>
-  </si>
-  <si>
-    <t>930819</t>
-  </si>
-  <si>
-    <t>有色金属</t>
-  </si>
-  <si>
-    <t>铜/铝等基础金属（*替换稀土产业*）</t>
-  </si>
-  <si>
-    <t>930846</t>
-  </si>
-  <si>
-    <t>医疗器械</t>
-  </si>
-  <si>
-    <t>高端器械国产替代，迈瑞/联影等龙头</t>
-  </si>
-  <si>
-    <t>1：高端医疗器械国产替代，进口替代加速；2：影像设备/体外诊断/高值耗材；3：50只中盘股，迈瑞/联影等龙头；4：3只ETF，技术壁垒高</t>
-  </si>
-  <si>
-    <t>930850</t>
-  </si>
-  <si>
-    <t>智能制造</t>
-  </si>
-  <si>
-    <t>工业4.0+AI融合</t>
-  </si>
-  <si>
-    <t>1：工业4.0+AI融合，“数实融合”核心载体；2：工业机器人/智能工厂/数字孪生；3：100只中盘股，平均市值180亿；4：4只ETF，2021年推出，契合新质生产力</t>
-  </si>
-  <si>
-    <t>930851</t>
-  </si>
-  <si>
-    <t>云计算</t>
-  </si>
-  <si>
-    <t>云服务厂商集中</t>
-  </si>
-  <si>
-    <t>1：东数西算工程，算力基础设施建设；2：IaaS/PaaS/SaaS全栈，阿里云/腾讯云/华为云生态；3：50只中盘股，平均市值200亿；4：5只ETF，政企上云持续受益</t>
-  </si>
-  <si>
-    <t>930853</t>
-  </si>
-  <si>
-    <t>医药100</t>
-  </si>
-  <si>
-    <t>医药细分龙头全覆盖</t>
-  </si>
-  <si>
-    <t>1：医药细分龙头全覆盖，避免单一环节风险；2：创新药30%+器械30%+CXO20%+中药20%；3：100只中大盘股，平均市值180亿；4：4只ETF，分散度高</t>
-  </si>
-  <si>
-    <t>930901</t>
-  </si>
-  <si>
-    <t>动漫游戏</t>
-  </si>
-  <si>
-    <t>游戏/动漫AIGC受益</t>
-  </si>
-  <si>
-    <t>1：数字文化出海，AIGC降本增效；2：米哈游/腾讯游戏/完美世界，全球化运营；3：50只小盘股，平均市值100亿；4：4只ETF，文化自信载体</t>
-  </si>
-  <si>
-    <t>930902</t>
-  </si>
-  <si>
-    <t>中证数据</t>
-  </si>
-  <si>
-    <t>数据要素市场化</t>
-  </si>
-  <si>
-    <t>1：数据要素市场化，“数据二十条”落地；2：数据采集-处理-交易-应用，交易所挂牌标的；3：50只小盘股，平均市值80亿；4：2只ETF，前沿探索型</t>
-  </si>
-  <si>
-    <t>930910</t>
-  </si>
-  <si>
-    <t>农牧渔</t>
-  </si>
-  <si>
-    <t>水产养殖现代化</t>
-  </si>
-  <si>
-    <t>1：蛋白供给多元化，水产养殖现代化；2：海大集团/国联水产等，水产+饲料；3：50只中盘股，平均市值100亿；4：1只细分指数，与畜牧互补</t>
-  </si>
-  <si>
-    <t>930912</t>
-  </si>
-  <si>
-    <t>300消费</t>
-  </si>
-  <si>
-    <t>消费龙头全覆盖（*替换线上消费重复*）</t>
-  </si>
-  <si>
-    <t>930916</t>
-  </si>
-  <si>
-    <t>300通信</t>
-  </si>
-  <si>
-    <t>5G-A/6G研发</t>
-  </si>
-  <si>
-    <t>通信</t>
-  </si>
-  <si>
-    <t>1：5G-A/6G研发，通信基础设施安全；2：主设备商（华为/中兴）+光通信+卫星通信；3：100只中大盘股，平均市值200亿；4：3只ETF，与TMT互补（通信侧重）</t>
-  </si>
-  <si>
-    <t>930927</t>
-  </si>
-  <si>
-    <t>稳健成长</t>
-  </si>
-  <si>
-    <t>质量+成长双优，规避纯周期</t>
-  </si>
-  <si>
-    <t>质量</t>
-  </si>
-  <si>
-    <t>1：高质量发展导向，规避纯周期波动；2：质量+成长双优（ROE&gt;15%+营收增速&gt;10%）；3：100只中大盘股，行业分散度高；4：2只ETF，Smart Beta代表</t>
-  </si>
-  <si>
-    <t>930944</t>
-  </si>
-  <si>
-    <t>内地资源</t>
-  </si>
-  <si>
-    <t>生活服务</t>
-  </si>
-  <si>
-    <t>生活资源视角（*替换餐饮指数重复*）</t>
-  </si>
-  <si>
-    <t>930948</t>
-  </si>
-  <si>
-    <t>内地地产</t>
-  </si>
-  <si>
-    <t>建材建筑</t>
-  </si>
-  <si>
-    <t>绿色建筑载体（*替换建筑材料重复*）</t>
-  </si>
-  <si>
-    <t>930952</t>
-  </si>
-  <si>
-    <t>300地产</t>
-  </si>
-  <si>
-    <t>水利基础设施</t>
-  </si>
-  <si>
-    <t>水利</t>
-  </si>
-  <si>
-    <t>1：水利基础设施补短板，防洪抗旱刚需；2：中国电建/中国能建水利业务，订单驱动；3：100只中大盘股，地产占比下降水利上升；4：3只ETF，传统行业转型样本</t>
-  </si>
-  <si>
-    <t>930959</t>
-  </si>
-  <si>
-    <t>银河99</t>
-  </si>
-  <si>
-    <t>基建+高端制造融合（*替换中证基建重复*）</t>
-  </si>
-  <si>
-    <t>930961</t>
-  </si>
-  <si>
-    <t>中证上游</t>
-  </si>
-  <si>
-    <t>资源开采/原材料（*已替换长江保护*）</t>
-  </si>
-  <si>
-    <t>930963</t>
-  </si>
-  <si>
-    <t>中证下游</t>
-  </si>
-  <si>
-    <t>消费端应用（*已替换苏州绿色发展*）</t>
-  </si>
-  <si>
-    <t>930971</t>
-  </si>
-  <si>
-    <t>等权90</t>
-  </si>
-  <si>
-    <t>应急产业</t>
-  </si>
-  <si>
-    <t>应急安全</t>
-  </si>
-  <si>
-    <t>1：应急产业写入安全发展规划，公共安全刚需；2：应急装备/消防设备/安防系统；3：90只中盘股，等权编制避免龙头垄断；4：1只主题指数，细分领域覆盖</t>
-  </si>
-  <si>
-    <t>930997</t>
-  </si>
-  <si>
-    <t>金融科技</t>
-  </si>
-  <si>
-    <t>数字金融基础设施</t>
-  </si>
-  <si>
-    <t>1：数字金融基础设施，支付/征信/风控；2：蚂蚁/腾讯金融科技/银行科技子公司；3：50只中盘股，平均市值250亿；4：3只ETF，与TMT互补（金融侧重）</t>
-  </si>
-  <si>
-    <t>931001</t>
-  </si>
-  <si>
-    <t>汽车指数</t>
-  </si>
-  <si>
-    <t>交通装备</t>
-  </si>
-  <si>
-    <t>整车+零部件全覆盖</t>
-  </si>
-  <si>
-    <t>1：整车+零部件全覆盖，电动化转型代表；2：比亚迪/长城/吉利，自主品牌崛起；3：100只中大盘股，平均市值300亿；4：5只ETF，下游整车视角</t>
-  </si>
-  <si>
-    <t>931021</t>
-  </si>
-  <si>
-    <t>家电龙头</t>
-  </si>
-  <si>
-    <t>白电全球化</t>
-  </si>
-  <si>
-    <t>1：白电龙头全球化，品牌出海加速；2：美的/格力/海尔，海外收入占比40%+；3：30只大盘股，平均市值800亿；4：4只ETF，全球化竞争力</t>
-  </si>
-  <si>
-    <t>931065</t>
-  </si>
-  <si>
-    <t>光伏龙头30</t>
-  </si>
-  <si>
-    <t>各环节龙头集中</t>
-  </si>
-  <si>
-    <t>1：规避产能过剩，聚焦各环节龙头；2：硅料-硅片-电池-组件-逆变器各环节前3名；3：30只中大盘股，集中度高；4：2只ETF，龙头溢价显著</t>
-  </si>
-  <si>
-    <t>931071</t>
-  </si>
-  <si>
-    <t>人工智能</t>
-  </si>
-  <si>
-    <t>AI大模型+算力+应用</t>
-  </si>
-  <si>
-    <t>1：“人工智能+"行动写入政府工作报告；2：大模型-算力-应用全链条，科大讯飞/商汤等；3：100只中盘股，平均市值180亿；4：8只ETF，2023年政策催化密集</t>
-  </si>
-  <si>
-    <t>931132</t>
-  </si>
-  <si>
-    <t>浙江新动能</t>
-  </si>
-  <si>
-    <t>浙江数字经济+制造双引擎</t>
-  </si>
-  <si>
-    <t>区域</t>
-  </si>
-  <si>
-    <t>1：浙江“数字经济+先进制造”双引擎；2：杭州/宁波高端制造集群（海康/大华/舜宇）；3：100只中盘股，区域特色鲜明；4：1只ETF，地方政策试验田</t>
-  </si>
-  <si>
-    <t>931139</t>
-  </si>
-  <si>
-    <t>长三角</t>
-  </si>
-  <si>
-    <t>长三角数字经济集群</t>
-  </si>
-  <si>
-    <t>1：长三角数字经济集群，一体化示范区；2：上海（芯片）-杭州（电商）-苏州（制造）协同；3：100只中大盘股，平均市值250亿；4：2只区域指数，政策高地</t>
-  </si>
-  <si>
-    <t>931140</t>
-  </si>
-  <si>
-    <t>医药50</t>
-  </si>
-  <si>
-    <t>研发驱动型创新药</t>
-  </si>
-  <si>
-    <t>1：规避集采敏感标的，聚焦研发驱动型；2：创新药企（恒瑞/百济/信达），管线丰富；3：50只中盘股，平均市值300亿；4：3只ETF，与中证医药互补（更聚焦创新）</t>
-  </si>
-  <si>
-    <t>931151</t>
-  </si>
-  <si>
-    <t>光伏产业</t>
-  </si>
-  <si>
-    <t>光伏中游制造</t>
-  </si>
-  <si>
-    <t>1：光伏制造全球主导，技术迭代（BC/HJT）持续；2：组件/逆变器/辅材中游制造集中；3：50只中盘股，平均市值150亿；4：5只ETF，规避上游硅料周期波动</t>
-  </si>
-  <si>
-    <t>931165</t>
-  </si>
-  <si>
-    <t>新兴科技100</t>
-  </si>
-  <si>
-    <t>科技赋能传统（*替换华福福建100*）</t>
-  </si>
-  <si>
-    <t>931167</t>
-  </si>
-  <si>
-    <t>先进制造100</t>
-  </si>
-  <si>
-    <t>传统制造智能化（*替换厦门指数*）</t>
-  </si>
-  <si>
-    <t>931230</t>
-  </si>
-  <si>
-    <t>汽车零部件</t>
-  </si>
-  <si>
-    <t>智能驾驶+新能源供应链</t>
-  </si>
-  <si>
-    <t>1：智能驾驶+新能源车供应链，全球竞争力；2：拓普集团/德赛西威，单车价值量提升；3：100只中盘股，平均市值150亿；4：4只ETF，中游零部件视角</t>
-  </si>
-  <si>
-    <t>931233</t>
-  </si>
-  <si>
-    <t>港股通央企红利</t>
-  </si>
-  <si>
-    <t>高端制造央企H股</t>
-  </si>
-  <si>
-    <t>1：央企高股息+港股估值修复双重逻辑；2：高端制造央企H股（中车/中船/中航）；3：50只港股大盘，平均股息率5%+；4：1只ETF，防御属性强</t>
-  </si>
-  <si>
-    <t>931234</t>
-  </si>
-  <si>
-    <t>港股通创新药</t>
-  </si>
-  <si>
-    <t>港股18A生物科技</t>
-  </si>
-  <si>
-    <t>跨境</t>
-  </si>
-  <si>
-    <t>1：港股18A生物科技，全球创新前沿阵地；2：信达/君实/康方等18A公司，临床阶段丰富；3：50只港股小盘，平均市值50亿；4：3只ETF，与A股创新药互补（更前沿）</t>
-  </si>
-  <si>
-    <t>931241</t>
-  </si>
-  <si>
-    <t>家居家电</t>
-  </si>
-  <si>
-    <t>智能家居中游</t>
-  </si>
-  <si>
-    <t>1：智能家居+绿色家电，消费升级+绿色转型；2：美的/海尔/欧派家居，智能化渗透率提升；3：50只中盘股，平均市值250亿；4：3只ETF，地产后周期属性</t>
-  </si>
-  <si>
-    <t>931243</t>
-  </si>
-  <si>
-    <t>诚通央企ESG</t>
-  </si>
-  <si>
-    <t>央企粮食安全压舱石</t>
-  </si>
-  <si>
-    <t>央企</t>
-  </si>
-  <si>
-    <t>1：央企粮食安全压舱石，中粮/中化主导；2：粮食贸易/种子/化肥/农药全链条；3：50只大盘股，央企占比90%；4：1只定制指数，安全属性突出</t>
-  </si>
-  <si>
-    <t>931247</t>
-  </si>
-  <si>
-    <t>中证信创</t>
-  </si>
-  <si>
-    <t>信创全栈</t>
-  </si>
-  <si>
-    <t>1：信息技术应用创新，安全可控刚性需求；2：CPU（龙芯/飞腾）-OS（麒麟）-数据库（达梦）全栈；3：100只中盘股，平均市值120亿；4：6只ETF，党政→行业扩散逻辑</t>
-  </si>
-  <si>
-    <t>931289</t>
-  </si>
-  <si>
-    <t>碳中和债</t>
-  </si>
-  <si>
-    <t>绿色债券</t>
-  </si>
-  <si>
-    <t>1：绿色金融工具创新，碳中和债发行加速；2：绿色债券发行人（央企/地方国企）；3：50只大盘股，债券指数衍生；4：1只债券指数，资金端视角</t>
-  </si>
-  <si>
-    <t>931375</t>
-  </si>
-  <si>
-    <t>300质量低波</t>
-  </si>
-  <si>
-    <t>长三角供应链韧性</t>
-  </si>
-  <si>
-    <t>1：长三角供应链韧性，质量+低波动双优；2：沪苏浙供应链龙头，质量管理体系完善；3：100只中大盘股，平均市值200亿；4：1只Smart Beta指数，防御属性强</t>
-  </si>
-  <si>
-    <t>931381</t>
-  </si>
-  <si>
-    <t>中证长三角</t>
-  </si>
-  <si>
-    <t>沪苏浙龙头</t>
-  </si>
-  <si>
-    <t>1：与国证长三角互补，侧重沪苏浙龙头；2：科创板企业占比30%，硬科技特色；3：150只中大盘股，流动性好于国证版；4：3只ETF，成分更均衡</t>
-  </si>
-  <si>
-    <t>931382</t>
-  </si>
-  <si>
-    <t>智选300 ESG领先</t>
-  </si>
-  <si>
-    <t>供应链ESG管理</t>
-  </si>
-  <si>
-    <t>ESG</t>
-  </si>
-  <si>
-    <t>1：供应链ESG管理，国际竞争力提升；2：ESG评级前20%企业，绿色供应链实践者；3：100只大盘股，平均市值400亿；4：2只ETF，国际接轨</t>
-  </si>
-  <si>
-    <t>931393</t>
-  </si>
-  <si>
-    <t>湖北指数</t>
-  </si>
-  <si>
-    <t>长江流域粮食主产区</t>
-  </si>
-  <si>
-    <t>1：湖北农业大省，长江流域粮食主产区；2：水稻/油菜/水产养殖，区域特色鲜明；3：50只中盘股，平均市值100亿；4：1只区域指数，地方政策支持</t>
-  </si>
-  <si>
-    <t>931395</t>
-  </si>
-  <si>
-    <t>沪港深300</t>
-  </si>
-  <si>
-    <t>跨市场消费龙头（*替换成渝经济圈重复*）</t>
-  </si>
-  <si>
-    <t>931404</t>
-  </si>
-  <si>
-    <t>SHS品牌消费50</t>
-  </si>
-  <si>
-    <t>中国品牌全球化</t>
-  </si>
-  <si>
-    <t>1：中国品牌全球化，文化自信载体；2：安踏H/李宁H/农夫山泉，品牌力提升；3：50只港股大盘，平均市值400亿；4：2只ETF，品牌出海</t>
-  </si>
-  <si>
-    <t>931406</t>
-  </si>
-  <si>
-    <t>5G 50</t>
-  </si>
-  <si>
-    <t>5G+文化新场景（*替换中证旅游重复*）</t>
-  </si>
-  <si>
-    <t>931440</t>
-  </si>
-  <si>
-    <t>创新药30</t>
-  </si>
-  <si>
-    <t>临床后期创新药</t>
-  </si>
-  <si>
-    <t>1：纯正创新药标的，医保谈判优化受益；2：临床后期（III期）创新药企，商业化在即；3：30只小盘股，平均市值100亿；4：2只ETF，高弹性但波动大</t>
-  </si>
-  <si>
-    <t>931447</t>
-  </si>
-  <si>
-    <t>科技先锋</t>
-  </si>
-  <si>
-    <t>量子/脑机接口前沿</t>
-  </si>
-  <si>
-    <t>主题</t>
-  </si>
-  <si>
-    <t>1：前沿技术探索，量子/脑机接口/6G；2：科研机构转化标的，技术不确定性高但想象空间大；3：30只小盘股，平均市值60亿；4：1只主题指数，高风险高弹性</t>
-  </si>
-  <si>
-    <t>931456</t>
-  </si>
-  <si>
-    <t>中国教育</t>
-  </si>
-  <si>
-    <t>职业教育+教育科技</t>
-  </si>
-  <si>
-    <t>教育</t>
-  </si>
-  <si>
-    <t>1：职业教育+教育科技，人口素质提升刚需；2：中公教育/传智教育，职教+IT培训；3：30只中盘股，平均市值80亿；4：1只主题指数，政策规范化后复苏</t>
-  </si>
-  <si>
-    <t>931461</t>
-  </si>
-  <si>
-    <t>电子50</t>
-  </si>
-  <si>
-    <t>消费电子+半导体设备</t>
-  </si>
-  <si>
-    <t>电子</t>
-  </si>
-  <si>
-    <t>1：消费电子复苏+半导体设备国产化；2：苹果链/华为链+半导体设备材料；3：50只中大盘股，平均市值250亿；4：4只ETF，流动性最佳电子指数</t>
-  </si>
-  <si>
-    <t>931463</t>
-  </si>
-  <si>
-    <t>300 ESG</t>
-  </si>
-  <si>
-    <t>银发经济ESG实践（*替换长寿经济重复*）</t>
-  </si>
-  <si>
-    <t>931469</t>
-  </si>
-  <si>
-    <t>云计算50</t>
-  </si>
-  <si>
-    <t>云计算细分龙头</t>
-  </si>
-  <si>
-    <t>1：聚焦云计算核心标的，规避纯概念股；2：50只云计算龙头，IaaS/PaaS/SaaS均衡；3：50只中大盘股，集中度高；4：2只ETF，与云计算指数互补（更聚焦）</t>
-  </si>
-  <si>
-    <t>931478</t>
-  </si>
-  <si>
-    <t>苏州绿色发展</t>
-  </si>
-  <si>
-    <t>地方绿色转型样板</t>
-  </si>
-  <si>
-    <t>区域特色</t>
-  </si>
-  <si>
-    <t>1：地方绿色转型样板，可复制性强；2：绿色制造/循环经济/环保服务；3：50只中盘股，苏州本地企业；4：1只区域指数，地方政策试验田</t>
-  </si>
-  <si>
-    <t>931480</t>
-  </si>
-  <si>
-    <t>线上消费</t>
-  </si>
-  <si>
-    <t>电商/本地生活</t>
-  </si>
-  <si>
-    <t>1：数字经济与消费融合，平台经济常态化；2：美团/拼多多/快手，本地生活+电商；3：50只中盘股，平均市值300亿；4：3只ETF（复用信息技术），消费端属性</t>
-  </si>
-  <si>
-    <t>931484</t>
-  </si>
-  <si>
-    <t>CS医药创新</t>
-  </si>
-  <si>
-    <t>创新药+创新器械</t>
-  </si>
-  <si>
-    <t>1：创新药+创新器械双轮驱动；2：迈瑞医疗/联影医疗等高端器械+创新药；3：50只中盘股，平均市值200亿；4：2只ETF，器械占比提升</t>
-  </si>
-  <si>
-    <t>931495</t>
-  </si>
-  <si>
-    <t>工业互联</t>
-  </si>
-  <si>
-    <t>工业互联网平台</t>
-  </si>
-  <si>
-    <t>1：工业互联网平台，制造业数字化转型枢纽；2：平台层（树根互联/卡奥斯）+应用层；3：50只中盘股，平均市值100亿；4：2只ETF，B2B属性强</t>
-  </si>
-  <si>
-    <t>931496</t>
-  </si>
-  <si>
-    <t>交银理财大湾区</t>
-  </si>
-  <si>
-    <t>大湾区智慧农业试点，政策试验田</t>
-  </si>
-  <si>
-    <t>智慧农业</t>
-  </si>
-  <si>
-    <t>1：大湾区智慧农业试点，政策试验田；2：垂直农业/植物工厂/农业机器人；3：30只小盘股，平均市值50亿；4：1只区域指数，前沿探索型</t>
-  </si>
-  <si>
-    <t>931529</t>
-  </si>
-  <si>
-    <t>国企数字经济</t>
-  </si>
-  <si>
-    <t>国企生物育种</t>
-  </si>
-  <si>
-    <t>生物育种</t>
-  </si>
-  <si>
-    <t>1：国企主导生物育种，基因编辑技术突破；2：中国农科院转化标的，CRISPR技术应用；3：50只中盘股，平均市值90亿；4：1只主题指数，前沿技术探索</t>
-  </si>
-  <si>
-    <t>931554</t>
-  </si>
-  <si>
-    <t>长江保护</t>
-  </si>
-  <si>
-    <t>长江生态修复</t>
-  </si>
-  <si>
-    <t>1：长江经济带生态修复，流域治理标杆；2：水环境治理/生态修复/环保设备；3：50只中盘股，长江沿线企业集中；4：1只区域指数（复用新能源），政策持续性强</t>
-  </si>
-  <si>
-    <t>931559</t>
-  </si>
-  <si>
-    <t>苏银理财长三角</t>
-  </si>
-  <si>
-    <t>长三角生态绿色一体化</t>
-  </si>
-  <si>
-    <t>1：长三角生态绿色一体化，示范区建设；2：环保/水利/绿色基建，区域协同项目；3：50只中盘股，沪苏浙皖企业；4：1只区域指数，政策试验田</t>
-  </si>
-  <si>
-    <t>931573</t>
-  </si>
-  <si>
-    <t>港股通科技</t>
-  </si>
-  <si>
-    <t>跨境电商出海</t>
-  </si>
-  <si>
-    <t>1：跨境电商出海，全球供应链重构；2：SHEIN/Temu，DTC模式创新；3：50只港股中盘（复用现代服务），平均市值200亿；4：2只ETF，跨境消费视角</t>
-  </si>
-  <si>
-    <t>931574</t>
-  </si>
-  <si>
-    <t>港股科技</t>
-  </si>
-  <si>
-    <t>港股互联网平台</t>
-  </si>
-  <si>
-    <t>1：港股互联网平台，估值修复+出海双逻辑；2：腾讯/美团/快手/小米，与A股互补；3：50只港股大盘，平均市值800亿；4：4只ETF，流动性最佳港股科技指数</t>
-  </si>
-  <si>
-    <t>931580</t>
-  </si>
-  <si>
-    <t>SHS游戏传媒</t>
-  </si>
-  <si>
-    <t>港股游戏出海</t>
-  </si>
-  <si>
-    <t>1：港股游戏出海，全球化运营能力；2：腾讯/网易/米哈游H股，海外收入占比50%+；3：50只港股中大盘，平均市值500亿；4：2只ETF，出海逻辑强</t>
-  </si>
-  <si>
-    <t>931582</t>
-  </si>
-  <si>
-    <t>数字经济</t>
-  </si>
-  <si>
-    <t>数字产业化+产业数字化</t>
-  </si>
-  <si>
-    <t>1：数字产业化+产业数字化双路径；2：数字内容/数字支付/数字政务等应用层；3：100只中大盘股，平均市值200亿；4：3只ETF，消费端属性强</t>
-  </si>
-  <si>
-    <t>931585</t>
-  </si>
-  <si>
-    <t>卫星导航</t>
-  </si>
-  <si>
-    <t>北斗应用层</t>
-  </si>
-  <si>
-    <t>1：北斗规模化应用，位置服务基础设施；2：芯片-终端-应用全链条，精准农业/智能驾驶受益；3：50只中盘股，平均市值150亿；4：3只ETF，应用场景持续拓展</t>
-  </si>
-  <si>
-    <t>931589</t>
-  </si>
-  <si>
-    <t>300成长创新</t>
-  </si>
-  <si>
-    <t>科技安全+创新</t>
-  </si>
-  <si>
-    <t>1：科技安全+创新双主线；2：半导体/软件/通信设备创新龙头；3：100只中盘股，成长性突出；4：2只ETF，与沪深300互补（创新侧重）</t>
-  </si>
-  <si>
-    <t>931594</t>
-  </si>
-  <si>
-    <t>卫星产业</t>
-  </si>
-  <si>
-    <t>低空经济基础设施</t>
-  </si>
-  <si>
-    <t>1：低空经济写入政府工作报告，十五五新增长点；2：卫星制造/发射服务/地面设备；3：50只小盘股，商业航天企业占比70%；4：2只ETF，政策催化密集</t>
-  </si>
-  <si>
-    <t>931644</t>
-  </si>
-  <si>
-    <t>消费电子</t>
-  </si>
-  <si>
-    <t>智能硬件上游</t>
-  </si>
-  <si>
-    <t>1：智能硬件创新，AR/VR/可穿戴设备；2：歌尔股份/立讯精密等，苹果链+创新硬件；3：50只中盘股，平均市值200亿；4：3只ETF，科技+消费融合</t>
-  </si>
-  <si>
-    <t>931646</t>
-  </si>
-  <si>
-    <t>SHS新消费</t>
-  </si>
-  <si>
-    <t>新消费品牌龙头</t>
-  </si>
-  <si>
-    <t>1：新消费品牌崛起，国潮+品质双驱动；2：安踏/李宁/珀莱雅等，品牌力+渠道力；3：50只中大盘股，平均市值300亿；4：3只ETF，消费结构升级代表</t>
-  </si>
-  <si>
-    <t>931652</t>
-  </si>
-  <si>
-    <t>厦门指数</t>
-  </si>
-  <si>
-    <t>厦门港口经济+制造</t>
-  </si>
-  <si>
-    <t>1：厦门港口经济+制造业转型样板；2：半导体封测/新能源材料/精密制造；3：50只中盘股，区域龙头集中；4：1只区域指数，流动性适中</t>
-  </si>
-  <si>
-    <t>931663</t>
-  </si>
-  <si>
-    <t>SHS消费龙头</t>
-  </si>
-  <si>
-    <t>国潮品牌</t>
-  </si>
-  <si>
-    <t>1：国潮崛起，文化自信+品质升级；2：波司登/李宁/安踏，设计+品牌双提升；3：50只中大盘股，平均市值300亿；4：2只ETF，文化输出载体</t>
-  </si>
-  <si>
-    <t>931687</t>
-  </si>
-  <si>
-    <t>风电产业</t>
-  </si>
-  <si>
-    <t>海上风电+大基地</t>
-  </si>
-  <si>
-    <t>1：海上风电+大基地建设，十五五装机目标明确；2：整机-叶片-塔筒-海缆全链条；3：50只中盘股，金风/明阳等龙头；4：2只ETF，与光伏形成互补</t>
-  </si>
-  <si>
-    <t>931695</t>
-  </si>
-  <si>
-    <t>成渝经济圈</t>
-  </si>
-  <si>
-    <t>西部供应链枢纽</t>
-  </si>
-  <si>
-    <t>1：西部消费中心，内需市场培育；2：成都/重庆餐饮/零售/文旅集群；3：100只中盘股（复用现代服务），平均市值150亿；4：2只区域指数，区域消费视角</t>
-  </si>
-  <si>
-    <t>931697</t>
-  </si>
-  <si>
-    <t>消费50策略</t>
-  </si>
-  <si>
-    <t>充电桩/换电服务</t>
-  </si>
-  <si>
-    <t>1：新能源消费端培育，充电桩/换电写入规划；2：充电桩运营商/换电服务商/充电设备；3：50只中盘股，特来电/星星充电等；4：1只ETF，消费属性强于制造端</t>
-  </si>
-  <si>
-    <t>931718</t>
-  </si>
-  <si>
-    <t>高端造质量成长50</t>
-  </si>
-  <si>
-    <t>质量+成长双优</t>
-  </si>
-  <si>
-    <t>1：高质量发展导向，规避纯概念炒作；2：质量（ROE&gt;15%）+成长（营收增速&gt;20%）双优；3：50只中大盘股，行业分散；4：1只ETF，Smart Beta策略</t>
-  </si>
-  <si>
-    <t>931725</t>
-  </si>
-  <si>
-    <t>中华联合优质成长</t>
-  </si>
-  <si>
-    <t>第三方检测认证</t>
-  </si>
-  <si>
-    <t>检验检测</t>
-  </si>
-  <si>
-    <t>1：质量强国，检验检测认证国产替代；2：华测检测/谱尼测试等第三方检测；3：50只中盘股，平均市值100亿；4：1只定制指数，细分领域稀缺</t>
-  </si>
-  <si>
-    <t>931743</t>
-  </si>
-  <si>
-    <t>半导体材料设备</t>
-  </si>
-  <si>
-    <t>上游“卡脖子”环节</t>
-  </si>
-  <si>
-    <t>1：国产替代刚性需求，大基金三期重点投向；2：聚焦光刻机/刻蚀机/光刻胶等“卡脖子”环节；3：50只小盘股，国产化率&lt;30%环节集中；4：2只ETF，弹性大但波动高</t>
-  </si>
-  <si>
-    <t>931746</t>
-  </si>
-  <si>
-    <t>储能产业</t>
-  </si>
-  <si>
-    <t>储能系统集成</t>
-  </si>
-  <si>
-    <t>1：新型电力系统关键，强制配储政策驱动；2：储能系统集成/电池管理/温控设备；3：50只中盘股，2023年后商业化加速；4：3只ETF，成长确定性高</t>
-  </si>
-  <si>
-    <t>931752</t>
-  </si>
-  <si>
-    <t>工程机械主题</t>
-  </si>
-  <si>
-    <t>新能源工程机械（*保留1次*）</t>
-  </si>
-  <si>
-    <t>1：新能源工程机械渗透率提升；2：三一/徐工电动化转型，出口+内需双驱动；3：30只中盘股（复用新能源），平均市值150亿；4：1只主题指数，特种装备视角</t>
-  </si>
-  <si>
-    <t>931772</t>
-  </si>
-  <si>
-    <t>SEEE碳中和</t>
-  </si>
-  <si>
-    <t>中证+上海环交所联合编制</t>
-  </si>
-  <si>
-    <t>1：中证+上海环交所联合编制，方法论权威；2：能源替代（风光）+节能减排（节能设备）双路径；3：100只中盘股，覆盖全市场；4：4只ETF，政策背书强</t>
-  </si>
-  <si>
-    <t>931778</t>
-  </si>
-  <si>
-    <t>农牧主题</t>
-  </si>
-  <si>
-    <t>养殖下游加工</t>
-  </si>
-  <si>
-    <t>1：养殖下游加工，食品工业化；2：屠宰/食品加工/冷链物流，双汇/龙大等；3：30只中盘股，平均市值80亿；4：1只主题指数，消费端属性强</t>
-  </si>
-  <si>
-    <t>931785</t>
-  </si>
-  <si>
-    <t>智选沪深港科技50</t>
-  </si>
-  <si>
-    <t>影视科技融合（*替换中证影视重复*）</t>
-  </si>
-  <si>
-    <t>931787</t>
-  </si>
-  <si>
-    <t>港股创新药</t>
-  </si>
-  <si>
-    <t>早期临床标的</t>
-  </si>
-  <si>
-    <t>1：与港股通创新药互补，覆盖更多临床阶段；2：侧重早期临床（I/II期）标的，风险收益比高；3：30只港股小盘，平均市值30亿；4：1只ETF，高风险高弹性</t>
-  </si>
-  <si>
-    <t>931789</t>
-  </si>
-  <si>
-    <t>中韩新能车</t>
-  </si>
-  <si>
-    <t>中韩产业链协同</t>
-  </si>
-  <si>
-    <t>1：中韩产业链协同，全球化布局；2：电池材料（隔膜/电解液）中韩企业互补；3：30只中盘股，A股+韩股；4：1只跨境指数，产业链视角</t>
-  </si>
-  <si>
-    <t>931790</t>
-  </si>
-  <si>
-    <t>中韩半导体</t>
-  </si>
-  <si>
-    <t>中韩半导体互补</t>
-  </si>
-  <si>
-    <t>1：中韩半导体产业链互补，技术合作深化；2：设备/材料/封测环节协同，规避地缘风险；3：30只中盘股，A股+韩股；4：1只跨境指数，全球化视角</t>
-  </si>
-  <si>
-    <t>931793</t>
-  </si>
-  <si>
-    <t>半导体15</t>
-  </si>
-  <si>
-    <t>极致聚焦核心15只</t>
-  </si>
-  <si>
-    <t>1：极致聚焦核心标的，国产替代加速受益；2：15只半导体核心标的（设计5+设备5+材料5）；3：15只中大盘股，龙头集中度高；4：1只ETF，高弹性但波动大</t>
-  </si>
-  <si>
-    <t>931799</t>
-  </si>
-  <si>
-    <t>国寿资产ESG绿色低碳100</t>
-  </si>
-  <si>
-    <t>保险资金绿色投资</t>
-  </si>
-  <si>
-    <t>1：保险资金绿色投资，长期资金入市标杆；2：绿色低碳全产业链，ESG评级前20%；3：100只中大盘股，机构持仓集中；4：1只定制指数，长期资金偏好</t>
-  </si>
-  <si>
-    <t>931834</t>
-  </si>
-  <si>
-    <t>华福福建100</t>
-  </si>
-  <si>
-    <t>福建制造业升级</t>
-  </si>
-  <si>
-    <t>1：福建传统制造业升级样板；2：纺织/鞋服/建材智能化改造；3：100只中盘股，平均市值120亿；4：1只区域指数（复用高端制造），地方政策支持</t>
-  </si>
-  <si>
-    <t>931837</t>
-  </si>
-  <si>
-    <t>央企现代产业</t>
-  </si>
-  <si>
-    <t>央企主导升级</t>
-  </si>
-  <si>
-    <t>1：央企主导产业升级，执行力强于民企；2：高端制造央企（中国中车/中国船舶/中国商飞）；3：50只大盘股，平均市值600亿；4：2只ETF，高股息+成长双属性</t>
-  </si>
-  <si>
-    <t>931865</t>
-  </si>
-  <si>
-    <t>中证半导</t>
-  </si>
-  <si>
-    <t>半导体全产业链</t>
-  </si>
-  <si>
-    <t>1：半导体全产业链支持，十五五资源倾斜；2：设计-制造-封测-设备全覆盖，龙头集中；3：50只中大盘股，平均市值300亿；4：8只ETF，流动性最佳半导体指数</t>
-  </si>
-  <si>
-    <t>931866</t>
-  </si>
-  <si>
-    <t>中证机床</t>
-  </si>
-  <si>
-    <t>工业母机专项</t>
-  </si>
-  <si>
-    <t>1：工业母机“04专项”延续，制造业基础保障；2：数控机床/加工中心/精密测量仪器；3：50只中盘股，国产高端机床占比60%；4：1只ETF，细分领域稀缺标的</t>
-  </si>
-  <si>
-    <t>931892</t>
-  </si>
-  <si>
-    <t>有色矿业</t>
-  </si>
-  <si>
-    <t>锂/钴/镍资源端</t>
-  </si>
-  <si>
-    <t>1：资源安全战略，锂/钴/镍自主可控；2：新能源金属资源端，紫金/赣锋等龙头；3：50只中盘股，平均市值200亿；4：2只ETF，与稀土产业互补（更广资源覆盖）</t>
-  </si>
-  <si>
-    <t>931897</t>
-  </si>
-  <si>
-    <t>绿色电力</t>
-  </si>
-  <si>
-    <t>风光运营资产</t>
-  </si>
-  <si>
-    <t>1：绿电交易+碳市场机制完善，运营资产受益；2：风电/光伏电站运营，现金流稳定；3：50只小盘股，平均市值80亿；4：2只ETF，高股息属性（3-4%）</t>
-  </si>
-  <si>
-    <t>931992</t>
-  </si>
-  <si>
-    <t>疫苗生物</t>
-  </si>
-  <si>
-    <t>疫苗+mRNA技术</t>
-  </si>
-  <si>
-    <t>1：公共卫生安全战略物资，mRNA技术突破；2：疫苗+生物制品，智飞/康希诺/沃森等；3：30只小盘股，平均市值80亿；4：2只ETF，技术迭代快</t>
-  </si>
-  <si>
-    <t>931994</t>
-  </si>
-  <si>
-    <t>电网设备主题</t>
-  </si>
-  <si>
-    <t>医疗用电安全</t>
-  </si>
-  <si>
-    <t>1：医疗用电安全，公共健康基础设施保障；2：UPS/应急电源/智能配电，医院刚需；3：30只中盘股，平均市值80亿；4：1只主题指数，细分领域稀缺</t>
-  </si>
-  <si>
-    <t>932000</t>
-  </si>
-  <si>
-    <t>中证2000</t>
-  </si>
-  <si>
-    <t>微盘股流动性改善后新基准</t>
-  </si>
-  <si>
-    <t>微盘</t>
-  </si>
-  <si>
-    <t>1：小微主体流动性改善工程核心标的；2：微盘股中质量较好标的，剔除ST/退市风险股；3：2000只微盘股，平均市值&lt;50亿；4：5只ETF，2023年推出，政策扶持明确</t>
-  </si>
-  <si>
-    <t>932037</t>
-  </si>
-  <si>
-    <t>央企现代能源</t>
-  </si>
-  <si>
-    <t>传统能源清洁化</t>
-  </si>
-  <si>
-    <t>央企转型</t>
-  </si>
-  <si>
-    <t>1：央企主导传统能源清洁化转型；2：国家能源集团/中国华能新能源装机提升；3：50只大盘股，平均市值500亿；4：2只ETF，转型执行力强</t>
-  </si>
-  <si>
-    <t>932038</t>
-  </si>
-  <si>
-    <t>央企科技引领</t>
-  </si>
-  <si>
-    <t>科技赋能传统</t>
-  </si>
-  <si>
-    <t>1：央企科技赋能传统产业升级；2：中国宝武工业互联网/中国建材新材料；3：50只大盘股，平均市值600亿；4：2只ETF，科技+传统融合</t>
-  </si>
-  <si>
-    <t>932039</t>
-  </si>
-  <si>
-    <t>央企股东回报</t>
-  </si>
-  <si>
-    <t>高股息转型标的</t>
-  </si>
-  <si>
-    <t>高股息</t>
-  </si>
-  <si>
-    <t>1：央企市值管理，高股息策略写入考核；2：传统产业升级标的，现金流稳定；3：50只大盘股，平均股息率5%+；4：3只ETF，防御属性强</t>
-  </si>
-  <si>
-    <t>932042</t>
-  </si>
-  <si>
-    <t>智选航空科技</t>
-  </si>
-  <si>
-    <t>大飞机产业链</t>
-  </si>
-  <si>
-    <t>1：大飞机专项，C919商业化加速；2：航空发动机/机身结构/航电系统；3：50只中盘股，产业链配套企业集中；4：1只ETF，主题性强</t>
-  </si>
-  <si>
-    <t>932056</t>
-  </si>
-  <si>
-    <t>海洋经济</t>
-  </si>
-  <si>
-    <t>蓝色经济+海洋物流</t>
-  </si>
-  <si>
-    <t>1：21世纪海上丝绸之路，蓝色经济；2：海洋物流/海洋装备/海洋渔业；3：50只中盘股，平均市值120亿；4：1只主题指数，区域特色鲜明</t>
-  </si>
-  <si>
-    <t>932066</t>
-  </si>
-  <si>
-    <t>半导体行业精选</t>
-  </si>
-  <si>
-    <t>第三代半导体</t>
-  </si>
-  <si>
-    <t>1：第三代半导体（碳化硅/氮化镓）专项扶持；2：碳化硅衬底-外延-器件，新能源车/光伏应用；3：30只小盘股，技术壁垒高；4：2只ETF，与中证半导互补（更聚焦新材料）</t>
-  </si>
-  <si>
-    <t>932068</t>
-  </si>
-  <si>
-    <t>长寿经济</t>
-  </si>
-  <si>
-    <t>银发经济终端</t>
-  </si>
-  <si>
-    <t>1：银发经济写入政府工作报告，人口结构变化；2：养老社区/康复器械/慢病管理；3：50只中盘股，平均市值120亿；4：2只ETF，需求刚性增长</t>
-  </si>
-  <si>
-    <t>932075</t>
-  </si>
-  <si>
-    <t>全指金融</t>
-  </si>
-  <si>
-    <t>绿色金融支持</t>
-  </si>
-  <si>
-    <t>1：绿色金融支持，碳中和债/转型金融工具创新；2：银行/券商绿色信贷/绿色债券承销；3：300只金融股，大盘为主；4：3只ETF，资金端保障逻辑</t>
-  </si>
-  <si>
-    <t>932076</t>
-  </si>
-  <si>
-    <t>全指地产</t>
-  </si>
-  <si>
-    <t>康养地产载体</t>
-  </si>
-  <si>
-    <t>1：康养地产转型，银发经济物理载体；2：万科/保利康养社区布局，传统地产转型样本；3：300只地产股，大盘为主；4：3只ETF，转型逻辑观察窗口</t>
-  </si>
-  <si>
-    <t>932077</t>
-  </si>
-  <si>
-    <t>全指能源行业</t>
-  </si>
-  <si>
-    <t>传统+新能源过渡</t>
-  </si>
-  <si>
-    <t>能源安全</t>
-  </si>
-  <si>
-    <t>1：传统能源+新能源过渡，能源安全底线；2：煤炭/石油/天然气+新能源，保障性电源；3：100只中大盘股，平均市值300亿；4：3只ETF，安全属性突出</t>
-  </si>
-  <si>
-    <t>932085</t>
-  </si>
-  <si>
-    <t>全指通信行业</t>
-  </si>
-  <si>
-    <t>5G/卫星通信</t>
-  </si>
-  <si>
-    <t>通信保障</t>
-  </si>
-  <si>
-    <t>1：5G/卫星通信基础设施，数字时代基础保障；2：中国移动/中国电信/中国卫通；3：50只大盘股，平均市值800亿；4：2只ETF，高股息（5%+）</t>
-  </si>
-  <si>
-    <t>932086</t>
-  </si>
-  <si>
-    <t>全指公用行业</t>
-  </si>
-  <si>
-    <t>运营类资产</t>
-  </si>
-  <si>
-    <t>1：与全指公用互补，侧重运营类资产；2：污水处理/垃圾焚烧/危废处理；3：100只中盘股，平均市值120亿；4：2只ETF，环保运营属性强</t>
-  </si>
-  <si>
-    <t>932153</t>
-  </si>
-  <si>
-    <t>港股通价值策略</t>
-  </si>
-  <si>
-    <t>消费价值股（*替换港股通科技重复*）</t>
-  </si>
-  <si>
-    <t>932257</t>
-  </si>
-  <si>
-    <t>国新央企小盘</t>
-  </si>
-  <si>
-    <t>央企隐形冠军</t>
-  </si>
-  <si>
-    <t>小盘成长</t>
-  </si>
-  <si>
-    <t>1：央企小盘隐形冠军，补链强链核心；2：细分领域“小巨人”，央企背景技术积累深；3：100只小盘股，平均市值50亿；4：1只主题指数，稀缺性高</t>
-  </si>
-  <si>
-    <t>932266</t>
-  </si>
-  <si>
-    <t>国企战略新兴</t>
-  </si>
-  <si>
-    <t>国企检验检测</t>
-  </si>
-  <si>
-    <t>1：国企主导战略新兴服务，检验检测/认证；2：中国检验认证集团等，标准制定者；3：50只大盘股，央企占比80%；4：1只主题指数，政策执行力强</t>
-  </si>
-  <si>
     <t>932357</t>
   </si>
   <si>
@@ -2175,138 +2280,6 @@
   </si>
   <si>
     <t>1：工信部“小巨人”认证，补链强链核心；2：100%成分股为专精特新企业，覆盖31个细分领域；3：100只小盘股，平均市值80亿；4：3只ETF，政策扶持持续性强</t>
-  </si>
-  <si>
-    <t>932359</t>
-  </si>
-  <si>
-    <t>国新国企人工智能</t>
-  </si>
-  <si>
-    <t>国企主导AI应用</t>
-  </si>
-  <si>
-    <t>1：国企主导AI政务/金融应用，安全可控；2：中国电子/中国电科AI平台，党政市场主导；3：50只大盘股，央企占比90%；4：1只主题指数，政策执行力强</t>
-  </si>
-  <si>
-    <t>932365</t>
-  </si>
-  <si>
-    <t>中证现金流</t>
-  </si>
-  <si>
-    <t>高现金流服务业</t>
-  </si>
-  <si>
-    <t>1：高现金流服务业，抗周期属性强；2：物业/检测/人力资源，经营性现金流稳定；3：100只小盘股，平均市值60亿；4：2只ETF，防御属性突出</t>
-  </si>
-  <si>
-    <t>932366</t>
-  </si>
-  <si>
-    <t>300现金流</t>
-  </si>
-  <si>
-    <t>高现金流传统行业</t>
-  </si>
-  <si>
-    <t>现金流</t>
-  </si>
-  <si>
-    <t>1：高现金流传统行业，转型基础好；2：建材/化工/机械，经营性现金流稳定；3：100只中大盘股，平均市值200亿；4：2只ETF，质量因子策略</t>
-  </si>
-  <si>
-    <t>932367</t>
-  </si>
-  <si>
-    <t>800现金流</t>
-  </si>
-  <si>
-    <t>800成分高现金流（*替换300质量重复*）</t>
-  </si>
-  <si>
-    <t>932422</t>
-  </si>
-  <si>
-    <t>国新港股通央企红</t>
-  </si>
-  <si>
-    <t>绿色能源央企H股</t>
-  </si>
-  <si>
-    <t>1：央企高股息+绿色转型双重逻辑；2：国家电投/三峡集团等绿色能源央企H股；3：50只港股大盘，平均股息率5%+；4：1只ETF，防御+成长兼备</t>
-  </si>
-  <si>
-    <t>932431</t>
-  </si>
-  <si>
-    <t>300质量</t>
-  </si>
-  <si>
-    <t>医药质量领先企业</t>
-  </si>
-  <si>
-    <t>1：高质量发展导向，规避集采冲击；2：医药行业质量领先（ROE&gt;15%+现金流&gt;0）；3：100只中大盘股，平均市值200亿；4：2只ETF，防御属性强</t>
-  </si>
-  <si>
-    <t>932444</t>
-  </si>
-  <si>
-    <t>互联互通中国50</t>
-  </si>
-  <si>
-    <t>港股新能源龙头</t>
-  </si>
-  <si>
-    <t>1：港股新能源龙头，估值修复+成长双逻辑；2：比亚迪H/理想/小鹏等，与A股互补；3：50只港股大盘，平均市值500亿+；4：2只ETF，跨境配置便利</t>
-  </si>
-  <si>
-    <t>932456</t>
-  </si>
-  <si>
-    <t>科创创业AI</t>
-  </si>
-  <si>
-    <t>AIGC应用</t>
-  </si>
-  <si>
-    <t>科技赋能</t>
-  </si>
-  <si>
-    <t>1：农业AI应用，智慧种植/病虫害识别；2：极飞科技/大疆农业等，无人机+AI；3：50只小盘股，平均市值70亿；4：1只主题指数（复用信息技术），科技交叉</t>
-  </si>
-  <si>
-    <t>932592</t>
-  </si>
-  <si>
-    <t>沪深港三地龙头</t>
-  </si>
-  <si>
-    <t>1：沪深港三地龙头，全球化配置；2：腾讯/阿里/美团/宁德等核心资产；3：50只超大盘股，平均市值1000亿+；4：3只ETF（HKD/USD/CNY），跨境便利</t>
-  </si>
-  <si>
-    <t>980017</t>
-  </si>
-  <si>
-    <t>国证芯片</t>
-  </si>
-  <si>
-    <t>港股半导体补充</t>
-  </si>
-  <si>
-    <t>1：港股半导体补充，规避A股估值波动；2：中芯国际H/华虹半导体等，与A股互补；3：30只港股，流动性好于纯A股小盘；4：1只ETF，跨境配置价值</t>
-  </si>
-  <si>
-    <t>H30597</t>
-  </si>
-  <si>
-    <t>新材料</t>
-  </si>
-  <si>
-    <t>高性能纤维/电子化学品</t>
-  </si>
-  <si>
-    <t>1：高性能纤维/电子化学品，“卡脖子”材料国产替代；2：碳纤维/芳纶/光刻胶/电子特气；3：50只中盘股，平均市值150亿；4：2只ETF，上游材料视角</t>
   </si>
 </sst>
 </file>
@@ -3285,7 +3258,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G180"/>
+  <dimension ref="A1:G177"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="11.625" style="2" customWidth="1"/>
@@ -3321,591 +3294,609 @@
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="2">
-        <v>399311</v>
+      <c r="A2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="2" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G3" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="2" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="D4" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="E4" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F4" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="G4" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="2" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="B5" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="C5" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="D5" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E5" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F5" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="G5" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="B6" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C6" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E6" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F6" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="G6" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="2" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="B7" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="C7" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D7" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E7" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="F7" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="G7" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="2" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B8" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C8" t="s">
-        <v>9</v>
+        <v>44</v>
       </c>
       <c r="D8" t="s">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="E8" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="F8" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="G8" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="2" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="B9" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="C9" t="s">
-        <v>9</v>
+        <v>51</v>
       </c>
       <c r="D9" t="s">
-        <v>10</v>
+        <v>52</v>
       </c>
       <c r="E9" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="F9" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="G9" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="2" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="B10" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="C10" t="s">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="D10" t="s">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="E10" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="F10" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="G10" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="2" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="B11" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="C11" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D11" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E11" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="F11" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="G11" t="s">
-        <v>52</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="2" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="B12" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="C12" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="D12" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="E12" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="F12" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="G12" t="s">
-        <v>56</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="2" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="B13" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="C13" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="D13" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E13" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="F13" t="s">
-        <v>12</v>
+        <v>70</v>
       </c>
       <c r="G13" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="2" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="B14" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="C14" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="D14" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E14" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="F14" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="G14" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="2" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="B15" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="C15" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="D15" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="E15" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="F15" t="s">
-        <v>17</v>
+        <v>79</v>
       </c>
       <c r="G15" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="2" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="B16" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="C16" t="s">
-        <v>74</v>
+        <v>34</v>
       </c>
       <c r="D16" t="s">
-        <v>73</v>
+        <v>35</v>
       </c>
       <c r="E16" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="F16" t="s">
-        <v>17</v>
+        <v>84</v>
       </c>
       <c r="G16" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="2" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="B17" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C17" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="D17" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="E17" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="F17" t="s">
-        <v>12</v>
+        <v>91</v>
       </c>
       <c r="G17" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="2" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="B18" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="C18" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="D18" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="E18" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="F18" t="s">
-        <v>17</v>
+        <v>98</v>
       </c>
       <c r="G18" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="2" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="B19" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="C19" t="s">
-        <v>91</v>
+        <v>44</v>
       </c>
       <c r="D19" t="s">
-        <v>92</v>
+        <v>45</v>
       </c>
       <c r="E19" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="F19" t="s">
-        <v>17</v>
+        <v>103</v>
       </c>
       <c r="G19" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B20" t="s">
+        <v>106</v>
+      </c>
+      <c r="C20" t="s">
         <v>95</v>
       </c>
-      <c r="B20" t="s">
+      <c r="D20" t="s">
         <v>96</v>
       </c>
-      <c r="C20" t="s">
-        <v>21</v>
-      </c>
-      <c r="D20" t="s">
-        <v>22</v>
-      </c>
       <c r="E20" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="F20" t="s">
-        <v>12</v>
+        <v>84</v>
       </c>
       <c r="G20" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="2" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="B21" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="C21" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D21" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E21" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="F21" t="s">
-        <v>39</v>
+        <v>112</v>
       </c>
       <c r="G21" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="2" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="B22" t="s">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="C22" t="s">
-        <v>105</v>
+        <v>9</v>
       </c>
       <c r="D22" t="s">
-        <v>106</v>
+        <v>10</v>
       </c>
       <c r="E22" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="F22" t="s">
-        <v>39</v>
+        <v>116</v>
       </c>
       <c r="G22" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="2" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="B23" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="C23" t="s">
-        <v>111</v>
+        <v>9</v>
       </c>
       <c r="D23" t="s">
-        <v>112</v>
+        <v>10</v>
       </c>
       <c r="E23" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="F23" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="G23" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="2" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="B24" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="C24" t="s">
-        <v>111</v>
+        <v>9</v>
       </c>
       <c r="D24" t="s">
+        <v>10</v>
+      </c>
+      <c r="E24" t="s">
+        <v>124</v>
+      </c>
+      <c r="F24" t="s">
         <v>112</v>
       </c>
-      <c r="E24" t="s">
-        <v>118</v>
-      </c>
-      <c r="F24" t="s">
-        <v>119</v>
-      </c>
       <c r="G24" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="2" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="B25" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="C25" t="s">
-        <v>9</v>
+        <v>128</v>
       </c>
       <c r="D25" t="s">
-        <v>10</v>
+        <v>129</v>
       </c>
       <c r="E25" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="F25" t="s">
-        <v>17</v>
+        <v>131</v>
       </c>
       <c r="G25" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="2" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="B26" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="C26" t="s">
-        <v>111</v>
+        <v>128</v>
       </c>
       <c r="D26" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="E26" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="F26" t="s">
-        <v>17</v>
+        <v>91</v>
       </c>
       <c r="G26" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27" s="2" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="B27" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="C27" t="s">
-        <v>79</v>
+        <v>15</v>
       </c>
       <c r="D27" t="s">
-        <v>80</v>
+        <v>16</v>
       </c>
       <c r="E27" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="F27" t="s">
-        <v>17</v>
+        <v>91</v>
       </c>
       <c r="G27" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28" s="2" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="B28" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="C28" t="s">
         <v>9</v>
@@ -3914,3514 +3905,3427 @@
         <v>10</v>
       </c>
       <c r="E28" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="F28" t="s">
-        <v>136</v>
+        <v>84</v>
       </c>
       <c r="G28" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" s="2" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="B29" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="C29" t="s">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="D29" t="s">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="E29" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="F29" t="s">
-        <v>17</v>
+        <v>54</v>
       </c>
       <c r="G29" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" s="2" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="B30" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="C30" t="s">
-        <v>105</v>
+        <v>88</v>
       </c>
       <c r="D30" t="s">
-        <v>106</v>
+        <v>89</v>
       </c>
       <c r="E30" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="F30" t="s">
-        <v>39</v>
+        <v>152</v>
       </c>
       <c r="G30" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31" s="2" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="B31" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="C31" t="s">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="D31" t="s">
-        <v>69</v>
+        <v>96</v>
       </c>
       <c r="E31" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="F31" t="s">
-        <v>17</v>
+        <v>79</v>
       </c>
       <c r="G31" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="2" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="B32" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="C32" t="s">
-        <v>9</v>
+        <v>44</v>
       </c>
       <c r="D32" t="s">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="E32" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F32" t="s">
-        <v>12</v>
+        <v>84</v>
       </c>
       <c r="G32" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
     </row>
     <row r="33" spans="1:7">
       <c r="A33" s="2" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="B33" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="C33" t="s">
-        <v>91</v>
+        <v>164</v>
       </c>
       <c r="D33" t="s">
-        <v>92</v>
+        <v>165</v>
       </c>
       <c r="E33" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="F33" t="s">
-        <v>17</v>
+        <v>84</v>
       </c>
       <c r="G33" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
     </row>
     <row r="34" spans="1:7">
       <c r="A34" s="2" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="B34" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="C34" t="s">
-        <v>74</v>
+        <v>22</v>
       </c>
       <c r="D34" t="s">
-        <v>73</v>
+        <v>23</v>
       </c>
       <c r="E34" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="F34" t="s">
-        <v>17</v>
+        <v>171</v>
       </c>
       <c r="G34" t="s">
-        <v>161</v>
+        <v>172</v>
       </c>
     </row>
     <row r="35" spans="1:7">
       <c r="A35" s="2" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="B35" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="C35" t="s">
-        <v>105</v>
+        <v>44</v>
       </c>
       <c r="D35" t="s">
-        <v>106</v>
+        <v>45</v>
       </c>
       <c r="E35" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="F35" t="s">
-        <v>17</v>
+        <v>131</v>
       </c>
       <c r="G35" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
     </row>
     <row r="36" spans="1:7">
       <c r="A36" s="2" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="B36" t="s">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="C36" t="s">
-        <v>74</v>
+        <v>15</v>
       </c>
       <c r="D36" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="E36" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="F36" t="s">
-        <v>114</v>
+        <v>180</v>
       </c>
       <c r="G36" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
     </row>
     <row r="37" spans="1:7">
       <c r="A37" s="2" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="B37" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="C37" t="s">
-        <v>91</v>
+        <v>9</v>
       </c>
       <c r="D37" t="s">
-        <v>92</v>
+        <v>10</v>
       </c>
       <c r="E37" t="s">
-        <v>172</v>
+        <v>184</v>
       </c>
       <c r="F37" t="s">
-        <v>119</v>
+        <v>84</v>
       </c>
       <c r="G37" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="2" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="B38" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="C38" t="s">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="D38" t="s">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="E38" t="s">
-        <v>176</v>
+        <v>188</v>
       </c>
       <c r="F38" t="s">
-        <v>177</v>
+        <v>70</v>
       </c>
       <c r="G38" t="s">
-        <v>178</v>
+        <v>189</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39" s="2" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="B39" t="s">
-        <v>180</v>
+        <v>191</v>
       </c>
       <c r="C39" t="s">
-        <v>85</v>
+        <v>44</v>
       </c>
       <c r="D39" t="s">
-        <v>86</v>
+        <v>45</v>
       </c>
       <c r="E39" t="s">
-        <v>181</v>
+        <v>192</v>
       </c>
       <c r="F39" t="s">
-        <v>39</v>
+        <v>112</v>
       </c>
       <c r="G39" t="s">
-        <v>182</v>
+        <v>193</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40" s="2" t="s">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="B40" t="s">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="C40" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="D40" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="E40" t="s">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="F40" t="s">
-        <v>31</v>
+        <v>112</v>
       </c>
       <c r="G40" t="s">
-        <v>31</v>
+        <v>197</v>
       </c>
     </row>
     <row r="41" spans="1:7">
       <c r="A41" s="2" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="B41" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
       <c r="C41" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="D41" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="E41" t="s">
-        <v>188</v>
+        <v>200</v>
       </c>
       <c r="F41" t="s">
-        <v>39</v>
+        <v>112</v>
       </c>
       <c r="G41" t="s">
-        <v>189</v>
+        <v>201</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42" s="2" t="s">
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="B42" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="C42" t="s">
-        <v>105</v>
+        <v>204</v>
       </c>
       <c r="D42" t="s">
-        <v>106</v>
+        <v>205</v>
       </c>
       <c r="E42" t="s">
-        <v>192</v>
+        <v>206</v>
       </c>
       <c r="F42" t="s">
         <v>12</v>
       </c>
       <c r="G42" t="s">
-        <v>193</v>
+        <v>12</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43" s="2" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="B43" t="s">
-        <v>184</v>
+        <v>208</v>
       </c>
       <c r="C43" t="s">
-        <v>74</v>
+        <v>51</v>
       </c>
       <c r="D43" t="s">
-        <v>73</v>
+        <v>52</v>
       </c>
       <c r="E43" t="s">
-        <v>195</v>
+        <v>209</v>
       </c>
       <c r="F43" t="s">
-        <v>39</v>
+        <v>112</v>
       </c>
       <c r="G43" t="s">
-        <v>196</v>
+        <v>210</v>
       </c>
     </row>
     <row r="44" spans="1:7">
       <c r="A44" s="2" t="s">
-        <v>197</v>
+        <v>211</v>
       </c>
       <c r="B44" t="s">
-        <v>198</v>
+        <v>212</v>
       </c>
       <c r="C44" t="s">
-        <v>68</v>
+        <v>128</v>
       </c>
       <c r="D44" t="s">
-        <v>69</v>
+        <v>129</v>
       </c>
       <c r="E44" t="s">
-        <v>199</v>
+        <v>213</v>
       </c>
       <c r="F44" t="s">
-        <v>114</v>
+        <v>70</v>
       </c>
       <c r="G44" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
     </row>
     <row r="45" spans="1:7">
       <c r="A45" s="2" t="s">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="B45" t="s">
-        <v>202</v>
+        <v>216</v>
       </c>
       <c r="C45" t="s">
-        <v>74</v>
+        <v>128</v>
       </c>
       <c r="D45" t="s">
-        <v>73</v>
+        <v>129</v>
       </c>
       <c r="E45" t="s">
-        <v>203</v>
+        <v>217</v>
       </c>
       <c r="F45" t="s">
-        <v>119</v>
+        <v>47</v>
       </c>
       <c r="G45" t="s">
-        <v>204</v>
+        <v>218</v>
       </c>
     </row>
     <row r="46" spans="1:7">
       <c r="A46" s="2" t="s">
-        <v>205</v>
+        <v>219</v>
       </c>
       <c r="B46" t="s">
-        <v>206</v>
+        <v>220</v>
       </c>
       <c r="C46" t="s">
-        <v>79</v>
+        <v>204</v>
       </c>
       <c r="D46" t="s">
-        <v>80</v>
+        <v>221</v>
       </c>
       <c r="E46" t="s">
-        <v>207</v>
+        <v>222</v>
       </c>
       <c r="F46" t="s">
-        <v>114</v>
+        <v>84</v>
       </c>
       <c r="G46" t="s">
-        <v>208</v>
+        <v>223</v>
       </c>
     </row>
     <row r="47" spans="1:7">
       <c r="A47" s="2" t="s">
-        <v>209</v>
+        <v>224</v>
       </c>
       <c r="B47" t="s">
-        <v>210</v>
+        <v>225</v>
       </c>
       <c r="C47" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D47" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E47" t="s">
-        <v>211</v>
+        <v>226</v>
       </c>
       <c r="F47" t="s">
-        <v>212</v>
+        <v>103</v>
       </c>
       <c r="G47" t="s">
-        <v>213</v>
+        <v>227</v>
       </c>
     </row>
     <row r="48" spans="1:7">
       <c r="A48" s="2" t="s">
-        <v>214</v>
+        <v>228</v>
       </c>
       <c r="B48" t="s">
-        <v>215</v>
+        <v>229</v>
       </c>
       <c r="C48" t="s">
-        <v>79</v>
+        <v>51</v>
       </c>
       <c r="D48" t="s">
-        <v>80</v>
+        <v>52</v>
       </c>
       <c r="E48" t="s">
-        <v>216</v>
+        <v>230</v>
       </c>
       <c r="F48" t="s">
-        <v>39</v>
+        <v>103</v>
       </c>
       <c r="G48" t="s">
-        <v>217</v>
+        <v>231</v>
       </c>
     </row>
     <row r="49" spans="1:7">
       <c r="A49" s="2" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="B49" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="C49" t="s">
-        <v>28</v>
+        <v>95</v>
       </c>
       <c r="D49" t="s">
-        <v>29</v>
+        <v>96</v>
       </c>
       <c r="E49" t="s">
-        <v>220</v>
+        <v>234</v>
       </c>
       <c r="F49" t="s">
-        <v>12</v>
+        <v>79</v>
       </c>
       <c r="G49" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
     </row>
     <row r="50" spans="1:7">
       <c r="A50" s="2" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="B50" t="s">
-        <v>223</v>
+        <v>237</v>
       </c>
       <c r="C50" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="D50" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="E50" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="F50" t="s">
-        <v>225</v>
+        <v>103</v>
       </c>
       <c r="G50" t="s">
-        <v>226</v>
+        <v>239</v>
       </c>
     </row>
     <row r="51" spans="1:7">
       <c r="A51" s="2" t="s">
-        <v>227</v>
+        <v>240</v>
       </c>
       <c r="B51" t="s">
-        <v>228</v>
+        <v>241</v>
       </c>
       <c r="C51" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D51" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="E51" t="s">
-        <v>229</v>
+        <v>242</v>
       </c>
       <c r="F51" t="s">
-        <v>212</v>
+        <v>243</v>
       </c>
       <c r="G51" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
     </row>
     <row r="52" spans="1:7">
       <c r="A52" s="2" t="s">
-        <v>231</v>
+        <v>245</v>
       </c>
       <c r="B52" t="s">
-        <v>232</v>
+        <v>246</v>
       </c>
       <c r="C52" t="s">
-        <v>91</v>
+        <v>51</v>
       </c>
       <c r="D52" t="s">
-        <v>92</v>
+        <v>52</v>
       </c>
       <c r="E52" t="s">
-        <v>233</v>
+        <v>247</v>
       </c>
       <c r="F52" t="s">
-        <v>212</v>
+        <v>47</v>
       </c>
       <c r="G52" t="s">
-        <v>234</v>
+        <v>248</v>
       </c>
     </row>
     <row r="53" spans="1:7">
       <c r="A53" s="2" t="s">
-        <v>235</v>
+        <v>249</v>
       </c>
       <c r="B53" t="s">
-        <v>236</v>
+        <v>250</v>
       </c>
       <c r="C53" t="s">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="D53" t="s">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="E53" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="F53" t="s">
-        <v>12</v>
+        <v>70</v>
       </c>
       <c r="G53" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="54" ht="15.75" spans="1:7">
-      <c r="A54" s="4">
-        <v>399971</v>
+        <v>252</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7">
+      <c r="A54" s="2" t="s">
+        <v>253</v>
       </c>
       <c r="B54" t="s">
-        <v>239</v>
+        <v>254</v>
       </c>
       <c r="C54" t="s">
-        <v>240</v>
+        <v>95</v>
       </c>
       <c r="D54" t="s">
-        <v>241</v>
+        <v>96</v>
       </c>
       <c r="E54" t="s">
-        <v>242</v>
+        <v>255</v>
       </c>
       <c r="F54" t="s">
-        <v>31</v>
+        <v>70</v>
       </c>
       <c r="G54" t="s">
-        <v>31</v>
+        <v>256</v>
       </c>
     </row>
     <row r="55" spans="1:7">
       <c r="A55" s="2" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="B55" t="s">
-        <v>244</v>
+        <v>258</v>
       </c>
       <c r="C55" t="s">
-        <v>105</v>
+        <v>15</v>
       </c>
       <c r="D55" t="s">
-        <v>106</v>
+        <v>16</v>
       </c>
       <c r="E55" t="s">
-        <v>245</v>
+        <v>259</v>
       </c>
       <c r="F55" t="s">
-        <v>39</v>
+        <v>131</v>
       </c>
       <c r="G55" t="s">
-        <v>246</v>
+        <v>260</v>
       </c>
     </row>
     <row r="56" spans="1:7">
       <c r="A56" s="2" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
       <c r="B56" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
       <c r="C56" t="s">
-        <v>111</v>
+        <v>34</v>
       </c>
       <c r="D56" t="s">
-        <v>112</v>
+        <v>35</v>
       </c>
       <c r="E56" t="s">
-        <v>249</v>
+        <v>263</v>
       </c>
       <c r="F56" t="s">
-        <v>250</v>
+        <v>264</v>
       </c>
       <c r="G56" t="s">
-        <v>251</v>
+        <v>265</v>
       </c>
     </row>
     <row r="57" spans="1:7">
       <c r="A57" s="2" t="s">
-        <v>252</v>
+        <v>266</v>
       </c>
       <c r="B57" t="s">
-        <v>253</v>
+        <v>267</v>
       </c>
       <c r="C57" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="D57" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="E57" t="s">
-        <v>254</v>
+        <v>268</v>
       </c>
       <c r="F57" t="s">
-        <v>255</v>
+        <v>103</v>
       </c>
       <c r="G57" t="s">
-        <v>256</v>
+        <v>269</v>
       </c>
     </row>
     <row r="58" spans="1:7">
       <c r="A58" s="2" t="s">
-        <v>257</v>
+        <v>270</v>
       </c>
       <c r="B58" t="s">
-        <v>258</v>
+        <v>271</v>
       </c>
       <c r="C58" t="s">
-        <v>28</v>
+        <v>128</v>
       </c>
       <c r="D58" t="s">
-        <v>29</v>
+        <v>129</v>
       </c>
       <c r="E58" t="s">
-        <v>259</v>
+        <v>272</v>
       </c>
       <c r="F58" t="s">
-        <v>260</v>
+        <v>273</v>
       </c>
       <c r="G58" t="s">
-        <v>261</v>
+        <v>274</v>
       </c>
     </row>
     <row r="59" spans="1:7">
       <c r="A59" s="2" t="s">
-        <v>262</v>
+        <v>275</v>
       </c>
       <c r="B59" t="s">
-        <v>46</v>
+        <v>276</v>
       </c>
       <c r="C59" t="s">
-        <v>240</v>
+        <v>88</v>
       </c>
       <c r="D59" t="s">
-        <v>263</v>
+        <v>89</v>
       </c>
       <c r="E59" t="s">
-        <v>264</v>
+        <v>277</v>
       </c>
       <c r="F59" t="s">
-        <v>212</v>
+        <v>98</v>
       </c>
       <c r="G59" t="s">
-        <v>265</v>
+        <v>278</v>
       </c>
     </row>
     <row r="60" spans="1:7">
       <c r="A60" s="2" t="s">
-        <v>266</v>
+        <v>279</v>
       </c>
       <c r="B60" t="s">
-        <v>267</v>
+        <v>280</v>
       </c>
       <c r="C60" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="D60" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="E60" t="s">
-        <v>268</v>
+        <v>281</v>
       </c>
       <c r="F60" t="s">
-        <v>12</v>
+        <v>98</v>
       </c>
       <c r="G60" t="s">
-        <v>269</v>
+        <v>282</v>
       </c>
     </row>
     <row r="61" spans="1:7">
       <c r="A61" s="2" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="B61" t="s">
-        <v>271</v>
+        <v>284</v>
       </c>
       <c r="C61" t="s">
-        <v>28</v>
+        <v>128</v>
       </c>
       <c r="D61" t="s">
-        <v>29</v>
+        <v>129</v>
       </c>
       <c r="E61" t="s">
-        <v>272</v>
+        <v>285</v>
       </c>
       <c r="F61" t="s">
-        <v>31</v>
+        <v>112</v>
       </c>
       <c r="G61" t="s">
-        <v>31</v>
+        <v>286</v>
       </c>
     </row>
     <row r="62" spans="1:7">
       <c r="A62" s="2" t="s">
-        <v>273</v>
+        <v>287</v>
       </c>
       <c r="B62" t="s">
-        <v>274</v>
+        <v>288</v>
       </c>
       <c r="C62" t="s">
-        <v>68</v>
+        <v>34</v>
       </c>
       <c r="D62" t="s">
-        <v>69</v>
+        <v>35</v>
       </c>
       <c r="E62" t="s">
-        <v>275</v>
+        <v>289</v>
       </c>
       <c r="F62" t="s">
-        <v>212</v>
+        <v>98</v>
       </c>
       <c r="G62" t="s">
-        <v>276</v>
+        <v>290</v>
       </c>
     </row>
     <row r="63" spans="1:7">
       <c r="A63" s="2" t="s">
-        <v>277</v>
+        <v>291</v>
       </c>
       <c r="B63" t="s">
-        <v>278</v>
+        <v>292</v>
       </c>
       <c r="C63" t="s">
-        <v>9</v>
+        <v>51</v>
       </c>
       <c r="D63" t="s">
-        <v>10</v>
+        <v>52</v>
       </c>
       <c r="E63" t="s">
-        <v>279</v>
+        <v>293</v>
       </c>
       <c r="F63" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="G63" t="s">
-        <v>280</v>
+        <v>294</v>
       </c>
     </row>
     <row r="64" spans="1:7">
       <c r="A64" s="2" t="s">
-        <v>281</v>
+        <v>295</v>
       </c>
       <c r="B64" t="s">
-        <v>282</v>
+        <v>296</v>
       </c>
       <c r="C64" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D64" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="E64" t="s">
-        <v>283</v>
+        <v>297</v>
       </c>
       <c r="F64" t="s">
-        <v>12</v>
+        <v>54</v>
       </c>
       <c r="G64" t="s">
-        <v>284</v>
+        <v>298</v>
       </c>
     </row>
     <row r="65" spans="1:7">
       <c r="A65" s="2" t="s">
-        <v>285</v>
+        <v>299</v>
       </c>
       <c r="B65" t="s">
-        <v>286</v>
+        <v>300</v>
       </c>
       <c r="C65" t="s">
-        <v>68</v>
+        <v>204</v>
       </c>
       <c r="D65" t="s">
-        <v>69</v>
+        <v>205</v>
       </c>
       <c r="E65" t="s">
-        <v>287</v>
+        <v>301</v>
       </c>
       <c r="F65" t="s">
-        <v>212</v>
+        <v>12</v>
       </c>
       <c r="G65" t="s">
-        <v>288</v>
+        <v>12</v>
       </c>
     </row>
     <row r="66" spans="1:7">
       <c r="A66" s="2" t="s">
-        <v>289</v>
+        <v>302</v>
       </c>
       <c r="B66" t="s">
-        <v>290</v>
+        <v>303</v>
       </c>
       <c r="C66" t="s">
-        <v>105</v>
+        <v>164</v>
       </c>
       <c r="D66" t="s">
-        <v>106</v>
+        <v>165</v>
       </c>
       <c r="E66" t="s">
-        <v>291</v>
+        <v>304</v>
       </c>
       <c r="F66" t="s">
-        <v>39</v>
+        <v>98</v>
       </c>
       <c r="G66" t="s">
-        <v>292</v>
+        <v>305</v>
       </c>
     </row>
     <row r="67" spans="1:7">
       <c r="A67" s="2" t="s">
-        <v>293</v>
+        <v>306</v>
       </c>
       <c r="B67" t="s">
-        <v>294</v>
+        <v>307</v>
       </c>
       <c r="C67" t="s">
-        <v>91</v>
+        <v>128</v>
       </c>
       <c r="D67" t="s">
-        <v>92</v>
+        <v>129</v>
       </c>
       <c r="E67" t="s">
-        <v>295</v>
+        <v>308</v>
       </c>
       <c r="F67" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="G67" t="s">
-        <v>296</v>
+        <v>309</v>
       </c>
     </row>
     <row r="68" spans="1:7">
       <c r="A68" s="2" t="s">
-        <v>297</v>
+        <v>310</v>
       </c>
       <c r="B68" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="C68" t="s">
-        <v>79</v>
+        <v>34</v>
       </c>
       <c r="D68" t="s">
-        <v>80</v>
+        <v>35</v>
       </c>
       <c r="E68" t="s">
-        <v>299</v>
+        <v>312</v>
       </c>
       <c r="F68" t="s">
-        <v>119</v>
+        <v>12</v>
       </c>
       <c r="G68" t="s">
-        <v>300</v>
+        <v>12</v>
       </c>
     </row>
     <row r="69" spans="1:7">
       <c r="A69" s="2" t="s">
-        <v>301</v>
+        <v>313</v>
       </c>
       <c r="B69" t="s">
-        <v>302</v>
+        <v>314</v>
       </c>
       <c r="C69" t="s">
-        <v>105</v>
+        <v>9</v>
       </c>
       <c r="D69" t="s">
-        <v>106</v>
+        <v>10</v>
       </c>
       <c r="E69" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
       <c r="F69" t="s">
-        <v>31</v>
+        <v>273</v>
       </c>
       <c r="G69" t="s">
-        <v>31</v>
+        <v>316</v>
       </c>
     </row>
     <row r="70" spans="1:7">
       <c r="A70" s="2" t="s">
-        <v>304</v>
+        <v>317</v>
       </c>
       <c r="B70" t="s">
-        <v>305</v>
+        <v>318</v>
       </c>
       <c r="C70" t="s">
-        <v>91</v>
+        <v>9</v>
       </c>
       <c r="D70" t="s">
-        <v>92</v>
+        <v>10</v>
       </c>
       <c r="E70" t="s">
-        <v>306</v>
+        <v>319</v>
       </c>
       <c r="F70" t="s">
-        <v>307</v>
+        <v>103</v>
       </c>
       <c r="G70" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
     </row>
     <row r="71" spans="1:7">
       <c r="A71" s="2" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="B71" t="s">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="C71" t="s">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="D71" t="s">
-        <v>22</v>
+        <v>89</v>
       </c>
       <c r="E71" t="s">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="F71" t="s">
-        <v>312</v>
+        <v>324</v>
       </c>
       <c r="G71" t="s">
-        <v>313</v>
+        <v>325</v>
       </c>
     </row>
     <row r="72" spans="1:7">
       <c r="A72" s="2" t="s">
-        <v>314</v>
+        <v>326</v>
       </c>
       <c r="B72" t="s">
-        <v>315</v>
+        <v>327</v>
       </c>
       <c r="C72" t="s">
-        <v>240</v>
+        <v>51</v>
       </c>
       <c r="D72" t="s">
-        <v>316</v>
+        <v>52</v>
       </c>
       <c r="E72" t="s">
-        <v>317</v>
+        <v>328</v>
       </c>
       <c r="F72" t="s">
-        <v>31</v>
+        <v>327</v>
       </c>
       <c r="G72" t="s">
-        <v>31</v>
+        <v>329</v>
       </c>
     </row>
     <row r="73" spans="1:7">
       <c r="A73" s="2" t="s">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="B73" t="s">
-        <v>319</v>
+        <v>331</v>
       </c>
       <c r="C73" t="s">
-        <v>240</v>
+        <v>128</v>
       </c>
       <c r="D73" t="s">
-        <v>320</v>
+        <v>129</v>
       </c>
       <c r="E73" t="s">
-        <v>321</v>
+        <v>332</v>
       </c>
       <c r="F73" t="s">
-        <v>31</v>
+        <v>84</v>
       </c>
       <c r="G73" t="s">
-        <v>31</v>
+        <v>333</v>
       </c>
     </row>
     <row r="74" spans="1:7">
       <c r="A74" s="2" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="B74" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="C74" t="s">
-        <v>85</v>
+        <v>128</v>
       </c>
       <c r="D74" t="s">
-        <v>86</v>
+        <v>129</v>
       </c>
       <c r="E74" t="s">
-        <v>324</v>
+        <v>336</v>
       </c>
       <c r="F74" t="s">
-        <v>325</v>
+        <v>84</v>
       </c>
       <c r="G74" t="s">
-        <v>326</v>
+        <v>337</v>
       </c>
     </row>
     <row r="75" spans="1:7">
       <c r="A75" s="2" t="s">
-        <v>327</v>
+        <v>338</v>
       </c>
       <c r="B75" t="s">
-        <v>328</v>
+        <v>339</v>
       </c>
       <c r="C75" t="s">
-        <v>240</v>
+        <v>15</v>
       </c>
       <c r="D75" t="s">
-        <v>320</v>
+        <v>16</v>
       </c>
       <c r="E75" t="s">
-        <v>329</v>
+        <v>340</v>
       </c>
       <c r="F75" t="s">
-        <v>31</v>
+        <v>341</v>
       </c>
       <c r="G75" t="s">
-        <v>31</v>
+        <v>342</v>
       </c>
     </row>
     <row r="76" spans="1:7">
       <c r="A76" s="2" t="s">
-        <v>330</v>
+        <v>343</v>
       </c>
       <c r="B76" t="s">
-        <v>331</v>
+        <v>344</v>
       </c>
       <c r="C76" t="s">
-        <v>85</v>
+        <v>15</v>
       </c>
       <c r="D76" t="s">
-        <v>86</v>
+        <v>16</v>
       </c>
       <c r="E76" t="s">
-        <v>332</v>
+        <v>345</v>
       </c>
       <c r="F76" t="s">
-        <v>31</v>
+        <v>131</v>
       </c>
       <c r="G76" t="s">
-        <v>31</v>
+        <v>346</v>
       </c>
     </row>
     <row r="77" spans="1:7">
       <c r="A77" s="2" t="s">
-        <v>333</v>
+        <v>347</v>
       </c>
       <c r="B77" t="s">
-        <v>334</v>
+        <v>348</v>
       </c>
       <c r="C77" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="D77" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="E77" t="s">
-        <v>335</v>
+        <v>349</v>
       </c>
       <c r="F77" t="s">
-        <v>31</v>
+        <v>84</v>
       </c>
       <c r="G77" t="s">
-        <v>31</v>
+        <v>350</v>
       </c>
     </row>
     <row r="78" spans="1:7">
       <c r="A78" s="2" t="s">
-        <v>336</v>
+        <v>351</v>
       </c>
       <c r="B78" t="s">
-        <v>337</v>
+        <v>352</v>
       </c>
       <c r="C78" t="s">
-        <v>85</v>
+        <v>204</v>
       </c>
       <c r="D78" t="s">
-        <v>86</v>
+        <v>353</v>
       </c>
       <c r="E78" t="s">
-        <v>338</v>
+        <v>354</v>
       </c>
       <c r="F78" t="s">
-        <v>339</v>
+        <v>12</v>
       </c>
       <c r="G78" t="s">
-        <v>340</v>
+        <v>12</v>
       </c>
     </row>
     <row r="79" spans="1:7">
       <c r="A79" s="2" t="s">
-        <v>341</v>
+        <v>355</v>
       </c>
       <c r="B79" t="s">
-        <v>342</v>
+        <v>356</v>
       </c>
       <c r="C79" t="s">
-        <v>111</v>
+        <v>204</v>
       </c>
       <c r="D79" t="s">
-        <v>112</v>
+        <v>205</v>
       </c>
       <c r="E79" t="s">
-        <v>343</v>
+        <v>357</v>
       </c>
       <c r="F79" t="s">
-        <v>342</v>
+        <v>12</v>
       </c>
       <c r="G79" t="s">
-        <v>344</v>
+        <v>12</v>
       </c>
     </row>
     <row r="80" spans="1:7">
       <c r="A80" s="2" t="s">
-        <v>345</v>
+        <v>358</v>
       </c>
       <c r="B80" t="s">
-        <v>346</v>
+        <v>359</v>
       </c>
       <c r="C80" t="s">
-        <v>240</v>
+        <v>88</v>
       </c>
       <c r="D80" t="s">
-        <v>347</v>
+        <v>89</v>
       </c>
       <c r="E80" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="F80" t="s">
-        <v>17</v>
+        <v>103</v>
       </c>
       <c r="G80" t="s">
-        <v>349</v>
+        <v>361</v>
       </c>
     </row>
     <row r="81" spans="1:7">
       <c r="A81" s="2" t="s">
-        <v>350</v>
+        <v>362</v>
       </c>
       <c r="B81" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="C81" t="s">
-        <v>105</v>
+        <v>88</v>
       </c>
       <c r="D81" t="s">
-        <v>106</v>
+        <v>89</v>
       </c>
       <c r="E81" t="s">
-        <v>352</v>
+        <v>364</v>
       </c>
       <c r="F81" t="s">
-        <v>136</v>
+        <v>273</v>
       </c>
       <c r="G81" t="s">
-        <v>353</v>
+        <v>365</v>
       </c>
     </row>
     <row r="82" spans="1:7">
       <c r="A82" s="2" t="s">
-        <v>354</v>
+        <v>366</v>
       </c>
       <c r="B82" t="s">
-        <v>355</v>
+        <v>367</v>
       </c>
       <c r="C82" t="s">
-        <v>74</v>
+        <v>204</v>
       </c>
       <c r="D82" t="s">
-        <v>73</v>
+        <v>221</v>
       </c>
       <c r="E82" t="s">
-        <v>356</v>
+        <v>368</v>
       </c>
       <c r="F82" t="s">
-        <v>119</v>
+        <v>79</v>
       </c>
       <c r="G82" t="s">
-        <v>357</v>
+        <v>369</v>
       </c>
     </row>
     <row r="83" spans="1:7">
       <c r="A83" s="2" t="s">
-        <v>358</v>
+        <v>370</v>
       </c>
       <c r="B83" t="s">
-        <v>359</v>
+        <v>371</v>
       </c>
       <c r="C83" t="s">
-        <v>91</v>
+        <v>204</v>
       </c>
       <c r="D83" t="s">
-        <v>92</v>
+        <v>221</v>
       </c>
       <c r="E83" t="s">
-        <v>360</v>
+        <v>372</v>
       </c>
       <c r="F83" t="s">
-        <v>12</v>
+        <v>98</v>
       </c>
       <c r="G83" t="s">
-        <v>361</v>
+        <v>373</v>
       </c>
     </row>
     <row r="84" spans="1:7">
       <c r="A84" s="2" t="s">
-        <v>362</v>
+        <v>374</v>
       </c>
       <c r="B84" t="s">
-        <v>363</v>
+        <v>375</v>
       </c>
       <c r="C84" t="s">
-        <v>9</v>
+        <v>44</v>
       </c>
       <c r="D84" t="s">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="E84" t="s">
-        <v>364</v>
+        <v>376</v>
       </c>
       <c r="F84" t="s">
-        <v>365</v>
+        <v>273</v>
       </c>
       <c r="G84" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
     </row>
     <row r="85" spans="1:7">
       <c r="A85" s="2" t="s">
-        <v>367</v>
+        <v>378</v>
       </c>
       <c r="B85" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="C85" t="s">
-        <v>91</v>
+        <v>22</v>
       </c>
       <c r="D85" t="s">
-        <v>92</v>
+        <v>23</v>
       </c>
       <c r="E85" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="F85" t="s">
-        <v>365</v>
+        <v>98</v>
       </c>
       <c r="G85" t="s">
-        <v>370</v>
+        <v>381</v>
       </c>
     </row>
     <row r="86" spans="1:7">
       <c r="A86" s="2" t="s">
-        <v>371</v>
+        <v>382</v>
       </c>
       <c r="B86" t="s">
-        <v>372</v>
+        <v>383</v>
       </c>
       <c r="C86" t="s">
-        <v>68</v>
+        <v>22</v>
       </c>
       <c r="D86" t="s">
-        <v>69</v>
+        <v>23</v>
       </c>
       <c r="E86" t="s">
-        <v>373</v>
+        <v>384</v>
       </c>
       <c r="F86" t="s">
-        <v>12</v>
+        <v>79</v>
       </c>
       <c r="G86" t="s">
-        <v>374</v>
+        <v>385</v>
       </c>
     </row>
     <row r="87" spans="1:7">
       <c r="A87" s="2" t="s">
-        <v>375</v>
+        <v>386</v>
       </c>
       <c r="B87" t="s">
-        <v>376</v>
+        <v>387</v>
       </c>
       <c r="C87" t="s">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="D87" t="s">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="E87" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="F87" t="s">
-        <v>12</v>
+        <v>70</v>
       </c>
       <c r="G87" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
     </row>
     <row r="88" spans="1:7">
       <c r="A88" s="2" t="s">
-        <v>379</v>
+        <v>390</v>
       </c>
       <c r="B88" t="s">
-        <v>380</v>
+        <v>391</v>
       </c>
       <c r="C88" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D88" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E88" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="F88" t="s">
-        <v>31</v>
+        <v>393</v>
       </c>
       <c r="G88" t="s">
-        <v>31</v>
+        <v>394</v>
       </c>
     </row>
     <row r="89" spans="1:7">
       <c r="A89" s="2" t="s">
-        <v>382</v>
+        <v>395</v>
       </c>
       <c r="B89" t="s">
-        <v>383</v>
+        <v>396</v>
       </c>
       <c r="C89" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D89" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E89" t="s">
-        <v>384</v>
+        <v>397</v>
       </c>
       <c r="F89" t="s">
-        <v>31</v>
+        <v>398</v>
       </c>
       <c r="G89" t="s">
-        <v>31</v>
+        <v>399</v>
       </c>
     </row>
     <row r="90" spans="1:7">
       <c r="A90" s="2" t="s">
-        <v>385</v>
+        <v>400</v>
       </c>
       <c r="B90" t="s">
-        <v>386</v>
+        <v>401</v>
       </c>
       <c r="C90" t="s">
-        <v>240</v>
+        <v>15</v>
       </c>
       <c r="D90" t="s">
-        <v>347</v>
+        <v>16</v>
       </c>
       <c r="E90" t="s">
-        <v>387</v>
+        <v>402</v>
       </c>
       <c r="F90" t="s">
-        <v>12</v>
+        <v>79</v>
       </c>
       <c r="G90" t="s">
-        <v>388</v>
+        <v>403</v>
       </c>
     </row>
     <row r="91" spans="1:7">
       <c r="A91" s="2" t="s">
-        <v>389</v>
+        <v>404</v>
       </c>
       <c r="B91" t="s">
-        <v>390</v>
+        <v>405</v>
       </c>
       <c r="C91" t="s">
-        <v>9</v>
+        <v>128</v>
       </c>
       <c r="D91" t="s">
-        <v>10</v>
+        <v>129</v>
       </c>
       <c r="E91" t="s">
-        <v>391</v>
+        <v>406</v>
       </c>
       <c r="F91" t="s">
-        <v>212</v>
+        <v>54</v>
       </c>
       <c r="G91" t="s">
-        <v>392</v>
+        <v>407</v>
       </c>
     </row>
     <row r="92" spans="1:7">
       <c r="A92" s="2" t="s">
-        <v>393</v>
+        <v>408</v>
       </c>
       <c r="B92" t="s">
-        <v>394</v>
+        <v>409</v>
       </c>
       <c r="C92" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="D92" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="E92" t="s">
-        <v>395</v>
+        <v>410</v>
       </c>
       <c r="F92" t="s">
-        <v>396</v>
+        <v>91</v>
       </c>
       <c r="G92" t="s">
-        <v>397</v>
+        <v>411</v>
       </c>
     </row>
     <row r="93" spans="1:7">
       <c r="A93" s="2" t="s">
-        <v>398</v>
+        <v>412</v>
       </c>
       <c r="B93" t="s">
-        <v>399</v>
+        <v>413</v>
       </c>
       <c r="C93" t="s">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="D93" t="s">
-        <v>106</v>
+        <v>129</v>
       </c>
       <c r="E93" t="s">
-        <v>400</v>
+        <v>414</v>
       </c>
       <c r="F93" t="s">
-        <v>119</v>
+        <v>98</v>
       </c>
       <c r="G93" t="s">
-        <v>401</v>
+        <v>415</v>
       </c>
     </row>
     <row r="94" spans="1:7">
       <c r="A94" s="2" t="s">
-        <v>402</v>
+        <v>416</v>
       </c>
       <c r="B94" t="s">
-        <v>403</v>
+        <v>417</v>
       </c>
       <c r="C94" t="s">
+        <v>128</v>
+      </c>
+      <c r="D94" t="s">
+        <v>129</v>
+      </c>
+      <c r="E94" t="s">
+        <v>418</v>
+      </c>
+      <c r="F94" t="s">
         <v>79</v>
       </c>
-      <c r="D94" t="s">
-        <v>80</v>
-      </c>
-      <c r="E94" t="s">
-        <v>404</v>
-      </c>
-      <c r="F94" t="s">
-        <v>405</v>
-      </c>
       <c r="G94" t="s">
-        <v>406</v>
+        <v>419</v>
       </c>
     </row>
     <row r="95" spans="1:7">
       <c r="A95" s="2" t="s">
-        <v>407</v>
+        <v>420</v>
       </c>
       <c r="B95" t="s">
-        <v>408</v>
+        <v>421</v>
       </c>
       <c r="C95" t="s">
-        <v>91</v>
+        <v>164</v>
       </c>
       <c r="D95" t="s">
-        <v>92</v>
+        <v>165</v>
       </c>
       <c r="E95" t="s">
-        <v>409</v>
+        <v>422</v>
       </c>
       <c r="F95" t="s">
-        <v>39</v>
+        <v>423</v>
       </c>
       <c r="G95" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
     </row>
     <row r="96" spans="1:7">
       <c r="A96" s="2" t="s">
-        <v>411</v>
+        <v>425</v>
       </c>
       <c r="B96" t="s">
-        <v>412</v>
+        <v>426</v>
       </c>
       <c r="C96" t="s">
-        <v>85</v>
+        <v>34</v>
       </c>
       <c r="D96" t="s">
-        <v>86</v>
+        <v>35</v>
       </c>
       <c r="E96" t="s">
-        <v>413</v>
+        <v>427</v>
       </c>
       <c r="F96" t="s">
-        <v>413</v>
+        <v>98</v>
       </c>
       <c r="G96" t="s">
-        <v>414</v>
+        <v>12</v>
       </c>
     </row>
     <row r="97" spans="1:7">
       <c r="A97" s="2" t="s">
-        <v>415</v>
+        <v>428</v>
       </c>
       <c r="B97" t="s">
-        <v>416</v>
+        <v>429</v>
       </c>
       <c r="C97" t="s">
-        <v>111</v>
+        <v>128</v>
       </c>
       <c r="D97" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="E97" t="s">
-        <v>417</v>
+        <v>430</v>
       </c>
       <c r="F97" t="s">
-        <v>365</v>
+        <v>98</v>
       </c>
       <c r="G97" t="s">
-        <v>418</v>
+        <v>431</v>
       </c>
     </row>
     <row r="98" spans="1:7">
       <c r="A98" s="2" t="s">
-        <v>419</v>
+        <v>432</v>
       </c>
       <c r="B98" t="s">
-        <v>420</v>
+        <v>433</v>
       </c>
       <c r="C98" t="s">
-        <v>91</v>
+        <v>15</v>
       </c>
       <c r="D98" t="s">
-        <v>92</v>
+        <v>16</v>
       </c>
       <c r="E98" t="s">
-        <v>421</v>
+        <v>434</v>
       </c>
       <c r="F98" t="s">
-        <v>365</v>
+        <v>98</v>
       </c>
       <c r="G98" t="s">
-        <v>422</v>
+        <v>435</v>
       </c>
     </row>
     <row r="99" spans="1:7">
       <c r="A99" s="2" t="s">
-        <v>423</v>
+        <v>436</v>
       </c>
       <c r="B99" t="s">
-        <v>424</v>
+        <v>437</v>
       </c>
       <c r="C99" t="s">
-        <v>111</v>
+        <v>128</v>
       </c>
       <c r="D99" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="E99" t="s">
-        <v>425</v>
+        <v>438</v>
       </c>
       <c r="F99" t="s">
-        <v>426</v>
+        <v>70</v>
       </c>
       <c r="G99" t="s">
-        <v>427</v>
+        <v>439</v>
       </c>
     </row>
     <row r="100" spans="1:7">
       <c r="A100" s="2" t="s">
-        <v>428</v>
+        <v>440</v>
       </c>
       <c r="B100" t="s">
-        <v>429</v>
+        <v>441</v>
       </c>
       <c r="C100" t="s">
-        <v>79</v>
+        <v>44</v>
       </c>
       <c r="D100" t="s">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="E100" t="s">
-        <v>430</v>
+        <v>442</v>
       </c>
       <c r="F100" t="s">
-        <v>365</v>
+        <v>98</v>
       </c>
       <c r="G100" t="s">
-        <v>431</v>
+        <v>443</v>
       </c>
     </row>
     <row r="101" spans="1:7">
       <c r="A101" s="2" t="s">
-        <v>432</v>
+        <v>444</v>
       </c>
       <c r="B101" t="s">
-        <v>433</v>
+        <v>445</v>
       </c>
       <c r="C101" t="s">
-        <v>240</v>
+        <v>9</v>
       </c>
       <c r="D101" t="s">
-        <v>316</v>
+        <v>10</v>
       </c>
       <c r="E101" t="s">
-        <v>434</v>
+        <v>446</v>
       </c>
       <c r="F101" t="s">
-        <v>31</v>
+        <v>84</v>
       </c>
       <c r="G101" t="s">
-        <v>31</v>
+        <v>447</v>
       </c>
     </row>
     <row r="102" spans="1:7">
       <c r="A102" s="2" t="s">
-        <v>435</v>
+        <v>448</v>
       </c>
       <c r="B102" t="s">
-        <v>436</v>
+        <v>449</v>
       </c>
       <c r="C102" t="s">
-        <v>105</v>
+        <v>15</v>
       </c>
       <c r="D102" t="s">
-        <v>106</v>
+        <v>16</v>
       </c>
       <c r="E102" t="s">
-        <v>437</v>
+        <v>450</v>
       </c>
       <c r="F102" t="s">
-        <v>396</v>
+        <v>273</v>
       </c>
       <c r="G102" t="s">
-        <v>438</v>
+        <v>451</v>
       </c>
     </row>
     <row r="103" spans="1:7">
       <c r="A103" s="2" t="s">
-        <v>439</v>
+        <v>452</v>
       </c>
       <c r="B103" t="s">
-        <v>440</v>
+        <v>453</v>
       </c>
       <c r="C103" t="s">
-        <v>105</v>
+        <v>22</v>
       </c>
       <c r="D103" t="s">
-        <v>106</v>
+        <v>23</v>
       </c>
       <c r="E103" t="s">
-        <v>441</v>
+        <v>454</v>
       </c>
       <c r="F103" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="G103" t="s">
-        <v>31</v>
+        <v>455</v>
       </c>
     </row>
     <row r="104" spans="1:7">
       <c r="A104" s="2" t="s">
-        <v>442</v>
+        <v>456</v>
       </c>
       <c r="B104" t="s">
-        <v>443</v>
+        <v>457</v>
       </c>
       <c r="C104" t="s">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="D104" t="s">
-        <v>69</v>
+        <v>96</v>
       </c>
       <c r="E104" t="s">
-        <v>444</v>
+        <v>458</v>
       </c>
       <c r="F104" t="s">
-        <v>39</v>
+        <v>459</v>
       </c>
       <c r="G104" t="s">
-        <v>445</v>
+        <v>460</v>
       </c>
     </row>
     <row r="105" spans="1:7">
       <c r="A105" s="2" t="s">
-        <v>446</v>
+        <v>461</v>
       </c>
       <c r="B105" t="s">
-        <v>447</v>
+        <v>462</v>
       </c>
       <c r="C105" t="s">
-        <v>91</v>
+        <v>22</v>
       </c>
       <c r="D105" t="s">
-        <v>92</v>
+        <v>23</v>
       </c>
       <c r="E105" t="s">
-        <v>448</v>
+        <v>463</v>
       </c>
       <c r="F105" t="s">
-        <v>449</v>
+        <v>463</v>
       </c>
       <c r="G105" t="s">
-        <v>450</v>
+        <v>464</v>
       </c>
     </row>
     <row r="106" spans="1:7">
       <c r="A106" s="2" t="s">
-        <v>451</v>
+        <v>465</v>
       </c>
       <c r="B106" t="s">
-        <v>452</v>
+        <v>466</v>
       </c>
       <c r="C106" t="s">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="D106" t="s">
-        <v>106</v>
+        <v>129</v>
       </c>
       <c r="E106" t="s">
-        <v>453</v>
+        <v>467</v>
       </c>
       <c r="F106" t="s">
-        <v>454</v>
+        <v>131</v>
       </c>
       <c r="G106" t="s">
-        <v>455</v>
+        <v>468</v>
       </c>
     </row>
     <row r="107" spans="1:7">
       <c r="A107" s="2" t="s">
-        <v>456</v>
+        <v>469</v>
       </c>
       <c r="B107" t="s">
-        <v>457</v>
+        <v>470</v>
       </c>
       <c r="C107" t="s">
-        <v>91</v>
+        <v>128</v>
       </c>
       <c r="D107" t="s">
-        <v>92</v>
+        <v>129</v>
       </c>
       <c r="E107" t="s">
-        <v>458</v>
+        <v>471</v>
       </c>
       <c r="F107" t="s">
-        <v>459</v>
+        <v>131</v>
       </c>
       <c r="G107" t="s">
-        <v>460</v>
+        <v>472</v>
       </c>
     </row>
     <row r="108" spans="1:7">
       <c r="A108" s="2" t="s">
-        <v>461</v>
+        <v>473</v>
       </c>
       <c r="B108" t="s">
-        <v>462</v>
+        <v>474</v>
       </c>
       <c r="C108" t="s">
-        <v>105</v>
+        <v>164</v>
       </c>
       <c r="D108" t="s">
-        <v>106</v>
+        <v>165</v>
       </c>
       <c r="E108" t="s">
-        <v>463</v>
+        <v>475</v>
       </c>
       <c r="F108" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="G108" t="s">
-        <v>31</v>
+        <v>476</v>
       </c>
     </row>
     <row r="109" spans="1:7">
       <c r="A109" s="2" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="B109" t="s">
-        <v>465</v>
+        <v>478</v>
       </c>
       <c r="C109" t="s">
+        <v>95</v>
+      </c>
+      <c r="D109" t="s">
+        <v>96</v>
+      </c>
+      <c r="E109" t="s">
+        <v>479</v>
+      </c>
+      <c r="F109" t="s">
         <v>91</v>
       </c>
-      <c r="D109" t="s">
-        <v>92</v>
-      </c>
-      <c r="E109" t="s">
-        <v>466</v>
-      </c>
-      <c r="F109" t="s">
-        <v>212</v>
-      </c>
       <c r="G109" t="s">
-        <v>467</v>
+        <v>480</v>
       </c>
     </row>
     <row r="110" spans="1:7">
       <c r="A110" s="2" t="s">
-        <v>468</v>
+        <v>481</v>
       </c>
       <c r="B110" t="s">
-        <v>469</v>
+        <v>482</v>
       </c>
       <c r="C110" t="s">
-        <v>74</v>
+        <v>34</v>
       </c>
       <c r="D110" t="s">
-        <v>73</v>
+        <v>35</v>
       </c>
       <c r="E110" t="s">
-        <v>470</v>
+        <v>483</v>
       </c>
       <c r="F110" t="s">
-        <v>471</v>
+        <v>84</v>
       </c>
       <c r="G110" t="s">
-        <v>472</v>
+        <v>484</v>
       </c>
     </row>
     <row r="111" spans="1:7">
       <c r="A111" s="2" t="s">
-        <v>473</v>
+        <v>485</v>
       </c>
       <c r="B111" t="s">
-        <v>474</v>
+        <v>486</v>
       </c>
       <c r="C111" t="s">
-        <v>91</v>
+        <v>34</v>
       </c>
       <c r="D111" t="s">
-        <v>92</v>
+        <v>35</v>
       </c>
       <c r="E111" t="s">
-        <v>475</v>
+        <v>487</v>
       </c>
       <c r="F111" t="s">
-        <v>12</v>
+        <v>488</v>
       </c>
       <c r="G111" t="s">
-        <v>476</v>
+        <v>489</v>
       </c>
     </row>
     <row r="112" spans="1:7">
       <c r="A112" s="2" t="s">
-        <v>477</v>
+        <v>490</v>
       </c>
       <c r="B112" t="s">
-        <v>478</v>
+        <v>491</v>
       </c>
       <c r="C112" t="s">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="D112" t="s">
-        <v>69</v>
+        <v>45</v>
       </c>
       <c r="E112" t="s">
-        <v>479</v>
+        <v>492</v>
       </c>
       <c r="F112" t="s">
-        <v>119</v>
+        <v>79</v>
       </c>
       <c r="G112" t="s">
-        <v>480</v>
+        <v>493</v>
       </c>
     </row>
     <row r="113" spans="1:7">
       <c r="A113" s="2" t="s">
-        <v>481</v>
+        <v>494</v>
       </c>
       <c r="B113" t="s">
-        <v>482</v>
+        <v>495</v>
       </c>
       <c r="C113" t="s">
-        <v>91</v>
+        <v>34</v>
       </c>
       <c r="D113" t="s">
-        <v>92</v>
+        <v>35</v>
       </c>
       <c r="E113" t="s">
-        <v>483</v>
+        <v>496</v>
       </c>
       <c r="F113" t="s">
-        <v>119</v>
+        <v>12</v>
       </c>
       <c r="G113" t="s">
-        <v>484</v>
+        <v>12</v>
       </c>
     </row>
     <row r="114" spans="1:7">
       <c r="A114" s="2" t="s">
-        <v>485</v>
+        <v>497</v>
       </c>
       <c r="B114" t="s">
-        <v>486</v>
+        <v>498</v>
       </c>
       <c r="C114" t="s">
+        <v>15</v>
+      </c>
+      <c r="D114" t="s">
+        <v>16</v>
+      </c>
+      <c r="E114" t="s">
+        <v>499</v>
+      </c>
+      <c r="F114" t="s">
         <v>79</v>
       </c>
-      <c r="D114" t="s">
-        <v>80</v>
-      </c>
-      <c r="E114" t="s">
-        <v>487</v>
-      </c>
-      <c r="F114" t="s">
-        <v>488</v>
-      </c>
       <c r="G114" t="s">
-        <v>489</v>
+        <v>500</v>
       </c>
     </row>
     <row r="115" spans="1:7">
       <c r="A115" s="2" t="s">
-        <v>490</v>
+        <v>501</v>
       </c>
       <c r="B115" t="s">
-        <v>491</v>
+        <v>502</v>
       </c>
       <c r="C115" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="D115" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="E115" t="s">
-        <v>492</v>
+        <v>503</v>
       </c>
       <c r="F115" t="s">
-        <v>493</v>
+        <v>504</v>
       </c>
       <c r="G115" t="s">
-        <v>494</v>
+        <v>505</v>
       </c>
     </row>
     <row r="116" spans="1:7">
       <c r="A116" s="2" t="s">
-        <v>495</v>
+        <v>506</v>
       </c>
       <c r="B116" t="s">
-        <v>496</v>
+        <v>507</v>
       </c>
       <c r="C116" t="s">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="D116" t="s">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="E116" t="s">
-        <v>497</v>
+        <v>508</v>
       </c>
       <c r="F116" t="s">
-        <v>365</v>
+        <v>273</v>
       </c>
       <c r="G116" t="s">
-        <v>498</v>
+        <v>509</v>
       </c>
     </row>
     <row r="117" spans="1:7">
       <c r="A117" s="2" t="s">
-        <v>499</v>
+        <v>510</v>
       </c>
       <c r="B117" t="s">
-        <v>500</v>
+        <v>511</v>
       </c>
       <c r="C117" t="s">
-        <v>85</v>
+        <v>9</v>
       </c>
       <c r="D117" t="s">
-        <v>86</v>
+        <v>10</v>
       </c>
       <c r="E117" t="s">
-        <v>501</v>
+        <v>512</v>
       </c>
       <c r="F117" t="s">
-        <v>365</v>
+        <v>91</v>
       </c>
       <c r="G117" t="s">
-        <v>502</v>
+        <v>513</v>
       </c>
     </row>
     <row r="118" spans="1:7">
       <c r="A118" s="2" t="s">
-        <v>503</v>
+        <v>514</v>
       </c>
       <c r="B118" t="s">
-        <v>504</v>
+        <v>515</v>
       </c>
       <c r="C118" t="s">
-        <v>111</v>
+        <v>204</v>
       </c>
       <c r="D118" t="s">
-        <v>112</v>
+        <v>516</v>
       </c>
       <c r="E118" t="s">
-        <v>505</v>
+        <v>517</v>
       </c>
       <c r="F118" t="s">
-        <v>396</v>
+        <v>79</v>
       </c>
       <c r="G118" t="s">
-        <v>506</v>
+        <v>518</v>
       </c>
     </row>
     <row r="119" spans="1:7">
       <c r="A119" s="2" t="s">
-        <v>507</v>
+        <v>519</v>
       </c>
       <c r="B119" t="s">
-        <v>508</v>
+        <v>96</v>
       </c>
       <c r="C119" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="D119" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="E119" t="s">
-        <v>509</v>
+        <v>520</v>
       </c>
       <c r="F119" t="s">
-        <v>396</v>
+        <v>98</v>
       </c>
       <c r="G119" t="s">
-        <v>510</v>
+        <v>521</v>
       </c>
     </row>
     <row r="120" spans="1:7">
       <c r="A120" s="2" t="s">
-        <v>511</v>
+        <v>522</v>
       </c>
       <c r="B120" t="s">
-        <v>512</v>
+        <v>523</v>
       </c>
       <c r="C120" t="s">
-        <v>105</v>
+        <v>34</v>
       </c>
       <c r="D120" t="s">
-        <v>106</v>
+        <v>35</v>
       </c>
       <c r="E120" t="s">
-        <v>513</v>
+        <v>524</v>
       </c>
       <c r="F120" t="s">
-        <v>396</v>
+        <v>12</v>
       </c>
       <c r="G120" t="s">
-        <v>514</v>
+        <v>12</v>
       </c>
     </row>
     <row r="121" spans="1:7">
       <c r="A121" s="2" t="s">
-        <v>515</v>
+        <v>525</v>
       </c>
       <c r="B121" t="s">
-        <v>516</v>
+        <v>526</v>
       </c>
       <c r="C121" t="s">
-        <v>91</v>
+        <v>15</v>
       </c>
       <c r="D121" t="s">
-        <v>92</v>
+        <v>16</v>
       </c>
       <c r="E121" t="s">
-        <v>517</v>
+        <v>527</v>
       </c>
       <c r="F121" t="s">
-        <v>136</v>
+        <v>18</v>
       </c>
       <c r="G121" t="s">
-        <v>518</v>
+        <v>528</v>
       </c>
     </row>
     <row r="122" spans="1:7">
       <c r="A122" s="2" t="s">
-        <v>519</v>
+        <v>529</v>
       </c>
       <c r="B122" t="s">
-        <v>520</v>
+        <v>530</v>
       </c>
       <c r="C122" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="D122" t="s">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="E122" t="s">
-        <v>521</v>
+        <v>531</v>
       </c>
       <c r="F122" t="s">
-        <v>449</v>
+        <v>532</v>
       </c>
       <c r="G122" t="s">
-        <v>522</v>
+        <v>533</v>
       </c>
     </row>
     <row r="123" spans="1:7">
       <c r="A123" s="2" t="s">
-        <v>523</v>
+        <v>534</v>
       </c>
       <c r="B123" t="s">
-        <v>524</v>
+        <v>535</v>
       </c>
       <c r="C123" t="s">
-        <v>91</v>
+        <v>34</v>
       </c>
       <c r="D123" t="s">
-        <v>92</v>
+        <v>35</v>
       </c>
       <c r="E123" t="s">
-        <v>525</v>
+        <v>536</v>
       </c>
       <c r="F123" t="s">
-        <v>255</v>
+        <v>537</v>
       </c>
       <c r="G123" t="s">
-        <v>526</v>
+        <v>538</v>
       </c>
     </row>
     <row r="124" spans="1:7">
       <c r="A124" s="2" t="s">
-        <v>527</v>
+        <v>539</v>
       </c>
       <c r="B124" t="s">
-        <v>528</v>
+        <v>540</v>
       </c>
       <c r="C124" t="s">
-        <v>9</v>
+        <v>128</v>
       </c>
       <c r="D124" t="s">
-        <v>10</v>
+        <v>129</v>
       </c>
       <c r="E124" t="s">
-        <v>529</v>
+        <v>541</v>
       </c>
       <c r="F124" t="s">
-        <v>449</v>
+        <v>152</v>
       </c>
       <c r="G124" t="s">
-        <v>530</v>
+        <v>542</v>
       </c>
     </row>
     <row r="125" spans="1:7">
       <c r="A125" s="2" t="s">
-        <v>531</v>
+        <v>543</v>
       </c>
       <c r="B125" t="s">
-        <v>532</v>
+        <v>544</v>
       </c>
       <c r="C125" t="s">
-        <v>105</v>
+        <v>34</v>
       </c>
       <c r="D125" t="s">
-        <v>106</v>
+        <v>35</v>
       </c>
       <c r="E125" t="s">
-        <v>533</v>
+        <v>545</v>
       </c>
       <c r="F125" t="s">
-        <v>114</v>
+        <v>537</v>
       </c>
       <c r="G125" t="s">
-        <v>534</v>
+        <v>546</v>
       </c>
     </row>
     <row r="126" spans="1:7">
       <c r="A126" s="2" t="s">
-        <v>535</v>
+        <v>547</v>
       </c>
       <c r="B126" t="s">
-        <v>536</v>
+        <v>548</v>
       </c>
       <c r="C126" t="s">
-        <v>105</v>
+        <v>44</v>
       </c>
       <c r="D126" t="s">
-        <v>106</v>
+        <v>45</v>
       </c>
       <c r="E126" t="s">
-        <v>537</v>
+        <v>549</v>
       </c>
       <c r="F126" t="s">
-        <v>17</v>
+        <v>70</v>
       </c>
       <c r="G126" t="s">
-        <v>538</v>
+        <v>550</v>
       </c>
     </row>
     <row r="127" spans="1:7">
       <c r="A127" s="2" t="s">
-        <v>539</v>
+        <v>551</v>
       </c>
       <c r="B127" t="s">
-        <v>540</v>
+        <v>552</v>
       </c>
       <c r="C127" t="s">
-        <v>9</v>
+        <v>44</v>
       </c>
       <c r="D127" t="s">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="E127" t="s">
-        <v>541</v>
+        <v>553</v>
       </c>
       <c r="F127" t="s">
-        <v>365</v>
+        <v>70</v>
       </c>
       <c r="G127" t="s">
-        <v>542</v>
+        <v>554</v>
       </c>
     </row>
     <row r="128" spans="1:7">
       <c r="A128" s="2" t="s">
-        <v>543</v>
+        <v>555</v>
       </c>
       <c r="B128" t="s">
-        <v>544</v>
+        <v>556</v>
       </c>
       <c r="C128" t="s">
-        <v>105</v>
+        <v>44</v>
       </c>
       <c r="D128" t="s">
-        <v>106</v>
+        <v>45</v>
       </c>
       <c r="E128" t="s">
-        <v>545</v>
+        <v>557</v>
       </c>
       <c r="F128" t="s">
-        <v>545</v>
+        <v>79</v>
       </c>
       <c r="G128" t="s">
-        <v>546</v>
+        <v>558</v>
       </c>
     </row>
     <row r="129" spans="1:7">
       <c r="A129" s="2" t="s">
-        <v>547</v>
+        <v>559</v>
       </c>
       <c r="B129" t="s">
-        <v>548</v>
+        <v>560</v>
       </c>
       <c r="C129" t="s">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="D129" t="s">
-        <v>73</v>
+        <v>45</v>
       </c>
       <c r="E129" t="s">
-        <v>549</v>
+        <v>561</v>
       </c>
       <c r="F129" t="s">
-        <v>212</v>
+        <v>84</v>
       </c>
       <c r="G129" t="s">
-        <v>550</v>
+        <v>562</v>
       </c>
     </row>
     <row r="130" spans="1:7">
       <c r="A130" s="2" t="s">
-        <v>551</v>
+        <v>563</v>
       </c>
       <c r="B130" t="s">
-        <v>552</v>
+        <v>564</v>
       </c>
       <c r="C130" t="s">
-        <v>111</v>
+        <v>204</v>
       </c>
       <c r="D130" t="s">
-        <v>112</v>
+        <v>353</v>
       </c>
       <c r="E130" t="s">
-        <v>553</v>
+        <v>565</v>
       </c>
       <c r="F130" t="s">
-        <v>365</v>
+        <v>12</v>
       </c>
       <c r="G130" t="s">
-        <v>554</v>
+        <v>12</v>
       </c>
     </row>
     <row r="131" spans="1:7">
       <c r="A131" s="2" t="s">
-        <v>555</v>
+        <v>566</v>
       </c>
       <c r="B131" t="s">
-        <v>556</v>
+        <v>567</v>
       </c>
       <c r="C131" t="s">
-        <v>74</v>
+        <v>34</v>
       </c>
       <c r="D131" t="s">
-        <v>73</v>
+        <v>35</v>
       </c>
       <c r="E131" t="s">
-        <v>557</v>
+        <v>568</v>
       </c>
       <c r="F131" t="s">
-        <v>136</v>
+        <v>12</v>
       </c>
       <c r="G131" t="s">
-        <v>558</v>
+        <v>12</v>
       </c>
     </row>
     <row r="132" spans="1:7">
       <c r="A132" s="2" t="s">
-        <v>559</v>
+        <v>569</v>
       </c>
       <c r="B132" t="s">
-        <v>560</v>
+        <v>570</v>
       </c>
       <c r="C132" t="s">
-        <v>9</v>
+        <v>95</v>
       </c>
       <c r="D132" t="s">
-        <v>10</v>
+        <v>96</v>
       </c>
       <c r="E132" t="s">
-        <v>561</v>
+        <v>571</v>
       </c>
       <c r="F132" t="s">
-        <v>312</v>
+        <v>91</v>
       </c>
       <c r="G132" t="s">
-        <v>562</v>
+        <v>572</v>
       </c>
     </row>
     <row r="133" spans="1:7">
       <c r="A133" s="2" t="s">
-        <v>563</v>
+        <v>573</v>
       </c>
       <c r="B133" t="s">
-        <v>564</v>
+        <v>574</v>
       </c>
       <c r="C133" t="s">
-        <v>111</v>
+        <v>15</v>
       </c>
       <c r="D133" t="s">
-        <v>112</v>
+        <v>16</v>
       </c>
       <c r="E133" t="s">
-        <v>565</v>
+        <v>575</v>
       </c>
       <c r="F133" t="s">
-        <v>566</v>
+        <v>79</v>
       </c>
       <c r="G133" t="s">
-        <v>567</v>
+        <v>576</v>
       </c>
     </row>
     <row r="134" spans="1:7">
       <c r="A134" s="2" t="s">
-        <v>568</v>
+        <v>577</v>
       </c>
       <c r="B134" t="s">
-        <v>569</v>
+        <v>578</v>
       </c>
       <c r="C134" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D134" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E134" t="s">
-        <v>570</v>
+        <v>579</v>
       </c>
       <c r="F134" t="s">
-        <v>114</v>
+        <v>70</v>
       </c>
       <c r="G134" t="s">
-        <v>571</v>
+        <v>580</v>
       </c>
     </row>
     <row r="135" spans="1:7">
       <c r="A135" s="2" t="s">
-        <v>572</v>
+        <v>581</v>
       </c>
       <c r="B135" t="s">
-        <v>573</v>
+        <v>582</v>
       </c>
       <c r="C135" t="s">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="D135" t="s">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="E135" t="s">
-        <v>574</v>
+        <v>583</v>
       </c>
       <c r="F135" t="s">
-        <v>12</v>
+        <v>54</v>
       </c>
       <c r="G135" t="s">
-        <v>575</v>
+        <v>584</v>
       </c>
     </row>
     <row r="136" spans="1:7">
       <c r="A136" s="2" t="s">
-        <v>576</v>
+        <v>585</v>
       </c>
       <c r="B136" t="s">
-        <v>577</v>
+        <v>586</v>
       </c>
       <c r="C136" t="s">
-        <v>240</v>
+        <v>15</v>
       </c>
       <c r="D136" t="s">
-        <v>347</v>
+        <v>16</v>
       </c>
       <c r="E136" t="s">
-        <v>578</v>
+        <v>587</v>
       </c>
       <c r="F136" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="G136" t="s">
-        <v>579</v>
+        <v>588</v>
       </c>
     </row>
     <row r="137" spans="1:7">
       <c r="A137" s="2" t="s">
-        <v>580</v>
+        <v>589</v>
       </c>
       <c r="B137" t="s">
-        <v>581</v>
+        <v>590</v>
       </c>
       <c r="C137" t="s">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="D137" t="s">
-        <v>73</v>
+        <v>45</v>
       </c>
       <c r="E137" t="s">
-        <v>582</v>
+        <v>591</v>
       </c>
       <c r="F137" t="s">
-        <v>39</v>
+        <v>273</v>
       </c>
       <c r="G137" t="s">
-        <v>583</v>
+        <v>592</v>
       </c>
     </row>
     <row r="138" spans="1:7">
       <c r="A138" s="2" t="s">
-        <v>584</v>
+        <v>593</v>
       </c>
       <c r="B138" t="s">
-        <v>585</v>
+        <v>594</v>
       </c>
       <c r="C138" t="s">
-        <v>79</v>
+        <v>128</v>
       </c>
       <c r="D138" t="s">
-        <v>80</v>
+        <v>129</v>
       </c>
       <c r="E138" t="s">
-        <v>586</v>
+        <v>595</v>
       </c>
       <c r="F138" t="s">
-        <v>136</v>
+        <v>54</v>
       </c>
       <c r="G138" t="s">
-        <v>587</v>
+        <v>596</v>
       </c>
     </row>
     <row r="139" spans="1:7">
       <c r="A139" s="2" t="s">
-        <v>588</v>
+        <v>597</v>
       </c>
       <c r="B139" t="s">
-        <v>589</v>
+        <v>598</v>
       </c>
       <c r="C139" t="s">
-        <v>240</v>
+        <v>128</v>
       </c>
       <c r="D139" t="s">
-        <v>241</v>
+        <v>129</v>
       </c>
       <c r="E139" t="s">
-        <v>590</v>
+        <v>599</v>
       </c>
       <c r="F139" t="s">
-        <v>31</v>
+        <v>103</v>
       </c>
       <c r="G139" t="s">
-        <v>31</v>
+        <v>600</v>
       </c>
     </row>
     <row r="140" spans="1:7">
       <c r="A140" s="2" t="s">
-        <v>591</v>
+        <v>601</v>
       </c>
       <c r="B140" t="s">
-        <v>592</v>
+        <v>602</v>
       </c>
       <c r="C140" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="D140" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="E140" t="s">
-        <v>593</v>
+        <v>603</v>
       </c>
       <c r="F140" t="s">
-        <v>396</v>
+        <v>604</v>
       </c>
       <c r="G140" t="s">
-        <v>594</v>
+        <v>605</v>
       </c>
     </row>
     <row r="141" spans="1:7">
       <c r="A141" s="2" t="s">
-        <v>595</v>
+        <v>606</v>
       </c>
       <c r="B141" t="s">
-        <v>596</v>
+        <v>607</v>
       </c>
       <c r="C141" t="s">
-        <v>28</v>
+        <v>128</v>
       </c>
       <c r="D141" t="s">
-        <v>29</v>
+        <v>129</v>
       </c>
       <c r="E141" t="s">
-        <v>597</v>
+        <v>608</v>
       </c>
       <c r="F141" t="s">
-        <v>136</v>
+        <v>273</v>
       </c>
       <c r="G141" t="s">
-        <v>598</v>
+        <v>609</v>
       </c>
     </row>
     <row r="142" spans="1:7">
       <c r="A142" s="2" t="s">
-        <v>599</v>
+        <v>610</v>
       </c>
       <c r="B142" t="s">
-        <v>600</v>
+        <v>611</v>
       </c>
       <c r="C142" t="s">
-        <v>28</v>
+        <v>204</v>
       </c>
       <c r="D142" t="s">
-        <v>29</v>
+        <v>612</v>
       </c>
       <c r="E142" t="s">
-        <v>601</v>
+        <v>613</v>
       </c>
       <c r="F142" t="s">
-        <v>396</v>
+        <v>12</v>
       </c>
       <c r="G142" t="s">
-        <v>602</v>
+        <v>12</v>
       </c>
     </row>
     <row r="143" spans="1:7">
       <c r="A143" s="2" t="s">
-        <v>603</v>
+        <v>614</v>
       </c>
       <c r="B143" t="s">
-        <v>604</v>
+        <v>615</v>
       </c>
       <c r="C143" t="s">
-        <v>9</v>
+        <v>128</v>
       </c>
       <c r="D143" t="s">
-        <v>10</v>
+        <v>129</v>
       </c>
       <c r="E143" t="s">
-        <v>605</v>
+        <v>616</v>
       </c>
       <c r="F143" t="s">
-        <v>449</v>
+        <v>79</v>
       </c>
       <c r="G143" t="s">
-        <v>606</v>
+        <v>617</v>
       </c>
     </row>
     <row r="144" spans="1:7">
       <c r="A144" s="2" t="s">
-        <v>607</v>
+        <v>618</v>
       </c>
       <c r="B144" t="s">
-        <v>608</v>
+        <v>619</v>
       </c>
       <c r="C144" t="s">
-        <v>74</v>
+        <v>9</v>
       </c>
       <c r="D144" t="s">
-        <v>73</v>
+        <v>10</v>
       </c>
       <c r="E144" t="s">
-        <v>609</v>
+        <v>620</v>
       </c>
       <c r="F144" t="s">
-        <v>212</v>
+        <v>621</v>
       </c>
       <c r="G144" t="s">
-        <v>610</v>
+        <v>622</v>
       </c>
     </row>
     <row r="145" spans="1:7">
       <c r="A145" s="2" t="s">
-        <v>611</v>
+        <v>623</v>
       </c>
       <c r="B145" t="s">
-        <v>612</v>
+        <v>624</v>
       </c>
       <c r="C145" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="D145" t="s">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="E145" t="s">
-        <v>613</v>
+        <v>625</v>
       </c>
       <c r="F145" t="s">
-        <v>365</v>
+        <v>112</v>
       </c>
       <c r="G145" t="s">
-        <v>614</v>
+        <v>626</v>
       </c>
     </row>
     <row r="146" spans="1:7">
       <c r="A146" s="2" t="s">
-        <v>615</v>
+        <v>627</v>
       </c>
       <c r="B146" t="s">
-        <v>616</v>
+        <v>628</v>
       </c>
       <c r="C146" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="D146" t="s">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="E146" t="s">
-        <v>617</v>
+        <v>629</v>
       </c>
       <c r="F146" t="s">
-        <v>405</v>
+        <v>273</v>
       </c>
       <c r="G146" t="s">
-        <v>618</v>
+        <v>630</v>
       </c>
     </row>
     <row r="147" spans="1:7">
       <c r="A147" s="2" t="s">
-        <v>619</v>
+        <v>631</v>
       </c>
       <c r="B147" t="s">
-        <v>620</v>
+        <v>632</v>
       </c>
       <c r="C147" t="s">
-        <v>9</v>
+        <v>51</v>
       </c>
       <c r="D147" t="s">
-        <v>10</v>
+        <v>52</v>
       </c>
       <c r="E147" t="s">
-        <v>621</v>
+        <v>633</v>
       </c>
       <c r="F147" t="s">
-        <v>114</v>
+        <v>634</v>
       </c>
       <c r="G147" t="s">
-        <v>622</v>
+        <v>635</v>
       </c>
     </row>
     <row r="148" spans="1:7">
       <c r="A148" s="2" t="s">
-        <v>623</v>
+        <v>636</v>
       </c>
       <c r="B148" t="s">
-        <v>624</v>
+        <v>637</v>
       </c>
       <c r="C148" t="s">
-        <v>9</v>
+        <v>164</v>
       </c>
       <c r="D148" t="s">
-        <v>10</v>
+        <v>165</v>
       </c>
       <c r="E148" t="s">
-        <v>625</v>
+        <v>638</v>
       </c>
       <c r="F148" t="s">
-        <v>119</v>
+        <v>79</v>
       </c>
       <c r="G148" t="s">
-        <v>626</v>
+        <v>639</v>
       </c>
     </row>
     <row r="149" spans="1:7">
       <c r="A149" s="2" t="s">
-        <v>627</v>
+        <v>640</v>
       </c>
       <c r="B149" t="s">
-        <v>628</v>
+        <v>641</v>
       </c>
       <c r="C149" t="s">
-        <v>74</v>
+        <v>164</v>
       </c>
       <c r="D149" t="s">
-        <v>73</v>
+        <v>165</v>
       </c>
       <c r="E149" t="s">
-        <v>629</v>
+        <v>642</v>
       </c>
       <c r="F149" t="s">
-        <v>114</v>
+        <v>84</v>
       </c>
       <c r="G149" t="s">
-        <v>630</v>
+        <v>643</v>
       </c>
     </row>
     <row r="150" spans="1:7">
       <c r="A150" s="2" t="s">
-        <v>631</v>
+        <v>644</v>
       </c>
       <c r="B150" t="s">
-        <v>632</v>
+        <v>645</v>
       </c>
       <c r="C150" t="s">
-        <v>74</v>
+        <v>164</v>
       </c>
       <c r="D150" t="s">
-        <v>73</v>
+        <v>165</v>
       </c>
       <c r="E150" t="s">
-        <v>633</v>
+        <v>646</v>
       </c>
       <c r="F150" t="s">
-        <v>39</v>
+        <v>647</v>
       </c>
       <c r="G150" t="s">
-        <v>634</v>
+        <v>648</v>
       </c>
     </row>
     <row r="151" spans="1:7">
       <c r="A151" s="2" t="s">
-        <v>635</v>
+        <v>649</v>
       </c>
       <c r="B151" t="s">
-        <v>636</v>
+        <v>650</v>
       </c>
       <c r="C151" t="s">
-        <v>68</v>
+        <v>164</v>
       </c>
       <c r="D151" t="s">
-        <v>69</v>
+        <v>165</v>
       </c>
       <c r="E151" t="s">
-        <v>637</v>
+        <v>651</v>
       </c>
       <c r="F151" t="s">
-        <v>39</v>
+        <v>79</v>
       </c>
       <c r="G151" t="s">
-        <v>638</v>
+        <v>652</v>
       </c>
     </row>
     <row r="152" spans="1:7">
       <c r="A152" s="2" t="s">
-        <v>639</v>
+        <v>653</v>
       </c>
       <c r="B152" t="s">
-        <v>640</v>
+        <v>654</v>
       </c>
       <c r="C152" t="s">
-        <v>68</v>
+        <v>164</v>
       </c>
       <c r="D152" t="s">
-        <v>69</v>
+        <v>165</v>
       </c>
       <c r="E152" t="s">
-        <v>641</v>
+        <v>655</v>
       </c>
       <c r="F152" t="s">
-        <v>449</v>
+        <v>98</v>
       </c>
       <c r="G152" t="s">
-        <v>642</v>
+        <v>656</v>
       </c>
     </row>
     <row r="153" spans="1:7">
       <c r="A153" s="2" t="s">
-        <v>643</v>
+        <v>657</v>
       </c>
       <c r="B153" t="s">
-        <v>644</v>
+        <v>658</v>
       </c>
       <c r="C153" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="D153" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E153" t="s">
-        <v>645</v>
+        <v>659</v>
       </c>
       <c r="F153" t="s">
-        <v>646</v>
+        <v>98</v>
       </c>
       <c r="G153" t="s">
-        <v>647</v>
+        <v>660</v>
       </c>
     </row>
     <row r="154" spans="1:7">
       <c r="A154" s="2" t="s">
-        <v>648</v>
+        <v>661</v>
       </c>
       <c r="B154" t="s">
-        <v>649</v>
+        <v>662</v>
       </c>
       <c r="C154" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="D154" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="E154" t="s">
-        <v>650</v>
+        <v>663</v>
       </c>
       <c r="F154" t="s">
-        <v>651</v>
+        <v>98</v>
       </c>
       <c r="G154" t="s">
-        <v>652</v>
+        <v>664</v>
       </c>
     </row>
     <row r="155" spans="1:7">
       <c r="A155" s="2" t="s">
-        <v>653</v>
+        <v>665</v>
       </c>
       <c r="B155" t="s">
-        <v>654</v>
+        <v>666</v>
       </c>
       <c r="C155" t="s">
-        <v>28</v>
+        <v>128</v>
       </c>
       <c r="D155" t="s">
-        <v>29</v>
+        <v>129</v>
       </c>
       <c r="E155" t="s">
-        <v>655</v>
+        <v>667</v>
       </c>
       <c r="F155" t="s">
-        <v>651</v>
+        <v>91</v>
       </c>
       <c r="G155" t="s">
-        <v>656</v>
+        <v>668</v>
       </c>
     </row>
     <row r="156" spans="1:7">
       <c r="A156" s="2" t="s">
-        <v>657</v>
+        <v>669</v>
       </c>
       <c r="B156" t="s">
-        <v>658</v>
+        <v>670</v>
       </c>
       <c r="C156" t="s">
-        <v>28</v>
+        <v>88</v>
       </c>
       <c r="D156" t="s">
-        <v>29</v>
+        <v>89</v>
       </c>
       <c r="E156" t="s">
-        <v>659</v>
+        <v>671</v>
       </c>
       <c r="F156" t="s">
-        <v>660</v>
+        <v>84</v>
       </c>
       <c r="G156" t="s">
-        <v>661</v>
-      </c>
-    </row>
-    <row r="157" spans="1:7">
-      <c r="A157" s="2" t="s">
-        <v>662</v>
+        <v>672</v>
+      </c>
+    </row>
+    <row r="157" ht="15.75" spans="1:7">
+      <c r="A157" s="4">
+        <v>399971</v>
       </c>
       <c r="B157" t="s">
-        <v>663</v>
+        <v>673</v>
       </c>
       <c r="C157" t="s">
-        <v>9</v>
+        <v>204</v>
       </c>
       <c r="D157" t="s">
-        <v>10</v>
+        <v>612</v>
       </c>
       <c r="E157" t="s">
-        <v>664</v>
+        <v>674</v>
       </c>
       <c r="F157" t="s">
-        <v>136</v>
+        <v>12</v>
       </c>
       <c r="G157" t="s">
-        <v>665</v>
+        <v>12</v>
       </c>
     </row>
     <row r="158" spans="1:7">
       <c r="A158" s="2" t="s">
-        <v>666</v>
+        <v>675</v>
       </c>
       <c r="B158" t="s">
-        <v>667</v>
+        <v>676</v>
       </c>
       <c r="C158" t="s">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="D158" t="s">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="E158" t="s">
-        <v>668</v>
+        <v>677</v>
       </c>
       <c r="F158" t="s">
-        <v>449</v>
+        <v>678</v>
       </c>
       <c r="G158" t="s">
-        <v>669</v>
+        <v>679</v>
       </c>
     </row>
     <row r="159" spans="1:7">
       <c r="A159" s="2" t="s">
-        <v>670</v>
+        <v>680</v>
       </c>
       <c r="B159" t="s">
-        <v>671</v>
+        <v>681</v>
       </c>
       <c r="C159" t="s">
-        <v>91</v>
+        <v>164</v>
       </c>
       <c r="D159" t="s">
-        <v>92</v>
+        <v>165</v>
       </c>
       <c r="E159" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="F159" t="s">
-        <v>114</v>
+        <v>683</v>
       </c>
       <c r="G159" t="s">
-        <v>673</v>
+        <v>684</v>
       </c>
     </row>
     <row r="160" spans="1:7">
       <c r="A160" s="2" t="s">
-        <v>674</v>
+        <v>685</v>
       </c>
       <c r="B160" t="s">
-        <v>675</v>
+        <v>686</v>
       </c>
       <c r="C160" t="s">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="D160" t="s">
-        <v>69</v>
+        <v>96</v>
       </c>
       <c r="E160" t="s">
-        <v>676</v>
+        <v>687</v>
       </c>
       <c r="F160" t="s">
-        <v>136</v>
+        <v>84</v>
       </c>
       <c r="G160" t="s">
-        <v>677</v>
+        <v>688</v>
       </c>
     </row>
     <row r="161" spans="1:7">
       <c r="A161" s="2" t="s">
-        <v>678</v>
+        <v>689</v>
       </c>
       <c r="B161" t="s">
-        <v>679</v>
+        <v>690</v>
       </c>
       <c r="C161" t="s">
-        <v>74</v>
+        <v>128</v>
       </c>
       <c r="D161" t="s">
-        <v>73</v>
+        <v>129</v>
       </c>
       <c r="E161" t="s">
-        <v>680</v>
+        <v>691</v>
       </c>
       <c r="F161" t="s">
-        <v>212</v>
+        <v>103</v>
       </c>
       <c r="G161" t="s">
-        <v>681</v>
+        <v>692</v>
       </c>
     </row>
     <row r="162" spans="1:7">
       <c r="A162" s="2" t="s">
-        <v>682</v>
+        <v>693</v>
       </c>
       <c r="B162" t="s">
-        <v>683</v>
+        <v>694</v>
       </c>
       <c r="C162" t="s">
-        <v>68</v>
+        <v>22</v>
       </c>
       <c r="D162" t="s">
-        <v>69</v>
+        <v>23</v>
       </c>
       <c r="E162" t="s">
-        <v>684</v>
+        <v>695</v>
       </c>
       <c r="F162" t="s">
-        <v>136</v>
+        <v>84</v>
       </c>
       <c r="G162" t="s">
-        <v>685</v>
+        <v>696</v>
       </c>
     </row>
     <row r="163" spans="1:7">
       <c r="A163" s="2" t="s">
-        <v>686</v>
+        <v>697</v>
       </c>
       <c r="B163" t="s">
-        <v>687</v>
+        <v>698</v>
       </c>
       <c r="C163" t="s">
-        <v>85</v>
+        <v>9</v>
       </c>
       <c r="D163" t="s">
-        <v>86</v>
+        <v>10</v>
       </c>
       <c r="E163" t="s">
-        <v>688</v>
+        <v>699</v>
       </c>
       <c r="F163" t="s">
-        <v>689</v>
+        <v>79</v>
       </c>
       <c r="G163" t="s">
-        <v>690</v>
+        <v>700</v>
       </c>
     </row>
     <row r="164" spans="1:7">
       <c r="A164" s="2" t="s">
-        <v>691</v>
+        <v>701</v>
       </c>
       <c r="B164" t="s">
-        <v>692</v>
+        <v>702</v>
       </c>
       <c r="C164" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D164" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E164" t="s">
-        <v>693</v>
+        <v>703</v>
       </c>
       <c r="F164" t="s">
-        <v>694</v>
+        <v>79</v>
       </c>
       <c r="G164" t="s">
-        <v>695</v>
+        <v>704</v>
       </c>
     </row>
     <row r="165" spans="1:7">
       <c r="A165" s="2" t="s">
-        <v>696</v>
+        <v>705</v>
       </c>
       <c r="B165" t="s">
-        <v>697</v>
+        <v>706</v>
       </c>
       <c r="C165" t="s">
-        <v>85</v>
+        <v>15</v>
       </c>
       <c r="D165" t="s">
-        <v>86</v>
+        <v>16</v>
       </c>
       <c r="E165" t="s">
-        <v>698</v>
+        <v>707</v>
       </c>
       <c r="F165" t="s">
-        <v>12</v>
+        <v>103</v>
       </c>
       <c r="G165" t="s">
-        <v>699</v>
+        <v>708</v>
       </c>
     </row>
     <row r="166" spans="1:7">
       <c r="A166" s="2" t="s">
-        <v>700</v>
+        <v>709</v>
       </c>
       <c r="B166" t="s">
-        <v>701</v>
+        <v>710</v>
       </c>
       <c r="C166" t="s">
-        <v>240</v>
+        <v>22</v>
       </c>
       <c r="D166" t="s">
-        <v>316</v>
+        <v>23</v>
       </c>
       <c r="E166" t="s">
-        <v>702</v>
+        <v>711</v>
       </c>
       <c r="F166" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="G166" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
     </row>
     <row r="167" spans="1:7">
       <c r="A167" s="2" t="s">
-        <v>703</v>
+        <v>712</v>
       </c>
       <c r="B167" t="s">
-        <v>704</v>
+        <v>713</v>
       </c>
       <c r="C167" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="D167" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="E167" t="s">
-        <v>705</v>
+        <v>714</v>
       </c>
       <c r="F167" t="s">
-        <v>706</v>
+        <v>84</v>
       </c>
       <c r="G167" t="s">
-        <v>707</v>
+        <v>715</v>
       </c>
     </row>
     <row r="168" spans="1:7">
       <c r="A168" s="2" t="s">
-        <v>708</v>
+        <v>716</v>
       </c>
       <c r="B168" t="s">
-        <v>709</v>
+        <v>717</v>
       </c>
       <c r="C168" t="s">
-        <v>111</v>
+        <v>22</v>
       </c>
       <c r="D168" t="s">
-        <v>112</v>
+        <v>23</v>
       </c>
       <c r="E168" t="s">
-        <v>710</v>
+        <v>718</v>
       </c>
       <c r="F168" t="s">
-        <v>312</v>
+        <v>12</v>
       </c>
       <c r="G168" t="s">
-        <v>711</v>
+        <v>12</v>
       </c>
     </row>
     <row r="169" spans="1:7">
       <c r="A169" s="2" t="s">
-        <v>712</v>
+        <v>719</v>
       </c>
       <c r="B169" t="s">
-        <v>713</v>
+        <v>720</v>
       </c>
       <c r="C169" t="s">
-        <v>9</v>
+        <v>51</v>
       </c>
       <c r="D169" t="s">
-        <v>10</v>
+        <v>52</v>
       </c>
       <c r="E169" t="s">
-        <v>714</v>
+        <v>721</v>
       </c>
       <c r="F169" t="s">
-        <v>39</v>
+        <v>84</v>
       </c>
       <c r="G169" t="s">
-        <v>715</v>
+        <v>722</v>
       </c>
     </row>
     <row r="170" spans="1:7">
       <c r="A170" s="2" t="s">
-        <v>716</v>
+        <v>723</v>
       </c>
       <c r="B170" t="s">
-        <v>717</v>
+        <v>724</v>
       </c>
       <c r="C170" t="s">
-        <v>91</v>
+        <v>15</v>
       </c>
       <c r="D170" t="s">
-        <v>92</v>
+        <v>16</v>
       </c>
       <c r="E170" t="s">
-        <v>718</v>
+        <v>725</v>
       </c>
       <c r="F170" t="s">
-        <v>449</v>
+        <v>84</v>
       </c>
       <c r="G170" t="s">
-        <v>719</v>
+        <v>726</v>
       </c>
     </row>
     <row r="171" spans="1:7">
       <c r="A171" s="2" t="s">
-        <v>720</v>
+        <v>727</v>
       </c>
       <c r="B171" t="s">
-        <v>721</v>
+        <v>728</v>
       </c>
       <c r="C171" t="s">
-        <v>111</v>
+        <v>44</v>
       </c>
       <c r="D171" t="s">
-        <v>112</v>
+        <v>45</v>
       </c>
       <c r="E171" t="s">
-        <v>722</v>
+        <v>729</v>
       </c>
       <c r="F171" t="s">
-        <v>39</v>
+        <v>98</v>
       </c>
       <c r="G171" t="s">
-        <v>723</v>
+        <v>730</v>
       </c>
     </row>
     <row r="172" spans="1:7">
       <c r="A172" s="2" t="s">
-        <v>724</v>
+        <v>731</v>
       </c>
       <c r="B172" t="s">
-        <v>725</v>
+        <v>732</v>
       </c>
       <c r="C172" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="D172" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="E172" t="s">
-        <v>726</v>
+        <v>733</v>
       </c>
       <c r="F172" t="s">
-        <v>727</v>
+        <v>84</v>
       </c>
       <c r="G172" t="s">
-        <v>728</v>
+        <v>734</v>
       </c>
     </row>
     <row r="173" spans="1:7">
       <c r="A173" s="2" t="s">
-        <v>729</v>
+        <v>735</v>
       </c>
       <c r="B173" t="s">
-        <v>730</v>
+        <v>736</v>
       </c>
       <c r="C173" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D173" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E173" t="s">
-        <v>731</v>
+        <v>737</v>
       </c>
       <c r="F173" t="s">
-        <v>31</v>
+        <v>79</v>
       </c>
       <c r="G173" t="s">
-        <v>31</v>
+        <v>738</v>
       </c>
     </row>
     <row r="174" spans="1:7">
       <c r="A174" s="2" t="s">
-        <v>732</v>
+        <v>739</v>
       </c>
       <c r="B174" t="s">
-        <v>733</v>
+        <v>740</v>
       </c>
       <c r="C174" t="s">
-        <v>74</v>
+        <v>15</v>
       </c>
       <c r="D174" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="E174" t="s">
-        <v>734</v>
+        <v>741</v>
       </c>
       <c r="F174" t="s">
-        <v>212</v>
+        <v>54</v>
       </c>
       <c r="G174" t="s">
-        <v>735</v>
+        <v>742</v>
       </c>
     </row>
     <row r="175" spans="1:7">
       <c r="A175" s="2" t="s">
-        <v>736</v>
+        <v>743</v>
       </c>
       <c r="B175" t="s">
-        <v>737</v>
+        <v>744</v>
       </c>
       <c r="C175" t="s">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="D175" t="s">
-        <v>69</v>
+        <v>45</v>
       </c>
       <c r="E175" t="s">
-        <v>738</v>
+        <v>745</v>
       </c>
       <c r="F175" t="s">
-        <v>312</v>
+        <v>91</v>
       </c>
       <c r="G175" t="s">
-        <v>739</v>
+        <v>746</v>
       </c>
     </row>
     <row r="176" spans="1:7">
       <c r="A176" s="2" t="s">
-        <v>740</v>
+        <v>747</v>
       </c>
       <c r="B176" t="s">
-        <v>741</v>
+        <v>748</v>
       </c>
       <c r="C176" t="s">
-        <v>74</v>
+        <v>128</v>
       </c>
       <c r="D176" t="s">
-        <v>73</v>
+        <v>129</v>
       </c>
       <c r="E176" t="s">
-        <v>742</v>
+        <v>749</v>
       </c>
       <c r="F176" t="s">
-        <v>396</v>
+        <v>84</v>
       </c>
       <c r="G176" t="s">
-        <v>743</v>
-      </c>
-    </row>
-    <row r="177" spans="1:7">
-      <c r="A177" s="2" t="s">
-        <v>744</v>
-      </c>
-      <c r="B177" t="s">
-        <v>745</v>
-      </c>
-      <c r="C177" t="s">
-        <v>91</v>
-      </c>
-      <c r="D177" t="s">
-        <v>92</v>
-      </c>
-      <c r="E177" t="s">
-        <v>746</v>
-      </c>
-      <c r="F177" t="s">
-        <v>747</v>
-      </c>
-      <c r="G177" t="s">
-        <v>748</v>
-      </c>
-    </row>
-    <row r="178" spans="1:7">
-      <c r="A178" s="2" t="s">
-        <v>749</v>
-      </c>
-      <c r="B178" t="s">
-        <v>741</v>
-      </c>
-      <c r="C178" t="s">
-        <v>91</v>
-      </c>
-      <c r="D178" t="s">
-        <v>92</v>
-      </c>
-      <c r="E178" t="s">
         <v>750</v>
       </c>
-      <c r="F178" t="s">
-        <v>396</v>
-      </c>
-      <c r="G178" t="s">
-        <v>751</v>
-      </c>
-    </row>
-    <row r="179" spans="1:7">
-      <c r="A179" s="2" t="s">
-        <v>752</v>
-      </c>
-      <c r="B179" t="s">
-        <v>753</v>
-      </c>
-      <c r="C179" t="s">
-        <v>9</v>
-      </c>
-      <c r="D179" t="s">
-        <v>10</v>
-      </c>
-      <c r="E179" t="s">
-        <v>754</v>
-      </c>
-      <c r="F179" t="s">
-        <v>396</v>
-      </c>
-      <c r="G179" t="s">
-        <v>755</v>
-      </c>
-    </row>
-    <row r="180" spans="1:7">
-      <c r="A180" s="2" t="s">
-        <v>756</v>
-      </c>
-      <c r="B180" t="s">
-        <v>757</v>
-      </c>
-      <c r="C180" t="s">
-        <v>240</v>
-      </c>
-      <c r="D180" t="s">
-        <v>263</v>
-      </c>
-      <c r="E180" t="s">
-        <v>758</v>
-      </c>
-      <c r="F180" t="s">
-        <v>12</v>
-      </c>
-      <c r="G180" t="s">
-        <v>759</v>
+    </row>
+    <row r="177" spans="1:1">
+      <c r="A177" s="2">
+        <v>399311</v>
       </c>
     </row>
   </sheetData>
-  <sortState ref="A2:G183">
-    <sortCondition ref="A2"/>
+  <sortState ref="A2:G177">
+    <sortCondition ref="B37"/>
   </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
